--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\売上\bigboss-special-page-claude-multi-store-sales-dashboard-4kty7j (1)\bigboss-special-page-claude-multi-store-sales-dashboard-4kty7j\dashboard\data\incoming\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\伊原\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{11D471DD-1992-42F1-875A-3C86D6F0A040}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C03EC878-5CB5-457F-8AAB-D501283D2C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -316,106 +316,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1042,296 +943,404 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
-        <v>46266</v>
+        <v>46023</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C2" s="7">
-        <v>669080</v>
+        <v>19440</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
-        <v>46267</v>
+        <v>46024</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C3" s="7">
-        <v>662770</v>
+        <v>217400</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="6">
-        <v>46268</v>
+        <v>46025</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C4" s="7">
-        <v>570160</v>
+        <v>419248</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="6">
-        <v>46269</v>
+        <v>46026</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C5" s="7">
-        <v>556680</v>
+        <v>101606</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
-        <v>46270</v>
+        <v>46027</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="7">
-        <v>642620</v>
+        <v>283530</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="6">
-        <v>46271</v>
+        <v>46028</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="7">
-        <v>502980</v>
+        <v>265276</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="6">
-        <v>46272</v>
+        <v>46029</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="7">
-        <v>601030</v>
+        <v>461850</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="6">
-        <v>46273</v>
+        <v>46030</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="7">
-        <v>568010</v>
+        <v>284240</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="6">
-        <v>46274</v>
+        <v>46031</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="7">
-        <v>604910</v>
+        <v>322376</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="6">
-        <v>46275</v>
+        <v>46032</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="7">
-        <v>724550</v>
+        <v>151728</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="6">
-        <v>46276</v>
+        <v>46033</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="7">
-        <v>592530</v>
+        <v>132600</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="6">
-        <v>46277</v>
+        <v>46034</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="7">
-        <v>563370</v>
+        <v>425520</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="6">
-        <v>46278</v>
+        <v>46035</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="7">
-        <v>615130</v>
+        <v>181420</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A15" s="6"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="7"/>
+      <c r="A15" s="6">
+        <v>46036</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C15" s="7">
+        <v>327140</v>
+      </c>
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="6"/>
-      <c r="B16" s="5"/>
-      <c r="C16" s="7"/>
+      <c r="A16" s="6">
+        <v>46037</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" s="7">
+        <v>279098</v>
+      </c>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="6"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="7"/>
+      <c r="A17" s="6">
+        <v>46038</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C17" s="7">
+        <v>540666</v>
+      </c>
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="6"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="7"/>
+      <c r="A18" s="6">
+        <v>46039</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="7">
+        <v>193138</v>
+      </c>
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="6"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="7"/>
+      <c r="A19" s="6">
+        <v>46040</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C19" s="7">
+        <v>92038</v>
+      </c>
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="6"/>
-      <c r="B20" s="5"/>
-      <c r="C20" s="7"/>
+      <c r="A20" s="6">
+        <v>46041</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="7">
+        <v>300298</v>
+      </c>
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="6"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="7"/>
+      <c r="A21" s="6">
+        <v>46042</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="7">
+        <v>98776</v>
+      </c>
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="6"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="7"/>
+      <c r="A22" s="6">
+        <v>46043</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C22" s="7">
+        <v>463480</v>
+      </c>
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="6"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="7"/>
+      <c r="A23" s="6">
+        <v>46044</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="7">
+        <v>288740</v>
+      </c>
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="6"/>
-      <c r="B24" s="5"/>
-      <c r="C24" s="7"/>
+      <c r="A24" s="6">
+        <v>46045</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="7">
+        <v>427696</v>
+      </c>
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="6"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="7"/>
+      <c r="A25" s="6">
+        <v>46046</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="7">
+        <v>129418</v>
+      </c>
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="6"/>
-      <c r="B26" s="5"/>
-      <c r="C26" s="7"/>
+      <c r="A26" s="6">
+        <v>46047</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C26" s="7">
+        <v>111438</v>
+      </c>
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="6"/>
-      <c r="B27" s="5"/>
-      <c r="C27" s="7"/>
+      <c r="A27" s="6">
+        <v>46048</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C27" s="7">
+        <v>286696</v>
+      </c>
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="6"/>
-      <c r="B28" s="5"/>
-      <c r="C28" s="7"/>
+      <c r="A28" s="6">
+        <v>46049</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C28" s="7">
+        <v>168260</v>
+      </c>
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="6"/>
-      <c r="B29" s="5"/>
-      <c r="C29" s="7"/>
+      <c r="A29" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C29" s="7">
+        <v>384154</v>
+      </c>
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="6"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="7"/>
+      <c r="A30" s="6">
+        <v>46051</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C30" s="7">
+        <v>148980</v>
+      </c>
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="6"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="7"/>
+      <c r="A31" s="6">
+        <v>46052</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C31" s="7">
+        <v>357858</v>
+      </c>
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="6"/>
-      <c r="B32" s="5"/>
-      <c r="C32" s="7"/>
+      <c r="A32" s="6">
+        <v>46053</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="7">
+        <v>123378</v>
+      </c>
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
@@ -1344,275 +1353,365 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A34" s="6">
-        <v>45901</v>
+        <v>46054</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C34" s="7">
-        <v>176920</v>
+        <v>87736</v>
       </c>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="6">
-        <v>45902</v>
+        <v>46055</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C35" s="7">
-        <v>161250</v>
+        <v>286230</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="6">
-        <v>45903</v>
+        <v>46056</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C36" s="7">
-        <v>333640</v>
+        <v>131920</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="6">
-        <v>45904</v>
+        <v>46057</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C37" s="7">
-        <v>145410</v>
+        <v>291560</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="6">
-        <v>45905</v>
+        <v>46058</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C38" s="7">
-        <v>419600</v>
+        <v>67676</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="6">
-        <v>45906</v>
+        <v>46059</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C39" s="7">
-        <v>78240</v>
+        <v>391060</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="6">
-        <v>45907</v>
+        <v>46060</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C40" s="7">
-        <v>68180</v>
+        <v>100196</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="6">
-        <v>45908</v>
+        <v>46061</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C41" s="7">
-        <v>322410</v>
+        <v>109056</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="6">
-        <v>45909</v>
+        <v>46062</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C42" s="7">
-        <v>72270</v>
+        <v>206672</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="6">
-        <v>45910</v>
+        <v>46063</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C43" s="7">
-        <v>350500</v>
+        <v>279014</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="6">
-        <v>45911</v>
+        <v>46064</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C44" s="7">
-        <v>132330</v>
+        <v>163880</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="6">
-        <v>45912</v>
+        <v>46065</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C45" s="7">
-        <v>282820</v>
+        <v>74360</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="6">
-        <v>45913</v>
+        <v>46066</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C46" s="7">
-        <v>140280</v>
+        <v>301300</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A47" s="6"/>
-      <c r="B47" s="5"/>
-      <c r="C47" s="7"/>
+      <c r="A47" s="6">
+        <v>46067</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="7">
+        <v>242780</v>
+      </c>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A48" s="6"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="7"/>
+      <c r="A48" s="6">
+        <v>46068</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C48" s="7">
+        <v>203380</v>
+      </c>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A49" s="6"/>
-      <c r="B49" s="5"/>
-      <c r="C49" s="7"/>
+      <c r="A49" s="6">
+        <v>46069</v>
+      </c>
+      <c r="B49" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C49" s="7">
+        <v>542880</v>
+      </c>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A50" s="6"/>
-      <c r="B50" s="5"/>
-      <c r="C50" s="7"/>
+      <c r="A50" s="6">
+        <v>46070</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C50" s="7">
+        <v>137520</v>
+      </c>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A51" s="6"/>
-      <c r="B51" s="5"/>
-      <c r="C51" s="7"/>
+      <c r="A51" s="6">
+        <v>46071</v>
+      </c>
+      <c r="B51" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" s="7">
+        <v>553260</v>
+      </c>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A52" s="6"/>
-      <c r="B52" s="5"/>
-      <c r="C52" s="7"/>
+      <c r="A52" s="6">
+        <v>46072</v>
+      </c>
+      <c r="B52" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" s="7">
+        <v>161800</v>
+      </c>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A53" s="6"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="7"/>
+      <c r="A53" s="6">
+        <v>46073</v>
+      </c>
+      <c r="B53" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C53" s="7">
+        <v>345520</v>
+      </c>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A54" s="6"/>
-      <c r="B54" s="5"/>
-      <c r="C54" s="7"/>
+      <c r="A54" s="6">
+        <v>46074</v>
+      </c>
+      <c r="B54" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C54" s="7">
+        <v>66280</v>
+      </c>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A55" s="6"/>
-      <c r="B55" s="5"/>
-      <c r="C55" s="7"/>
+      <c r="A55" s="6">
+        <v>46075</v>
+      </c>
+      <c r="B55" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C55" s="7">
+        <v>161382</v>
+      </c>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A56" s="6"/>
-      <c r="B56" s="5"/>
-      <c r="C56" s="7"/>
+      <c r="A56" s="6">
+        <v>46076</v>
+      </c>
+      <c r="B56" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" s="7">
+        <v>298998</v>
+      </c>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A57" s="6"/>
-      <c r="B57" s="5"/>
-      <c r="C57" s="7"/>
+      <c r="A57" s="6">
+        <v>46077</v>
+      </c>
+      <c r="B57" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C57" s="7">
+        <v>150238</v>
+      </c>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A58" s="6"/>
-      <c r="B58" s="5"/>
-      <c r="C58" s="7"/>
+      <c r="A58" s="6">
+        <v>46078</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C58" s="7">
+        <v>298532</v>
+      </c>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A59" s="6"/>
-      <c r="B59" s="5"/>
-      <c r="C59" s="7"/>
+      <c r="A59" s="6">
+        <v>46079</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C59" s="7">
+        <v>71188</v>
+      </c>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A60" s="6"/>
-      <c r="B60" s="5"/>
-      <c r="C60" s="7"/>
+      <c r="A60" s="6">
+        <v>46080</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C60" s="7">
+        <v>526234</v>
+      </c>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A61" s="6"/>
-      <c r="B61" s="5"/>
-      <c r="C61" s="7"/>
+      <c r="A61" s="6">
+        <v>46081</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" s="7">
+        <v>109398</v>
+      </c>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
@@ -1624,219 +1723,405 @@
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A63" s="6"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="7"/>
+      <c r="A63" s="6">
+        <v>46082</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C63" s="7">
+        <v>91758</v>
+      </c>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A64" s="6"/>
-      <c r="B64" s="5"/>
-      <c r="C64" s="7"/>
+      <c r="A64" s="6">
+        <v>46083</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C64" s="7">
+        <v>314596</v>
+      </c>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6"/>
-      <c r="B65" s="5"/>
-      <c r="C65" s="7"/>
+      <c r="A65" s="6">
+        <v>46084</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="7">
+        <v>125496</v>
+      </c>
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="6"/>
-      <c r="B66" s="5"/>
-      <c r="C66" s="7"/>
+      <c r="A66" s="6">
+        <v>46085</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C66" s="7">
+        <v>302060</v>
+      </c>
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="6"/>
-      <c r="B67" s="5"/>
-      <c r="C67" s="7"/>
+      <c r="A67" s="6">
+        <v>46086</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C67" s="7">
+        <v>425528</v>
+      </c>
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="6"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="7"/>
+      <c r="A68" s="6">
+        <v>46087</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C68" s="7">
+        <v>371328</v>
+      </c>
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="6"/>
-      <c r="B69" s="5"/>
-      <c r="C69" s="7"/>
+      <c r="A69" s="6">
+        <v>46088</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C69" s="7">
+        <v>161314</v>
+      </c>
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A70" s="6"/>
-      <c r="B70" s="5"/>
-      <c r="C70" s="7"/>
+      <c r="A70" s="6">
+        <v>46089</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" s="7">
+        <v>114896</v>
+      </c>
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A71" s="6"/>
-      <c r="B71" s="5"/>
-      <c r="C71" s="7"/>
+      <c r="A71" s="6">
+        <v>46090</v>
+      </c>
+      <c r="B71" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" s="7">
+        <v>528594</v>
+      </c>
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A72" s="6"/>
-      <c r="B72" s="5"/>
-      <c r="C72" s="7"/>
+      <c r="A72" s="6">
+        <v>46091</v>
+      </c>
+      <c r="B72" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C72" s="7">
+        <v>125612</v>
+      </c>
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A73" s="6"/>
-      <c r="B73" s="5"/>
-      <c r="C73" s="7"/>
+      <c r="A73" s="6">
+        <v>46092</v>
+      </c>
+      <c r="B73" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="7">
+        <v>481572</v>
+      </c>
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A74" s="6"/>
-      <c r="B74" s="5"/>
-      <c r="C74" s="7"/>
+      <c r="A74" s="6">
+        <v>46093</v>
+      </c>
+      <c r="B74" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" s="7">
+        <v>200796</v>
+      </c>
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A75" s="6"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="7"/>
+      <c r="A75" s="6">
+        <v>46094</v>
+      </c>
+      <c r="B75" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C75" s="7">
+        <v>606820</v>
+      </c>
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A76" s="6"/>
-      <c r="B76" s="5"/>
-      <c r="C76" s="7"/>
+      <c r="A76" s="6">
+        <v>46095</v>
+      </c>
+      <c r="B76" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C76" s="7">
+        <v>128480</v>
+      </c>
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A77" s="6"/>
-      <c r="B77" s="5"/>
-      <c r="C77" s="7"/>
+      <c r="A77" s="6">
+        <v>46096</v>
+      </c>
+      <c r="B77" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="7">
+        <v>208216</v>
+      </c>
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A78" s="6"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="7"/>
+      <c r="A78" s="6">
+        <v>46097</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" s="7">
+        <v>411898</v>
+      </c>
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A79" s="6"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="7"/>
+      <c r="A79" s="6">
+        <v>46098</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C79" s="7">
+        <v>204760</v>
+      </c>
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A80" s="6"/>
-      <c r="B80" s="5"/>
-      <c r="C80" s="7"/>
+      <c r="A80" s="6">
+        <v>46099</v>
+      </c>
+      <c r="B80" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C80" s="7">
+        <v>411900</v>
+      </c>
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A81" s="6"/>
-      <c r="B81" s="5"/>
-      <c r="C81" s="7"/>
+      <c r="A81" s="6">
+        <v>46100</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C81" s="7">
+        <v>623320</v>
+      </c>
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A82" s="6"/>
-      <c r="B82" s="5"/>
-      <c r="C82" s="7"/>
+      <c r="A82" s="6">
+        <v>46101</v>
+      </c>
+      <c r="B82" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C82" s="7">
+        <v>684078</v>
+      </c>
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A83" s="6"/>
-      <c r="B83" s="5"/>
-      <c r="C83" s="7"/>
+      <c r="A83" s="6">
+        <v>46102</v>
+      </c>
+      <c r="B83" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" s="7">
+        <v>195280</v>
+      </c>
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A84" s="6"/>
-      <c r="B84" s="5"/>
-      <c r="C84" s="7"/>
+      <c r="A84" s="6">
+        <v>46103</v>
+      </c>
+      <c r="B84" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C84" s="7">
+        <v>128620</v>
+      </c>
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A85" s="6"/>
-      <c r="B85" s="5"/>
-      <c r="C85" s="7"/>
+      <c r="A85" s="6">
+        <v>46104</v>
+      </c>
+      <c r="B85" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C85" s="7">
+        <v>367338</v>
+      </c>
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A86" s="6"/>
-      <c r="B86" s="5"/>
-      <c r="C86" s="7"/>
+      <c r="A86" s="6">
+        <v>46105</v>
+      </c>
+      <c r="B86" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C86" s="7">
+        <v>137080</v>
+      </c>
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A87" s="6"/>
-      <c r="B87" s="5"/>
-      <c r="C87" s="7"/>
+      <c r="A87" s="6">
+        <v>46106</v>
+      </c>
+      <c r="B87" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C87" s="7">
+        <v>551880</v>
+      </c>
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A88" s="6"/>
-      <c r="B88" s="5"/>
-      <c r="C88" s="7"/>
+      <c r="A88" s="6">
+        <v>46107</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C88" s="7">
+        <v>73100</v>
+      </c>
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A89" s="6"/>
-      <c r="B89" s="5"/>
-      <c r="C89" s="7"/>
+      <c r="A89" s="6">
+        <v>46108</v>
+      </c>
+      <c r="B89" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" s="7">
+        <v>700520</v>
+      </c>
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A90" s="6"/>
-      <c r="B90" s="5"/>
-      <c r="C90" s="7"/>
+      <c r="A90" s="6">
+        <v>46109</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C90" s="7">
+        <v>129180</v>
+      </c>
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A91" s="6"/>
-      <c r="B91" s="5"/>
-      <c r="C91" s="7"/>
+      <c r="A91" s="6">
+        <v>46110</v>
+      </c>
+      <c r="B91" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C91" s="7">
+        <v>130158</v>
+      </c>
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A92" s="6"/>
-      <c r="B92" s="5"/>
-      <c r="C92" s="7"/>
+      <c r="A92" s="6">
+        <v>46111</v>
+      </c>
+      <c r="B92" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C92" s="7">
+        <v>382360</v>
+      </c>
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A93" s="6"/>
-      <c r="B93" s="5"/>
-      <c r="C93" s="7"/>
+      <c r="A93" s="6">
+        <v>46112</v>
+      </c>
+      <c r="B93" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C93" s="7">
+        <v>262540</v>
+      </c>
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
@@ -1848,212 +2133,392 @@
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A95" s="6"/>
-      <c r="B95" s="5"/>
-      <c r="C95" s="7"/>
+      <c r="A95" s="6">
+        <v>46113</v>
+      </c>
+      <c r="B95" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" s="7">
+        <v>515800</v>
+      </c>
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A96" s="6"/>
-      <c r="B96" s="5"/>
-      <c r="C96" s="7"/>
+      <c r="A96" s="6">
+        <v>46114</v>
+      </c>
+      <c r="B96" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C96" s="7">
+        <v>210360</v>
+      </c>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A97" s="6"/>
-      <c r="B97" s="5"/>
-      <c r="C97" s="7"/>
+      <c r="A97" s="6">
+        <v>46115</v>
+      </c>
+      <c r="B97" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C97" s="7">
+        <v>615300</v>
+      </c>
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A98" s="6"/>
-      <c r="B98" s="5"/>
-      <c r="C98" s="7"/>
+      <c r="A98" s="6">
+        <v>46116</v>
+      </c>
+      <c r="B98" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C98" s="7">
+        <v>252400</v>
+      </c>
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A99" s="6"/>
-      <c r="B99" s="5"/>
-      <c r="C99" s="7"/>
+      <c r="A99" s="6">
+        <v>46117</v>
+      </c>
+      <c r="B99" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C99" s="7">
+        <v>229740</v>
+      </c>
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A100" s="6"/>
-      <c r="B100" s="5"/>
-      <c r="C100" s="7"/>
+      <c r="A100" s="6">
+        <v>46118</v>
+      </c>
+      <c r="B100" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C100" s="7">
+        <v>410700</v>
+      </c>
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A101" s="6"/>
-      <c r="B101" s="5"/>
-      <c r="C101" s="7"/>
+      <c r="A101" s="6">
+        <v>46119</v>
+      </c>
+      <c r="B101" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C101" s="7">
+        <v>337180</v>
+      </c>
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A102" s="6"/>
-      <c r="B102" s="5"/>
-      <c r="C102" s="7"/>
+      <c r="A102" s="6">
+        <v>46120</v>
+      </c>
+      <c r="B102" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C102" s="7">
+        <v>493600</v>
+      </c>
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A103" s="6"/>
-      <c r="B103" s="5"/>
-      <c r="C103" s="7"/>
+      <c r="A103" s="6">
+        <v>46121</v>
+      </c>
+      <c r="B103" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" s="7">
+        <v>254660</v>
+      </c>
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A104" s="6"/>
-      <c r="B104" s="5"/>
-      <c r="C104" s="7"/>
+      <c r="A104" s="6">
+        <v>46122</v>
+      </c>
+      <c r="B104" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C104" s="7">
+        <v>349360</v>
+      </c>
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A105" s="6"/>
-      <c r="B105" s="5"/>
-      <c r="C105" s="7"/>
+      <c r="A105" s="6">
+        <v>46123</v>
+      </c>
+      <c r="B105" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C105" s="7">
+        <v>158360</v>
+      </c>
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A106" s="6"/>
-      <c r="B106" s="5"/>
-      <c r="C106" s="7"/>
+      <c r="A106" s="6">
+        <v>46124</v>
+      </c>
+      <c r="B106" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C106" s="7">
+        <v>218920</v>
+      </c>
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A107" s="6"/>
-      <c r="B107" s="5"/>
-      <c r="C107" s="7"/>
+      <c r="A107" s="6">
+        <v>46125</v>
+      </c>
+      <c r="B107" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C107" s="7">
+        <v>506620</v>
+      </c>
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A108" s="6"/>
-      <c r="B108" s="5"/>
-      <c r="C108" s="7"/>
+      <c r="A108" s="6">
+        <v>46126</v>
+      </c>
+      <c r="B108" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C108" s="7">
+        <v>208020</v>
+      </c>
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A109" s="6"/>
-      <c r="B109" s="5"/>
-      <c r="C109" s="7"/>
+      <c r="A109" s="6">
+        <v>46127</v>
+      </c>
+      <c r="B109" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C109" s="7">
+        <v>350020</v>
+      </c>
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A110" s="6"/>
-      <c r="B110" s="5"/>
-      <c r="C110" s="7"/>
+      <c r="A110" s="6">
+        <v>46128</v>
+      </c>
+      <c r="B110" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C110" s="7">
+        <v>364360</v>
+      </c>
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A111" s="6"/>
-      <c r="B111" s="5"/>
-      <c r="C111" s="7"/>
+      <c r="A111" s="6">
+        <v>46129</v>
+      </c>
+      <c r="B111" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C111" s="7">
+        <v>809060</v>
+      </c>
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A112" s="6"/>
-      <c r="B112" s="5"/>
-      <c r="C112" s="7"/>
+      <c r="A112" s="6">
+        <v>46130</v>
+      </c>
+      <c r="B112" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C112" s="7">
+        <v>312340</v>
+      </c>
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A113" s="6"/>
-      <c r="B113" s="5"/>
-      <c r="C113" s="7"/>
+      <c r="A113" s="6">
+        <v>46131</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C113" s="7">
+        <v>271580</v>
+      </c>
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A114" s="6"/>
-      <c r="B114" s="5"/>
-      <c r="C114" s="7"/>
+      <c r="A114" s="6">
+        <v>46132</v>
+      </c>
+      <c r="B114" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" s="7">
+        <v>478400</v>
+      </c>
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A115" s="6"/>
-      <c r="B115" s="5"/>
-      <c r="C115" s="7"/>
+      <c r="A115" s="6">
+        <v>46133</v>
+      </c>
+      <c r="B115" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C115" s="7">
+        <v>327960</v>
+      </c>
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A116" s="6"/>
-      <c r="B116" s="5"/>
-      <c r="C116" s="7"/>
+      <c r="A116" s="6">
+        <v>46134</v>
+      </c>
+      <c r="B116" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C116" s="7">
+        <v>528500</v>
+      </c>
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A117" s="6"/>
-      <c r="B117" s="5"/>
-      <c r="C117" s="7"/>
+      <c r="A117" s="6">
+        <v>46135</v>
+      </c>
+      <c r="B117" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C117" s="7">
+        <v>379120</v>
+      </c>
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A118" s="6"/>
-      <c r="B118" s="5"/>
-      <c r="C118" s="7"/>
+      <c r="A118" s="6">
+        <v>46136</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C118" s="7">
+        <v>832730</v>
+      </c>
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A119" s="6"/>
-      <c r="B119" s="5"/>
-      <c r="C119" s="7"/>
+      <c r="A119" s="6">
+        <v>46137</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C119" s="7">
+        <v>372180</v>
+      </c>
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A120" s="6"/>
-      <c r="B120" s="5"/>
-      <c r="C120" s="7"/>
+      <c r="A120" s="6">
+        <v>46138</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C120" s="7">
+        <v>318200</v>
+      </c>
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A121" s="6"/>
-      <c r="B121" s="5"/>
-      <c r="C121" s="7"/>
+      <c r="A121" s="6">
+        <v>46139</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C121" s="7">
+        <v>664340</v>
+      </c>
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A122" s="6"/>
-      <c r="B122" s="5"/>
-      <c r="C122" s="7"/>
+      <c r="A122" s="6">
+        <v>46140</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C122" s="7">
+        <v>647560</v>
+      </c>
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A123" s="6"/>
-      <c r="B123" s="5"/>
-      <c r="C123" s="7"/>
+      <c r="A123" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C123" s="7">
+        <v>691430</v>
+      </c>
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A124" s="6"/>
-      <c r="B124" s="5"/>
-      <c r="C124" s="7"/>
+      <c r="A124" s="6">
+        <v>46142</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C124" s="7">
+        <v>592490</v>
+      </c>
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
@@ -2065,219 +2530,405 @@
       <c r="E125" s="5"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A126" s="6"/>
-      <c r="B126" s="5"/>
-      <c r="C126" s="7"/>
+      <c r="A126" s="6">
+        <v>46143</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C126" s="7">
+        <v>549980</v>
+      </c>
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A127" s="6"/>
-      <c r="B127" s="5"/>
-      <c r="C127" s="7"/>
+      <c r="A127" s="6">
+        <v>46144</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C127" s="7">
+        <v>499190</v>
+      </c>
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A128" s="6"/>
-      <c r="B128" s="5"/>
-      <c r="C128" s="7"/>
+      <c r="A128" s="6">
+        <v>46145</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C128" s="7">
+        <v>706360</v>
+      </c>
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A129" s="6"/>
-      <c r="B129" s="5"/>
-      <c r="C129" s="7"/>
+      <c r="A129" s="6">
+        <v>46146</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C129" s="7">
+        <v>346300</v>
+      </c>
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A130" s="6"/>
-      <c r="B130" s="5"/>
-      <c r="C130" s="7"/>
+      <c r="A130" s="6">
+        <v>46147</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C130" s="7">
+        <v>191030</v>
+      </c>
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A131" s="6"/>
-      <c r="B131" s="5"/>
-      <c r="C131" s="7"/>
+      <c r="A131" s="6">
+        <v>46148</v>
+      </c>
+      <c r="B131" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C131" s="7">
+        <v>304950</v>
+      </c>
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A132" s="6"/>
-      <c r="B132" s="5"/>
-      <c r="C132" s="7"/>
+      <c r="A132" s="6">
+        <v>46149</v>
+      </c>
+      <c r="B132" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C132" s="7">
+        <v>312220</v>
+      </c>
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A133" s="6"/>
-      <c r="B133" s="5"/>
-      <c r="C133" s="7"/>
+      <c r="A133" s="6">
+        <v>46150</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C133" s="7">
+        <v>631150</v>
+      </c>
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A134" s="6"/>
-      <c r="B134" s="5"/>
-      <c r="C134" s="7"/>
+      <c r="A134" s="6">
+        <v>46151</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C134" s="7">
+        <v>769760</v>
+      </c>
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A135" s="6"/>
-      <c r="B135" s="5"/>
-      <c r="C135" s="7"/>
+      <c r="A135" s="6">
+        <v>46152</v>
+      </c>
+      <c r="B135" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C135" s="7">
+        <v>365430</v>
+      </c>
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A136" s="6"/>
-      <c r="B136" s="5"/>
-      <c r="C136" s="7"/>
+      <c r="A136" s="6">
+        <v>46153</v>
+      </c>
+      <c r="B136" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C136" s="7">
+        <v>678380</v>
+      </c>
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A137" s="6"/>
-      <c r="B137" s="5"/>
-      <c r="C137" s="7"/>
+      <c r="A137" s="6">
+        <v>46154</v>
+      </c>
+      <c r="B137" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C137" s="7">
+        <v>1208410</v>
+      </c>
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A138" s="6"/>
-      <c r="B138" s="5"/>
-      <c r="C138" s="7"/>
+      <c r="A138" s="6">
+        <v>46155</v>
+      </c>
+      <c r="B138" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C138" s="7">
+        <v>1054460</v>
+      </c>
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A139" s="6"/>
-      <c r="B139" s="5"/>
-      <c r="C139" s="7"/>
+      <c r="A139" s="6">
+        <v>46156</v>
+      </c>
+      <c r="B139" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C139" s="7">
+        <v>346900</v>
+      </c>
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A140" s="6"/>
-      <c r="B140" s="5"/>
-      <c r="C140" s="7"/>
+      <c r="A140" s="6">
+        <v>46157</v>
+      </c>
+      <c r="B140" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C140" s="7">
+        <v>627020</v>
+      </c>
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A141" s="6"/>
-      <c r="B141" s="5"/>
-      <c r="C141" s="7"/>
+      <c r="A141" s="6">
+        <v>46158</v>
+      </c>
+      <c r="B141" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C141" s="7">
+        <v>294920</v>
+      </c>
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A142" s="6"/>
-      <c r="B142" s="5"/>
-      <c r="C142" s="7"/>
+      <c r="A142" s="6">
+        <v>46159</v>
+      </c>
+      <c r="B142" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C142" s="7">
+        <v>145580</v>
+      </c>
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A143" s="6"/>
-      <c r="B143" s="5"/>
-      <c r="C143" s="7"/>
+      <c r="A143" s="6">
+        <v>46160</v>
+      </c>
+      <c r="B143" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C143" s="7">
+        <v>429560</v>
+      </c>
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A144" s="6"/>
-      <c r="B144" s="5"/>
-      <c r="C144" s="7"/>
+      <c r="A144" s="6">
+        <v>46161</v>
+      </c>
+      <c r="B144" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C144" s="7">
+        <v>420280</v>
+      </c>
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A145" s="6"/>
-      <c r="B145" s="5"/>
-      <c r="C145" s="7"/>
+      <c r="A145" s="6">
+        <v>46162</v>
+      </c>
+      <c r="B145" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C145" s="7">
+        <v>298680</v>
+      </c>
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A146" s="6"/>
-      <c r="B146" s="5"/>
-      <c r="C146" s="7"/>
+      <c r="A146" s="6">
+        <v>46163</v>
+      </c>
+      <c r="B146" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C146" s="7">
+        <v>237460</v>
+      </c>
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A147" s="6"/>
-      <c r="B147" s="5"/>
-      <c r="C147" s="7"/>
+      <c r="A147" s="6">
+        <v>46164</v>
+      </c>
+      <c r="B147" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C147" s="7">
+        <v>532060</v>
+      </c>
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A148" s="6"/>
-      <c r="B148" s="5"/>
-      <c r="C148" s="7"/>
+      <c r="A148" s="6">
+        <v>46165</v>
+      </c>
+      <c r="B148" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C148" s="7">
+        <v>202140</v>
+      </c>
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A149" s="6"/>
-      <c r="B149" s="5"/>
-      <c r="C149" s="7"/>
+      <c r="A149" s="6">
+        <v>46166</v>
+      </c>
+      <c r="B149" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C149" s="7">
+        <v>133920</v>
+      </c>
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A150" s="6"/>
-      <c r="B150" s="5"/>
-      <c r="C150" s="7"/>
+      <c r="A150" s="6">
+        <v>46167</v>
+      </c>
+      <c r="B150" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C150" s="7">
+        <v>472880</v>
+      </c>
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A151" s="6"/>
-      <c r="B151" s="5"/>
-      <c r="C151" s="7"/>
+      <c r="A151" s="6">
+        <v>46168</v>
+      </c>
+      <c r="B151" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C151" s="7">
+        <v>325760</v>
+      </c>
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A152" s="6"/>
-      <c r="B152" s="5"/>
-      <c r="C152" s="7"/>
+      <c r="A152" s="6">
+        <v>46169</v>
+      </c>
+      <c r="B152" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C152" s="7">
+        <v>365200</v>
+      </c>
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A153" s="6"/>
-      <c r="B153" s="5"/>
-      <c r="C153" s="7"/>
+      <c r="A153" s="6">
+        <v>46170</v>
+      </c>
+      <c r="B153" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C153" s="7">
+        <v>431700</v>
+      </c>
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A154" s="6"/>
-      <c r="B154" s="5"/>
-      <c r="C154" s="7"/>
+      <c r="A154" s="6">
+        <v>46171</v>
+      </c>
+      <c r="B154" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C154" s="7">
+        <v>442180</v>
+      </c>
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A155" s="6"/>
-      <c r="B155" s="5"/>
-      <c r="C155" s="7"/>
+      <c r="A155" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B155" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C155" s="7">
+        <v>293080</v>
+      </c>
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A156" s="6"/>
-      <c r="B156" s="5"/>
-      <c r="C156" s="7"/>
+      <c r="A156" s="6">
+        <v>46173</v>
+      </c>
+      <c r="B156" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C156" s="7">
+        <v>284960</v>
+      </c>
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
@@ -2289,212 +2940,392 @@
       <c r="E157" s="5"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A158" s="6"/>
-      <c r="B158" s="5"/>
-      <c r="C158" s="7"/>
+      <c r="A158" s="6">
+        <v>46174</v>
+      </c>
+      <c r="B158" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C158" s="7">
+        <v>264640</v>
+      </c>
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A159" s="6"/>
-      <c r="B159" s="5"/>
-      <c r="C159" s="7"/>
+      <c r="A159" s="6">
+        <v>46175</v>
+      </c>
+      <c r="B159" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C159" s="7">
+        <v>365400</v>
+      </c>
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A160" s="6"/>
-      <c r="B160" s="5"/>
-      <c r="C160" s="7"/>
+      <c r="A160" s="6">
+        <v>46176</v>
+      </c>
+      <c r="B160" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C160" s="7">
+        <v>313860</v>
+      </c>
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A161" s="6"/>
-      <c r="B161" s="5"/>
-      <c r="C161" s="7"/>
+      <c r="A161" s="6">
+        <v>46177</v>
+      </c>
+      <c r="B161" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C161" s="7">
+        <v>349340</v>
+      </c>
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A162" s="6"/>
-      <c r="B162" s="5"/>
-      <c r="C162" s="7"/>
+      <c r="A162" s="6">
+        <v>46178</v>
+      </c>
+      <c r="B162" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C162" s="7">
+        <v>262280</v>
+      </c>
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A163" s="6"/>
-      <c r="B163" s="5"/>
-      <c r="C163" s="7"/>
+      <c r="A163" s="6">
+        <v>46179</v>
+      </c>
+      <c r="B163" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C163" s="7">
+        <v>310040</v>
+      </c>
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A164" s="6"/>
-      <c r="B164" s="5"/>
-      <c r="C164" s="7"/>
+      <c r="A164" s="6">
+        <v>46180</v>
+      </c>
+      <c r="B164" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C164" s="7">
+        <v>318700</v>
+      </c>
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A165" s="6"/>
-      <c r="B165" s="5"/>
-      <c r="C165" s="7"/>
+      <c r="A165" s="6">
+        <v>46181</v>
+      </c>
+      <c r="B165" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C165" s="7">
+        <v>361500</v>
+      </c>
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A166" s="6"/>
-      <c r="B166" s="5"/>
-      <c r="C166" s="7"/>
+      <c r="A166" s="6">
+        <v>46182</v>
+      </c>
+      <c r="B166" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C166" s="7">
+        <v>344360</v>
+      </c>
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A167" s="6"/>
-      <c r="B167" s="5"/>
-      <c r="C167" s="7"/>
+      <c r="A167" s="6">
+        <v>46183</v>
+      </c>
+      <c r="B167" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C167" s="7">
+        <v>294020</v>
+      </c>
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A168" s="6"/>
-      <c r="B168" s="5"/>
-      <c r="C168" s="7"/>
+      <c r="A168" s="6">
+        <v>46184</v>
+      </c>
+      <c r="B168" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C168" s="7">
+        <v>358600</v>
+      </c>
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A169" s="6"/>
-      <c r="B169" s="5"/>
-      <c r="C169" s="7"/>
+      <c r="A169" s="6">
+        <v>46185</v>
+      </c>
+      <c r="B169" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C169" s="7">
+        <v>312220</v>
+      </c>
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A170" s="6"/>
-      <c r="B170" s="5"/>
-      <c r="C170" s="7"/>
+      <c r="A170" s="6">
+        <v>46186</v>
+      </c>
+      <c r="B170" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C170" s="7">
+        <v>413660</v>
+      </c>
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A171" s="6"/>
-      <c r="B171" s="5"/>
-      <c r="C171" s="7"/>
+      <c r="A171" s="6">
+        <v>46187</v>
+      </c>
+      <c r="B171" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C171" s="7">
+        <v>267780</v>
+      </c>
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A172" s="6"/>
-      <c r="B172" s="5"/>
-      <c r="C172" s="7"/>
+      <c r="A172" s="6">
+        <v>46188</v>
+      </c>
+      <c r="B172" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C172" s="7">
+        <v>411280</v>
+      </c>
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A173" s="6"/>
-      <c r="B173" s="5"/>
-      <c r="C173" s="7"/>
+      <c r="A173" s="6">
+        <v>46189</v>
+      </c>
+      <c r="B173" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C173" s="7">
+        <v>396660</v>
+      </c>
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A174" s="6"/>
-      <c r="B174" s="5"/>
-      <c r="C174" s="7"/>
+      <c r="A174" s="6">
+        <v>46190</v>
+      </c>
+      <c r="B174" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C174" s="7">
+        <v>402380</v>
+      </c>
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A175" s="6"/>
-      <c r="B175" s="5"/>
-      <c r="C175" s="7"/>
+      <c r="A175" s="6">
+        <v>46191</v>
+      </c>
+      <c r="B175" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C175" s="7">
+        <v>425040</v>
+      </c>
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A176" s="6"/>
-      <c r="B176" s="5"/>
-      <c r="C176" s="7"/>
+      <c r="A176" s="6">
+        <v>46192</v>
+      </c>
+      <c r="B176" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C176" s="7">
+        <v>507860</v>
+      </c>
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A177" s="6"/>
-      <c r="B177" s="5"/>
-      <c r="C177" s="7"/>
+      <c r="A177" s="6">
+        <v>46193</v>
+      </c>
+      <c r="B177" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C177" s="7">
+        <v>539200</v>
+      </c>
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A178" s="6"/>
-      <c r="B178" s="5"/>
-      <c r="C178" s="7"/>
+      <c r="A178" s="6">
+        <v>46194</v>
+      </c>
+      <c r="B178" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C178" s="7">
+        <v>299200</v>
+      </c>
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A179" s="6"/>
-      <c r="B179" s="5"/>
-      <c r="C179" s="7"/>
+      <c r="A179" s="6">
+        <v>46195</v>
+      </c>
+      <c r="B179" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C179" s="7">
+        <v>1228860</v>
+      </c>
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A180" s="6"/>
-      <c r="B180" s="5"/>
-      <c r="C180" s="7"/>
+      <c r="A180" s="6">
+        <v>46196</v>
+      </c>
+      <c r="B180" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C180" s="7">
+        <v>1833640</v>
+      </c>
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A181" s="6"/>
-      <c r="B181" s="5"/>
-      <c r="C181" s="7"/>
+      <c r="A181" s="6">
+        <v>46197</v>
+      </c>
+      <c r="B181" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C181" s="7">
+        <v>6264870</v>
+      </c>
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A182" s="6"/>
-      <c r="B182" s="5"/>
-      <c r="C182" s="7"/>
+      <c r="A182" s="6">
+        <v>46198</v>
+      </c>
+      <c r="B182" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C182" s="7">
+        <v>3949520</v>
+      </c>
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A183" s="6"/>
-      <c r="B183" s="5"/>
-      <c r="C183" s="7"/>
+      <c r="A183" s="6">
+        <v>46199</v>
+      </c>
+      <c r="B183" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C183" s="7">
+        <v>1934700</v>
+      </c>
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A184" s="6"/>
-      <c r="B184" s="5"/>
-      <c r="C184" s="7"/>
+      <c r="A184" s="6">
+        <v>46200</v>
+      </c>
+      <c r="B184" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C184" s="7">
+        <v>1080800</v>
+      </c>
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A185" s="6"/>
-      <c r="B185" s="5"/>
-      <c r="C185" s="7"/>
+      <c r="A185" s="6">
+        <v>46201</v>
+      </c>
+      <c r="B185" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C185" s="7">
+        <v>451860</v>
+      </c>
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A186" s="6"/>
-      <c r="B186" s="5"/>
-      <c r="C186" s="7"/>
+      <c r="A186" s="6">
+        <v>46202</v>
+      </c>
+      <c r="B186" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C186" s="7">
+        <v>555040</v>
+      </c>
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A187" s="6"/>
-      <c r="B187" s="5"/>
-      <c r="C187" s="7"/>
+      <c r="A187" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B187" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C187" s="7">
+        <v>574460</v>
+      </c>
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
@@ -2506,212 +3337,392 @@
       <c r="E188" s="5"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A189" s="6"/>
-      <c r="B189" s="5"/>
-      <c r="C189" s="7"/>
+      <c r="A189" s="6">
+        <v>45809</v>
+      </c>
+      <c r="B189" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C189" s="7">
+        <v>74900</v>
+      </c>
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A190" s="6"/>
-      <c r="B190" s="5"/>
-      <c r="C190" s="7"/>
+      <c r="A190" s="6">
+        <v>45810</v>
+      </c>
+      <c r="B190" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C190" s="7">
+        <v>290210</v>
+      </c>
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A191" s="6"/>
-      <c r="B191" s="5"/>
-      <c r="C191" s="7"/>
+      <c r="A191" s="6">
+        <v>45811</v>
+      </c>
+      <c r="B191" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C191" s="7">
+        <v>540460</v>
+      </c>
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A192" s="6"/>
-      <c r="B192" s="5"/>
-      <c r="C192" s="7"/>
+      <c r="A192" s="6">
+        <v>45812</v>
+      </c>
+      <c r="B192" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C192" s="7">
+        <v>79000</v>
+      </c>
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A193" s="6"/>
-      <c r="B193" s="5"/>
-      <c r="C193" s="7"/>
+      <c r="A193" s="6">
+        <v>45813</v>
+      </c>
+      <c r="B193" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C193" s="7">
+        <v>391580</v>
+      </c>
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A194" s="6"/>
-      <c r="B194" s="5"/>
-      <c r="C194" s="7"/>
+      <c r="A194" s="6">
+        <v>45814</v>
+      </c>
+      <c r="B194" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C194" s="7">
+        <v>511320</v>
+      </c>
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A195" s="6"/>
-      <c r="B195" s="5"/>
-      <c r="C195" s="7"/>
+      <c r="A195" s="6">
+        <v>45815</v>
+      </c>
+      <c r="B195" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C195" s="7">
+        <v>409070</v>
+      </c>
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A196" s="6"/>
-      <c r="B196" s="5"/>
-      <c r="C196" s="7"/>
+      <c r="A196" s="6">
+        <v>45816</v>
+      </c>
+      <c r="B196" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C196" s="7">
+        <v>394490</v>
+      </c>
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A197" s="6"/>
-      <c r="B197" s="5"/>
-      <c r="C197" s="7"/>
+      <c r="A197" s="6">
+        <v>45817</v>
+      </c>
+      <c r="B197" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C197" s="7">
+        <v>320110</v>
+      </c>
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A198" s="6"/>
-      <c r="B198" s="5"/>
-      <c r="C198" s="7"/>
+      <c r="A198" s="6">
+        <v>45818</v>
+      </c>
+      <c r="B198" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C198" s="7">
+        <v>974890</v>
+      </c>
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A199" s="6"/>
-      <c r="B199" s="5"/>
-      <c r="C199" s="7"/>
+      <c r="A199" s="6">
+        <v>45819</v>
+      </c>
+      <c r="B199" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C199" s="7">
+        <v>171000</v>
+      </c>
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A200" s="6"/>
-      <c r="B200" s="5"/>
-      <c r="C200" s="7"/>
+      <c r="A200" s="6">
+        <v>45820</v>
+      </c>
+      <c r="B200" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C200" s="7">
+        <v>704600</v>
+      </c>
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A201" s="6"/>
-      <c r="B201" s="5"/>
-      <c r="C201" s="7"/>
+      <c r="A201" s="6">
+        <v>45821</v>
+      </c>
+      <c r="B201" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C201" s="7">
+        <v>947360</v>
+      </c>
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A202" s="6"/>
-      <c r="B202" s="5"/>
-      <c r="C202" s="7"/>
+      <c r="A202" s="6">
+        <v>45822</v>
+      </c>
+      <c r="B202" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C202" s="7">
+        <v>796310</v>
+      </c>
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A203" s="6"/>
-      <c r="B203" s="5"/>
-      <c r="C203" s="7"/>
+      <c r="A203" s="6">
+        <v>45823</v>
+      </c>
+      <c r="B203" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C203" s="7">
+        <v>1020020</v>
+      </c>
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A204" s="6"/>
-      <c r="B204" s="5"/>
-      <c r="C204" s="7"/>
+      <c r="A204" s="6">
+        <v>45824</v>
+      </c>
+      <c r="B204" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C204" s="7">
+        <v>8014770</v>
+      </c>
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A205" s="6"/>
-      <c r="B205" s="5"/>
-      <c r="C205" s="7"/>
+      <c r="A205" s="6">
+        <v>45825</v>
+      </c>
+      <c r="B205" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C205" s="7">
+        <v>2346920</v>
+      </c>
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A206" s="6"/>
-      <c r="B206" s="5"/>
-      <c r="C206" s="7"/>
+      <c r="A206" s="6">
+        <v>45826</v>
+      </c>
+      <c r="B206" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C206" s="7">
+        <v>2261990</v>
+      </c>
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A207" s="6"/>
-      <c r="B207" s="5"/>
-      <c r="C207" s="7"/>
+      <c r="A207" s="6">
+        <v>45827</v>
+      </c>
+      <c r="B207" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C207" s="7">
+        <v>451860</v>
+      </c>
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A208" s="6"/>
-      <c r="B208" s="5"/>
-      <c r="C208" s="7"/>
+      <c r="A208" s="6">
+        <v>45828</v>
+      </c>
+      <c r="B208" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C208" s="7">
+        <v>650870</v>
+      </c>
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A209" s="6"/>
-      <c r="B209" s="5"/>
-      <c r="C209" s="7"/>
+      <c r="A209" s="6">
+        <v>45829</v>
+      </c>
+      <c r="B209" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C209" s="7">
+        <v>470000</v>
+      </c>
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A210" s="6"/>
-      <c r="B210" s="5"/>
-      <c r="C210" s="7"/>
+      <c r="A210" s="6">
+        <v>45830</v>
+      </c>
+      <c r="B210" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C210" s="7">
+        <v>58200</v>
+      </c>
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A211" s="6"/>
-      <c r="B211" s="5"/>
-      <c r="C211" s="7"/>
+      <c r="A211" s="6">
+        <v>45831</v>
+      </c>
+      <c r="B211" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C211" s="7">
+        <v>374800</v>
+      </c>
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A212" s="6"/>
-      <c r="B212" s="5"/>
-      <c r="C212" s="7"/>
+      <c r="A212" s="6">
+        <v>45832</v>
+      </c>
+      <c r="B212" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C212" s="7">
+        <v>221620</v>
+      </c>
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A213" s="6"/>
-      <c r="B213" s="5"/>
-      <c r="C213" s="7"/>
+      <c r="A213" s="6">
+        <v>45833</v>
+      </c>
+      <c r="B213" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C213" s="7">
+        <v>243880</v>
+      </c>
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A214" s="6"/>
-      <c r="B214" s="5"/>
-      <c r="C214" s="7"/>
+      <c r="A214" s="6">
+        <v>45834</v>
+      </c>
+      <c r="B214" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C214" s="7">
+        <v>234460</v>
+      </c>
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A215" s="6"/>
-      <c r="B215" s="5"/>
-      <c r="C215" s="7"/>
+      <c r="A215" s="6">
+        <v>45835</v>
+      </c>
+      <c r="B215" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C215" s="7">
+        <v>167180</v>
+      </c>
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A216" s="6"/>
-      <c r="B216" s="5"/>
-      <c r="C216" s="7"/>
+      <c r="A216" s="6">
+        <v>45836</v>
+      </c>
+      <c r="B216" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C216" s="7">
+        <v>124180</v>
+      </c>
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A217" s="6"/>
-      <c r="B217" s="5"/>
-      <c r="C217" s="7"/>
+      <c r="A217" s="6">
+        <v>45837</v>
+      </c>
+      <c r="B217" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C217" s="7">
+        <v>0</v>
+      </c>
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A218" s="6"/>
-      <c r="B218" s="5"/>
-      <c r="C218" s="7"/>
+      <c r="A218" s="6">
+        <v>45838</v>
+      </c>
+      <c r="B218" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C218" s="7">
+        <v>404030</v>
+      </c>
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
@@ -2723,219 +3734,405 @@
       <c r="E219" s="5"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A220" s="6"/>
-      <c r="B220" s="5"/>
-      <c r="C220" s="7"/>
+      <c r="A220" s="6">
+        <v>46204</v>
+      </c>
+      <c r="B220" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C220" s="7">
+        <v>399740</v>
+      </c>
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A221" s="6"/>
-      <c r="B221" s="5"/>
-      <c r="C221" s="7"/>
+      <c r="A221" s="6">
+        <v>46205</v>
+      </c>
+      <c r="B221" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C221" s="7">
+        <v>481660</v>
+      </c>
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A222" s="6"/>
-      <c r="B222" s="5"/>
-      <c r="C222" s="7"/>
+      <c r="A222" s="6">
+        <v>46206</v>
+      </c>
+      <c r="B222" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C222" s="7">
+        <v>598700</v>
+      </c>
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A223" s="6"/>
-      <c r="B223" s="5"/>
-      <c r="C223" s="7"/>
+      <c r="A223" s="6">
+        <v>46207</v>
+      </c>
+      <c r="B223" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C223" s="7">
+        <v>513340</v>
+      </c>
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A224" s="6"/>
-      <c r="B224" s="5"/>
-      <c r="C224" s="7"/>
+      <c r="A224" s="6">
+        <v>46208</v>
+      </c>
+      <c r="B224" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C224" s="7">
+        <v>163030</v>
+      </c>
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A225" s="6"/>
-      <c r="B225" s="5"/>
-      <c r="C225" s="7"/>
+      <c r="A225" s="6">
+        <v>46209</v>
+      </c>
+      <c r="B225" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C225" s="7">
+        <v>668350</v>
+      </c>
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A226" s="6"/>
-      <c r="B226" s="5"/>
-      <c r="C226" s="7"/>
+      <c r="A226" s="6">
+        <v>46210</v>
+      </c>
+      <c r="B226" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C226" s="7">
+        <v>578760</v>
+      </c>
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A227" s="6"/>
-      <c r="B227" s="5"/>
-      <c r="C227" s="7"/>
+      <c r="A227" s="6">
+        <v>46211</v>
+      </c>
+      <c r="B227" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C227" s="7">
+        <v>510560</v>
+      </c>
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A228" s="6"/>
-      <c r="B228" s="5"/>
-      <c r="C228" s="7"/>
+      <c r="A228" s="6">
+        <v>46212</v>
+      </c>
+      <c r="B228" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C228" s="7">
+        <v>481660</v>
+      </c>
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A229" s="6"/>
-      <c r="B229" s="5"/>
-      <c r="C229" s="7"/>
+      <c r="A229" s="6">
+        <v>46213</v>
+      </c>
+      <c r="B229" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C229" s="7">
+        <v>202060</v>
+      </c>
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A230" s="6"/>
-      <c r="B230" s="5"/>
-      <c r="C230" s="7"/>
+      <c r="A230" s="6">
+        <v>46214</v>
+      </c>
+      <c r="B230" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C230" s="7">
+        <v>524910</v>
+      </c>
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A231" s="6"/>
-      <c r="B231" s="5"/>
-      <c r="C231" s="7"/>
+      <c r="A231" s="6">
+        <v>46215</v>
+      </c>
+      <c r="B231" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C231" s="7">
+        <v>227920</v>
+      </c>
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A232" s="6"/>
-      <c r="B232" s="5"/>
-      <c r="C232" s="7"/>
+      <c r="A232" s="6">
+        <v>46216</v>
+      </c>
+      <c r="B232" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C232" s="7">
+        <v>331020</v>
+      </c>
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A233" s="6"/>
-      <c r="B233" s="5"/>
-      <c r="C233" s="7"/>
+      <c r="A233" s="6">
+        <v>46217</v>
+      </c>
+      <c r="B233" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C233" s="7">
+        <v>392280</v>
+      </c>
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A234" s="6"/>
-      <c r="B234" s="5"/>
-      <c r="C234" s="7"/>
+      <c r="A234" s="6">
+        <v>46218</v>
+      </c>
+      <c r="B234" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C234" s="7">
+        <v>531280</v>
+      </c>
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A235" s="6"/>
-      <c r="B235" s="5"/>
-      <c r="C235" s="7"/>
+      <c r="A235" s="6">
+        <v>46219</v>
+      </c>
+      <c r="B235" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C235" s="7">
+        <v>412000</v>
+      </c>
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A236" s="6"/>
-      <c r="B236" s="5"/>
-      <c r="C236" s="7"/>
+      <c r="A236" s="6">
+        <v>46220</v>
+      </c>
+      <c r="B236" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C236" s="7">
+        <v>278330</v>
+      </c>
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A237" s="6"/>
-      <c r="B237" s="5"/>
-      <c r="C237" s="7"/>
+      <c r="A237" s="6">
+        <v>46221</v>
+      </c>
+      <c r="B237" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C237" s="7">
+        <v>417040</v>
+      </c>
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A238" s="6"/>
-      <c r="B238" s="5"/>
-      <c r="C238" s="7"/>
+      <c r="A238" s="6">
+        <v>46222</v>
+      </c>
+      <c r="B238" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C238" s="7">
+        <v>273420</v>
+      </c>
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A239" s="6"/>
-      <c r="B239" s="5"/>
-      <c r="C239" s="7"/>
+      <c r="A239" s="6">
+        <v>46223</v>
+      </c>
+      <c r="B239" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C239" s="7">
+        <v>320200</v>
+      </c>
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A240" s="6"/>
-      <c r="B240" s="5"/>
-      <c r="C240" s="7"/>
+      <c r="A240" s="6">
+        <v>46224</v>
+      </c>
+      <c r="B240" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C240" s="7">
+        <v>273730</v>
+      </c>
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A241" s="6"/>
-      <c r="B241" s="5"/>
-      <c r="C241" s="7"/>
+      <c r="A241" s="6">
+        <v>46225</v>
+      </c>
+      <c r="B241" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C241" s="7">
+        <v>437930</v>
+      </c>
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A242" s="6"/>
-      <c r="B242" s="5"/>
-      <c r="C242" s="7"/>
+      <c r="A242" s="6">
+        <v>46226</v>
+      </c>
+      <c r="B242" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C242" s="7">
+        <v>228460</v>
+      </c>
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A243" s="6"/>
-      <c r="B243" s="5"/>
-      <c r="C243" s="7"/>
+      <c r="A243" s="6">
+        <v>46227</v>
+      </c>
+      <c r="B243" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C243" s="7">
+        <v>660860</v>
+      </c>
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A244" s="6"/>
-      <c r="B244" s="5"/>
-      <c r="C244" s="7"/>
+      <c r="A244" s="6">
+        <v>46228</v>
+      </c>
+      <c r="B244" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C244" s="7">
+        <v>490970</v>
+      </c>
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A245" s="6"/>
-      <c r="B245" s="5"/>
-      <c r="C245" s="7"/>
+      <c r="A245" s="6">
+        <v>46229</v>
+      </c>
+      <c r="B245" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C245" s="7">
+        <v>200900</v>
+      </c>
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A246" s="6"/>
-      <c r="B246" s="5"/>
-      <c r="C246" s="7"/>
+      <c r="A246" s="6">
+        <v>46230</v>
+      </c>
+      <c r="B246" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C246" s="7">
+        <v>305240</v>
+      </c>
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A247" s="6"/>
-      <c r="B247" s="5"/>
-      <c r="C247" s="7"/>
+      <c r="A247" s="6">
+        <v>46231</v>
+      </c>
+      <c r="B247" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C247" s="7">
+        <v>595250</v>
+      </c>
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A248" s="6"/>
-      <c r="B248" s="5"/>
-      <c r="C248" s="7"/>
+      <c r="A248" s="6">
+        <v>46232</v>
+      </c>
+      <c r="B248" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C248" s="7">
+        <v>379450</v>
+      </c>
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A249" s="6"/>
-      <c r="B249" s="5"/>
-      <c r="C249" s="7"/>
+      <c r="A249" s="6">
+        <v>46233</v>
+      </c>
+      <c r="B249" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C249" s="7">
+        <v>567710</v>
+      </c>
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A250" s="6"/>
-      <c r="B250" s="5"/>
-      <c r="C250" s="7"/>
+      <c r="A250" s="6">
+        <v>46234</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C250" s="7">
+        <v>421430</v>
+      </c>
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
@@ -2947,219 +4144,405 @@
       <c r="E251" s="5"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A252" s="6"/>
-      <c r="B252" s="5"/>
-      <c r="C252" s="7"/>
+      <c r="A252" s="6">
+        <v>45839</v>
+      </c>
+      <c r="B252" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C252" s="7">
+        <v>214820</v>
+      </c>
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A253" s="6"/>
-      <c r="B253" s="5"/>
-      <c r="C253" s="7"/>
+      <c r="A253" s="6">
+        <v>45840</v>
+      </c>
+      <c r="B253" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C253" s="7">
+        <v>282630</v>
+      </c>
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A254" s="6"/>
-      <c r="B254" s="5"/>
-      <c r="C254" s="7"/>
+      <c r="A254" s="6">
+        <v>45841</v>
+      </c>
+      <c r="B254" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C254" s="7">
+        <v>227700</v>
+      </c>
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A255" s="6"/>
-      <c r="B255" s="5"/>
-      <c r="C255" s="7"/>
+      <c r="A255" s="6">
+        <v>45842</v>
+      </c>
+      <c r="B255" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C255" s="7">
+        <v>278950</v>
+      </c>
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A256" s="6"/>
-      <c r="B256" s="5"/>
-      <c r="C256" s="7"/>
+      <c r="A256" s="6">
+        <v>45843</v>
+      </c>
+      <c r="B256" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C256" s="7">
+        <v>191430</v>
+      </c>
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A257" s="6"/>
-      <c r="B257" s="5"/>
-      <c r="C257" s="7"/>
+      <c r="A257" s="6">
+        <v>45844</v>
+      </c>
+      <c r="B257" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C257" s="7">
+        <v>152210</v>
+      </c>
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A258" s="6"/>
-      <c r="B258" s="5"/>
-      <c r="C258" s="7"/>
+      <c r="A258" s="6">
+        <v>45845</v>
+      </c>
+      <c r="B258" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C258" s="7">
+        <v>60910</v>
+      </c>
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A259" s="6"/>
-      <c r="B259" s="5"/>
-      <c r="C259" s="7"/>
+      <c r="A259" s="6">
+        <v>45846</v>
+      </c>
+      <c r="B259" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C259" s="7">
+        <v>336320</v>
+      </c>
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A260" s="6"/>
-      <c r="B260" s="5"/>
-      <c r="C260" s="7"/>
+      <c r="A260" s="6">
+        <v>45847</v>
+      </c>
+      <c r="B260" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C260" s="7">
+        <v>164550</v>
+      </c>
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A261" s="6"/>
-      <c r="B261" s="5"/>
-      <c r="C261" s="7"/>
+      <c r="A261" s="6">
+        <v>45848</v>
+      </c>
+      <c r="B261" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C261" s="7">
+        <v>319070</v>
+      </c>
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A262" s="6"/>
-      <c r="B262" s="5"/>
-      <c r="C262" s="7"/>
+      <c r="A262" s="6">
+        <v>45849</v>
+      </c>
+      <c r="B262" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C262" s="7">
+        <v>214700</v>
+      </c>
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A263" s="6"/>
-      <c r="B263" s="5"/>
-      <c r="C263" s="7"/>
+      <c r="A263" s="6">
+        <v>45850</v>
+      </c>
+      <c r="B263" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C263" s="7">
+        <v>234680</v>
+      </c>
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A264" s="6"/>
-      <c r="B264" s="5"/>
-      <c r="C264" s="7"/>
+      <c r="A264" s="6">
+        <v>45851</v>
+      </c>
+      <c r="B264" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C264" s="7">
+        <v>177820</v>
+      </c>
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A265" s="6"/>
-      <c r="B265" s="5"/>
-      <c r="C265" s="7"/>
+      <c r="A265" s="6">
+        <v>45852</v>
+      </c>
+      <c r="B265" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C265" s="7">
+        <v>227340</v>
+      </c>
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A266" s="6"/>
-      <c r="B266" s="5"/>
-      <c r="C266" s="7"/>
+      <c r="A266" s="6">
+        <v>45853</v>
+      </c>
+      <c r="B266" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C266" s="7">
+        <v>226730</v>
+      </c>
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A267" s="6"/>
-      <c r="B267" s="5"/>
-      <c r="C267" s="7"/>
+      <c r="A267" s="6">
+        <v>45854</v>
+      </c>
+      <c r="B267" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C267" s="7">
+        <v>201680</v>
+      </c>
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A268" s="6"/>
-      <c r="B268" s="5"/>
-      <c r="C268" s="7"/>
+      <c r="A268" s="6">
+        <v>45855</v>
+      </c>
+      <c r="B268" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C268" s="7">
+        <v>262800</v>
+      </c>
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A269" s="6"/>
-      <c r="B269" s="5"/>
-      <c r="C269" s="7"/>
+      <c r="A269" s="6">
+        <v>45856</v>
+      </c>
+      <c r="B269" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C269" s="7">
+        <v>205440</v>
+      </c>
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A270" s="6"/>
-      <c r="B270" s="5"/>
-      <c r="C270" s="7"/>
+      <c r="A270" s="6">
+        <v>45857</v>
+      </c>
+      <c r="B270" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C270" s="7">
+        <v>206000</v>
+      </c>
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A271" s="6"/>
-      <c r="B271" s="5"/>
-      <c r="C271" s="7"/>
+      <c r="A271" s="6">
+        <v>45858</v>
+      </c>
+      <c r="B271" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C271" s="7">
+        <v>159460</v>
+      </c>
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A272" s="6"/>
-      <c r="B272" s="5"/>
-      <c r="C272" s="7"/>
+      <c r="A272" s="6">
+        <v>45859</v>
+      </c>
+      <c r="B272" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C272" s="7">
+        <v>126860</v>
+      </c>
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A273" s="6"/>
-      <c r="B273" s="5"/>
-      <c r="C273" s="7"/>
+      <c r="A273" s="6">
+        <v>45860</v>
+      </c>
+      <c r="B273" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C273" s="7">
+        <v>119430</v>
+      </c>
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A274" s="6"/>
-      <c r="B274" s="5"/>
-      <c r="C274" s="7"/>
+      <c r="A274" s="6">
+        <v>45861</v>
+      </c>
+      <c r="B274" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C274" s="7">
+        <v>185160</v>
+      </c>
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A275" s="6"/>
-      <c r="B275" s="5"/>
-      <c r="C275" s="7"/>
+      <c r="A275" s="6">
+        <v>45862</v>
+      </c>
+      <c r="B275" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C275" s="7">
+        <v>330350</v>
+      </c>
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A276" s="6"/>
-      <c r="B276" s="5"/>
-      <c r="C276" s="7"/>
+      <c r="A276" s="6">
+        <v>45863</v>
+      </c>
+      <c r="B276" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C276" s="7">
+        <v>229580</v>
+      </c>
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A277" s="6"/>
-      <c r="B277" s="5"/>
-      <c r="C277" s="7"/>
+      <c r="A277" s="6">
+        <v>45864</v>
+      </c>
+      <c r="B277" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C277" s="7">
+        <v>217790</v>
+      </c>
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A278" s="6"/>
-      <c r="B278" s="5"/>
-      <c r="C278" s="7"/>
+      <c r="A278" s="6">
+        <v>45865</v>
+      </c>
+      <c r="B278" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C278" s="7">
+        <v>114200</v>
+      </c>
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A279" s="6"/>
-      <c r="B279" s="5"/>
-      <c r="C279" s="7"/>
+      <c r="A279" s="6">
+        <v>45866</v>
+      </c>
+      <c r="B279" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C279" s="7">
+        <v>235500</v>
+      </c>
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A280" s="6"/>
-      <c r="B280" s="5"/>
-      <c r="C280" s="7"/>
+      <c r="A280" s="6">
+        <v>45867</v>
+      </c>
+      <c r="B280" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C280" s="7">
+        <v>235130</v>
+      </c>
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A281" s="6"/>
-      <c r="B281" s="5"/>
-      <c r="C281" s="7"/>
+      <c r="A281" s="6">
+        <v>45868</v>
+      </c>
+      <c r="B281" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C281" s="7">
+        <v>156160</v>
+      </c>
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A282" s="6"/>
-      <c r="B282" s="5"/>
-      <c r="C282" s="7"/>
+      <c r="A282" s="6">
+        <v>45869</v>
+      </c>
+      <c r="B282" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C282" s="7">
+        <v>197300</v>
+      </c>
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
@@ -3171,219 +4554,405 @@
       <c r="E283" s="5"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A284" s="6"/>
-      <c r="B284" s="5"/>
-      <c r="C284" s="7"/>
+      <c r="A284" s="6">
+        <v>46235</v>
+      </c>
+      <c r="B284" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C284" s="7">
+        <v>403860</v>
+      </c>
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A285" s="6"/>
-      <c r="B285" s="5"/>
-      <c r="C285" s="7"/>
+      <c r="A285" s="6">
+        <v>46236</v>
+      </c>
+      <c r="B285" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C285" s="7">
+        <v>511340</v>
+      </c>
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A286" s="6"/>
-      <c r="B286" s="5"/>
-      <c r="C286" s="7"/>
+      <c r="A286" s="6">
+        <v>46237</v>
+      </c>
+      <c r="B286" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C286" s="7">
+        <v>801850</v>
+      </c>
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A287" s="6"/>
-      <c r="B287" s="5"/>
-      <c r="C287" s="7"/>
+      <c r="A287" s="6">
+        <v>46238</v>
+      </c>
+      <c r="B287" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C287" s="7">
+        <v>1108210</v>
+      </c>
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A288" s="6"/>
-      <c r="B288" s="5"/>
-      <c r="C288" s="7"/>
+      <c r="A288" s="6">
+        <v>46239</v>
+      </c>
+      <c r="B288" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C288" s="7">
+        <v>1169610</v>
+      </c>
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A289" s="6"/>
-      <c r="B289" s="5"/>
-      <c r="C289" s="7"/>
+      <c r="A289" s="6">
+        <v>46240</v>
+      </c>
+      <c r="B289" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C289" s="7">
+        <v>1138260</v>
+      </c>
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A290" s="6"/>
-      <c r="B290" s="5"/>
-      <c r="C290" s="7"/>
+      <c r="A290" s="6">
+        <v>46241</v>
+      </c>
+      <c r="B290" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C290" s="7">
+        <v>1135070</v>
+      </c>
       <c r="D290" s="7"/>
       <c r="E290" s="5"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A291" s="6"/>
-      <c r="B291" s="5"/>
-      <c r="C291" s="7"/>
+      <c r="A291" s="6">
+        <v>46242</v>
+      </c>
+      <c r="B291" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C291" s="7">
+        <v>1228060</v>
+      </c>
       <c r="D291" s="7"/>
       <c r="E291" s="5"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A292" s="6"/>
-      <c r="B292" s="5"/>
-      <c r="C292" s="7"/>
+      <c r="A292" s="6">
+        <v>46243</v>
+      </c>
+      <c r="B292" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C292" s="7">
+        <v>1093320</v>
+      </c>
       <c r="D292" s="7"/>
       <c r="E292" s="5"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A293" s="6"/>
-      <c r="B293" s="5"/>
-      <c r="C293" s="7"/>
+      <c r="A293" s="6">
+        <v>46244</v>
+      </c>
+      <c r="B293" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C293" s="7">
+        <v>1570110</v>
+      </c>
       <c r="D293" s="7"/>
       <c r="E293" s="5"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A294" s="6"/>
-      <c r="B294" s="5"/>
-      <c r="C294" s="7"/>
+      <c r="A294" s="6">
+        <v>46245</v>
+      </c>
+      <c r="B294" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C294" s="7">
+        <v>1547130</v>
+      </c>
       <c r="D294" s="7"/>
       <c r="E294" s="5"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A295" s="6"/>
-      <c r="B295" s="5"/>
-      <c r="C295" s="7"/>
+      <c r="A295" s="6">
+        <v>46246</v>
+      </c>
+      <c r="B295" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C295" s="7">
+        <v>1476040</v>
+      </c>
       <c r="D295" s="7"/>
       <c r="E295" s="5"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A296" s="6"/>
-      <c r="B296" s="5"/>
-      <c r="C296" s="7"/>
+      <c r="A296" s="6">
+        <v>46247</v>
+      </c>
+      <c r="B296" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C296" s="7">
+        <v>1127130</v>
+      </c>
       <c r="D296" s="7"/>
       <c r="E296" s="5"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A297" s="6"/>
-      <c r="B297" s="5"/>
-      <c r="C297" s="7"/>
+      <c r="A297" s="6">
+        <v>46248</v>
+      </c>
+      <c r="B297" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C297" s="7">
+        <v>1048500</v>
+      </c>
       <c r="D297" s="7"/>
       <c r="E297" s="5"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A298" s="6"/>
-      <c r="B298" s="5"/>
-      <c r="C298" s="7"/>
+      <c r="A298" s="6">
+        <v>46249</v>
+      </c>
+      <c r="B298" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C298" s="7">
+        <v>1036030</v>
+      </c>
       <c r="D298" s="7"/>
       <c r="E298" s="5"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A299" s="6"/>
-      <c r="B299" s="5"/>
-      <c r="C299" s="7"/>
+      <c r="A299" s="6">
+        <v>46250</v>
+      </c>
+      <c r="B299" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C299" s="7">
+        <v>1187540</v>
+      </c>
       <c r="D299" s="7"/>
       <c r="E299" s="5"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A300" s="6"/>
-      <c r="B300" s="5"/>
-      <c r="C300" s="7"/>
+      <c r="A300" s="6">
+        <v>46251</v>
+      </c>
+      <c r="B300" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C300" s="7">
+        <v>1147050</v>
+      </c>
       <c r="D300" s="7"/>
       <c r="E300" s="5"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A301" s="6"/>
-      <c r="B301" s="5"/>
-      <c r="C301" s="7"/>
+      <c r="A301" s="6">
+        <v>46252</v>
+      </c>
+      <c r="B301" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C301" s="7">
+        <v>1068720</v>
+      </c>
       <c r="D301" s="7"/>
       <c r="E301" s="5"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A302" s="6"/>
-      <c r="B302" s="5"/>
-      <c r="C302" s="7"/>
+      <c r="A302" s="6">
+        <v>46253</v>
+      </c>
+      <c r="B302" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C302" s="7">
+        <v>1136240</v>
+      </c>
       <c r="D302" s="7"/>
       <c r="E302" s="5"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A303" s="6"/>
-      <c r="B303" s="5"/>
-      <c r="C303" s="7"/>
+      <c r="A303" s="6">
+        <v>46254</v>
+      </c>
+      <c r="B303" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C303" s="7">
+        <v>1171640</v>
+      </c>
       <c r="D303" s="7"/>
       <c r="E303" s="5"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A304" s="6"/>
-      <c r="B304" s="5"/>
-      <c r="C304" s="7"/>
+      <c r="A304" s="6">
+        <v>46255</v>
+      </c>
+      <c r="B304" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C304" s="7">
+        <v>1082950</v>
+      </c>
       <c r="D304" s="7"/>
       <c r="E304" s="5"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A305" s="6"/>
-      <c r="B305" s="5"/>
-      <c r="C305" s="7"/>
+      <c r="A305" s="6">
+        <v>46256</v>
+      </c>
+      <c r="B305" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C305" s="7">
+        <v>957480</v>
+      </c>
       <c r="D305" s="7"/>
       <c r="E305" s="5"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A306" s="6"/>
-      <c r="B306" s="5"/>
-      <c r="C306" s="7"/>
+      <c r="A306" s="6">
+        <v>46257</v>
+      </c>
+      <c r="B306" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C306" s="7">
+        <v>986280</v>
+      </c>
       <c r="D306" s="7"/>
       <c r="E306" s="5"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A307" s="6"/>
-      <c r="B307" s="5"/>
-      <c r="C307" s="7"/>
+      <c r="A307" s="6">
+        <v>46258</v>
+      </c>
+      <c r="B307" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C307" s="7">
+        <v>1130890</v>
+      </c>
       <c r="D307" s="7"/>
       <c r="E307" s="5"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A308" s="6"/>
-      <c r="B308" s="5"/>
-      <c r="C308" s="7"/>
+      <c r="A308" s="6">
+        <v>46259</v>
+      </c>
+      <c r="B308" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C308" s="7">
+        <v>1229900</v>
+      </c>
       <c r="D308" s="7"/>
       <c r="E308" s="5"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A309" s="6"/>
-      <c r="B309" s="5"/>
-      <c r="C309" s="7"/>
+      <c r="A309" s="6">
+        <v>46260</v>
+      </c>
+      <c r="B309" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C309" s="7">
+        <v>1327380</v>
+      </c>
       <c r="D309" s="7"/>
       <c r="E309" s="5"/>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A310" s="6"/>
-      <c r="B310" s="5"/>
-      <c r="C310" s="7"/>
+      <c r="A310" s="6">
+        <v>46261</v>
+      </c>
+      <c r="B310" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C310" s="7">
+        <v>1141620</v>
+      </c>
       <c r="D310" s="7"/>
       <c r="E310" s="5"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A311" s="6"/>
-      <c r="B311" s="5"/>
-      <c r="C311" s="7"/>
+      <c r="A311" s="6">
+        <v>46262</v>
+      </c>
+      <c r="B311" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C311" s="7">
+        <v>1134920</v>
+      </c>
       <c r="D311" s="7"/>
       <c r="E311" s="5"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A312" s="6"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="7"/>
+      <c r="A312" s="6">
+        <v>46263</v>
+      </c>
+      <c r="B312" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C312" s="7">
+        <v>1360250</v>
+      </c>
       <c r="D312" s="7"/>
       <c r="E312" s="5"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A313" s="6"/>
-      <c r="B313" s="5"/>
-      <c r="C313" s="7"/>
+      <c r="A313" s="6">
+        <v>46264</v>
+      </c>
+      <c r="B313" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C313" s="7">
+        <v>1351580</v>
+      </c>
       <c r="D313" s="7"/>
       <c r="E313" s="5"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A314" s="6"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="7"/>
+      <c r="A314" s="6">
+        <v>46265</v>
+      </c>
+      <c r="B314" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C314" s="7">
+        <v>1164740</v>
+      </c>
       <c r="D314" s="7"/>
       <c r="E314" s="5"/>
     </row>
@@ -3395,219 +4964,405 @@
       <c r="E315" s="5"/>
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A316" s="6"/>
-      <c r="B316" s="5"/>
-      <c r="C316" s="7"/>
+      <c r="A316" s="6">
+        <v>45870</v>
+      </c>
+      <c r="B316" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C316" s="7">
+        <v>167220</v>
+      </c>
       <c r="D316" s="7"/>
       <c r="E316" s="5"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A317" s="6"/>
-      <c r="B317" s="5"/>
-      <c r="C317" s="7"/>
+      <c r="A317" s="6">
+        <v>45871</v>
+      </c>
+      <c r="B317" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C317" s="7">
+        <v>350380</v>
+      </c>
       <c r="D317" s="7"/>
       <c r="E317" s="5"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A318" s="6"/>
-      <c r="B318" s="5"/>
-      <c r="C318" s="7"/>
+      <c r="A318" s="6">
+        <v>45872</v>
+      </c>
+      <c r="B318" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C318" s="7">
+        <v>346970</v>
+      </c>
       <c r="D318" s="7"/>
       <c r="E318" s="5"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A319" s="6"/>
-      <c r="B319" s="5"/>
-      <c r="C319" s="7"/>
+      <c r="A319" s="6">
+        <v>45873</v>
+      </c>
+      <c r="B319" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C319" s="7">
+        <v>143340</v>
+      </c>
       <c r="D319" s="7"/>
       <c r="E319" s="5"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A320" s="6"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="7"/>
+      <c r="A320" s="6">
+        <v>45874</v>
+      </c>
+      <c r="B320" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C320" s="7">
+        <v>132060</v>
+      </c>
       <c r="D320" s="7"/>
       <c r="E320" s="5"/>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A321" s="6"/>
-      <c r="B321" s="5"/>
-      <c r="C321" s="7"/>
+      <c r="A321" s="6">
+        <v>45875</v>
+      </c>
+      <c r="B321" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C321" s="7">
+        <v>629120</v>
+      </c>
       <c r="D321" s="7"/>
       <c r="E321" s="5"/>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A322" s="6"/>
-      <c r="B322" s="5"/>
-      <c r="C322" s="7"/>
+      <c r="A322" s="6">
+        <v>45876</v>
+      </c>
+      <c r="B322" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C322" s="7">
+        <v>218300</v>
+      </c>
       <c r="D322" s="7"/>
       <c r="E322" s="5"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A323" s="6"/>
-      <c r="B323" s="5"/>
-      <c r="C323" s="7"/>
+      <c r="A323" s="6">
+        <v>45877</v>
+      </c>
+      <c r="B323" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C323" s="7">
+        <v>428020</v>
+      </c>
       <c r="D323" s="7"/>
       <c r="E323" s="5"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A324" s="6"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="7"/>
+      <c r="A324" s="6">
+        <v>45878</v>
+      </c>
+      <c r="B324" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C324" s="7">
+        <v>232460</v>
+      </c>
       <c r="D324" s="7"/>
       <c r="E324" s="5"/>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A325" s="6"/>
-      <c r="B325" s="5"/>
-      <c r="C325" s="7"/>
+      <c r="A325" s="6">
+        <v>45879</v>
+      </c>
+      <c r="B325" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C325" s="7">
+        <v>231720</v>
+      </c>
       <c r="D325" s="7"/>
       <c r="E325" s="5"/>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A326" s="6"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="7"/>
+      <c r="A326" s="6">
+        <v>45880</v>
+      </c>
+      <c r="B326" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C326" s="7">
+        <v>495660</v>
+      </c>
       <c r="D326" s="7"/>
       <c r="E326" s="5"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A327" s="6"/>
-      <c r="B327" s="5"/>
-      <c r="C327" s="7"/>
+      <c r="A327" s="6">
+        <v>45881</v>
+      </c>
+      <c r="B327" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C327" s="7">
+        <v>265910</v>
+      </c>
       <c r="D327" s="7"/>
       <c r="E327" s="5"/>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A328" s="6"/>
-      <c r="B328" s="5"/>
-      <c r="C328" s="7"/>
+      <c r="A328" s="6">
+        <v>45882</v>
+      </c>
+      <c r="B328" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C328" s="7">
+        <v>291880</v>
+      </c>
       <c r="D328" s="7"/>
       <c r="E328" s="5"/>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A329" s="6"/>
-      <c r="B329" s="5"/>
-      <c r="C329" s="7"/>
+      <c r="A329" s="6">
+        <v>45883</v>
+      </c>
+      <c r="B329" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C329" s="7">
+        <v>239340</v>
+      </c>
       <c r="D329" s="7"/>
       <c r="E329" s="5"/>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A330" s="6"/>
-      <c r="B330" s="5"/>
-      <c r="C330" s="7"/>
+      <c r="A330" s="6">
+        <v>45884</v>
+      </c>
+      <c r="B330" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C330" s="7">
+        <v>362550</v>
+      </c>
       <c r="D330" s="7"/>
       <c r="E330" s="5"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A331" s="6"/>
-      <c r="B331" s="5"/>
-      <c r="C331" s="7"/>
+      <c r="A331" s="6">
+        <v>45885</v>
+      </c>
+      <c r="B331" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C331" s="7">
+        <v>242910</v>
+      </c>
       <c r="D331" s="7"/>
       <c r="E331" s="5"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A332" s="6"/>
-      <c r="B332" s="5"/>
-      <c r="C332" s="7"/>
+      <c r="A332" s="6">
+        <v>45886</v>
+      </c>
+      <c r="B332" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C332" s="7">
+        <v>81400</v>
+      </c>
       <c r="D332" s="7"/>
       <c r="E332" s="5"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A333" s="6"/>
-      <c r="B333" s="5"/>
-      <c r="C333" s="7"/>
+      <c r="A333" s="6">
+        <v>45887</v>
+      </c>
+      <c r="B333" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C333" s="7">
+        <v>319750</v>
+      </c>
       <c r="D333" s="7"/>
       <c r="E333" s="5"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A334" s="6"/>
-      <c r="B334" s="5"/>
-      <c r="C334" s="7"/>
+      <c r="A334" s="6">
+        <v>45888</v>
+      </c>
+      <c r="B334" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C334" s="7">
+        <v>419530</v>
+      </c>
       <c r="D334" s="7"/>
       <c r="E334" s="5"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A335" s="6"/>
-      <c r="B335" s="5"/>
-      <c r="C335" s="7"/>
+      <c r="A335" s="6">
+        <v>45889</v>
+      </c>
+      <c r="B335" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C335" s="7">
+        <v>329950</v>
+      </c>
       <c r="D335" s="7"/>
       <c r="E335" s="5"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A336" s="6"/>
-      <c r="B336" s="5"/>
-      <c r="C336" s="7"/>
+      <c r="A336" s="6">
+        <v>45890</v>
+      </c>
+      <c r="B336" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C336" s="7">
+        <v>170250</v>
+      </c>
       <c r="D336" s="7"/>
       <c r="E336" s="5"/>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A337" s="6"/>
-      <c r="B337" s="5"/>
-      <c r="C337" s="7"/>
+      <c r="A337" s="6">
+        <v>45891</v>
+      </c>
+      <c r="B337" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C337" s="7">
+        <v>425050</v>
+      </c>
       <c r="D337" s="7"/>
       <c r="E337" s="5"/>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A338" s="6"/>
-      <c r="B338" s="5"/>
-      <c r="C338" s="7"/>
+      <c r="A338" s="6">
+        <v>45892</v>
+      </c>
+      <c r="B338" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C338" s="7">
+        <v>150670</v>
+      </c>
       <c r="D338" s="7"/>
       <c r="E338" s="5"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A339" s="6"/>
-      <c r="B339" s="5"/>
-      <c r="C339" s="7"/>
+      <c r="A339" s="6">
+        <v>45893</v>
+      </c>
+      <c r="B339" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C339" s="7">
+        <v>128730</v>
+      </c>
       <c r="D339" s="7"/>
       <c r="E339" s="5"/>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A340" s="6"/>
-      <c r="B340" s="5"/>
-      <c r="C340" s="7"/>
+      <c r="A340" s="6">
+        <v>45894</v>
+      </c>
+      <c r="B340" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C340" s="7">
+        <v>377400</v>
+      </c>
       <c r="D340" s="7"/>
       <c r="E340" s="5"/>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A341" s="6"/>
-      <c r="B341" s="5"/>
-      <c r="C341" s="7"/>
+      <c r="A341" s="6">
+        <v>45895</v>
+      </c>
+      <c r="B341" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C341" s="7">
+        <v>74620</v>
+      </c>
       <c r="D341" s="7"/>
       <c r="E341" s="5"/>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A342" s="6"/>
-      <c r="B342" s="5"/>
-      <c r="C342" s="7"/>
+      <c r="A342" s="6">
+        <v>45896</v>
+      </c>
+      <c r="B342" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C342" s="7">
+        <v>391520</v>
+      </c>
       <c r="D342" s="7"/>
       <c r="E342" s="5"/>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A343" s="6"/>
-      <c r="B343" s="5"/>
-      <c r="C343" s="7"/>
+      <c r="A343" s="6">
+        <v>45897</v>
+      </c>
+      <c r="B343" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C343" s="7">
+        <v>158820</v>
+      </c>
       <c r="D343" s="7"/>
       <c r="E343" s="5"/>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A344" s="6"/>
-      <c r="B344" s="5"/>
-      <c r="C344" s="7"/>
+      <c r="A344" s="6">
+        <v>45898</v>
+      </c>
+      <c r="B344" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C344" s="7">
+        <v>360880</v>
+      </c>
       <c r="D344" s="7"/>
       <c r="E344" s="5"/>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A345" s="6"/>
-      <c r="B345" s="5"/>
-      <c r="C345" s="7"/>
+      <c r="A345" s="6">
+        <v>45899</v>
+      </c>
+      <c r="B345" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C345" s="7">
+        <v>100140</v>
+      </c>
       <c r="D345" s="7"/>
       <c r="E345" s="5"/>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A346" s="6"/>
-      <c r="B346" s="5"/>
-      <c r="C346" s="7"/>
+      <c r="A346" s="6">
+        <v>45900</v>
+      </c>
+      <c r="B346" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C346" s="7">
+        <v>243510</v>
+      </c>
       <c r="D346" s="7"/>
       <c r="E346" s="5"/>
     </row>
@@ -3619,212 +5374,392 @@
       <c r="E347" s="5"/>
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A348" s="6"/>
-      <c r="B348" s="5"/>
-      <c r="C348" s="7"/>
+      <c r="A348" s="6">
+        <v>45901</v>
+      </c>
+      <c r="B348" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C348" s="7">
+        <v>176920</v>
+      </c>
       <c r="D348" s="7"/>
       <c r="E348" s="5"/>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A349" s="6"/>
-      <c r="B349" s="5"/>
-      <c r="C349" s="7"/>
+      <c r="A349" s="6">
+        <v>45902</v>
+      </c>
+      <c r="B349" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C349" s="7">
+        <v>161250</v>
+      </c>
       <c r="D349" s="7"/>
       <c r="E349" s="5"/>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A350" s="6"/>
-      <c r="B350" s="5"/>
-      <c r="C350" s="7"/>
+      <c r="A350" s="6">
+        <v>45903</v>
+      </c>
+      <c r="B350" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C350" s="7">
+        <v>333640</v>
+      </c>
       <c r="D350" s="7"/>
       <c r="E350" s="5"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A351" s="6"/>
-      <c r="B351" s="5"/>
-      <c r="C351" s="7"/>
+      <c r="A351" s="6">
+        <v>45904</v>
+      </c>
+      <c r="B351" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C351" s="7">
+        <v>145410</v>
+      </c>
       <c r="D351" s="7"/>
       <c r="E351" s="5"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A352" s="6"/>
-      <c r="B352" s="5"/>
-      <c r="C352" s="7"/>
+      <c r="A352" s="6">
+        <v>45905</v>
+      </c>
+      <c r="B352" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C352" s="7">
+        <v>419600</v>
+      </c>
       <c r="D352" s="7"/>
       <c r="E352" s="5"/>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A353" s="6"/>
-      <c r="B353" s="5"/>
-      <c r="C353" s="7"/>
+      <c r="A353" s="6">
+        <v>45906</v>
+      </c>
+      <c r="B353" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C353" s="7">
+        <v>78240</v>
+      </c>
       <c r="D353" s="7"/>
       <c r="E353" s="5"/>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A354" s="6"/>
-      <c r="B354" s="5"/>
-      <c r="C354" s="7"/>
+      <c r="A354" s="6">
+        <v>45907</v>
+      </c>
+      <c r="B354" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C354" s="7">
+        <v>68180</v>
+      </c>
       <c r="D354" s="7"/>
       <c r="E354" s="5"/>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A355" s="6"/>
-      <c r="B355" s="5"/>
-      <c r="C355" s="7"/>
+      <c r="A355" s="6">
+        <v>45908</v>
+      </c>
+      <c r="B355" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C355" s="7">
+        <v>322410</v>
+      </c>
       <c r="D355" s="7"/>
       <c r="E355" s="5"/>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A356" s="6"/>
-      <c r="B356" s="5"/>
-      <c r="C356" s="7"/>
+      <c r="A356" s="6">
+        <v>45909</v>
+      </c>
+      <c r="B356" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C356" s="7">
+        <v>72270</v>
+      </c>
       <c r="D356" s="7"/>
       <c r="E356" s="5"/>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A357" s="6"/>
-      <c r="B357" s="5"/>
-      <c r="C357" s="7"/>
+      <c r="A357" s="6">
+        <v>45910</v>
+      </c>
+      <c r="B357" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C357" s="7">
+        <v>350500</v>
+      </c>
       <c r="D357" s="7"/>
       <c r="E357" s="5"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A358" s="6"/>
-      <c r="B358" s="5"/>
-      <c r="C358" s="7"/>
+      <c r="A358" s="6">
+        <v>45911</v>
+      </c>
+      <c r="B358" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C358" s="7">
+        <v>132330</v>
+      </c>
       <c r="D358" s="7"/>
       <c r="E358" s="5"/>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A359" s="6"/>
-      <c r="B359" s="5"/>
-      <c r="C359" s="7"/>
+      <c r="A359" s="6">
+        <v>45912</v>
+      </c>
+      <c r="B359" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C359" s="7">
+        <v>282820</v>
+      </c>
       <c r="D359" s="7"/>
       <c r="E359" s="5"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A360" s="6"/>
-      <c r="B360" s="5"/>
-      <c r="C360" s="7"/>
+      <c r="A360" s="6">
+        <v>45913</v>
+      </c>
+      <c r="B360" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C360" s="7">
+        <v>140280</v>
+      </c>
       <c r="D360" s="7"/>
       <c r="E360" s="5"/>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A361" s="6"/>
-      <c r="B361" s="5"/>
-      <c r="C361" s="7"/>
+      <c r="A361" s="6">
+        <v>45914</v>
+      </c>
+      <c r="B361" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C361" s="7">
+        <v>81480</v>
+      </c>
       <c r="D361" s="7"/>
       <c r="E361" s="5"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A362" s="6"/>
-      <c r="B362" s="5"/>
-      <c r="C362" s="7"/>
+      <c r="A362" s="6">
+        <v>45915</v>
+      </c>
+      <c r="B362" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C362" s="7">
+        <v>185160</v>
+      </c>
       <c r="D362" s="7"/>
       <c r="E362" s="5"/>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A363" s="6"/>
-      <c r="B363" s="5"/>
-      <c r="C363" s="7"/>
+      <c r="A363" s="6">
+        <v>45916</v>
+      </c>
+      <c r="B363" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C363" s="7">
+        <v>92420</v>
+      </c>
       <c r="D363" s="7"/>
       <c r="E363" s="5"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A364" s="6"/>
-      <c r="B364" s="5"/>
-      <c r="C364" s="7"/>
+      <c r="A364" s="6">
+        <v>45917</v>
+      </c>
+      <c r="B364" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C364" s="7">
+        <v>200030</v>
+      </c>
       <c r="D364" s="7"/>
       <c r="E364" s="5"/>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A365" s="6"/>
-      <c r="B365" s="5"/>
-      <c r="C365" s="7"/>
+      <c r="A365" s="6">
+        <v>45918</v>
+      </c>
+      <c r="B365" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C365" s="7">
+        <v>109950</v>
+      </c>
       <c r="D365" s="7"/>
       <c r="E365" s="5"/>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A366" s="6"/>
-      <c r="B366" s="5"/>
-      <c r="C366" s="7"/>
+      <c r="A366" s="6">
+        <v>45919</v>
+      </c>
+      <c r="B366" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C366" s="7">
+        <v>317560</v>
+      </c>
       <c r="D366" s="7"/>
       <c r="E366" s="5"/>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A367" s="6"/>
-      <c r="B367" s="5"/>
-      <c r="C367" s="7"/>
+      <c r="A367" s="6">
+        <v>45920</v>
+      </c>
+      <c r="B367" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C367" s="7">
+        <v>136720</v>
+      </c>
       <c r="D367" s="7"/>
       <c r="E367" s="5"/>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A368" s="6"/>
-      <c r="B368" s="5"/>
-      <c r="C368" s="7"/>
+      <c r="A368" s="6">
+        <v>45921</v>
+      </c>
+      <c r="B368" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C368" s="7">
+        <v>84350</v>
+      </c>
       <c r="D368" s="7"/>
       <c r="E368" s="5"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A369" s="6"/>
-      <c r="B369" s="5"/>
-      <c r="C369" s="7"/>
+      <c r="A369" s="6">
+        <v>45922</v>
+      </c>
+      <c r="B369" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C369" s="7">
+        <v>367710</v>
+      </c>
       <c r="D369" s="7"/>
       <c r="E369" s="5"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A370" s="6"/>
-      <c r="B370" s="5"/>
-      <c r="C370" s="7"/>
+      <c r="A370" s="6">
+        <v>45923</v>
+      </c>
+      <c r="B370" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C370" s="7">
+        <v>180390</v>
+      </c>
       <c r="D370" s="7"/>
       <c r="E370" s="5"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A371" s="6"/>
-      <c r="B371" s="5"/>
-      <c r="C371" s="7"/>
+      <c r="A371" s="6">
+        <v>45924</v>
+      </c>
+      <c r="B371" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C371" s="7">
+        <v>233430</v>
+      </c>
       <c r="D371" s="7"/>
       <c r="E371" s="5"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A372" s="6"/>
-      <c r="B372" s="5"/>
-      <c r="C372" s="7"/>
+      <c r="A372" s="6">
+        <v>45925</v>
+      </c>
+      <c r="B372" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C372" s="7">
+        <v>409620</v>
+      </c>
       <c r="D372" s="7"/>
       <c r="E372" s="5"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A373" s="6"/>
-      <c r="B373" s="5"/>
-      <c r="C373" s="7"/>
+      <c r="A373" s="6">
+        <v>45926</v>
+      </c>
+      <c r="B373" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C373" s="7">
+        <v>343820</v>
+      </c>
       <c r="D373" s="7"/>
       <c r="E373" s="5"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A374" s="6"/>
-      <c r="B374" s="5"/>
-      <c r="C374" s="7"/>
+      <c r="A374" s="6">
+        <v>45927</v>
+      </c>
+      <c r="B374" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C374" s="7">
+        <v>1077030</v>
+      </c>
       <c r="D374" s="7"/>
       <c r="E374" s="5"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A375" s="6"/>
-      <c r="B375" s="5"/>
-      <c r="C375" s="7"/>
+      <c r="A375" s="6">
+        <v>45928</v>
+      </c>
+      <c r="B375" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C375" s="7">
+        <v>67140</v>
+      </c>
       <c r="D375" s="7"/>
       <c r="E375" s="5"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A376" s="6"/>
-      <c r="B376" s="5"/>
-      <c r="C376" s="7"/>
+      <c r="A376" s="6">
+        <v>45929</v>
+      </c>
+      <c r="B376" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C376" s="7">
+        <v>2051880</v>
+      </c>
       <c r="D376" s="7"/>
       <c r="E376" s="5"/>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A377" s="6"/>
-      <c r="B377" s="5"/>
-      <c r="C377" s="7"/>
+      <c r="A377" s="6">
+        <v>45930</v>
+      </c>
+      <c r="B377" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C377" s="7">
+        <v>1105220</v>
+      </c>
       <c r="D377" s="7"/>
       <c r="E377" s="5"/>
     </row>
@@ -3836,219 +5771,405 @@
       <c r="E378" s="5"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A379" s="6"/>
-      <c r="B379" s="5"/>
-      <c r="C379" s="7"/>
+      <c r="A379" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B379" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C379" s="7">
+        <v>1989180</v>
+      </c>
       <c r="D379" s="7"/>
       <c r="E379" s="5"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A380" s="6"/>
-      <c r="B380" s="5"/>
-      <c r="C380" s="7"/>
+      <c r="A380" s="6">
+        <v>45932</v>
+      </c>
+      <c r="B380" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C380" s="7">
+        <v>4134460</v>
+      </c>
       <c r="D380" s="7"/>
       <c r="E380" s="5"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A381" s="6"/>
-      <c r="B381" s="5"/>
-      <c r="C381" s="7"/>
+      <c r="A381" s="6">
+        <v>45933</v>
+      </c>
+      <c r="B381" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C381" s="7">
+        <v>345820</v>
+      </c>
       <c r="D381" s="7"/>
       <c r="E381" s="5"/>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A382" s="6"/>
-      <c r="B382" s="5"/>
-      <c r="C382" s="7"/>
+      <c r="A382" s="6">
+        <v>45934</v>
+      </c>
+      <c r="B382" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C382" s="7">
+        <v>570800</v>
+      </c>
       <c r="D382" s="7"/>
       <c r="E382" s="5"/>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A383" s="6"/>
-      <c r="B383" s="5"/>
-      <c r="C383" s="7"/>
+      <c r="A383" s="6">
+        <v>45935</v>
+      </c>
+      <c r="B383" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C383" s="7">
+        <v>103870</v>
+      </c>
       <c r="D383" s="7"/>
       <c r="E383" s="5"/>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A384" s="6"/>
-      <c r="B384" s="5"/>
-      <c r="C384" s="7"/>
+      <c r="A384" s="6">
+        <v>45936</v>
+      </c>
+      <c r="B384" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C384" s="7">
+        <v>162140</v>
+      </c>
       <c r="D384" s="7"/>
       <c r="E384" s="5"/>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A385" s="6"/>
-      <c r="B385" s="5"/>
-      <c r="C385" s="7"/>
+      <c r="A385" s="6">
+        <v>45937</v>
+      </c>
+      <c r="B385" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C385" s="7">
+        <v>328620</v>
+      </c>
       <c r="D385" s="7"/>
       <c r="E385" s="5"/>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A386" s="6"/>
-      <c r="B386" s="5"/>
-      <c r="C386" s="7"/>
+      <c r="A386" s="6">
+        <v>45938</v>
+      </c>
+      <c r="B386" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C386" s="7">
+        <v>262770</v>
+      </c>
       <c r="D386" s="7"/>
       <c r="E386" s="5"/>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A387" s="6"/>
-      <c r="B387" s="5"/>
-      <c r="C387" s="7"/>
+      <c r="A387" s="6">
+        <v>45939</v>
+      </c>
+      <c r="B387" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C387" s="7">
+        <v>151040</v>
+      </c>
       <c r="D387" s="7"/>
       <c r="E387" s="5"/>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A388" s="6"/>
-      <c r="B388" s="5"/>
-      <c r="C388" s="7"/>
+      <c r="A388" s="6">
+        <v>45940</v>
+      </c>
+      <c r="B388" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C388" s="7">
+        <v>91550</v>
+      </c>
       <c r="D388" s="7"/>
       <c r="E388" s="5"/>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A389" s="6"/>
-      <c r="B389" s="5"/>
-      <c r="C389" s="7"/>
+      <c r="A389" s="6">
+        <v>45941</v>
+      </c>
+      <c r="B389" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C389" s="7">
+        <v>257130</v>
+      </c>
       <c r="D389" s="7"/>
       <c r="E389" s="5"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A390" s="6"/>
-      <c r="B390" s="5"/>
-      <c r="C390" s="7"/>
+      <c r="A390" s="6">
+        <v>45942</v>
+      </c>
+      <c r="B390" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C390" s="7">
+        <v>100020</v>
+      </c>
       <c r="D390" s="7"/>
       <c r="E390" s="5"/>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A391" s="6"/>
-      <c r="B391" s="5"/>
-      <c r="C391" s="7"/>
+      <c r="A391" s="6">
+        <v>45943</v>
+      </c>
+      <c r="B391" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C391" s="7">
+        <v>302750</v>
+      </c>
       <c r="D391" s="7"/>
       <c r="E391" s="5"/>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A392" s="6"/>
-      <c r="B392" s="5"/>
-      <c r="C392" s="7"/>
+      <c r="A392" s="6">
+        <v>45944</v>
+      </c>
+      <c r="B392" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C392" s="7">
+        <v>19200</v>
+      </c>
       <c r="D392" s="7"/>
       <c r="E392" s="5"/>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A393" s="6"/>
-      <c r="B393" s="5"/>
-      <c r="C393" s="7"/>
+      <c r="A393" s="6">
+        <v>45945</v>
+      </c>
+      <c r="B393" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C393" s="7">
+        <v>304860</v>
+      </c>
       <c r="D393" s="7"/>
       <c r="E393" s="5"/>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A394" s="6"/>
-      <c r="B394" s="5"/>
-      <c r="C394" s="7"/>
+      <c r="A394" s="6">
+        <v>45946</v>
+      </c>
+      <c r="B394" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C394" s="7">
+        <v>183530</v>
+      </c>
       <c r="D394" s="7"/>
       <c r="E394" s="5"/>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A395" s="6"/>
-      <c r="B395" s="5"/>
-      <c r="C395" s="7"/>
+      <c r="A395" s="6">
+        <v>45947</v>
+      </c>
+      <c r="B395" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C395" s="7">
+        <v>226720</v>
+      </c>
       <c r="D395" s="7"/>
       <c r="E395" s="5"/>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A396" s="6"/>
-      <c r="B396" s="5"/>
-      <c r="C396" s="7"/>
+      <c r="A396" s="6">
+        <v>45948</v>
+      </c>
+      <c r="B396" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C396" s="7">
+        <v>243580</v>
+      </c>
       <c r="D396" s="7"/>
       <c r="E396" s="5"/>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A397" s="6"/>
-      <c r="B397" s="5"/>
-      <c r="C397" s="7"/>
+      <c r="A397" s="6">
+        <v>45949</v>
+      </c>
+      <c r="B397" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C397" s="7">
+        <v>124270</v>
+      </c>
       <c r="D397" s="7"/>
       <c r="E397" s="5"/>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A398" s="6"/>
-      <c r="B398" s="5"/>
-      <c r="C398" s="7"/>
+      <c r="A398" s="6">
+        <v>45950</v>
+      </c>
+      <c r="B398" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C398" s="7">
+        <v>305340</v>
+      </c>
       <c r="D398" s="7"/>
       <c r="E398" s="5"/>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A399" s="6"/>
-      <c r="B399" s="5"/>
-      <c r="C399" s="7"/>
+      <c r="A399" s="6">
+        <v>45951</v>
+      </c>
+      <c r="B399" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C399" s="7">
+        <v>164440</v>
+      </c>
       <c r="D399" s="7"/>
       <c r="E399" s="5"/>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A400" s="6"/>
-      <c r="B400" s="5"/>
-      <c r="C400" s="7"/>
+      <c r="A400" s="6">
+        <v>45952</v>
+      </c>
+      <c r="B400" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C400" s="7">
+        <v>298630</v>
+      </c>
       <c r="D400" s="7"/>
       <c r="E400" s="5"/>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A401" s="6"/>
-      <c r="B401" s="5"/>
-      <c r="C401" s="7"/>
+      <c r="A401" s="6">
+        <v>45953</v>
+      </c>
+      <c r="B401" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C401" s="7">
+        <v>124770</v>
+      </c>
       <c r="D401" s="7"/>
       <c r="E401" s="5"/>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A402" s="6"/>
-      <c r="B402" s="5"/>
-      <c r="C402" s="7"/>
+      <c r="A402" s="6">
+        <v>45954</v>
+      </c>
+      <c r="B402" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C402" s="7">
+        <v>322480</v>
+      </c>
       <c r="D402" s="7"/>
       <c r="E402" s="5"/>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A403" s="6"/>
-      <c r="B403" s="5"/>
-      <c r="C403" s="7"/>
+      <c r="A403" s="6">
+        <v>45955</v>
+      </c>
+      <c r="B403" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C403" s="7">
+        <v>119920</v>
+      </c>
       <c r="D403" s="7"/>
       <c r="E403" s="5"/>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A404" s="6"/>
-      <c r="B404" s="5"/>
-      <c r="C404" s="7"/>
+      <c r="A404" s="6">
+        <v>45956</v>
+      </c>
+      <c r="B404" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C404" s="7">
+        <v>54910</v>
+      </c>
       <c r="D404" s="7"/>
       <c r="E404" s="5"/>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A405" s="6"/>
-      <c r="B405" s="5"/>
-      <c r="C405" s="7"/>
+      <c r="A405" s="6">
+        <v>45957</v>
+      </c>
+      <c r="B405" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C405" s="7">
+        <v>174580</v>
+      </c>
       <c r="D405" s="7"/>
       <c r="E405" s="5"/>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A406" s="6"/>
-      <c r="B406" s="5"/>
-      <c r="C406" s="7"/>
+      <c r="A406" s="6">
+        <v>45958</v>
+      </c>
+      <c r="B406" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C406" s="7">
+        <v>169870</v>
+      </c>
       <c r="D406" s="7"/>
       <c r="E406" s="5"/>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A407" s="6"/>
-      <c r="B407" s="5"/>
-      <c r="C407" s="7"/>
+      <c r="A407" s="6">
+        <v>45959</v>
+      </c>
+      <c r="B407" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C407" s="7">
+        <v>285820</v>
+      </c>
       <c r="D407" s="7"/>
       <c r="E407" s="5"/>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A408" s="6"/>
-      <c r="B408" s="5"/>
-      <c r="C408" s="7"/>
+      <c r="A408" s="6">
+        <v>45960</v>
+      </c>
+      <c r="B408" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C408" s="7">
+        <v>95860</v>
+      </c>
       <c r="D408" s="7"/>
       <c r="E408" s="5"/>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A409" s="6"/>
-      <c r="B409" s="5"/>
-      <c r="C409" s="7"/>
+      <c r="A409" s="6">
+        <v>45961</v>
+      </c>
+      <c r="B409" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C409" s="7">
+        <v>299210</v>
+      </c>
       <c r="D409" s="7"/>
       <c r="E409" s="5"/>
     </row>
@@ -4060,212 +6181,392 @@
       <c r="E410" s="5"/>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A411" s="6"/>
-      <c r="B411" s="5"/>
-      <c r="C411" s="7"/>
+      <c r="A411" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B411" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C411" s="7">
+        <v>156540</v>
+      </c>
       <c r="D411" s="7"/>
       <c r="E411" s="5"/>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A412" s="6"/>
-      <c r="B412" s="5"/>
-      <c r="C412" s="7"/>
+      <c r="A412" s="6">
+        <v>45963</v>
+      </c>
+      <c r="B412" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C412" s="7">
+        <v>86300</v>
+      </c>
       <c r="D412" s="7"/>
       <c r="E412" s="5"/>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A413" s="6"/>
-      <c r="B413" s="5"/>
-      <c r="C413" s="7"/>
+      <c r="A413" s="6">
+        <v>45964</v>
+      </c>
+      <c r="B413" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C413" s="7">
+        <v>243260</v>
+      </c>
       <c r="D413" s="7"/>
       <c r="E413" s="5"/>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A414" s="6"/>
-      <c r="B414" s="5"/>
-      <c r="C414" s="7"/>
+      <c r="A414" s="6">
+        <v>45965</v>
+      </c>
+      <c r="B414" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C414" s="7">
+        <v>137780</v>
+      </c>
       <c r="D414" s="7"/>
       <c r="E414" s="5"/>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A415" s="6"/>
-      <c r="B415" s="5"/>
-      <c r="C415" s="7"/>
+      <c r="A415" s="6">
+        <v>45966</v>
+      </c>
+      <c r="B415" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C415" s="7">
+        <v>295550</v>
+      </c>
       <c r="D415" s="7"/>
       <c r="E415" s="5"/>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A416" s="6"/>
-      <c r="B416" s="5"/>
-      <c r="C416" s="7"/>
+      <c r="A416" s="6">
+        <v>45967</v>
+      </c>
+      <c r="B416" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C416" s="7">
+        <v>69600</v>
+      </c>
       <c r="D416" s="7"/>
       <c r="E416" s="5"/>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A417" s="6"/>
-      <c r="B417" s="5"/>
-      <c r="C417" s="7"/>
+      <c r="A417" s="6">
+        <v>45968</v>
+      </c>
+      <c r="B417" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C417" s="7">
+        <v>277840</v>
+      </c>
       <c r="D417" s="7"/>
       <c r="E417" s="5"/>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A418" s="6"/>
-      <c r="B418" s="5"/>
-      <c r="C418" s="7"/>
+      <c r="A418" s="6">
+        <v>45969</v>
+      </c>
+      <c r="B418" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C418" s="7">
+        <v>149140</v>
+      </c>
       <c r="D418" s="7"/>
       <c r="E418" s="5"/>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A419" s="6"/>
-      <c r="B419" s="5"/>
-      <c r="C419" s="7"/>
+      <c r="A419" s="6">
+        <v>45970</v>
+      </c>
+      <c r="B419" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C419" s="7">
+        <v>92820</v>
+      </c>
       <c r="D419" s="7"/>
       <c r="E419" s="5"/>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A420" s="6"/>
-      <c r="B420" s="5"/>
-      <c r="C420" s="7"/>
+      <c r="A420" s="6">
+        <v>45971</v>
+      </c>
+      <c r="B420" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C420" s="7">
+        <v>307960</v>
+      </c>
       <c r="D420" s="7"/>
       <c r="E420" s="5"/>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A421" s="6"/>
-      <c r="B421" s="5"/>
-      <c r="C421" s="7"/>
+      <c r="A421" s="6">
+        <v>45972</v>
+      </c>
+      <c r="B421" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C421" s="7">
+        <v>140610</v>
+      </c>
       <c r="D421" s="7"/>
       <c r="E421" s="5"/>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A422" s="6"/>
-      <c r="B422" s="5"/>
-      <c r="C422" s="7"/>
+      <c r="A422" s="6">
+        <v>45973</v>
+      </c>
+      <c r="B422" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C422" s="7">
+        <v>342970</v>
+      </c>
       <c r="D422" s="7"/>
       <c r="E422" s="5"/>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A423" s="6"/>
-      <c r="B423" s="5"/>
-      <c r="C423" s="7"/>
+      <c r="A423" s="6">
+        <v>45974</v>
+      </c>
+      <c r="B423" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C423" s="7">
+        <v>76850</v>
+      </c>
       <c r="D423" s="7"/>
       <c r="E423" s="5"/>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A424" s="6"/>
-      <c r="B424" s="5"/>
-      <c r="C424" s="7"/>
+      <c r="A424" s="6">
+        <v>45975</v>
+      </c>
+      <c r="B424" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C424" s="7">
+        <v>267000</v>
+      </c>
       <c r="D424" s="7"/>
       <c r="E424" s="5"/>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A425" s="6"/>
-      <c r="B425" s="5"/>
-      <c r="C425" s="7"/>
+      <c r="A425" s="6">
+        <v>45976</v>
+      </c>
+      <c r="B425" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C425" s="7">
+        <v>102640</v>
+      </c>
       <c r="D425" s="7"/>
       <c r="E425" s="5"/>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A426" s="6"/>
-      <c r="B426" s="5"/>
-      <c r="C426" s="7"/>
+      <c r="A426" s="6">
+        <v>45977</v>
+      </c>
+      <c r="B426" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C426" s="7">
+        <v>157870</v>
+      </c>
       <c r="D426" s="7"/>
       <c r="E426" s="5"/>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A427" s="6"/>
-      <c r="B427" s="5"/>
-      <c r="C427" s="7"/>
+      <c r="A427" s="6">
+        <v>45978</v>
+      </c>
+      <c r="B427" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C427" s="7">
+        <v>232460</v>
+      </c>
       <c r="D427" s="7"/>
       <c r="E427" s="5"/>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A428" s="6"/>
-      <c r="B428" s="5"/>
-      <c r="C428" s="7"/>
+      <c r="A428" s="6">
+        <v>45979</v>
+      </c>
+      <c r="B428" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C428" s="7">
+        <v>144140</v>
+      </c>
       <c r="D428" s="7"/>
       <c r="E428" s="5"/>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A429" s="6"/>
-      <c r="B429" s="5"/>
-      <c r="C429" s="7"/>
+      <c r="A429" s="6">
+        <v>45980</v>
+      </c>
+      <c r="B429" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C429" s="7">
+        <v>254720</v>
+      </c>
       <c r="D429" s="7"/>
       <c r="E429" s="5"/>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A430" s="6"/>
-      <c r="B430" s="5"/>
-      <c r="C430" s="7"/>
+      <c r="A430" s="6">
+        <v>45981</v>
+      </c>
+      <c r="B430" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C430" s="7">
+        <v>185740</v>
+      </c>
       <c r="D430" s="7"/>
       <c r="E430" s="5"/>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A431" s="6"/>
-      <c r="B431" s="5"/>
-      <c r="C431" s="7"/>
+      <c r="A431" s="6">
+        <v>45982</v>
+      </c>
+      <c r="B431" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C431" s="7">
+        <v>441520</v>
+      </c>
       <c r="D431" s="7"/>
       <c r="E431" s="5"/>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A432" s="6"/>
-      <c r="B432" s="5"/>
-      <c r="C432" s="7"/>
+      <c r="A432" s="6">
+        <v>45983</v>
+      </c>
+      <c r="B432" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C432" s="7">
+        <v>126440</v>
+      </c>
       <c r="D432" s="7"/>
       <c r="E432" s="5"/>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A433" s="6"/>
-      <c r="B433" s="5"/>
-      <c r="C433" s="7"/>
+      <c r="A433" s="6">
+        <v>45984</v>
+      </c>
+      <c r="B433" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C433" s="7">
+        <v>219280</v>
+      </c>
       <c r="D433" s="7"/>
       <c r="E433" s="5"/>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A434" s="6"/>
-      <c r="B434" s="5"/>
-      <c r="C434" s="7"/>
+      <c r="A434" s="6">
+        <v>45985</v>
+      </c>
+      <c r="B434" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C434" s="7">
+        <v>299150</v>
+      </c>
       <c r="D434" s="7"/>
       <c r="E434" s="5"/>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A435" s="6"/>
-      <c r="B435" s="5"/>
-      <c r="C435" s="7"/>
+      <c r="A435" s="6">
+        <v>45986</v>
+      </c>
+      <c r="B435" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C435" s="7">
+        <v>178920</v>
+      </c>
       <c r="D435" s="7"/>
       <c r="E435" s="5"/>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A436" s="6"/>
-      <c r="B436" s="5"/>
-      <c r="C436" s="7"/>
+      <c r="A436" s="6">
+        <v>45987</v>
+      </c>
+      <c r="B436" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C436" s="7">
+        <v>193500</v>
+      </c>
       <c r="D436" s="7"/>
       <c r="E436" s="5"/>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A437" s="6"/>
-      <c r="B437" s="5"/>
-      <c r="C437" s="7"/>
+      <c r="A437" s="6">
+        <v>45988</v>
+      </c>
+      <c r="B437" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C437" s="7">
+        <v>169700</v>
+      </c>
       <c r="D437" s="7"/>
       <c r="E437" s="5"/>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A438" s="6"/>
-      <c r="B438" s="5"/>
-      <c r="C438" s="7"/>
+      <c r="A438" s="6">
+        <v>45989</v>
+      </c>
+      <c r="B438" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C438" s="7">
+        <v>146540</v>
+      </c>
       <c r="D438" s="7"/>
       <c r="E438" s="5"/>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A439" s="6"/>
-      <c r="B439" s="5"/>
-      <c r="C439" s="7"/>
+      <c r="A439" s="6">
+        <v>45990</v>
+      </c>
+      <c r="B439" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C439" s="7">
+        <v>82540</v>
+      </c>
       <c r="D439" s="7"/>
       <c r="E439" s="5"/>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A440" s="6"/>
-      <c r="B440" s="5"/>
-      <c r="C440" s="7"/>
+      <c r="A440" s="6">
+        <v>45991</v>
+      </c>
+      <c r="B440" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C440" s="7">
+        <v>98580</v>
+      </c>
       <c r="D440" s="7"/>
       <c r="E440" s="5"/>
     </row>
@@ -4277,219 +6578,405 @@
       <c r="E441" s="5"/>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A442" s="6"/>
-      <c r="B442" s="5"/>
-      <c r="C442" s="7"/>
+      <c r="A442" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B442" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C442" s="7">
+        <v>155060</v>
+      </c>
       <c r="D442" s="7"/>
       <c r="E442" s="5"/>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A443" s="6"/>
-      <c r="B443" s="5"/>
-      <c r="C443" s="7"/>
+      <c r="A443" s="6">
+        <v>45993</v>
+      </c>
+      <c r="B443" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C443" s="7">
+        <v>619638</v>
+      </c>
       <c r="D443" s="7"/>
       <c r="E443" s="5"/>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A444" s="6"/>
-      <c r="B444" s="5"/>
-      <c r="C444" s="7"/>
+      <c r="A444" s="6">
+        <v>45994</v>
+      </c>
+      <c r="B444" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C444" s="7">
+        <v>132380</v>
+      </c>
       <c r="D444" s="7"/>
       <c r="E444" s="5"/>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A445" s="6"/>
-      <c r="B445" s="5"/>
-      <c r="C445" s="7"/>
+      <c r="A445" s="6">
+        <v>45995</v>
+      </c>
+      <c r="B445" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C445" s="7">
+        <v>373160</v>
+      </c>
       <c r="D445" s="7"/>
       <c r="E445" s="5"/>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A446" s="6"/>
-      <c r="B446" s="5"/>
-      <c r="C446" s="7"/>
+      <c r="A446" s="6">
+        <v>45996</v>
+      </c>
+      <c r="B446" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C446" s="7">
+        <v>527060</v>
+      </c>
       <c r="D446" s="7"/>
       <c r="E446" s="5"/>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A447" s="6"/>
-      <c r="B447" s="5"/>
-      <c r="C447" s="7"/>
+      <c r="A447" s="6">
+        <v>45997</v>
+      </c>
+      <c r="B447" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C447" s="7">
+        <v>99160</v>
+      </c>
       <c r="D447" s="7"/>
       <c r="E447" s="5"/>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A448" s="6"/>
-      <c r="B448" s="5"/>
-      <c r="C448" s="7"/>
+      <c r="A448" s="6">
+        <v>45998</v>
+      </c>
+      <c r="B448" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C448" s="7">
+        <v>33880</v>
+      </c>
       <c r="D448" s="7"/>
       <c r="E448" s="5"/>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A449" s="6"/>
-      <c r="B449" s="5"/>
-      <c r="C449" s="7"/>
+      <c r="A449" s="6">
+        <v>45999</v>
+      </c>
+      <c r="B449" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C449" s="7">
+        <v>152160</v>
+      </c>
       <c r="D449" s="7"/>
       <c r="E449" s="5"/>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A450" s="6"/>
-      <c r="B450" s="5"/>
-      <c r="C450" s="7"/>
+      <c r="A450" s="6">
+        <v>46000</v>
+      </c>
+      <c r="B450" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C450" s="7">
+        <v>293050</v>
+      </c>
       <c r="D450" s="7"/>
       <c r="E450" s="5"/>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A451" s="6"/>
-      <c r="B451" s="5"/>
-      <c r="C451" s="7"/>
+      <c r="A451" s="6">
+        <v>46001</v>
+      </c>
+      <c r="B451" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C451" s="7">
+        <v>204900</v>
+      </c>
       <c r="D451" s="7"/>
       <c r="E451" s="5"/>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A452" s="6"/>
-      <c r="B452" s="5"/>
-      <c r="C452" s="7"/>
+      <c r="A452" s="6">
+        <v>46002</v>
+      </c>
+      <c r="B452" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C452" s="7">
+        <v>569102</v>
+      </c>
       <c r="D452" s="7"/>
       <c r="E452" s="5"/>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A453" s="6"/>
-      <c r="B453" s="5"/>
-      <c r="C453" s="7"/>
+      <c r="A453" s="6">
+        <v>46003</v>
+      </c>
+      <c r="B453" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C453" s="7">
+        <v>362904</v>
+      </c>
       <c r="D453" s="7"/>
       <c r="E453" s="5"/>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A454" s="6"/>
-      <c r="B454" s="5"/>
-      <c r="C454" s="7"/>
+      <c r="A454" s="6">
+        <v>46004</v>
+      </c>
+      <c r="B454" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C454" s="7">
+        <v>200280</v>
+      </c>
       <c r="D454" s="7"/>
       <c r="E454" s="5"/>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A455" s="6"/>
-      <c r="B455" s="5"/>
-      <c r="C455" s="7"/>
+      <c r="A455" s="6">
+        <v>46005</v>
+      </c>
+      <c r="B455" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C455" s="7">
+        <v>56458</v>
+      </c>
       <c r="D455" s="7"/>
       <c r="E455" s="5"/>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A456" s="6"/>
-      <c r="B456" s="5"/>
-      <c r="C456" s="7"/>
+      <c r="A456" s="6">
+        <v>46006</v>
+      </c>
+      <c r="B456" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C456" s="7">
+        <v>440040</v>
+      </c>
       <c r="D456" s="7"/>
       <c r="E456" s="5"/>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A457" s="6"/>
-      <c r="B457" s="5"/>
-      <c r="C457" s="7"/>
+      <c r="A457" s="6">
+        <v>46007</v>
+      </c>
+      <c r="B457" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C457" s="7">
+        <v>317760</v>
+      </c>
       <c r="D457" s="7"/>
       <c r="E457" s="5"/>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A458" s="6"/>
-      <c r="B458" s="5"/>
-      <c r="C458" s="7"/>
+      <c r="A458" s="6">
+        <v>46008</v>
+      </c>
+      <c r="B458" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C458" s="7">
+        <v>222876</v>
+      </c>
       <c r="D458" s="7"/>
       <c r="E458" s="5"/>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A459" s="6"/>
-      <c r="B459" s="5"/>
-      <c r="C459" s="7"/>
+      <c r="A459" s="6">
+        <v>46009</v>
+      </c>
+      <c r="B459" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C459" s="7">
+        <v>249580</v>
+      </c>
       <c r="D459" s="7"/>
       <c r="E459" s="5"/>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A460" s="6"/>
-      <c r="B460" s="5"/>
-      <c r="C460" s="7"/>
+      <c r="A460" s="6">
+        <v>46010</v>
+      </c>
+      <c r="B460" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C460" s="7">
+        <v>483230</v>
+      </c>
       <c r="D460" s="7"/>
       <c r="E460" s="5"/>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A461" s="6"/>
-      <c r="B461" s="5"/>
-      <c r="C461" s="7"/>
+      <c r="A461" s="6">
+        <v>46011</v>
+      </c>
+      <c r="B461" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C461" s="7">
+        <v>464008</v>
+      </c>
       <c r="D461" s="7"/>
       <c r="E461" s="5"/>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A462" s="6"/>
-      <c r="B462" s="5"/>
-      <c r="C462" s="7"/>
+      <c r="A462" s="6">
+        <v>46012</v>
+      </c>
+      <c r="B462" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C462" s="7">
+        <v>363418</v>
+      </c>
       <c r="D462" s="7"/>
       <c r="E462" s="5"/>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A463" s="6"/>
-      <c r="B463" s="5"/>
-      <c r="C463" s="7"/>
+      <c r="A463" s="6">
+        <v>46013</v>
+      </c>
+      <c r="B463" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C463" s="7">
+        <v>218138</v>
+      </c>
       <c r="D463" s="7"/>
       <c r="E463" s="5"/>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A464" s="6"/>
-      <c r="B464" s="5"/>
-      <c r="C464" s="7"/>
+      <c r="A464" s="6">
+        <v>46014</v>
+      </c>
+      <c r="B464" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C464" s="7">
+        <v>202640</v>
+      </c>
       <c r="D464" s="7"/>
       <c r="E464" s="5"/>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A465" s="6"/>
-      <c r="B465" s="5"/>
-      <c r="C465" s="7"/>
+      <c r="A465" s="6">
+        <v>46015</v>
+      </c>
+      <c r="B465" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C465" s="7">
+        <v>283540</v>
+      </c>
       <c r="D465" s="7"/>
       <c r="E465" s="5"/>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A466" s="6"/>
-      <c r="B466" s="5"/>
-      <c r="C466" s="7"/>
+      <c r="A466" s="6">
+        <v>46016</v>
+      </c>
+      <c r="B466" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C466" s="7">
+        <v>250380</v>
+      </c>
       <c r="D466" s="7"/>
       <c r="E466" s="5"/>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A467" s="6"/>
-      <c r="B467" s="5"/>
-      <c r="C467" s="7"/>
+      <c r="A467" s="6">
+        <v>46017</v>
+      </c>
+      <c r="B467" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C467" s="7">
+        <v>633928</v>
+      </c>
       <c r="D467" s="7"/>
       <c r="E467" s="5"/>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A468" s="6"/>
-      <c r="B468" s="5"/>
-      <c r="C468" s="7"/>
+      <c r="A468" s="6">
+        <v>46018</v>
+      </c>
+      <c r="B468" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C468" s="7">
+        <v>858218</v>
+      </c>
       <c r="D468" s="7"/>
       <c r="E468" s="5"/>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A469" s="6"/>
-      <c r="B469" s="5"/>
-      <c r="C469" s="7"/>
+      <c r="A469" s="6">
+        <v>46019</v>
+      </c>
+      <c r="B469" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C469" s="7">
+        <v>362272</v>
+      </c>
       <c r="D469" s="7"/>
       <c r="E469" s="5"/>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A470" s="6"/>
-      <c r="B470" s="5"/>
-      <c r="C470" s="7"/>
+      <c r="A470" s="6">
+        <v>46020</v>
+      </c>
+      <c r="B470" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C470" s="7">
+        <v>531110</v>
+      </c>
       <c r="D470" s="7"/>
       <c r="E470" s="5"/>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A471" s="6"/>
-      <c r="B471" s="5"/>
-      <c r="C471" s="7"/>
+      <c r="A471" s="6">
+        <v>46021</v>
+      </c>
+      <c r="B471" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C471" s="7">
+        <v>240494</v>
+      </c>
       <c r="D471" s="7"/>
       <c r="E471" s="5"/>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A472" s="6"/>
-      <c r="B472" s="5"/>
-      <c r="C472" s="7"/>
+      <c r="A472" s="6">
+        <v>46022</v>
+      </c>
+      <c r="B472" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C472" s="7">
+        <v>365244</v>
+      </c>
       <c r="D472" s="7"/>
       <c r="E472" s="5"/>
     </row>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\伊原\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\incoming\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C03EC878-5CB5-457F-8AAB-D501283D2C3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A765161-A86F-4DC9-87FA-F80CE3317874}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="47">
   <si>
     <t>日付</t>
   </si>
@@ -915,7 +915,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E801"/>
+  <dimension ref="A1:E897"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -943,1185 +943,789 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="6">
-        <v>46023</v>
+        <v>46266</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C2" s="7">
-        <v>19440</v>
+      <c r="C2">
+        <v>669080</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="6">
-        <v>46024</v>
+        <v>46267</v>
       </c>
       <c r="B3" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C3" s="7">
-        <v>217400</v>
+      <c r="C3">
+        <v>662770</v>
       </c>
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="6">
-        <v>46025</v>
+        <v>46268</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="7">
-        <v>419248</v>
+      <c r="C4">
+        <v>570160</v>
       </c>
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="6">
-        <v>46026</v>
+        <v>46269</v>
       </c>
       <c r="B5" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" s="7">
-        <v>101606</v>
+      <c r="C5">
+        <v>556680</v>
       </c>
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="6">
-        <v>46027</v>
+        <v>46270</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C6" s="7">
-        <v>283530</v>
+      <c r="C6">
+        <v>642620</v>
       </c>
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="6">
-        <v>46028</v>
+        <v>46271</v>
       </c>
       <c r="B7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C7" s="7">
-        <v>265276</v>
+      <c r="C7">
+        <v>502980</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="6">
-        <v>46029</v>
+        <v>46272</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C8" s="7">
-        <v>461850</v>
+      <c r="C8">
+        <v>601030</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="6">
-        <v>46030</v>
+        <v>46273</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C9" s="7">
-        <v>284240</v>
+      <c r="C9">
+        <v>568010</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="6">
-        <v>46031</v>
+        <v>46274</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C10" s="7">
-        <v>322376</v>
+      <c r="C10">
+        <v>604910</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="6">
-        <v>46032</v>
+        <v>46275</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="7">
-        <v>151728</v>
+      <c r="C11">
+        <v>724550</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="6">
-        <v>46033</v>
+        <v>46276</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="7">
-        <v>132600</v>
+      <c r="C12">
+        <v>592530</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="6">
-        <v>46034</v>
+        <v>46277</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C13" s="7">
-        <v>425520</v>
+      <c r="C13">
+        <v>563370</v>
       </c>
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="6">
-        <v>46035</v>
+        <v>46278</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C14" s="7">
-        <v>181420</v>
+      <c r="C14">
+        <v>615130</v>
       </c>
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="6">
-        <v>46036</v>
+        <v>46279</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C15" s="7">
-        <v>327140</v>
+      <c r="C15">
+        <v>690050</v>
       </c>
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A16" s="6">
-        <v>46037</v>
-      </c>
-      <c r="B16" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C16" s="7">
-        <v>279098</v>
-      </c>
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A17" s="6">
-        <v>46038</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C17" s="7">
-        <v>540666</v>
-      </c>
+    <row r="17" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A18" s="6">
-        <v>46039</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C18" s="7">
-        <v>193138</v>
-      </c>
+    <row r="18" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A19" s="6">
-        <v>46040</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C19" s="7">
-        <v>92038</v>
-      </c>
+    <row r="19" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A20" s="6">
-        <v>46041</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="7">
-        <v>300298</v>
-      </c>
+    <row r="20" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A21" s="6">
-        <v>46042</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C21" s="7">
-        <v>98776</v>
-      </c>
+    <row r="21" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A22" s="6">
-        <v>46043</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C22" s="7">
-        <v>463480</v>
-      </c>
+    <row r="22" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A23" s="6">
-        <v>46044</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C23" s="7">
-        <v>288740</v>
-      </c>
+    <row r="23" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A24" s="6">
-        <v>46045</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C24" s="7">
-        <v>427696</v>
-      </c>
+    <row r="24" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A25" s="6">
-        <v>46046</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="7">
-        <v>129418</v>
-      </c>
+    <row r="25" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A26" s="6">
-        <v>46047</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C26" s="7">
-        <v>111438</v>
-      </c>
+    <row r="26" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A27" s="6">
-        <v>46048</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C27" s="7">
-        <v>286696</v>
-      </c>
+    <row r="27" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A28" s="6">
-        <v>46049</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C28" s="7">
-        <v>168260</v>
-      </c>
+    <row r="28" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A29" s="6">
-        <v>46050</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C29" s="7">
-        <v>384154</v>
-      </c>
+    <row r="29" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A30" s="6">
-        <v>46051</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C30" s="7">
-        <v>148980</v>
-      </c>
+    <row r="30" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A31" s="6">
-        <v>46052</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="7">
-        <v>357858</v>
-      </c>
+    <row r="31" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A32" s="6">
-        <v>46053</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C32" s="7">
-        <v>123378</v>
-      </c>
+    <row r="32" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A33" s="6"/>
-      <c r="B33" s="5"/>
-      <c r="C33" s="7"/>
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A34" s="6">
-        <v>46054</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="7">
-        <v>87736</v>
-      </c>
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="6">
-        <v>46055</v>
+        <v>45901</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C35" s="7">
-        <v>286230</v>
+      <c r="C35">
+        <v>176920</v>
       </c>
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="6">
-        <v>46056</v>
+        <v>45902</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C36" s="7">
-        <v>131920</v>
+      <c r="C36">
+        <v>161250</v>
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="6">
-        <v>46057</v>
+        <v>45903</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C37" s="7">
-        <v>291560</v>
+      <c r="C37">
+        <v>333640</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="6">
-        <v>46058</v>
+        <v>45904</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C38" s="7">
-        <v>67676</v>
+      <c r="C38">
+        <v>145410</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="6">
-        <v>46059</v>
+        <v>45905</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C39" s="7">
-        <v>391060</v>
+      <c r="C39">
+        <v>419600</v>
       </c>
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="6">
-        <v>46060</v>
+        <v>45906</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C40" s="7">
-        <v>100196</v>
+      <c r="C40">
+        <v>78240</v>
       </c>
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="6">
-        <v>46061</v>
+        <v>45907</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C41" s="7">
-        <v>109056</v>
+      <c r="C41">
+        <v>68180</v>
       </c>
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="6">
-        <v>46062</v>
+        <v>45908</v>
       </c>
       <c r="B42" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C42" s="7">
-        <v>206672</v>
+      <c r="C42">
+        <v>322410</v>
       </c>
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="6">
-        <v>46063</v>
+        <v>45909</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C43" s="7">
-        <v>279014</v>
+      <c r="C43">
+        <v>72270</v>
       </c>
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="6">
-        <v>46064</v>
+        <v>45910</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C44" s="7">
-        <v>163880</v>
+      <c r="C44">
+        <v>350500</v>
       </c>
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="6">
-        <v>46065</v>
+        <v>45911</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C45" s="7">
-        <v>74360</v>
+      <c r="C45">
+        <v>132330</v>
       </c>
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="6">
-        <v>46066</v>
+        <v>45912</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C46" s="7">
-        <v>301300</v>
+      <c r="C46">
+        <v>282820</v>
       </c>
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="6">
-        <v>46067</v>
+        <v>45913</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C47" s="7">
-        <v>242780</v>
+      <c r="C47">
+        <v>140280</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="6">
-        <v>46068</v>
+        <v>45914</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C48" s="7">
-        <v>203380</v>
+      <c r="C48">
+        <v>81480</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="6">
-        <v>46069</v>
+        <v>45915</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="7">
-        <v>542880</v>
+      <c r="C49">
+        <v>185160</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="6">
-        <v>46070</v>
+        <v>45916</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C50" s="7">
-        <v>137520</v>
+      <c r="C50">
+        <v>92420</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="6">
-        <v>46071</v>
+        <v>45917</v>
       </c>
       <c r="B51" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C51" s="7">
-        <v>553260</v>
+      <c r="C51">
+        <v>200030</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="6">
-        <v>46072</v>
+        <v>45918</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C52" s="7">
-        <v>161800</v>
+      <c r="C52">
+        <v>109950</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="6">
-        <v>46073</v>
+        <v>45919</v>
       </c>
       <c r="B53" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C53" s="7">
-        <v>345520</v>
+      <c r="C53">
+        <v>317560</v>
       </c>
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="6">
-        <v>46074</v>
+        <v>45920</v>
       </c>
       <c r="B54" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C54" s="7">
-        <v>66280</v>
+      <c r="C54">
+        <v>136720</v>
       </c>
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="6">
-        <v>46075</v>
+        <v>45921</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C55" s="7">
-        <v>161382</v>
+      <c r="C55">
+        <v>84350</v>
       </c>
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="6">
-        <v>46076</v>
+        <v>45922</v>
       </c>
       <c r="B56" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C56" s="7">
-        <v>298998</v>
+      <c r="C56">
+        <v>367710</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="6">
-        <v>46077</v>
+        <v>45923</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C57" s="7">
-        <v>150238</v>
+      <c r="C57">
+        <v>180390</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="6">
-        <v>46078</v>
+        <v>45924</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C58" s="7">
-        <v>298532</v>
+      <c r="C58">
+        <v>233430</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="6">
-        <v>46079</v>
+        <v>45925</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C59" s="7">
-        <v>71188</v>
+      <c r="C59">
+        <v>409620</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="6">
-        <v>46080</v>
+        <v>45926</v>
       </c>
       <c r="B60" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C60" s="7">
-        <v>526234</v>
+      <c r="C60">
+        <v>343820</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="6">
-        <v>46081</v>
+        <v>45927</v>
       </c>
       <c r="B61" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C61" s="7">
-        <v>109398</v>
+      <c r="C61">
+        <v>1077030</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A62" s="6"/>
-      <c r="B62" s="5"/>
-      <c r="C62" s="7"/>
+      <c r="A62" s="6">
+        <v>45928</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C62">
+        <v>67140</v>
+      </c>
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="6">
-        <v>46082</v>
+        <v>45929</v>
       </c>
       <c r="B63" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C63" s="7">
-        <v>91758</v>
+      <c r="C63">
+        <v>2051880</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="6">
-        <v>46083</v>
+        <v>45930</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C64" s="7">
-        <v>314596</v>
+      <c r="C64">
+        <v>1105220</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A65" s="6">
-        <v>46084</v>
-      </c>
-      <c r="B65" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="7">
-        <v>125496</v>
-      </c>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A66" s="6">
-        <v>46085</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" s="7">
-        <v>302060</v>
-      </c>
+    <row r="66" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A67" s="6">
-        <v>46086</v>
-      </c>
-      <c r="B67" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C67" s="7">
-        <v>425528</v>
-      </c>
+    <row r="67" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A68" s="6">
-        <v>46087</v>
-      </c>
-      <c r="B68" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C68" s="7">
-        <v>371328</v>
-      </c>
+    <row r="68" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A69" s="6">
-        <v>46088</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C69" s="7">
-        <v>161314</v>
-      </c>
+    <row r="69" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A70" s="6">
-        <v>46089</v>
-      </c>
-      <c r="B70" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C70" s="7">
-        <v>114896</v>
-      </c>
+    <row r="70" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A71" s="6">
-        <v>46090</v>
-      </c>
-      <c r="B71" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C71" s="7">
-        <v>528594</v>
-      </c>
+    <row r="71" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A72" s="6">
-        <v>46091</v>
-      </c>
-      <c r="B72" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C72" s="7">
-        <v>125612</v>
-      </c>
+    <row r="72" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A73" s="6">
-        <v>46092</v>
-      </c>
-      <c r="B73" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C73" s="7">
-        <v>481572</v>
-      </c>
+    <row r="73" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A74" s="6">
-        <v>46093</v>
-      </c>
-      <c r="B74" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C74" s="7">
-        <v>200796</v>
-      </c>
+    <row r="74" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A75" s="6">
-        <v>46094</v>
-      </c>
-      <c r="B75" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C75" s="7">
-        <v>606820</v>
-      </c>
+    <row r="75" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A76" s="6">
-        <v>46095</v>
-      </c>
-      <c r="B76" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C76" s="7">
-        <v>128480</v>
-      </c>
+    <row r="76" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A77" s="6">
-        <v>46096</v>
-      </c>
-      <c r="B77" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C77" s="7">
-        <v>208216</v>
-      </c>
+    <row r="77" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A78" s="6">
-        <v>46097</v>
-      </c>
-      <c r="B78" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C78" s="7">
-        <v>411898</v>
-      </c>
+    <row r="78" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A79" s="6">
-        <v>46098</v>
-      </c>
-      <c r="B79" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C79" s="7">
-        <v>204760</v>
-      </c>
+    <row r="79" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A80" s="6">
-        <v>46099</v>
-      </c>
-      <c r="B80" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C80" s="7">
-        <v>411900</v>
-      </c>
+    <row r="80" spans="4:5" x14ac:dyDescent="0.15">
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A81" s="6">
-        <v>46100</v>
-      </c>
-      <c r="B81" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C81" s="7">
-        <v>623320</v>
-      </c>
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A82" s="6">
-        <v>46101</v>
-      </c>
-      <c r="B82" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C82" s="7">
-        <v>684078</v>
-      </c>
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A83" s="6">
-        <v>46102</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C83" s="7">
-        <v>195280</v>
-      </c>
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A84" s="6">
-        <v>46103</v>
-      </c>
-      <c r="B84" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C84" s="7">
-        <v>128620</v>
-      </c>
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A85" s="6">
-        <v>46104</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C85" s="7">
-        <v>367338</v>
-      </c>
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A86" s="6">
-        <v>46105</v>
-      </c>
-      <c r="B86" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C86" s="7">
-        <v>137080</v>
-      </c>
+      <c r="A86" s="6"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="7"/>
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A87" s="6">
-        <v>46106</v>
-      </c>
-      <c r="B87" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C87" s="7">
-        <v>551880</v>
-      </c>
+      <c r="A87" s="6"/>
+      <c r="B87" s="5"/>
+      <c r="C87" s="7"/>
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A88" s="6">
-        <v>46107</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C88" s="7">
-        <v>73100</v>
-      </c>
+      <c r="A88" s="6"/>
+      <c r="B88" s="5"/>
+      <c r="C88" s="7"/>
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A89" s="6">
-        <v>46108</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C89" s="7">
-        <v>700520</v>
-      </c>
+      <c r="A89" s="6"/>
+      <c r="B89" s="5"/>
+      <c r="C89" s="7"/>
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A90" s="6">
-        <v>46109</v>
-      </c>
-      <c r="B90" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C90" s="7">
-        <v>129180</v>
-      </c>
+      <c r="A90" s="6"/>
+      <c r="B90" s="5"/>
+      <c r="C90" s="7"/>
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A91" s="6">
-        <v>46110</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C91" s="7">
-        <v>130158</v>
-      </c>
+      <c r="A91" s="6"/>
+      <c r="B91" s="5"/>
+      <c r="C91" s="7"/>
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A92" s="6">
-        <v>46111</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C92" s="7">
-        <v>382360</v>
-      </c>
+      <c r="A92" s="6"/>
+      <c r="B92" s="5"/>
+      <c r="C92" s="7"/>
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A93" s="6">
-        <v>46112</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C93" s="7">
-        <v>262540</v>
-      </c>
+      <c r="A93" s="6"/>
+      <c r="B93" s="5"/>
+      <c r="C93" s="7"/>
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
@@ -2133,2825 +1737,2807 @@
       <c r="E94" s="5"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A95" s="6">
-        <v>46113</v>
-      </c>
-      <c r="B95" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C95" s="7">
-        <v>515800</v>
-      </c>
+      <c r="A95" s="6"/>
+      <c r="B95" s="5"/>
+      <c r="C95" s="7"/>
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A96" s="6">
-        <v>46114</v>
-      </c>
-      <c r="B96" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C96" s="7">
-        <v>210360</v>
-      </c>
+      <c r="A96" s="6"/>
+      <c r="B96" s="5"/>
+      <c r="C96" s="7"/>
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A97" s="6">
-        <v>46115</v>
-      </c>
-      <c r="B97" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C97" s="7">
-        <v>615300</v>
-      </c>
+      <c r="A97" s="6"/>
+      <c r="B97" s="5"/>
+      <c r="C97" s="7"/>
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="6">
-        <v>46116</v>
+        <v>46023</v>
       </c>
       <c r="B98" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C98" s="7">
-        <v>252400</v>
+        <v>19440</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="6">
-        <v>46117</v>
+        <v>46024</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C99" s="7">
-        <v>229740</v>
+        <v>217400</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="6">
-        <v>46118</v>
+        <v>46025</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C100" s="7">
-        <v>410700</v>
+        <v>419248</v>
       </c>
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="6">
-        <v>46119</v>
+        <v>46026</v>
       </c>
       <c r="B101" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C101" s="7">
-        <v>337180</v>
+        <v>101606</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="6">
-        <v>46120</v>
+        <v>46027</v>
       </c>
       <c r="B102" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C102" s="7">
-        <v>493600</v>
+        <v>283530</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
     <row r="103" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A103" s="6">
-        <v>46121</v>
+        <v>46028</v>
       </c>
       <c r="B103" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C103" s="7">
-        <v>254660</v>
+        <v>265276</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A104" s="6">
-        <v>46122</v>
+        <v>46029</v>
       </c>
       <c r="B104" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C104" s="7">
-        <v>349360</v>
+        <v>461850</v>
       </c>
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A105" s="6">
-        <v>46123</v>
+        <v>46030</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C105" s="7">
-        <v>158360</v>
+        <v>284240</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A106" s="6">
-        <v>46124</v>
+        <v>46031</v>
       </c>
       <c r="B106" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C106" s="7">
-        <v>218920</v>
+        <v>322376</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A107" s="6">
-        <v>46125</v>
+        <v>46032</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C107" s="7">
-        <v>506620</v>
+        <v>151728</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A108" s="6">
-        <v>46126</v>
+        <v>46033</v>
       </c>
       <c r="B108" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C108" s="7">
-        <v>208020</v>
+        <v>132600</v>
       </c>
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A109" s="6">
-        <v>46127</v>
+        <v>46034</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C109" s="7">
-        <v>350020</v>
+        <v>425520</v>
       </c>
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A110" s="6">
-        <v>46128</v>
+        <v>46035</v>
       </c>
       <c r="B110" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C110" s="7">
-        <v>364360</v>
+        <v>181420</v>
       </c>
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A111" s="6">
-        <v>46129</v>
+        <v>46036</v>
       </c>
       <c r="B111" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C111" s="7">
-        <v>809060</v>
+        <v>327140</v>
       </c>
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A112" s="6">
-        <v>46130</v>
+        <v>46037</v>
       </c>
       <c r="B112" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C112" s="7">
-        <v>312340</v>
+        <v>279098</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A113" s="6">
-        <v>46131</v>
+        <v>46038</v>
       </c>
       <c r="B113" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C113" s="7">
-        <v>271580</v>
+        <v>540666</v>
       </c>
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A114" s="6">
-        <v>46132</v>
+        <v>46039</v>
       </c>
       <c r="B114" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C114" s="7">
-        <v>478400</v>
+        <v>193138</v>
       </c>
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A115" s="6">
-        <v>46133</v>
+        <v>46040</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C115" s="7">
-        <v>327960</v>
+        <v>92038</v>
       </c>
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A116" s="6">
-        <v>46134</v>
+        <v>46041</v>
       </c>
       <c r="B116" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C116" s="7">
-        <v>528500</v>
+        <v>300298</v>
       </c>
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
     <row r="117" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A117" s="6">
-        <v>46135</v>
+        <v>46042</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C117" s="7">
-        <v>379120</v>
+        <v>98776</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
     <row r="118" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A118" s="6">
-        <v>46136</v>
+        <v>46043</v>
       </c>
       <c r="B118" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C118" s="7">
-        <v>832730</v>
+        <v>463480</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A119" s="6">
-        <v>46137</v>
+        <v>46044</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C119" s="7">
-        <v>372180</v>
+        <v>288740</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A120" s="6">
-        <v>46138</v>
+        <v>46045</v>
       </c>
       <c r="B120" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C120" s="7">
-        <v>318200</v>
+        <v>427696</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
     <row r="121" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A121" s="6">
-        <v>46139</v>
+        <v>46046</v>
       </c>
       <c r="B121" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C121" s="7">
-        <v>664340</v>
+        <v>129418</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
     <row r="122" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A122" s="6">
-        <v>46140</v>
+        <v>46047</v>
       </c>
       <c r="B122" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C122" s="7">
-        <v>647560</v>
+        <v>111438</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A123" s="6">
-        <v>46141</v>
+        <v>46048</v>
       </c>
       <c r="B123" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C123" s="7">
-        <v>691430</v>
+        <v>286696</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A124" s="6">
-        <v>46142</v>
+        <v>46049</v>
       </c>
       <c r="B124" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C124" s="7">
-        <v>592490</v>
+        <v>168260</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A125" s="6"/>
-      <c r="B125" s="5"/>
-      <c r="C125" s="7"/>
+      <c r="A125" s="6">
+        <v>46050</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C125" s="7">
+        <v>384154</v>
+      </c>
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A126" s="6">
-        <v>46143</v>
+        <v>46051</v>
       </c>
       <c r="B126" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C126" s="7">
-        <v>549980</v>
+        <v>148980</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A127" s="6">
-        <v>46144</v>
+        <v>46052</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C127" s="7">
-        <v>499190</v>
+        <v>357858</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A128" s="6">
-        <v>46145</v>
+        <v>46053</v>
       </c>
       <c r="B128" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C128" s="7">
-        <v>706360</v>
+        <v>123378</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A129" s="6">
-        <v>46146</v>
-      </c>
-      <c r="B129" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C129" s="7">
-        <v>346300</v>
-      </c>
+      <c r="A129" s="6"/>
+      <c r="B129" s="5"/>
+      <c r="C129" s="7"/>
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A130" s="6">
-        <v>46147</v>
+        <v>46054</v>
       </c>
       <c r="B130" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C130" s="7">
-        <v>191030</v>
+        <v>87736</v>
       </c>
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A131" s="6">
-        <v>46148</v>
+        <v>46055</v>
       </c>
       <c r="B131" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C131" s="7">
-        <v>304950</v>
+        <v>286230</v>
       </c>
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
     <row r="132" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A132" s="6">
-        <v>46149</v>
+        <v>46056</v>
       </c>
       <c r="B132" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C132" s="7">
-        <v>312220</v>
+        <v>131920</v>
       </c>
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A133" s="6">
-        <v>46150</v>
+        <v>46057</v>
       </c>
       <c r="B133" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C133" s="7">
-        <v>631150</v>
+        <v>291560</v>
       </c>
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A134" s="6">
-        <v>46151</v>
+        <v>46058</v>
       </c>
       <c r="B134" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C134" s="7">
-        <v>769760</v>
+        <v>67676</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A135" s="6">
-        <v>46152</v>
+        <v>46059</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C135" s="7">
-        <v>365430</v>
+        <v>391060</v>
       </c>
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A136" s="6">
-        <v>46153</v>
+        <v>46060</v>
       </c>
       <c r="B136" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C136" s="7">
-        <v>678380</v>
+        <v>100196</v>
       </c>
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A137" s="6">
-        <v>46154</v>
+        <v>46061</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C137" s="7">
-        <v>1208410</v>
+        <v>109056</v>
       </c>
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A138" s="6">
-        <v>46155</v>
+        <v>46062</v>
       </c>
       <c r="B138" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C138" s="7">
-        <v>1054460</v>
+        <v>206672</v>
       </c>
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A139" s="6">
-        <v>46156</v>
+        <v>46063</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C139" s="7">
-        <v>346900</v>
+        <v>279014</v>
       </c>
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A140" s="6">
-        <v>46157</v>
+        <v>46064</v>
       </c>
       <c r="B140" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C140" s="7">
-        <v>627020</v>
+        <v>163880</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A141" s="6">
-        <v>46158</v>
+        <v>46065</v>
       </c>
       <c r="B141" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C141" s="7">
-        <v>294920</v>
+        <v>74360</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A142" s="6">
-        <v>46159</v>
+        <v>46066</v>
       </c>
       <c r="B142" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C142" s="7">
-        <v>145580</v>
+        <v>301300</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A143" s="6">
-        <v>46160</v>
+        <v>46067</v>
       </c>
       <c r="B143" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C143" s="7">
-        <v>429560</v>
+        <v>242780</v>
       </c>
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A144" s="6">
-        <v>46161</v>
+        <v>46068</v>
       </c>
       <c r="B144" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C144" s="7">
-        <v>420280</v>
+        <v>203380</v>
       </c>
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
     <row r="145" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A145" s="6">
-        <v>46162</v>
+        <v>46069</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C145" s="7">
-        <v>298680</v>
+        <v>542880</v>
       </c>
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A146" s="6">
-        <v>46163</v>
+        <v>46070</v>
       </c>
       <c r="B146" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C146" s="7">
-        <v>237460</v>
+        <v>137520</v>
       </c>
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="6">
-        <v>46164</v>
+        <v>46071</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C147" s="7">
-        <v>532060</v>
+        <v>553260</v>
       </c>
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="6">
-        <v>46165</v>
+        <v>46072</v>
       </c>
       <c r="B148" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C148" s="7">
-        <v>202140</v>
+        <v>161800</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="6">
-        <v>46166</v>
+        <v>46073</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C149" s="7">
-        <v>133920</v>
+        <v>345520</v>
       </c>
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A150" s="6">
-        <v>46167</v>
+        <v>46074</v>
       </c>
       <c r="B150" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C150" s="7">
-        <v>472880</v>
+        <v>66280</v>
       </c>
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A151" s="6">
-        <v>46168</v>
+        <v>46075</v>
       </c>
       <c r="B151" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C151" s="7">
-        <v>325760</v>
+        <v>161382</v>
       </c>
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A152" s="6">
-        <v>46169</v>
+        <v>46076</v>
       </c>
       <c r="B152" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C152" s="7">
-        <v>365200</v>
+        <v>298998</v>
       </c>
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
     <row r="153" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A153" s="6">
-        <v>46170</v>
+        <v>46077</v>
       </c>
       <c r="B153" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C153" s="7">
-        <v>431700</v>
+        <v>150238</v>
       </c>
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A154" s="6">
-        <v>46171</v>
+        <v>46078</v>
       </c>
       <c r="B154" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C154" s="7">
-        <v>442180</v>
+        <v>298532</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A155" s="6">
-        <v>46172</v>
+        <v>46079</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C155" s="7">
-        <v>293080</v>
+        <v>71188</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A156" s="6">
-        <v>46173</v>
+        <v>46080</v>
       </c>
       <c r="B156" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C156" s="7">
-        <v>284960</v>
+        <v>526234</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A157" s="6"/>
-      <c r="B157" s="5"/>
-      <c r="C157" s="7"/>
+      <c r="A157" s="6">
+        <v>46081</v>
+      </c>
+      <c r="B157" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C157" s="7">
+        <v>109398</v>
+      </c>
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
     <row r="158" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A158" s="6">
-        <v>46174</v>
-      </c>
-      <c r="B158" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C158" s="7">
-        <v>264640</v>
-      </c>
+      <c r="A158" s="6"/>
+      <c r="B158" s="5"/>
+      <c r="C158" s="7"/>
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A159" s="6">
-        <v>46175</v>
+        <v>46082</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C159" s="7">
-        <v>365400</v>
+        <v>91758</v>
       </c>
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A160" s="6">
-        <v>46176</v>
+        <v>46083</v>
       </c>
       <c r="B160" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C160" s="7">
-        <v>313860</v>
+        <v>314596</v>
       </c>
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
     <row r="161" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A161" s="6">
-        <v>46177</v>
+        <v>46084</v>
       </c>
       <c r="B161" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C161" s="7">
-        <v>349340</v>
+        <v>125496</v>
       </c>
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A162" s="6">
-        <v>46178</v>
+        <v>46085</v>
       </c>
       <c r="B162" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C162" s="7">
-        <v>262280</v>
+        <v>302060</v>
       </c>
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A163" s="6">
-        <v>46179</v>
+        <v>46086</v>
       </c>
       <c r="B163" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C163" s="7">
-        <v>310040</v>
+        <v>425528</v>
       </c>
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A164" s="6">
-        <v>46180</v>
+        <v>46087</v>
       </c>
       <c r="B164" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C164" s="7">
-        <v>318700</v>
+        <v>371328</v>
       </c>
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A165" s="6">
-        <v>46181</v>
+        <v>46088</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C165" s="7">
-        <v>361500</v>
+        <v>161314</v>
       </c>
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
     <row r="166" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A166" s="6">
-        <v>46182</v>
+        <v>46089</v>
       </c>
       <c r="B166" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C166" s="7">
-        <v>344360</v>
+        <v>114896</v>
       </c>
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A167" s="6">
-        <v>46183</v>
+        <v>46090</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C167" s="7">
-        <v>294020</v>
+        <v>528594</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A168" s="6">
-        <v>46184</v>
+        <v>46091</v>
       </c>
       <c r="B168" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C168" s="7">
-        <v>358600</v>
+        <v>125612</v>
       </c>
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A169" s="6">
-        <v>46185</v>
+        <v>46092</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C169" s="7">
-        <v>312220</v>
+        <v>481572</v>
       </c>
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A170" s="6">
-        <v>46186</v>
+        <v>46093</v>
       </c>
       <c r="B170" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C170" s="7">
-        <v>413660</v>
+        <v>200796</v>
       </c>
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
     <row r="171" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A171" s="6">
-        <v>46187</v>
+        <v>46094</v>
       </c>
       <c r="B171" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C171" s="7">
-        <v>267780</v>
+        <v>606820</v>
       </c>
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A172" s="6">
-        <v>46188</v>
+        <v>46095</v>
       </c>
       <c r="B172" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C172" s="7">
-        <v>411280</v>
+        <v>128480</v>
       </c>
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A173" s="6">
-        <v>46189</v>
+        <v>46096</v>
       </c>
       <c r="B173" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C173" s="7">
-        <v>396660</v>
+        <v>208216</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
     <row r="174" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A174" s="6">
-        <v>46190</v>
+        <v>46097</v>
       </c>
       <c r="B174" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C174" s="7">
-        <v>402380</v>
+        <v>411898</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
     <row r="175" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A175" s="6">
-        <v>46191</v>
+        <v>46098</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C175" s="7">
-        <v>425040</v>
+        <v>204760</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
     <row r="176" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A176" s="6">
-        <v>46192</v>
+        <v>46099</v>
       </c>
       <c r="B176" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C176" s="7">
-        <v>507860</v>
+        <v>411900</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
     <row r="177" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A177" s="6">
-        <v>46193</v>
+        <v>46100</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C177" s="7">
-        <v>539200</v>
+        <v>623320</v>
       </c>
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
     <row r="178" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A178" s="6">
-        <v>46194</v>
+        <v>46101</v>
       </c>
       <c r="B178" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C178" s="7">
-        <v>299200</v>
+        <v>684078</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
     <row r="179" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A179" s="6">
-        <v>46195</v>
+        <v>46102</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C179" s="7">
-        <v>1228860</v>
+        <v>195280</v>
       </c>
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
     <row r="180" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A180" s="6">
-        <v>46196</v>
+        <v>46103</v>
       </c>
       <c r="B180" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C180" s="7">
-        <v>1833640</v>
+        <v>128620</v>
       </c>
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
     <row r="181" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A181" s="6">
-        <v>46197</v>
+        <v>46104</v>
       </c>
       <c r="B181" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C181" s="7">
-        <v>6264870</v>
+        <v>367338</v>
       </c>
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
     <row r="182" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A182" s="6">
-        <v>46198</v>
+        <v>46105</v>
       </c>
       <c r="B182" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C182" s="7">
-        <v>3949520</v>
+        <v>137080</v>
       </c>
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
     <row r="183" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A183" s="6">
-        <v>46199</v>
+        <v>46106</v>
       </c>
       <c r="B183" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C183" s="7">
-        <v>1934700</v>
+        <v>551880</v>
       </c>
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
     <row r="184" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A184" s="6">
-        <v>46200</v>
+        <v>46107</v>
       </c>
       <c r="B184" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C184" s="7">
-        <v>1080800</v>
+        <v>73100</v>
       </c>
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
     <row r="185" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A185" s="6">
-        <v>46201</v>
+        <v>46108</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C185" s="7">
-        <v>451860</v>
+        <v>700520</v>
       </c>
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
     <row r="186" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A186" s="6">
-        <v>46202</v>
+        <v>46109</v>
       </c>
       <c r="B186" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C186" s="7">
-        <v>555040</v>
+        <v>129180</v>
       </c>
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
     <row r="187" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A187" s="6">
-        <v>46203</v>
+        <v>46110</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C187" s="7">
-        <v>574460</v>
+        <v>130158</v>
       </c>
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
     <row r="188" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A188" s="6"/>
-      <c r="B188" s="5"/>
-      <c r="C188" s="7"/>
+      <c r="A188" s="6">
+        <v>46111</v>
+      </c>
+      <c r="B188" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C188" s="7">
+        <v>382360</v>
+      </c>
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
     <row r="189" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A189" s="6">
-        <v>45809</v>
+        <v>46112</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C189" s="7">
-        <v>74900</v>
+        <v>262540</v>
       </c>
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
     <row r="190" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A190" s="6">
-        <v>45810</v>
-      </c>
-      <c r="B190" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C190" s="7">
-        <v>290210</v>
-      </c>
+      <c r="A190" s="6"/>
+      <c r="B190" s="5"/>
+      <c r="C190" s="7"/>
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
     <row r="191" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A191" s="6">
-        <v>45811</v>
+        <v>46113</v>
       </c>
       <c r="B191" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C191" s="7">
-        <v>540460</v>
+        <v>515800</v>
       </c>
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
     <row r="192" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A192" s="6">
-        <v>45812</v>
+        <v>46114</v>
       </c>
       <c r="B192" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C192" s="7">
-        <v>79000</v>
+        <v>210360</v>
       </c>
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
     <row r="193" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A193" s="6">
-        <v>45813</v>
+        <v>46115</v>
       </c>
       <c r="B193" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C193" s="7">
-        <v>391580</v>
+        <v>615300</v>
       </c>
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
     <row r="194" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A194" s="6">
-        <v>45814</v>
+        <v>46116</v>
       </c>
       <c r="B194" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C194" s="7">
-        <v>511320</v>
+        <v>252400</v>
       </c>
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
     <row r="195" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A195" s="6">
-        <v>45815</v>
+        <v>46117</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C195" s="7">
-        <v>409070</v>
+        <v>229740</v>
       </c>
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
     <row r="196" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A196" s="6">
-        <v>45816</v>
+        <v>46118</v>
       </c>
       <c r="B196" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C196" s="7">
-        <v>394490</v>
+        <v>410700</v>
       </c>
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
     <row r="197" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A197" s="6">
-        <v>45817</v>
+        <v>46119</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C197" s="7">
-        <v>320110</v>
+        <v>337180</v>
       </c>
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
     <row r="198" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A198" s="6">
-        <v>45818</v>
+        <v>46120</v>
       </c>
       <c r="B198" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C198" s="7">
-        <v>974890</v>
+        <v>493600</v>
       </c>
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
     <row r="199" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A199" s="6">
-        <v>45819</v>
+        <v>46121</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C199" s="7">
-        <v>171000</v>
+        <v>254660</v>
       </c>
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
     <row r="200" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A200" s="6">
-        <v>45820</v>
+        <v>46122</v>
       </c>
       <c r="B200" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C200" s="7">
-        <v>704600</v>
+        <v>349360</v>
       </c>
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
     <row r="201" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A201" s="6">
-        <v>45821</v>
+        <v>46123</v>
       </c>
       <c r="B201" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C201" s="7">
-        <v>947360</v>
+        <v>158360</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
     <row r="202" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A202" s="6">
-        <v>45822</v>
+        <v>46124</v>
       </c>
       <c r="B202" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C202" s="7">
-        <v>796310</v>
+        <v>218920</v>
       </c>
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
     <row r="203" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A203" s="6">
-        <v>45823</v>
+        <v>46125</v>
       </c>
       <c r="B203" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C203" s="7">
-        <v>1020020</v>
+        <v>506620</v>
       </c>
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
     <row r="204" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A204" s="6">
-        <v>45824</v>
+        <v>46126</v>
       </c>
       <c r="B204" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C204" s="7">
-        <v>8014770</v>
+        <v>208020</v>
       </c>
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
     <row r="205" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A205" s="6">
-        <v>45825</v>
+        <v>46127</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C205" s="7">
-        <v>2346920</v>
+        <v>350020</v>
       </c>
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
     <row r="206" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A206" s="6">
-        <v>45826</v>
+        <v>46128</v>
       </c>
       <c r="B206" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C206" s="7">
-        <v>2261990</v>
+        <v>364360</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
     <row r="207" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A207" s="6">
-        <v>45827</v>
+        <v>46129</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C207" s="7">
-        <v>451860</v>
+        <v>809060</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
     <row r="208" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A208" s="6">
-        <v>45828</v>
+        <v>46130</v>
       </c>
       <c r="B208" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C208" s="7">
-        <v>650870</v>
+        <v>312340</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
     <row r="209" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A209" s="6">
-        <v>45829</v>
+        <v>46131</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C209" s="7">
-        <v>470000</v>
+        <v>271580</v>
       </c>
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
     <row r="210" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A210" s="6">
-        <v>45830</v>
+        <v>46132</v>
       </c>
       <c r="B210" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C210" s="7">
-        <v>58200</v>
+        <v>478400</v>
       </c>
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
     <row r="211" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A211" s="6">
-        <v>45831</v>
+        <v>46133</v>
       </c>
       <c r="B211" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C211" s="7">
-        <v>374800</v>
+        <v>327960</v>
       </c>
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
     <row r="212" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A212" s="6">
-        <v>45832</v>
+        <v>46134</v>
       </c>
       <c r="B212" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C212" s="7">
-        <v>221620</v>
+        <v>528500</v>
       </c>
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
     <row r="213" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A213" s="6">
-        <v>45833</v>
+        <v>46135</v>
       </c>
       <c r="B213" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C213" s="7">
-        <v>243880</v>
+        <v>379120</v>
       </c>
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
     <row r="214" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A214" s="6">
-        <v>45834</v>
+        <v>46136</v>
       </c>
       <c r="B214" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C214" s="7">
-        <v>234460</v>
+        <v>832730</v>
       </c>
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
     <row r="215" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A215" s="6">
-        <v>45835</v>
+        <v>46137</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C215" s="7">
-        <v>167180</v>
+        <v>372180</v>
       </c>
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
     <row r="216" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A216" s="6">
-        <v>45836</v>
+        <v>46138</v>
       </c>
       <c r="B216" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C216" s="7">
-        <v>124180</v>
+        <v>318200</v>
       </c>
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
     <row r="217" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A217" s="6">
-        <v>45837</v>
+        <v>46139</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C217" s="7">
-        <v>0</v>
+        <v>664340</v>
       </c>
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
     <row r="218" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A218" s="6">
-        <v>45838</v>
+        <v>46140</v>
       </c>
       <c r="B218" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C218" s="7">
-        <v>404030</v>
+        <v>647560</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
     <row r="219" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A219" s="6"/>
-      <c r="B219" s="5"/>
-      <c r="C219" s="7"/>
+      <c r="A219" s="6">
+        <v>46141</v>
+      </c>
+      <c r="B219" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C219" s="7">
+        <v>691430</v>
+      </c>
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
     <row r="220" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A220" s="6">
-        <v>46204</v>
+        <v>46142</v>
       </c>
       <c r="B220" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C220" s="7">
-        <v>399740</v>
+        <v>592490</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
     <row r="221" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A221" s="6">
-        <v>46205</v>
-      </c>
-      <c r="B221" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C221" s="7">
-        <v>481660</v>
-      </c>
+      <c r="A221" s="6"/>
+      <c r="B221" s="5"/>
+      <c r="C221" s="7"/>
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
     <row r="222" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A222" s="6">
-        <v>46206</v>
+        <v>46143</v>
       </c>
       <c r="B222" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C222" s="7">
-        <v>598700</v>
+        <v>549980</v>
       </c>
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
     <row r="223" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A223" s="6">
-        <v>46207</v>
+        <v>46144</v>
       </c>
       <c r="B223" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C223" s="7">
-        <v>513340</v>
+        <v>499190</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
     <row r="224" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A224" s="6">
-        <v>46208</v>
+        <v>46145</v>
       </c>
       <c r="B224" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C224" s="7">
-        <v>163030</v>
+        <v>706360</v>
       </c>
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
     <row r="225" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A225" s="6">
-        <v>46209</v>
+        <v>46146</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C225" s="7">
-        <v>668350</v>
+        <v>346300</v>
       </c>
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
     <row r="226" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A226" s="6">
-        <v>46210</v>
+        <v>46147</v>
       </c>
       <c r="B226" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C226" s="7">
-        <v>578760</v>
+        <v>191030</v>
       </c>
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
     <row r="227" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A227" s="6">
-        <v>46211</v>
+        <v>46148</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C227" s="7">
-        <v>510560</v>
+        <v>304950</v>
       </c>
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
     <row r="228" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A228" s="6">
-        <v>46212</v>
+        <v>46149</v>
       </c>
       <c r="B228" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C228" s="7">
-        <v>481660</v>
+        <v>312220</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
     <row r="229" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A229" s="6">
-        <v>46213</v>
+        <v>46150</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C229" s="7">
-        <v>202060</v>
+        <v>631150</v>
       </c>
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
     <row r="230" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A230" s="6">
-        <v>46214</v>
+        <v>46151</v>
       </c>
       <c r="B230" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C230" s="7">
-        <v>524910</v>
+        <v>769760</v>
       </c>
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
     <row r="231" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A231" s="6">
-        <v>46215</v>
+        <v>46152</v>
       </c>
       <c r="B231" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C231" s="7">
-        <v>227920</v>
+        <v>365430</v>
       </c>
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
     <row r="232" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A232" s="6">
-        <v>46216</v>
+        <v>46153</v>
       </c>
       <c r="B232" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C232" s="7">
-        <v>331020</v>
+        <v>678380</v>
       </c>
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
     <row r="233" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A233" s="6">
-        <v>46217</v>
+        <v>46154</v>
       </c>
       <c r="B233" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C233" s="7">
-        <v>392280</v>
+        <v>1208410</v>
       </c>
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
     <row r="234" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A234" s="6">
-        <v>46218</v>
+        <v>46155</v>
       </c>
       <c r="B234" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C234" s="7">
-        <v>531280</v>
+        <v>1054460</v>
       </c>
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
     <row r="235" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A235" s="6">
-        <v>46219</v>
+        <v>46156</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C235" s="7">
-        <v>412000</v>
+        <v>346900</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
     <row r="236" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A236" s="6">
-        <v>46220</v>
+        <v>46157</v>
       </c>
       <c r="B236" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C236" s="7">
-        <v>278330</v>
+        <v>627020</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
     <row r="237" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A237" s="6">
-        <v>46221</v>
+        <v>46158</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C237" s="7">
-        <v>417040</v>
+        <v>294920</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
     <row r="238" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A238" s="6">
-        <v>46222</v>
+        <v>46159</v>
       </c>
       <c r="B238" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C238" s="7">
-        <v>273420</v>
+        <v>145580</v>
       </c>
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
     <row r="239" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A239" s="6">
-        <v>46223</v>
+        <v>46160</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C239" s="7">
-        <v>320200</v>
+        <v>429560</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
     <row r="240" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A240" s="6">
-        <v>46224</v>
+        <v>46161</v>
       </c>
       <c r="B240" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C240" s="7">
-        <v>273730</v>
+        <v>420280</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
     <row r="241" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A241" s="6">
-        <v>46225</v>
+        <v>46162</v>
       </c>
       <c r="B241" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C241" s="7">
-        <v>437930</v>
+        <v>298680</v>
       </c>
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
     <row r="242" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A242" s="6">
-        <v>46226</v>
+        <v>46163</v>
       </c>
       <c r="B242" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C242" s="7">
-        <v>228460</v>
+        <v>237460</v>
       </c>
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
     <row r="243" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A243" s="6">
-        <v>46227</v>
+        <v>46164</v>
       </c>
       <c r="B243" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C243" s="7">
-        <v>660860</v>
+        <v>532060</v>
       </c>
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
     <row r="244" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A244" s="6">
-        <v>46228</v>
+        <v>46165</v>
       </c>
       <c r="B244" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C244" s="7">
-        <v>490970</v>
+        <v>202140</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
     <row r="245" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A245" s="6">
-        <v>46229</v>
+        <v>46166</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C245" s="7">
-        <v>200900</v>
+        <v>133920</v>
       </c>
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
     <row r="246" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A246" s="6">
-        <v>46230</v>
+        <v>46167</v>
       </c>
       <c r="B246" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C246" s="7">
-        <v>305240</v>
+        <v>472880</v>
       </c>
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
     <row r="247" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A247" s="6">
-        <v>46231</v>
+        <v>46168</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C247" s="7">
-        <v>595250</v>
+        <v>325760</v>
       </c>
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
     <row r="248" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A248" s="6">
-        <v>46232</v>
+        <v>46169</v>
       </c>
       <c r="B248" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C248" s="7">
-        <v>379450</v>
+        <v>365200</v>
       </c>
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
     <row r="249" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A249" s="6">
-        <v>46233</v>
+        <v>46170</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C249" s="7">
-        <v>567710</v>
+        <v>431700</v>
       </c>
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
     <row r="250" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A250" s="6">
-        <v>46234</v>
+        <v>46171</v>
       </c>
       <c r="B250" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C250" s="7">
-        <v>421430</v>
+        <v>442180</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
     <row r="251" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A251" s="6"/>
-      <c r="B251" s="5"/>
-      <c r="C251" s="7"/>
+      <c r="A251" s="6">
+        <v>46172</v>
+      </c>
+      <c r="B251" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C251" s="7">
+        <v>293080</v>
+      </c>
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
     <row r="252" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A252" s="6">
-        <v>45839</v>
+        <v>46173</v>
       </c>
       <c r="B252" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C252" s="7">
-        <v>214820</v>
+        <v>284960</v>
       </c>
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
     <row r="253" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A253" s="6">
-        <v>45840</v>
-      </c>
-      <c r="B253" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C253" s="7">
-        <v>282630</v>
-      </c>
+      <c r="A253" s="6"/>
+      <c r="B253" s="5"/>
+      <c r="C253" s="7"/>
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
     <row r="254" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A254" s="6">
-        <v>45841</v>
+        <v>46174</v>
       </c>
       <c r="B254" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C254" s="7">
-        <v>227700</v>
+        <v>264640</v>
       </c>
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
     <row r="255" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A255" s="6">
-        <v>45842</v>
+        <v>46175</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C255" s="7">
-        <v>278950</v>
+        <v>365400</v>
       </c>
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
     <row r="256" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A256" s="6">
-        <v>45843</v>
+        <v>46176</v>
       </c>
       <c r="B256" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C256" s="7">
-        <v>191430</v>
+        <v>313860</v>
       </c>
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
     <row r="257" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A257" s="6">
-        <v>45844</v>
+        <v>46177</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C257" s="7">
-        <v>152210</v>
+        <v>349340</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
     <row r="258" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A258" s="6">
-        <v>45845</v>
+        <v>46178</v>
       </c>
       <c r="B258" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C258" s="7">
-        <v>60910</v>
+        <v>262280</v>
       </c>
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
     <row r="259" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A259" s="6">
-        <v>45846</v>
+        <v>46179</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C259" s="7">
-        <v>336320</v>
+        <v>310040</v>
       </c>
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
     <row r="260" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A260" s="6">
-        <v>45847</v>
+        <v>46180</v>
       </c>
       <c r="B260" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C260" s="7">
-        <v>164550</v>
+        <v>318700</v>
       </c>
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
     <row r="261" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A261" s="6">
-        <v>45848</v>
+        <v>46181</v>
       </c>
       <c r="B261" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C261" s="7">
-        <v>319070</v>
+        <v>361500</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
     <row r="262" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A262" s="6">
-        <v>45849</v>
+        <v>46182</v>
       </c>
       <c r="B262" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C262" s="7">
-        <v>214700</v>
+        <v>344360</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
     <row r="263" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A263" s="6">
-        <v>45850</v>
+        <v>46183</v>
       </c>
       <c r="B263" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C263" s="7">
-        <v>234680</v>
+        <v>294020</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
     <row r="264" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A264" s="6">
-        <v>45851</v>
+        <v>46184</v>
       </c>
       <c r="B264" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C264" s="7">
-        <v>177820</v>
+        <v>358600</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
     <row r="265" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A265" s="6">
-        <v>45852</v>
+        <v>46185</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C265" s="7">
-        <v>227340</v>
+        <v>312220</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
     <row r="266" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A266" s="6">
-        <v>45853</v>
+        <v>46186</v>
       </c>
       <c r="B266" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C266" s="7">
-        <v>226730</v>
+        <v>413660</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
     <row r="267" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A267" s="6">
-        <v>45854</v>
+        <v>46187</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C267" s="7">
-        <v>201680</v>
+        <v>267780</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
     <row r="268" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A268" s="6">
-        <v>45855</v>
+        <v>46188</v>
       </c>
       <c r="B268" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C268" s="7">
-        <v>262800</v>
+        <v>411280</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
     <row r="269" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A269" s="6">
-        <v>45856</v>
+        <v>46189</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C269" s="7">
-        <v>205440</v>
+        <v>396660</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
     <row r="270" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A270" s="6">
-        <v>45857</v>
+        <v>46190</v>
       </c>
       <c r="B270" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C270" s="7">
-        <v>206000</v>
+        <v>402380</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
     <row r="271" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A271" s="6">
-        <v>45858</v>
+        <v>46191</v>
       </c>
       <c r="B271" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C271" s="7">
-        <v>159460</v>
+        <v>425040</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
     <row r="272" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A272" s="6">
-        <v>45859</v>
+        <v>46192</v>
       </c>
       <c r="B272" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C272" s="7">
-        <v>126860</v>
+        <v>507860</v>
       </c>
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
     <row r="273" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A273" s="6">
-        <v>45860</v>
+        <v>46193</v>
       </c>
       <c r="B273" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C273" s="7">
-        <v>119430</v>
+        <v>539200</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
     <row r="274" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A274" s="6">
-        <v>45861</v>
+        <v>46194</v>
       </c>
       <c r="B274" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C274" s="7">
-        <v>185160</v>
+        <v>299200</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
     <row r="275" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A275" s="6">
-        <v>45862</v>
+        <v>46195</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C275" s="7">
-        <v>330350</v>
+        <v>1228860</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
     <row r="276" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A276" s="6">
-        <v>45863</v>
+        <v>46196</v>
       </c>
       <c r="B276" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C276" s="7">
-        <v>229580</v>
+        <v>1833640</v>
       </c>
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
     <row r="277" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A277" s="6">
-        <v>45864</v>
+        <v>46197</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C277" s="7">
-        <v>217790</v>
+        <v>6264870</v>
       </c>
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
     <row r="278" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A278" s="6">
-        <v>45865</v>
+        <v>46198</v>
       </c>
       <c r="B278" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C278" s="7">
-        <v>114200</v>
+        <v>3949520</v>
       </c>
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
     <row r="279" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A279" s="6">
-        <v>45866</v>
+        <v>46199</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C279" s="7">
-        <v>235500</v>
+        <v>1934700</v>
       </c>
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
     <row r="280" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A280" s="6">
-        <v>45867</v>
+        <v>46200</v>
       </c>
       <c r="B280" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C280" s="7">
-        <v>235130</v>
+        <v>1080800</v>
       </c>
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
     <row r="281" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A281" s="6">
-        <v>45868</v>
+        <v>46201</v>
       </c>
       <c r="B281" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C281" s="7">
-        <v>156160</v>
+        <v>451860</v>
       </c>
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
     <row r="282" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A282" s="6">
-        <v>45869</v>
+        <v>46202</v>
       </c>
       <c r="B282" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C282" s="7">
-        <v>197300</v>
+        <v>555040</v>
       </c>
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
     <row r="283" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A283" s="6"/>
-      <c r="B283" s="5"/>
-      <c r="C283" s="7"/>
+      <c r="A283" s="6">
+        <v>46203</v>
+      </c>
+      <c r="B283" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C283" s="7">
+        <v>574460</v>
+      </c>
       <c r="D283" s="7"/>
       <c r="E283" s="5"/>
     </row>
     <row r="284" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A284" s="6">
-        <v>46235</v>
-      </c>
-      <c r="B284" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C284" s="7">
-        <v>403860</v>
-      </c>
+      <c r="A284" s="6"/>
+      <c r="B284" s="5"/>
+      <c r="C284" s="7"/>
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
     <row r="285" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A285" s="6">
-        <v>46236</v>
+        <v>45809</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C285" s="7">
-        <v>511340</v>
+        <v>74900</v>
       </c>
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
     <row r="286" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A286" s="6">
-        <v>46237</v>
+        <v>45810</v>
       </c>
       <c r="B286" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C286" s="7">
-        <v>801850</v>
+        <v>290210</v>
       </c>
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
     <row r="287" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A287" s="6">
-        <v>46238</v>
+        <v>45811</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C287" s="7">
-        <v>1108210</v>
+        <v>540460</v>
       </c>
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
     <row r="288" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A288" s="6">
-        <v>46239</v>
+        <v>45812</v>
       </c>
       <c r="B288" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C288" s="7">
-        <v>1169610</v>
+        <v>79000</v>
       </c>
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
     <row r="289" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A289" s="6">
-        <v>46240</v>
+        <v>45813</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C289" s="7">
-        <v>1138260</v>
+        <v>391580</v>
       </c>
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
     <row r="290" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A290" s="6">
-        <v>46241</v>
+        <v>45814</v>
       </c>
       <c r="B290" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C290" s="7">
-        <v>1135070</v>
+        <v>511320</v>
       </c>
       <c r="D290" s="7"/>
       <c r="E290" s="5"/>
     </row>
     <row r="291" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A291" s="6">
-        <v>46242</v>
+        <v>45815</v>
       </c>
       <c r="B291" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C291" s="7">
-        <v>1228060</v>
+        <v>409070</v>
       </c>
       <c r="D291" s="7"/>
       <c r="E291" s="5"/>
     </row>
     <row r="292" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A292" s="6">
-        <v>46243</v>
+        <v>45816</v>
       </c>
       <c r="B292" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C292" s="7">
-        <v>1093320</v>
+        <v>394490</v>
       </c>
       <c r="D292" s="7"/>
       <c r="E292" s="5"/>
     </row>
     <row r="293" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A293" s="6">
-        <v>46244</v>
+        <v>45817</v>
       </c>
       <c r="B293" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C293" s="7">
-        <v>1570110</v>
+        <v>320110</v>
       </c>
       <c r="D293" s="7"/>
       <c r="E293" s="5"/>
     </row>
     <row r="294" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A294" s="6">
-        <v>46245</v>
+        <v>45818</v>
       </c>
       <c r="B294" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C294" s="7">
-        <v>1547130</v>
+        <v>974890</v>
       </c>
       <c r="D294" s="7"/>
       <c r="E294" s="5"/>
     </row>
     <row r="295" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A295" s="6">
-        <v>46246</v>
+        <v>45819</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C295" s="7">
-        <v>1476040</v>
+        <v>171000</v>
       </c>
       <c r="D295" s="7"/>
       <c r="E295" s="5"/>
     </row>
     <row r="296" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A296" s="6">
-        <v>46247</v>
+        <v>45820</v>
       </c>
       <c r="B296" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C296" s="7">
-        <v>1127130</v>
+        <v>704600</v>
       </c>
       <c r="D296" s="7"/>
       <c r="E296" s="5"/>
     </row>
     <row r="297" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A297" s="6">
-        <v>46248</v>
+        <v>45821</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C297" s="7">
-        <v>1048500</v>
+        <v>947360</v>
       </c>
       <c r="D297" s="7"/>
       <c r="E297" s="5"/>
     </row>
     <row r="298" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A298" s="6">
-        <v>46249</v>
+        <v>45822</v>
       </c>
       <c r="B298" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C298" s="7">
-        <v>1036030</v>
+        <v>796310</v>
       </c>
       <c r="D298" s="7"/>
       <c r="E298" s="5"/>
     </row>
     <row r="299" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A299" s="6">
-        <v>46250</v>
+        <v>45823</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C299" s="7">
-        <v>1187540</v>
+        <v>1020020</v>
       </c>
       <c r="D299" s="7"/>
       <c r="E299" s="5"/>
     </row>
     <row r="300" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A300" s="6">
-        <v>46251</v>
+        <v>45824</v>
       </c>
       <c r="B300" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C300" s="7">
-        <v>1147050</v>
+        <v>8014770</v>
       </c>
       <c r="D300" s="7"/>
       <c r="E300" s="5"/>
     </row>
     <row r="301" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A301" s="6">
-        <v>46252</v>
+        <v>45825</v>
       </c>
       <c r="B301" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C301" s="7">
-        <v>1068720</v>
+        <v>2346920</v>
       </c>
       <c r="D301" s="7"/>
       <c r="E301" s="5"/>
     </row>
     <row r="302" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A302" s="6">
-        <v>46253</v>
+        <v>45826</v>
       </c>
       <c r="B302" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C302" s="7">
-        <v>1136240</v>
+        <v>2261990</v>
       </c>
       <c r="D302" s="7"/>
       <c r="E302" s="5"/>
     </row>
     <row r="303" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A303" s="6">
-        <v>46254</v>
+        <v>45827</v>
       </c>
       <c r="B303" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C303" s="7">
-        <v>1171640</v>
+        <v>451860</v>
       </c>
       <c r="D303" s="7"/>
       <c r="E303" s="5"/>
     </row>
     <row r="304" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A304" s="6">
-        <v>46255</v>
+        <v>45828</v>
       </c>
       <c r="B304" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C304" s="7">
-        <v>1082950</v>
+        <v>650870</v>
       </c>
       <c r="D304" s="7"/>
       <c r="E304" s="5"/>
     </row>
     <row r="305" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A305" s="6">
-        <v>46256</v>
+        <v>45829</v>
       </c>
       <c r="B305" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C305" s="7">
-        <v>957480</v>
+        <v>470000</v>
       </c>
       <c r="D305" s="7"/>
       <c r="E305" s="5"/>
     </row>
     <row r="306" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A306" s="6">
-        <v>46257</v>
+        <v>45830</v>
       </c>
       <c r="B306" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C306" s="7">
-        <v>986280</v>
+        <v>58200</v>
       </c>
       <c r="D306" s="7"/>
       <c r="E306" s="5"/>
     </row>
     <row r="307" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A307" s="6">
-        <v>46258</v>
+        <v>45831</v>
       </c>
       <c r="B307" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C307" s="7">
-        <v>1130890</v>
+        <v>374800</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="5"/>
     </row>
     <row r="308" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A308" s="6">
-        <v>46259</v>
+        <v>45832</v>
       </c>
       <c r="B308" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C308" s="7">
-        <v>1229900</v>
+        <v>221620</v>
       </c>
       <c r="D308" s="7"/>
       <c r="E308" s="5"/>
     </row>
     <row r="309" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A309" s="6">
-        <v>46260</v>
+        <v>45833</v>
       </c>
       <c r="B309" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C309" s="7">
-        <v>1327380</v>
+        <v>243880</v>
       </c>
       <c r="D309" s="7"/>
       <c r="E309" s="5"/>
     </row>
     <row r="310" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A310" s="6">
-        <v>46261</v>
+        <v>45834</v>
       </c>
       <c r="B310" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C310" s="7">
-        <v>1141620</v>
+        <v>234460</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="5"/>
     </row>
     <row r="311" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A311" s="6">
-        <v>46262</v>
+        <v>45835</v>
       </c>
       <c r="B311" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C311" s="7">
-        <v>1134920</v>
+        <v>167180</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="5"/>
     </row>
     <row r="312" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A312" s="6">
-        <v>46263</v>
+        <v>45836</v>
       </c>
       <c r="B312" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C312" s="7">
-        <v>1360250</v>
+        <v>124180</v>
       </c>
       <c r="D312" s="7"/>
       <c r="E312" s="5"/>
     </row>
     <row r="313" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A313" s="6">
-        <v>46264</v>
+        <v>45837</v>
       </c>
       <c r="B313" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C313" s="7">
-        <v>1351580</v>
+        <v>0</v>
       </c>
       <c r="D313" s="7"/>
       <c r="E313" s="5"/>
     </row>
     <row r="314" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A314" s="6">
-        <v>46265</v>
+        <v>45838</v>
       </c>
       <c r="B314" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C314" s="7">
-        <v>1164740</v>
+        <v>404030</v>
       </c>
       <c r="D314" s="7"/>
       <c r="E314" s="5"/>
@@ -4965,403 +4551,403 @@
     </row>
     <row r="316" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A316" s="6">
-        <v>45870</v>
+        <v>46204</v>
       </c>
       <c r="B316" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C316" s="7">
-        <v>167220</v>
+        <v>399740</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="5"/>
     </row>
     <row r="317" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A317" s="6">
-        <v>45871</v>
+        <v>46205</v>
       </c>
       <c r="B317" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C317" s="7">
-        <v>350380</v>
+        <v>481660</v>
       </c>
       <c r="D317" s="7"/>
       <c r="E317" s="5"/>
     </row>
     <row r="318" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A318" s="6">
-        <v>45872</v>
+        <v>46206</v>
       </c>
       <c r="B318" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C318" s="7">
-        <v>346970</v>
+        <v>598700</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="5"/>
     </row>
     <row r="319" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A319" s="6">
-        <v>45873</v>
+        <v>46207</v>
       </c>
       <c r="B319" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C319" s="7">
-        <v>143340</v>
+        <v>513340</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="5"/>
     </row>
     <row r="320" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A320" s="6">
-        <v>45874</v>
+        <v>46208</v>
       </c>
       <c r="B320" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C320" s="7">
-        <v>132060</v>
+        <v>163030</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="5"/>
     </row>
     <row r="321" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A321" s="6">
-        <v>45875</v>
+        <v>46209</v>
       </c>
       <c r="B321" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C321" s="7">
-        <v>629120</v>
+        <v>668350</v>
       </c>
       <c r="D321" s="7"/>
       <c r="E321" s="5"/>
     </row>
     <row r="322" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A322" s="6">
-        <v>45876</v>
+        <v>46210</v>
       </c>
       <c r="B322" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C322" s="7">
-        <v>218300</v>
+        <v>578760</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="5"/>
     </row>
     <row r="323" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A323" s="6">
-        <v>45877</v>
+        <v>46211</v>
       </c>
       <c r="B323" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C323" s="7">
-        <v>428020</v>
+        <v>510560</v>
       </c>
       <c r="D323" s="7"/>
       <c r="E323" s="5"/>
     </row>
     <row r="324" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A324" s="6">
-        <v>45878</v>
+        <v>46212</v>
       </c>
       <c r="B324" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C324" s="7">
-        <v>232460</v>
+        <v>481660</v>
       </c>
       <c r="D324" s="7"/>
       <c r="E324" s="5"/>
     </row>
     <row r="325" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A325" s="6">
-        <v>45879</v>
+        <v>46213</v>
       </c>
       <c r="B325" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C325" s="7">
-        <v>231720</v>
+        <v>202060</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="5"/>
     </row>
     <row r="326" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A326" s="6">
-        <v>45880</v>
+        <v>46214</v>
       </c>
       <c r="B326" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C326" s="7">
-        <v>495660</v>
+        <v>524910</v>
       </c>
       <c r="D326" s="7"/>
       <c r="E326" s="5"/>
     </row>
     <row r="327" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A327" s="6">
-        <v>45881</v>
+        <v>46215</v>
       </c>
       <c r="B327" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C327" s="7">
-        <v>265910</v>
+        <v>227920</v>
       </c>
       <c r="D327" s="7"/>
       <c r="E327" s="5"/>
     </row>
     <row r="328" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A328" s="6">
-        <v>45882</v>
+        <v>46216</v>
       </c>
       <c r="B328" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C328" s="7">
-        <v>291880</v>
+        <v>331020</v>
       </c>
       <c r="D328" s="7"/>
       <c r="E328" s="5"/>
     </row>
     <row r="329" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A329" s="6">
-        <v>45883</v>
+        <v>46217</v>
       </c>
       <c r="B329" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C329" s="7">
-        <v>239340</v>
+        <v>392280</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="5"/>
     </row>
     <row r="330" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A330" s="6">
-        <v>45884</v>
+        <v>46218</v>
       </c>
       <c r="B330" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C330" s="7">
-        <v>362550</v>
+        <v>531280</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="5"/>
     </row>
     <row r="331" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A331" s="6">
-        <v>45885</v>
+        <v>46219</v>
       </c>
       <c r="B331" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C331" s="7">
-        <v>242910</v>
+        <v>412000</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="5"/>
     </row>
     <row r="332" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A332" s="6">
-        <v>45886</v>
+        <v>46220</v>
       </c>
       <c r="B332" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C332" s="7">
-        <v>81400</v>
+        <v>278330</v>
       </c>
       <c r="D332" s="7"/>
       <c r="E332" s="5"/>
     </row>
     <row r="333" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A333" s="6">
-        <v>45887</v>
+        <v>46221</v>
       </c>
       <c r="B333" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C333" s="7">
-        <v>319750</v>
+        <v>417040</v>
       </c>
       <c r="D333" s="7"/>
       <c r="E333" s="5"/>
     </row>
     <row r="334" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A334" s="6">
-        <v>45888</v>
+        <v>46222</v>
       </c>
       <c r="B334" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C334" s="7">
-        <v>419530</v>
+        <v>273420</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="5"/>
     </row>
     <row r="335" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A335" s="6">
-        <v>45889</v>
+        <v>46223</v>
       </c>
       <c r="B335" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C335" s="7">
-        <v>329950</v>
+        <v>320200</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="5"/>
     </row>
     <row r="336" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A336" s="6">
-        <v>45890</v>
+        <v>46224</v>
       </c>
       <c r="B336" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C336" s="7">
-        <v>170250</v>
+        <v>273730</v>
       </c>
       <c r="D336" s="7"/>
       <c r="E336" s="5"/>
     </row>
     <row r="337" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A337" s="6">
-        <v>45891</v>
+        <v>46225</v>
       </c>
       <c r="B337" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C337" s="7">
-        <v>425050</v>
+        <v>437930</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="5"/>
     </row>
     <row r="338" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A338" s="6">
-        <v>45892</v>
+        <v>46226</v>
       </c>
       <c r="B338" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C338" s="7">
-        <v>150670</v>
+        <v>228460</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="5"/>
     </row>
     <row r="339" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A339" s="6">
-        <v>45893</v>
+        <v>46227</v>
       </c>
       <c r="B339" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C339" s="7">
-        <v>128730</v>
+        <v>660860</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="5"/>
     </row>
     <row r="340" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A340" s="6">
-        <v>45894</v>
+        <v>46228</v>
       </c>
       <c r="B340" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C340" s="7">
-        <v>377400</v>
+        <v>490970</v>
       </c>
       <c r="D340" s="7"/>
       <c r="E340" s="5"/>
     </row>
     <row r="341" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A341" s="6">
-        <v>45895</v>
+        <v>46229</v>
       </c>
       <c r="B341" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C341" s="7">
-        <v>74620</v>
+        <v>200900</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="5"/>
     </row>
     <row r="342" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A342" s="6">
-        <v>45896</v>
+        <v>46230</v>
       </c>
       <c r="B342" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C342" s="7">
-        <v>391520</v>
+        <v>305240</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="5"/>
     </row>
     <row r="343" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A343" s="6">
-        <v>45897</v>
+        <v>46231</v>
       </c>
       <c r="B343" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C343" s="7">
-        <v>158820</v>
+        <v>595250</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="5"/>
     </row>
     <row r="344" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A344" s="6">
-        <v>45898</v>
+        <v>46232</v>
       </c>
       <c r="B344" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C344" s="7">
-        <v>360880</v>
+        <v>379450</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="5"/>
     </row>
     <row r="345" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A345" s="6">
-        <v>45899</v>
+        <v>46233</v>
       </c>
       <c r="B345" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C345" s="7">
-        <v>100140</v>
+        <v>567710</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="5"/>
     </row>
     <row r="346" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A346" s="6">
-        <v>45900</v>
+        <v>46234</v>
       </c>
       <c r="B346" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C346" s="7">
-        <v>243510</v>
+        <v>421430</v>
       </c>
       <c r="D346" s="7"/>
       <c r="E346" s="5"/>
@@ -5375,1615 +4961,1621 @@
     </row>
     <row r="348" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A348" s="6">
-        <v>45901</v>
+        <v>45839</v>
       </c>
       <c r="B348" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C348" s="7">
-        <v>176920</v>
+        <v>214820</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="5"/>
     </row>
     <row r="349" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A349" s="6">
-        <v>45902</v>
+        <v>45840</v>
       </c>
       <c r="B349" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C349" s="7">
-        <v>161250</v>
+        <v>282630</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="5"/>
     </row>
     <row r="350" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A350" s="6">
-        <v>45903</v>
+        <v>45841</v>
       </c>
       <c r="B350" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C350" s="7">
-        <v>333640</v>
+        <v>227700</v>
       </c>
       <c r="D350" s="7"/>
       <c r="E350" s="5"/>
     </row>
     <row r="351" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A351" s="6">
-        <v>45904</v>
+        <v>45842</v>
       </c>
       <c r="B351" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C351" s="7">
-        <v>145410</v>
+        <v>278950</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="5"/>
     </row>
     <row r="352" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A352" s="6">
-        <v>45905</v>
+        <v>45843</v>
       </c>
       <c r="B352" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C352" s="7">
-        <v>419600</v>
+        <v>191430</v>
       </c>
       <c r="D352" s="7"/>
       <c r="E352" s="5"/>
     </row>
     <row r="353" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A353" s="6">
-        <v>45906</v>
+        <v>45844</v>
       </c>
       <c r="B353" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C353" s="7">
-        <v>78240</v>
+        <v>152210</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="5"/>
     </row>
     <row r="354" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A354" s="6">
-        <v>45907</v>
+        <v>45845</v>
       </c>
       <c r="B354" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C354" s="7">
-        <v>68180</v>
+        <v>60910</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="5"/>
     </row>
     <row r="355" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A355" s="6">
-        <v>45908</v>
+        <v>45846</v>
       </c>
       <c r="B355" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C355" s="7">
-        <v>322410</v>
+        <v>336320</v>
       </c>
       <c r="D355" s="7"/>
       <c r="E355" s="5"/>
     </row>
     <row r="356" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A356" s="6">
-        <v>45909</v>
+        <v>45847</v>
       </c>
       <c r="B356" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C356" s="7">
-        <v>72270</v>
+        <v>164550</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="5"/>
     </row>
     <row r="357" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A357" s="6">
-        <v>45910</v>
+        <v>45848</v>
       </c>
       <c r="B357" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C357" s="7">
-        <v>350500</v>
+        <v>319070</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="5"/>
     </row>
     <row r="358" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A358" s="6">
-        <v>45911</v>
+        <v>45849</v>
       </c>
       <c r="B358" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C358" s="7">
-        <v>132330</v>
+        <v>214700</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="5"/>
     </row>
     <row r="359" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A359" s="6">
-        <v>45912</v>
+        <v>45850</v>
       </c>
       <c r="B359" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C359" s="7">
-        <v>282820</v>
+        <v>234680</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="5"/>
     </row>
     <row r="360" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A360" s="6">
-        <v>45913</v>
+        <v>45851</v>
       </c>
       <c r="B360" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C360" s="7">
-        <v>140280</v>
+        <v>177820</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="5"/>
     </row>
     <row r="361" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A361" s="6">
-        <v>45914</v>
+        <v>45852</v>
       </c>
       <c r="B361" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C361" s="7">
-        <v>81480</v>
+        <v>227340</v>
       </c>
       <c r="D361" s="7"/>
       <c r="E361" s="5"/>
     </row>
     <row r="362" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A362" s="6">
-        <v>45915</v>
+        <v>45853</v>
       </c>
       <c r="B362" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C362" s="7">
-        <v>185160</v>
+        <v>226730</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="5"/>
     </row>
     <row r="363" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A363" s="6">
-        <v>45916</v>
+        <v>45854</v>
       </c>
       <c r="B363" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C363" s="7">
-        <v>92420</v>
+        <v>201680</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="5"/>
     </row>
     <row r="364" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A364" s="6">
-        <v>45917</v>
+        <v>45855</v>
       </c>
       <c r="B364" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C364" s="7">
-        <v>200030</v>
+        <v>262800</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="5"/>
     </row>
     <row r="365" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A365" s="6">
-        <v>45918</v>
+        <v>45856</v>
       </c>
       <c r="B365" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C365" s="7">
-        <v>109950</v>
+        <v>205440</v>
       </c>
       <c r="D365" s="7"/>
       <c r="E365" s="5"/>
     </row>
     <row r="366" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A366" s="6">
-        <v>45919</v>
+        <v>45857</v>
       </c>
       <c r="B366" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C366" s="7">
-        <v>317560</v>
+        <v>206000</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="5"/>
     </row>
     <row r="367" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A367" s="6">
-        <v>45920</v>
+        <v>45858</v>
       </c>
       <c r="B367" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C367" s="7">
-        <v>136720</v>
+        <v>159460</v>
       </c>
       <c r="D367" s="7"/>
       <c r="E367" s="5"/>
     </row>
     <row r="368" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A368" s="6">
-        <v>45921</v>
+        <v>45859</v>
       </c>
       <c r="B368" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C368" s="7">
-        <v>84350</v>
+        <v>126860</v>
       </c>
       <c r="D368" s="7"/>
       <c r="E368" s="5"/>
     </row>
     <row r="369" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A369" s="6">
-        <v>45922</v>
+        <v>45860</v>
       </c>
       <c r="B369" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C369" s="7">
-        <v>367710</v>
+        <v>119430</v>
       </c>
       <c r="D369" s="7"/>
       <c r="E369" s="5"/>
     </row>
     <row r="370" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A370" s="6">
-        <v>45923</v>
+        <v>45861</v>
       </c>
       <c r="B370" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C370" s="7">
-        <v>180390</v>
+        <v>185160</v>
       </c>
       <c r="D370" s="7"/>
       <c r="E370" s="5"/>
     </row>
     <row r="371" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A371" s="6">
-        <v>45924</v>
+        <v>45862</v>
       </c>
       <c r="B371" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C371" s="7">
-        <v>233430</v>
+        <v>330350</v>
       </c>
       <c r="D371" s="7"/>
       <c r="E371" s="5"/>
     </row>
     <row r="372" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A372" s="6">
-        <v>45925</v>
+        <v>45863</v>
       </c>
       <c r="B372" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C372" s="7">
-        <v>409620</v>
+        <v>229580</v>
       </c>
       <c r="D372" s="7"/>
       <c r="E372" s="5"/>
     </row>
     <row r="373" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A373" s="6">
-        <v>45926</v>
+        <v>45864</v>
       </c>
       <c r="B373" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C373" s="7">
-        <v>343820</v>
+        <v>217790</v>
       </c>
       <c r="D373" s="7"/>
       <c r="E373" s="5"/>
     </row>
     <row r="374" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A374" s="6">
-        <v>45927</v>
+        <v>45865</v>
       </c>
       <c r="B374" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C374" s="7">
-        <v>1077030</v>
+        <v>114200</v>
       </c>
       <c r="D374" s="7"/>
       <c r="E374" s="5"/>
     </row>
     <row r="375" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A375" s="6">
-        <v>45928</v>
+        <v>45866</v>
       </c>
       <c r="B375" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C375" s="7">
-        <v>67140</v>
+        <v>235500</v>
       </c>
       <c r="D375" s="7"/>
       <c r="E375" s="5"/>
     </row>
     <row r="376" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A376" s="6">
-        <v>45929</v>
+        <v>45867</v>
       </c>
       <c r="B376" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C376" s="7">
-        <v>2051880</v>
+        <v>235130</v>
       </c>
       <c r="D376" s="7"/>
       <c r="E376" s="5"/>
     </row>
     <row r="377" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A377" s="6">
-        <v>45930</v>
+        <v>45868</v>
       </c>
       <c r="B377" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C377" s="7">
-        <v>1105220</v>
+        <v>156160</v>
       </c>
       <c r="D377" s="7"/>
       <c r="E377" s="5"/>
     </row>
     <row r="378" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A378" s="6"/>
-      <c r="B378" s="5"/>
-      <c r="C378" s="7"/>
+      <c r="A378" s="6">
+        <v>45869</v>
+      </c>
+      <c r="B378" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C378" s="7">
+        <v>197300</v>
+      </c>
       <c r="D378" s="7"/>
       <c r="E378" s="5"/>
     </row>
     <row r="379" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A379" s="6">
-        <v>45931</v>
-      </c>
-      <c r="B379" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C379" s="7">
-        <v>1989180</v>
-      </c>
+      <c r="A379" s="6"/>
+      <c r="B379" s="5"/>
+      <c r="C379" s="7"/>
       <c r="D379" s="7"/>
       <c r="E379" s="5"/>
     </row>
     <row r="380" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A380" s="6">
-        <v>45932</v>
+        <v>46235</v>
       </c>
       <c r="B380" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C380" s="7">
-        <v>4134460</v>
+        <v>403860</v>
       </c>
       <c r="D380" s="7"/>
       <c r="E380" s="5"/>
     </row>
     <row r="381" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A381" s="6">
-        <v>45933</v>
+        <v>46236</v>
       </c>
       <c r="B381" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C381" s="7">
-        <v>345820</v>
+        <v>511340</v>
       </c>
       <c r="D381" s="7"/>
       <c r="E381" s="5"/>
     </row>
     <row r="382" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A382" s="6">
-        <v>45934</v>
+        <v>46237</v>
       </c>
       <c r="B382" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C382" s="7">
-        <v>570800</v>
+        <v>801850</v>
       </c>
       <c r="D382" s="7"/>
       <c r="E382" s="5"/>
     </row>
     <row r="383" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A383" s="6">
-        <v>45935</v>
+        <v>46238</v>
       </c>
       <c r="B383" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C383" s="7">
-        <v>103870</v>
+        <v>1108210</v>
       </c>
       <c r="D383" s="7"/>
       <c r="E383" s="5"/>
     </row>
     <row r="384" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A384" s="6">
-        <v>45936</v>
+        <v>46239</v>
       </c>
       <c r="B384" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C384" s="7">
-        <v>162140</v>
+        <v>1169610</v>
       </c>
       <c r="D384" s="7"/>
       <c r="E384" s="5"/>
     </row>
     <row r="385" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A385" s="6">
-        <v>45937</v>
+        <v>46240</v>
       </c>
       <c r="B385" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C385" s="7">
-        <v>328620</v>
+        <v>1138260</v>
       </c>
       <c r="D385" s="7"/>
       <c r="E385" s="5"/>
     </row>
     <row r="386" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A386" s="6">
-        <v>45938</v>
+        <v>46241</v>
       </c>
       <c r="B386" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C386" s="7">
-        <v>262770</v>
+        <v>1135070</v>
       </c>
       <c r="D386" s="7"/>
       <c r="E386" s="5"/>
     </row>
     <row r="387" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A387" s="6">
-        <v>45939</v>
+        <v>46242</v>
       </c>
       <c r="B387" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C387" s="7">
-        <v>151040</v>
+        <v>1228060</v>
       </c>
       <c r="D387" s="7"/>
       <c r="E387" s="5"/>
     </row>
     <row r="388" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A388" s="6">
-        <v>45940</v>
+        <v>46243</v>
       </c>
       <c r="B388" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C388" s="7">
-        <v>91550</v>
+        <v>1093320</v>
       </c>
       <c r="D388" s="7"/>
       <c r="E388" s="5"/>
     </row>
     <row r="389" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A389" s="6">
-        <v>45941</v>
+        <v>46244</v>
       </c>
       <c r="B389" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C389" s="7">
-        <v>257130</v>
+        <v>1570110</v>
       </c>
       <c r="D389" s="7"/>
       <c r="E389" s="5"/>
     </row>
     <row r="390" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A390" s="6">
-        <v>45942</v>
+        <v>46245</v>
       </c>
       <c r="B390" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C390" s="7">
-        <v>100020</v>
+        <v>1547130</v>
       </c>
       <c r="D390" s="7"/>
       <c r="E390" s="5"/>
     </row>
     <row r="391" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A391" s="6">
-        <v>45943</v>
+        <v>46246</v>
       </c>
       <c r="B391" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C391" s="7">
-        <v>302750</v>
+        <v>1476040</v>
       </c>
       <c r="D391" s="7"/>
       <c r="E391" s="5"/>
     </row>
     <row r="392" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A392" s="6">
-        <v>45944</v>
+        <v>46247</v>
       </c>
       <c r="B392" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C392" s="7">
-        <v>19200</v>
+        <v>1127130</v>
       </c>
       <c r="D392" s="7"/>
       <c r="E392" s="5"/>
     </row>
     <row r="393" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A393" s="6">
-        <v>45945</v>
+        <v>46248</v>
       </c>
       <c r="B393" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C393" s="7">
-        <v>304860</v>
+        <v>1048500</v>
       </c>
       <c r="D393" s="7"/>
       <c r="E393" s="5"/>
     </row>
     <row r="394" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A394" s="6">
-        <v>45946</v>
+        <v>46249</v>
       </c>
       <c r="B394" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C394" s="7">
-        <v>183530</v>
+        <v>1036030</v>
       </c>
       <c r="D394" s="7"/>
       <c r="E394" s="5"/>
     </row>
     <row r="395" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A395" s="6">
-        <v>45947</v>
+        <v>46250</v>
       </c>
       <c r="B395" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C395" s="7">
-        <v>226720</v>
+        <v>1187540</v>
       </c>
       <c r="D395" s="7"/>
       <c r="E395" s="5"/>
     </row>
     <row r="396" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A396" s="6">
-        <v>45948</v>
+        <v>46251</v>
       </c>
       <c r="B396" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C396" s="7">
-        <v>243580</v>
+        <v>1147050</v>
       </c>
       <c r="D396" s="7"/>
       <c r="E396" s="5"/>
     </row>
     <row r="397" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A397" s="6">
-        <v>45949</v>
+        <v>46252</v>
       </c>
       <c r="B397" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C397" s="7">
-        <v>124270</v>
+        <v>1068720</v>
       </c>
       <c r="D397" s="7"/>
       <c r="E397" s="5"/>
     </row>
     <row r="398" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A398" s="6">
-        <v>45950</v>
+        <v>46253</v>
       </c>
       <c r="B398" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C398" s="7">
-        <v>305340</v>
+        <v>1136240</v>
       </c>
       <c r="D398" s="7"/>
       <c r="E398" s="5"/>
     </row>
     <row r="399" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A399" s="6">
-        <v>45951</v>
+        <v>46254</v>
       </c>
       <c r="B399" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C399" s="7">
-        <v>164440</v>
+        <v>1171640</v>
       </c>
       <c r="D399" s="7"/>
       <c r="E399" s="5"/>
     </row>
     <row r="400" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A400" s="6">
-        <v>45952</v>
+        <v>46255</v>
       </c>
       <c r="B400" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C400" s="7">
-        <v>298630</v>
+        <v>1082950</v>
       </c>
       <c r="D400" s="7"/>
       <c r="E400" s="5"/>
     </row>
     <row r="401" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A401" s="6">
-        <v>45953</v>
+        <v>46256</v>
       </c>
       <c r="B401" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C401" s="7">
-        <v>124770</v>
+        <v>957480</v>
       </c>
       <c r="D401" s="7"/>
       <c r="E401" s="5"/>
     </row>
     <row r="402" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A402" s="6">
-        <v>45954</v>
+        <v>46257</v>
       </c>
       <c r="B402" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C402" s="7">
-        <v>322480</v>
+        <v>986280</v>
       </c>
       <c r="D402" s="7"/>
       <c r="E402" s="5"/>
     </row>
     <row r="403" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A403" s="6">
-        <v>45955</v>
+        <v>46258</v>
       </c>
       <c r="B403" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C403" s="7">
-        <v>119920</v>
+        <v>1130890</v>
       </c>
       <c r="D403" s="7"/>
       <c r="E403" s="5"/>
     </row>
     <row r="404" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A404" s="6">
-        <v>45956</v>
+        <v>46259</v>
       </c>
       <c r="B404" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C404" s="7">
-        <v>54910</v>
+        <v>1229900</v>
       </c>
       <c r="D404" s="7"/>
       <c r="E404" s="5"/>
     </row>
     <row r="405" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A405" s="6">
-        <v>45957</v>
+        <v>46260</v>
       </c>
       <c r="B405" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C405" s="7">
-        <v>174580</v>
+        <v>1327380</v>
       </c>
       <c r="D405" s="7"/>
       <c r="E405" s="5"/>
     </row>
     <row r="406" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A406" s="6">
-        <v>45958</v>
+        <v>46261</v>
       </c>
       <c r="B406" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C406" s="7">
-        <v>169870</v>
+        <v>1141620</v>
       </c>
       <c r="D406" s="7"/>
       <c r="E406" s="5"/>
     </row>
     <row r="407" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A407" s="6">
-        <v>45959</v>
+        <v>46262</v>
       </c>
       <c r="B407" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C407" s="7">
-        <v>285820</v>
+        <v>1134920</v>
       </c>
       <c r="D407" s="7"/>
       <c r="E407" s="5"/>
     </row>
     <row r="408" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A408" s="6">
-        <v>45960</v>
+        <v>46263</v>
       </c>
       <c r="B408" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C408" s="7">
-        <v>95860</v>
+        <v>1360250</v>
       </c>
       <c r="D408" s="7"/>
       <c r="E408" s="5"/>
     </row>
     <row r="409" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A409" s="6">
-        <v>45961</v>
+        <v>46264</v>
       </c>
       <c r="B409" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C409" s="7">
-        <v>299210</v>
+        <v>1351580</v>
       </c>
       <c r="D409" s="7"/>
       <c r="E409" s="5"/>
     </row>
     <row r="410" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A410" s="6"/>
-      <c r="B410" s="5"/>
-      <c r="C410" s="7"/>
+      <c r="A410" s="6">
+        <v>46265</v>
+      </c>
+      <c r="B410" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C410" s="7">
+        <v>1164740</v>
+      </c>
       <c r="D410" s="7"/>
       <c r="E410" s="5"/>
     </row>
     <row r="411" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A411" s="6">
-        <v>45962</v>
-      </c>
-      <c r="B411" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C411" s="7">
-        <v>156540</v>
-      </c>
+      <c r="A411" s="6"/>
+      <c r="B411" s="5"/>
+      <c r="C411" s="7"/>
       <c r="D411" s="7"/>
       <c r="E411" s="5"/>
     </row>
     <row r="412" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A412" s="6">
-        <v>45963</v>
+        <v>45870</v>
       </c>
       <c r="B412" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C412" s="7">
-        <v>86300</v>
+        <v>167220</v>
       </c>
       <c r="D412" s="7"/>
       <c r="E412" s="5"/>
     </row>
     <row r="413" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A413" s="6">
-        <v>45964</v>
+        <v>45871</v>
       </c>
       <c r="B413" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C413" s="7">
-        <v>243260</v>
+        <v>350380</v>
       </c>
       <c r="D413" s="7"/>
       <c r="E413" s="5"/>
     </row>
     <row r="414" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A414" s="6">
-        <v>45965</v>
+        <v>45872</v>
       </c>
       <c r="B414" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C414" s="7">
-        <v>137780</v>
+        <v>346970</v>
       </c>
       <c r="D414" s="7"/>
       <c r="E414" s="5"/>
     </row>
     <row r="415" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A415" s="6">
-        <v>45966</v>
+        <v>45873</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C415" s="7">
-        <v>295550</v>
+        <v>143340</v>
       </c>
       <c r="D415" s="7"/>
       <c r="E415" s="5"/>
     </row>
     <row r="416" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A416" s="6">
-        <v>45967</v>
+        <v>45874</v>
       </c>
       <c r="B416" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C416" s="7">
-        <v>69600</v>
+        <v>132060</v>
       </c>
       <c r="D416" s="7"/>
       <c r="E416" s="5"/>
     </row>
     <row r="417" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A417" s="6">
-        <v>45968</v>
+        <v>45875</v>
       </c>
       <c r="B417" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C417" s="7">
-        <v>277840</v>
+        <v>629120</v>
       </c>
       <c r="D417" s="7"/>
       <c r="E417" s="5"/>
     </row>
     <row r="418" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A418" s="6">
-        <v>45969</v>
+        <v>45876</v>
       </c>
       <c r="B418" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C418" s="7">
-        <v>149140</v>
+        <v>218300</v>
       </c>
       <c r="D418" s="7"/>
       <c r="E418" s="5"/>
     </row>
     <row r="419" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A419" s="6">
-        <v>45970</v>
+        <v>45877</v>
       </c>
       <c r="B419" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C419" s="7">
-        <v>92820</v>
+        <v>428020</v>
       </c>
       <c r="D419" s="7"/>
       <c r="E419" s="5"/>
     </row>
     <row r="420" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A420" s="6">
-        <v>45971</v>
+        <v>45878</v>
       </c>
       <c r="B420" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C420" s="7">
-        <v>307960</v>
+        <v>232460</v>
       </c>
       <c r="D420" s="7"/>
       <c r="E420" s="5"/>
     </row>
     <row r="421" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A421" s="6">
-        <v>45972</v>
+        <v>45879</v>
       </c>
       <c r="B421" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C421" s="7">
-        <v>140610</v>
+        <v>231720</v>
       </c>
       <c r="D421" s="7"/>
       <c r="E421" s="5"/>
     </row>
     <row r="422" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A422" s="6">
-        <v>45973</v>
+        <v>45880</v>
       </c>
       <c r="B422" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C422" s="7">
-        <v>342970</v>
+        <v>495660</v>
       </c>
       <c r="D422" s="7"/>
       <c r="E422" s="5"/>
     </row>
     <row r="423" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A423" s="6">
-        <v>45974</v>
+        <v>45881</v>
       </c>
       <c r="B423" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C423" s="7">
-        <v>76850</v>
+        <v>265910</v>
       </c>
       <c r="D423" s="7"/>
       <c r="E423" s="5"/>
     </row>
     <row r="424" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A424" s="6">
-        <v>45975</v>
+        <v>45882</v>
       </c>
       <c r="B424" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C424" s="7">
-        <v>267000</v>
+        <v>291880</v>
       </c>
       <c r="D424" s="7"/>
       <c r="E424" s="5"/>
     </row>
     <row r="425" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A425" s="6">
-        <v>45976</v>
+        <v>45883</v>
       </c>
       <c r="B425" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C425" s="7">
-        <v>102640</v>
+        <v>239340</v>
       </c>
       <c r="D425" s="7"/>
       <c r="E425" s="5"/>
     </row>
     <row r="426" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A426" s="6">
-        <v>45977</v>
+        <v>45884</v>
       </c>
       <c r="B426" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C426" s="7">
-        <v>157870</v>
+        <v>362550</v>
       </c>
       <c r="D426" s="7"/>
       <c r="E426" s="5"/>
     </row>
     <row r="427" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A427" s="6">
-        <v>45978</v>
+        <v>45885</v>
       </c>
       <c r="B427" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C427" s="7">
-        <v>232460</v>
+        <v>242910</v>
       </c>
       <c r="D427" s="7"/>
       <c r="E427" s="5"/>
     </row>
     <row r="428" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A428" s="6">
-        <v>45979</v>
+        <v>45886</v>
       </c>
       <c r="B428" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C428" s="7">
-        <v>144140</v>
+        <v>81400</v>
       </c>
       <c r="D428" s="7"/>
       <c r="E428" s="5"/>
     </row>
     <row r="429" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A429" s="6">
-        <v>45980</v>
+        <v>45887</v>
       </c>
       <c r="B429" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C429" s="7">
-        <v>254720</v>
+        <v>319750</v>
       </c>
       <c r="D429" s="7"/>
       <c r="E429" s="5"/>
     </row>
     <row r="430" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A430" s="6">
-        <v>45981</v>
+        <v>45888</v>
       </c>
       <c r="B430" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C430" s="7">
-        <v>185740</v>
+        <v>419530</v>
       </c>
       <c r="D430" s="7"/>
       <c r="E430" s="5"/>
     </row>
     <row r="431" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A431" s="6">
-        <v>45982</v>
+        <v>45889</v>
       </c>
       <c r="B431" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C431" s="7">
-        <v>441520</v>
+        <v>329950</v>
       </c>
       <c r="D431" s="7"/>
       <c r="E431" s="5"/>
     </row>
     <row r="432" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A432" s="6">
-        <v>45983</v>
+        <v>45890</v>
       </c>
       <c r="B432" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C432" s="7">
-        <v>126440</v>
+        <v>170250</v>
       </c>
       <c r="D432" s="7"/>
       <c r="E432" s="5"/>
     </row>
     <row r="433" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A433" s="6">
-        <v>45984</v>
+        <v>45891</v>
       </c>
       <c r="B433" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C433" s="7">
-        <v>219280</v>
+        <v>425050</v>
       </c>
       <c r="D433" s="7"/>
       <c r="E433" s="5"/>
     </row>
     <row r="434" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A434" s="6">
-        <v>45985</v>
+        <v>45892</v>
       </c>
       <c r="B434" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C434" s="7">
-        <v>299150</v>
+        <v>150670</v>
       </c>
       <c r="D434" s="7"/>
       <c r="E434" s="5"/>
     </row>
     <row r="435" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A435" s="6">
-        <v>45986</v>
+        <v>45893</v>
       </c>
       <c r="B435" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C435" s="7">
-        <v>178920</v>
+        <v>128730</v>
       </c>
       <c r="D435" s="7"/>
       <c r="E435" s="5"/>
     </row>
     <row r="436" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A436" s="6">
-        <v>45987</v>
+        <v>45894</v>
       </c>
       <c r="B436" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C436" s="7">
-        <v>193500</v>
+        <v>377400</v>
       </c>
       <c r="D436" s="7"/>
       <c r="E436" s="5"/>
     </row>
     <row r="437" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A437" s="6">
-        <v>45988</v>
+        <v>45895</v>
       </c>
       <c r="B437" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C437" s="7">
-        <v>169700</v>
+        <v>74620</v>
       </c>
       <c r="D437" s="7"/>
       <c r="E437" s="5"/>
     </row>
     <row r="438" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A438" s="6">
-        <v>45989</v>
+        <v>45896</v>
       </c>
       <c r="B438" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C438" s="7">
-        <v>146540</v>
+        <v>391520</v>
       </c>
       <c r="D438" s="7"/>
       <c r="E438" s="5"/>
     </row>
     <row r="439" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A439" s="6">
-        <v>45990</v>
+        <v>45897</v>
       </c>
       <c r="B439" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C439" s="7">
-        <v>82540</v>
+        <v>158820</v>
       </c>
       <c r="D439" s="7"/>
       <c r="E439" s="5"/>
     </row>
     <row r="440" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A440" s="6">
-        <v>45991</v>
+        <v>45898</v>
       </c>
       <c r="B440" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C440" s="7">
-        <v>98580</v>
+        <v>360880</v>
       </c>
       <c r="D440" s="7"/>
       <c r="E440" s="5"/>
     </row>
     <row r="441" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A441" s="6"/>
-      <c r="B441" s="5"/>
-      <c r="C441" s="7"/>
+      <c r="A441" s="6">
+        <v>45899</v>
+      </c>
+      <c r="B441" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C441" s="7">
+        <v>100140</v>
+      </c>
       <c r="D441" s="7"/>
       <c r="E441" s="5"/>
     </row>
     <row r="442" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A442" s="6">
-        <v>45992</v>
+        <v>45900</v>
       </c>
       <c r="B442" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C442" s="7">
-        <v>155060</v>
+        <v>243510</v>
       </c>
       <c r="D442" s="7"/>
       <c r="E442" s="5"/>
     </row>
     <row r="443" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A443" s="6">
-        <v>45993</v>
-      </c>
-      <c r="B443" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C443" s="7">
-        <v>619638</v>
-      </c>
+      <c r="A443" s="6"/>
+      <c r="B443" s="5"/>
+      <c r="C443" s="7"/>
       <c r="D443" s="7"/>
       <c r="E443" s="5"/>
     </row>
     <row r="444" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A444" s="6">
-        <v>45994</v>
+        <v>45901</v>
       </c>
       <c r="B444" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C444" s="7">
-        <v>132380</v>
+        <v>176920</v>
       </c>
       <c r="D444" s="7"/>
       <c r="E444" s="5"/>
     </row>
     <row r="445" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A445" s="6">
-        <v>45995</v>
+        <v>45902</v>
       </c>
       <c r="B445" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C445" s="7">
-        <v>373160</v>
+        <v>161250</v>
       </c>
       <c r="D445" s="7"/>
       <c r="E445" s="5"/>
     </row>
     <row r="446" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A446" s="6">
-        <v>45996</v>
+        <v>45903</v>
       </c>
       <c r="B446" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C446" s="7">
-        <v>527060</v>
+        <v>333640</v>
       </c>
       <c r="D446" s="7"/>
       <c r="E446" s="5"/>
     </row>
     <row r="447" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A447" s="6">
-        <v>45997</v>
+        <v>45904</v>
       </c>
       <c r="B447" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C447" s="7">
-        <v>99160</v>
+        <v>145410</v>
       </c>
       <c r="D447" s="7"/>
       <c r="E447" s="5"/>
     </row>
     <row r="448" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A448" s="6">
-        <v>45998</v>
+        <v>45905</v>
       </c>
       <c r="B448" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C448" s="7">
-        <v>33880</v>
+        <v>419600</v>
       </c>
       <c r="D448" s="7"/>
       <c r="E448" s="5"/>
     </row>
     <row r="449" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A449" s="6">
-        <v>45999</v>
+        <v>45906</v>
       </c>
       <c r="B449" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C449" s="7">
-        <v>152160</v>
+        <v>78240</v>
       </c>
       <c r="D449" s="7"/>
       <c r="E449" s="5"/>
     </row>
     <row r="450" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A450" s="6">
-        <v>46000</v>
+        <v>45907</v>
       </c>
       <c r="B450" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C450" s="7">
-        <v>293050</v>
+        <v>68180</v>
       </c>
       <c r="D450" s="7"/>
       <c r="E450" s="5"/>
     </row>
     <row r="451" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A451" s="6">
-        <v>46001</v>
+        <v>45908</v>
       </c>
       <c r="B451" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C451" s="7">
-        <v>204900</v>
+        <v>322410</v>
       </c>
       <c r="D451" s="7"/>
       <c r="E451" s="5"/>
     </row>
     <row r="452" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A452" s="6">
-        <v>46002</v>
+        <v>45909</v>
       </c>
       <c r="B452" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C452" s="7">
-        <v>569102</v>
+        <v>72270</v>
       </c>
       <c r="D452" s="7"/>
       <c r="E452" s="5"/>
     </row>
     <row r="453" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A453" s="6">
-        <v>46003</v>
+        <v>45910</v>
       </c>
       <c r="B453" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C453" s="7">
-        <v>362904</v>
+        <v>350500</v>
       </c>
       <c r="D453" s="7"/>
       <c r="E453" s="5"/>
     </row>
     <row r="454" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A454" s="6">
-        <v>46004</v>
+        <v>45911</v>
       </c>
       <c r="B454" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C454" s="7">
-        <v>200280</v>
+        <v>132330</v>
       </c>
       <c r="D454" s="7"/>
       <c r="E454" s="5"/>
     </row>
     <row r="455" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A455" s="6">
-        <v>46005</v>
+        <v>45912</v>
       </c>
       <c r="B455" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C455" s="7">
-        <v>56458</v>
+        <v>282820</v>
       </c>
       <c r="D455" s="7"/>
       <c r="E455" s="5"/>
     </row>
     <row r="456" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A456" s="6">
-        <v>46006</v>
+        <v>45913</v>
       </c>
       <c r="B456" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C456" s="7">
-        <v>440040</v>
+        <v>140280</v>
       </c>
       <c r="D456" s="7"/>
       <c r="E456" s="5"/>
     </row>
     <row r="457" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A457" s="6">
-        <v>46007</v>
+        <v>45914</v>
       </c>
       <c r="B457" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C457" s="7">
-        <v>317760</v>
+        <v>81480</v>
       </c>
       <c r="D457" s="7"/>
       <c r="E457" s="5"/>
     </row>
     <row r="458" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A458" s="6">
-        <v>46008</v>
+        <v>45915</v>
       </c>
       <c r="B458" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C458" s="7">
-        <v>222876</v>
+        <v>185160</v>
       </c>
       <c r="D458" s="7"/>
       <c r="E458" s="5"/>
     </row>
     <row r="459" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A459" s="6">
-        <v>46009</v>
+        <v>45916</v>
       </c>
       <c r="B459" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C459" s="7">
-        <v>249580</v>
+        <v>92420</v>
       </c>
       <c r="D459" s="7"/>
       <c r="E459" s="5"/>
     </row>
     <row r="460" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A460" s="6">
-        <v>46010</v>
+        <v>45917</v>
       </c>
       <c r="B460" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C460" s="7">
-        <v>483230</v>
+        <v>200030</v>
       </c>
       <c r="D460" s="7"/>
       <c r="E460" s="5"/>
     </row>
     <row r="461" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A461" s="6">
-        <v>46011</v>
+        <v>45918</v>
       </c>
       <c r="B461" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C461" s="7">
-        <v>464008</v>
+        <v>109950</v>
       </c>
       <c r="D461" s="7"/>
       <c r="E461" s="5"/>
     </row>
     <row r="462" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A462" s="6">
-        <v>46012</v>
+        <v>45919</v>
       </c>
       <c r="B462" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C462" s="7">
-        <v>363418</v>
+        <v>317560</v>
       </c>
       <c r="D462" s="7"/>
       <c r="E462" s="5"/>
     </row>
     <row r="463" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A463" s="6">
-        <v>46013</v>
+        <v>45920</v>
       </c>
       <c r="B463" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C463" s="7">
-        <v>218138</v>
+        <v>136720</v>
       </c>
       <c r="D463" s="7"/>
       <c r="E463" s="5"/>
     </row>
     <row r="464" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A464" s="6">
-        <v>46014</v>
+        <v>45921</v>
       </c>
       <c r="B464" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C464" s="7">
-        <v>202640</v>
+        <v>84350</v>
       </c>
       <c r="D464" s="7"/>
       <c r="E464" s="5"/>
     </row>
     <row r="465" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A465" s="6">
-        <v>46015</v>
+        <v>45922</v>
       </c>
       <c r="B465" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C465" s="7">
-        <v>283540</v>
+        <v>367710</v>
       </c>
       <c r="D465" s="7"/>
       <c r="E465" s="5"/>
     </row>
     <row r="466" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A466" s="6">
-        <v>46016</v>
+        <v>45923</v>
       </c>
       <c r="B466" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C466" s="7">
-        <v>250380</v>
+        <v>180390</v>
       </c>
       <c r="D466" s="7"/>
       <c r="E466" s="5"/>
     </row>
     <row r="467" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A467" s="6">
-        <v>46017</v>
+        <v>45924</v>
       </c>
       <c r="B467" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C467" s="7">
-        <v>633928</v>
+        <v>233430</v>
       </c>
       <c r="D467" s="7"/>
       <c r="E467" s="5"/>
     </row>
     <row r="468" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A468" s="6">
-        <v>46018</v>
+        <v>45925</v>
       </c>
       <c r="B468" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C468" s="7">
-        <v>858218</v>
+        <v>409620</v>
       </c>
       <c r="D468" s="7"/>
       <c r="E468" s="5"/>
     </row>
     <row r="469" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A469" s="6">
-        <v>46019</v>
+        <v>45926</v>
       </c>
       <c r="B469" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C469" s="7">
-        <v>362272</v>
+        <v>343820</v>
       </c>
       <c r="D469" s="7"/>
       <c r="E469" s="5"/>
     </row>
     <row r="470" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A470" s="6">
-        <v>46020</v>
+        <v>45927</v>
       </c>
       <c r="B470" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C470" s="7">
-        <v>531110</v>
+        <v>1077030</v>
       </c>
       <c r="D470" s="7"/>
       <c r="E470" s="5"/>
     </row>
     <row r="471" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A471" s="6">
-        <v>46021</v>
+        <v>45928</v>
       </c>
       <c r="B471" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C471" s="7">
-        <v>240494</v>
+        <v>67140</v>
       </c>
       <c r="D471" s="7"/>
       <c r="E471" s="5"/>
     </row>
     <row r="472" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A472" s="6">
-        <v>46022</v>
+        <v>45929</v>
       </c>
       <c r="B472" s="5" t="s">
         <v>46</v>
       </c>
       <c r="C472" s="7">
-        <v>365244</v>
+        <v>2051880</v>
       </c>
       <c r="D472" s="7"/>
       <c r="E472" s="5"/>
     </row>
     <row r="473" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A473" s="6"/>
-      <c r="B473" s="5"/>
-      <c r="C473" s="7"/>
+      <c r="A473" s="6">
+        <v>45930</v>
+      </c>
+      <c r="B473" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C473" s="7">
+        <v>1105220</v>
+      </c>
       <c r="D473" s="7"/>
       <c r="E473" s="5"/>
     </row>
@@ -6995,219 +6587,405 @@
       <c r="E474" s="5"/>
     </row>
     <row r="475" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A475" s="6"/>
-      <c r="B475" s="5"/>
-      <c r="C475" s="7"/>
+      <c r="A475" s="6">
+        <v>45931</v>
+      </c>
+      <c r="B475" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C475" s="7">
+        <v>1989180</v>
+      </c>
       <c r="D475" s="7"/>
       <c r="E475" s="5"/>
     </row>
     <row r="476" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A476" s="6"/>
-      <c r="B476" s="5"/>
-      <c r="C476" s="7"/>
+      <c r="A476" s="6">
+        <v>45932</v>
+      </c>
+      <c r="B476" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C476" s="7">
+        <v>4134460</v>
+      </c>
       <c r="D476" s="7"/>
       <c r="E476" s="5"/>
     </row>
     <row r="477" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A477" s="6"/>
-      <c r="B477" s="5"/>
-      <c r="C477" s="7"/>
+      <c r="A477" s="6">
+        <v>45933</v>
+      </c>
+      <c r="B477" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C477" s="7">
+        <v>345820</v>
+      </c>
       <c r="D477" s="7"/>
       <c r="E477" s="5"/>
     </row>
     <row r="478" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A478" s="6"/>
-      <c r="B478" s="5"/>
-      <c r="C478" s="7"/>
+      <c r="A478" s="6">
+        <v>45934</v>
+      </c>
+      <c r="B478" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C478" s="7">
+        <v>570800</v>
+      </c>
       <c r="D478" s="7"/>
       <c r="E478" s="5"/>
     </row>
     <row r="479" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A479" s="6"/>
-      <c r="B479" s="5"/>
-      <c r="C479" s="7"/>
+      <c r="A479" s="6">
+        <v>45935</v>
+      </c>
+      <c r="B479" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C479" s="7">
+        <v>103870</v>
+      </c>
       <c r="D479" s="7"/>
       <c r="E479" s="5"/>
     </row>
     <row r="480" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A480" s="6"/>
-      <c r="B480" s="5"/>
-      <c r="C480" s="7"/>
+      <c r="A480" s="6">
+        <v>45936</v>
+      </c>
+      <c r="B480" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C480" s="7">
+        <v>162140</v>
+      </c>
       <c r="D480" s="7"/>
       <c r="E480" s="5"/>
     </row>
     <row r="481" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A481" s="6"/>
-      <c r="B481" s="5"/>
-      <c r="C481" s="7"/>
+      <c r="A481" s="6">
+        <v>45937</v>
+      </c>
+      <c r="B481" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C481" s="7">
+        <v>328620</v>
+      </c>
       <c r="D481" s="7"/>
       <c r="E481" s="5"/>
     </row>
     <row r="482" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A482" s="6"/>
-      <c r="B482" s="5"/>
-      <c r="C482" s="7"/>
+      <c r="A482" s="6">
+        <v>45938</v>
+      </c>
+      <c r="B482" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C482" s="7">
+        <v>262770</v>
+      </c>
       <c r="D482" s="7"/>
       <c r="E482" s="5"/>
     </row>
     <row r="483" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A483" s="6"/>
-      <c r="B483" s="5"/>
-      <c r="C483" s="7"/>
+      <c r="A483" s="6">
+        <v>45939</v>
+      </c>
+      <c r="B483" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C483" s="7">
+        <v>151040</v>
+      </c>
       <c r="D483" s="7"/>
       <c r="E483" s="5"/>
     </row>
     <row r="484" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A484" s="6"/>
-      <c r="B484" s="5"/>
-      <c r="C484" s="7"/>
+      <c r="A484" s="6">
+        <v>45940</v>
+      </c>
+      <c r="B484" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C484" s="7">
+        <v>91550</v>
+      </c>
       <c r="D484" s="7"/>
       <c r="E484" s="5"/>
     </row>
     <row r="485" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A485" s="6"/>
-      <c r="B485" s="5"/>
-      <c r="C485" s="7"/>
+      <c r="A485" s="6">
+        <v>45941</v>
+      </c>
+      <c r="B485" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C485" s="7">
+        <v>257130</v>
+      </c>
       <c r="D485" s="7"/>
       <c r="E485" s="5"/>
     </row>
     <row r="486" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A486" s="6"/>
-      <c r="B486" s="5"/>
-      <c r="C486" s="7"/>
+      <c r="A486" s="6">
+        <v>45942</v>
+      </c>
+      <c r="B486" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C486" s="7">
+        <v>100020</v>
+      </c>
       <c r="D486" s="7"/>
       <c r="E486" s="5"/>
     </row>
     <row r="487" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A487" s="6"/>
-      <c r="B487" s="5"/>
-      <c r="C487" s="7"/>
+      <c r="A487" s="6">
+        <v>45943</v>
+      </c>
+      <c r="B487" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C487" s="7">
+        <v>302750</v>
+      </c>
       <c r="D487" s="7"/>
       <c r="E487" s="5"/>
     </row>
     <row r="488" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A488" s="6"/>
-      <c r="B488" s="5"/>
-      <c r="C488" s="7"/>
+      <c r="A488" s="6">
+        <v>45944</v>
+      </c>
+      <c r="B488" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C488" s="7">
+        <v>19200</v>
+      </c>
       <c r="D488" s="7"/>
       <c r="E488" s="5"/>
     </row>
     <row r="489" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A489" s="6"/>
-      <c r="B489" s="5"/>
-      <c r="C489" s="7"/>
+      <c r="A489" s="6">
+        <v>45945</v>
+      </c>
+      <c r="B489" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C489" s="7">
+        <v>304860</v>
+      </c>
       <c r="D489" s="7"/>
       <c r="E489" s="5"/>
     </row>
     <row r="490" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A490" s="6"/>
-      <c r="B490" s="5"/>
-      <c r="C490" s="7"/>
+      <c r="A490" s="6">
+        <v>45946</v>
+      </c>
+      <c r="B490" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C490" s="7">
+        <v>183530</v>
+      </c>
       <c r="D490" s="7"/>
       <c r="E490" s="5"/>
     </row>
     <row r="491" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A491" s="6"/>
-      <c r="B491" s="5"/>
-      <c r="C491" s="7"/>
+      <c r="A491" s="6">
+        <v>45947</v>
+      </c>
+      <c r="B491" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C491" s="7">
+        <v>226720</v>
+      </c>
       <c r="D491" s="7"/>
       <c r="E491" s="5"/>
     </row>
     <row r="492" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A492" s="6"/>
-      <c r="B492" s="5"/>
-      <c r="C492" s="7"/>
+      <c r="A492" s="6">
+        <v>45948</v>
+      </c>
+      <c r="B492" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C492" s="7">
+        <v>243580</v>
+      </c>
       <c r="D492" s="7"/>
       <c r="E492" s="5"/>
     </row>
     <row r="493" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A493" s="6"/>
-      <c r="B493" s="5"/>
-      <c r="C493" s="7"/>
+      <c r="A493" s="6">
+        <v>45949</v>
+      </c>
+      <c r="B493" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C493" s="7">
+        <v>124270</v>
+      </c>
       <c r="D493" s="7"/>
       <c r="E493" s="5"/>
     </row>
     <row r="494" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A494" s="6"/>
-      <c r="B494" s="5"/>
-      <c r="C494" s="7"/>
+      <c r="A494" s="6">
+        <v>45950</v>
+      </c>
+      <c r="B494" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C494" s="7">
+        <v>305340</v>
+      </c>
       <c r="D494" s="7"/>
       <c r="E494" s="5"/>
     </row>
     <row r="495" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A495" s="6"/>
-      <c r="B495" s="5"/>
-      <c r="C495" s="7"/>
+      <c r="A495" s="6">
+        <v>45951</v>
+      </c>
+      <c r="B495" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C495" s="7">
+        <v>164440</v>
+      </c>
       <c r="D495" s="7"/>
       <c r="E495" s="5"/>
     </row>
     <row r="496" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A496" s="6"/>
-      <c r="B496" s="5"/>
-      <c r="C496" s="7"/>
+      <c r="A496" s="6">
+        <v>45952</v>
+      </c>
+      <c r="B496" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C496" s="7">
+        <v>298630</v>
+      </c>
       <c r="D496" s="7"/>
       <c r="E496" s="5"/>
     </row>
     <row r="497" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A497" s="6"/>
-      <c r="B497" s="5"/>
-      <c r="C497" s="7"/>
+      <c r="A497" s="6">
+        <v>45953</v>
+      </c>
+      <c r="B497" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C497" s="7">
+        <v>124770</v>
+      </c>
       <c r="D497" s="7"/>
       <c r="E497" s="5"/>
     </row>
     <row r="498" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A498" s="6"/>
-      <c r="B498" s="5"/>
-      <c r="C498" s="7"/>
+      <c r="A498" s="6">
+        <v>45954</v>
+      </c>
+      <c r="B498" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C498" s="7">
+        <v>322480</v>
+      </c>
       <c r="D498" s="7"/>
       <c r="E498" s="5"/>
     </row>
     <row r="499" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A499" s="6"/>
-      <c r="B499" s="5"/>
-      <c r="C499" s="7"/>
+      <c r="A499" s="6">
+        <v>45955</v>
+      </c>
+      <c r="B499" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C499" s="7">
+        <v>119920</v>
+      </c>
       <c r="D499" s="7"/>
       <c r="E499" s="5"/>
     </row>
     <row r="500" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A500" s="6"/>
-      <c r="B500" s="5"/>
-      <c r="C500" s="7"/>
+      <c r="A500" s="6">
+        <v>45956</v>
+      </c>
+      <c r="B500" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C500" s="7">
+        <v>54910</v>
+      </c>
       <c r="D500" s="7"/>
       <c r="E500" s="5"/>
     </row>
     <row r="501" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A501" s="6"/>
-      <c r="B501" s="5"/>
-      <c r="C501" s="7"/>
+      <c r="A501" s="6">
+        <v>45957</v>
+      </c>
+      <c r="B501" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C501" s="7">
+        <v>174580</v>
+      </c>
       <c r="D501" s="7"/>
       <c r="E501" s="5"/>
     </row>
     <row r="502" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A502" s="6"/>
-      <c r="B502" s="5"/>
-      <c r="C502" s="7"/>
+      <c r="A502" s="6">
+        <v>45958</v>
+      </c>
+      <c r="B502" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C502" s="7">
+        <v>169870</v>
+      </c>
       <c r="D502" s="7"/>
       <c r="E502" s="5"/>
     </row>
     <row r="503" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A503" s="6"/>
-      <c r="B503" s="5"/>
-      <c r="C503" s="7"/>
+      <c r="A503" s="6">
+        <v>45959</v>
+      </c>
+      <c r="B503" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C503" s="7">
+        <v>285820</v>
+      </c>
       <c r="D503" s="7"/>
       <c r="E503" s="5"/>
     </row>
     <row r="504" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A504" s="6"/>
-      <c r="B504" s="5"/>
-      <c r="C504" s="7"/>
+      <c r="A504" s="6">
+        <v>45960</v>
+      </c>
+      <c r="B504" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C504" s="7">
+        <v>95860</v>
+      </c>
       <c r="D504" s="7"/>
       <c r="E504" s="5"/>
     </row>
     <row r="505" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A505" s="6"/>
-      <c r="B505" s="5"/>
-      <c r="C505" s="7"/>
+      <c r="A505" s="6">
+        <v>45961</v>
+      </c>
+      <c r="B505" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C505" s="7">
+        <v>299210</v>
+      </c>
       <c r="D505" s="7"/>
       <c r="E505" s="5"/>
     </row>
@@ -7219,212 +6997,392 @@
       <c r="E506" s="5"/>
     </row>
     <row r="507" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A507" s="6"/>
-      <c r="B507" s="5"/>
-      <c r="C507" s="7"/>
+      <c r="A507" s="6">
+        <v>45962</v>
+      </c>
+      <c r="B507" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C507" s="7">
+        <v>156540</v>
+      </c>
       <c r="D507" s="7"/>
       <c r="E507" s="5"/>
     </row>
     <row r="508" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A508" s="6"/>
-      <c r="B508" s="5"/>
-      <c r="C508" s="7"/>
+      <c r="A508" s="6">
+        <v>45963</v>
+      </c>
+      <c r="B508" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C508" s="7">
+        <v>86300</v>
+      </c>
       <c r="D508" s="7"/>
       <c r="E508" s="5"/>
     </row>
     <row r="509" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A509" s="6"/>
-      <c r="B509" s="5"/>
-      <c r="C509" s="7"/>
+      <c r="A509" s="6">
+        <v>45964</v>
+      </c>
+      <c r="B509" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C509" s="7">
+        <v>243260</v>
+      </c>
       <c r="D509" s="7"/>
       <c r="E509" s="5"/>
     </row>
     <row r="510" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A510" s="6"/>
-      <c r="B510" s="5"/>
-      <c r="C510" s="7"/>
+      <c r="A510" s="6">
+        <v>45965</v>
+      </c>
+      <c r="B510" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C510" s="7">
+        <v>137780</v>
+      </c>
       <c r="D510" s="7"/>
       <c r="E510" s="5"/>
     </row>
     <row r="511" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A511" s="6"/>
-      <c r="B511" s="5"/>
-      <c r="C511" s="7"/>
+      <c r="A511" s="6">
+        <v>45966</v>
+      </c>
+      <c r="B511" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C511" s="7">
+        <v>295550</v>
+      </c>
       <c r="D511" s="7"/>
       <c r="E511" s="5"/>
     </row>
     <row r="512" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A512" s="6"/>
-      <c r="B512" s="5"/>
-      <c r="C512" s="7"/>
+      <c r="A512" s="6">
+        <v>45967</v>
+      </c>
+      <c r="B512" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C512" s="7">
+        <v>69600</v>
+      </c>
       <c r="D512" s="7"/>
       <c r="E512" s="5"/>
     </row>
     <row r="513" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A513" s="6"/>
-      <c r="B513" s="5"/>
-      <c r="C513" s="7"/>
+      <c r="A513" s="6">
+        <v>45968</v>
+      </c>
+      <c r="B513" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C513" s="7">
+        <v>277840</v>
+      </c>
       <c r="D513" s="7"/>
       <c r="E513" s="5"/>
     </row>
     <row r="514" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A514" s="6"/>
-      <c r="B514" s="5"/>
-      <c r="C514" s="7"/>
+      <c r="A514" s="6">
+        <v>45969</v>
+      </c>
+      <c r="B514" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C514" s="7">
+        <v>149140</v>
+      </c>
       <c r="D514" s="7"/>
       <c r="E514" s="5"/>
     </row>
     <row r="515" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A515" s="6"/>
-      <c r="B515" s="5"/>
-      <c r="C515" s="7"/>
+      <c r="A515" s="6">
+        <v>45970</v>
+      </c>
+      <c r="B515" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C515" s="7">
+        <v>92820</v>
+      </c>
       <c r="D515" s="7"/>
       <c r="E515" s="5"/>
     </row>
     <row r="516" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A516" s="6"/>
-      <c r="B516" s="5"/>
-      <c r="C516" s="7"/>
+      <c r="A516" s="6">
+        <v>45971</v>
+      </c>
+      <c r="B516" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C516" s="7">
+        <v>307960</v>
+      </c>
       <c r="D516" s="7"/>
       <c r="E516" s="5"/>
     </row>
     <row r="517" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A517" s="6"/>
-      <c r="B517" s="5"/>
-      <c r="C517" s="7"/>
+      <c r="A517" s="6">
+        <v>45972</v>
+      </c>
+      <c r="B517" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C517" s="7">
+        <v>140610</v>
+      </c>
       <c r="D517" s="7"/>
       <c r="E517" s="5"/>
     </row>
     <row r="518" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A518" s="6"/>
-      <c r="B518" s="5"/>
-      <c r="C518" s="7"/>
+      <c r="A518" s="6">
+        <v>45973</v>
+      </c>
+      <c r="B518" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C518" s="7">
+        <v>342970</v>
+      </c>
       <c r="D518" s="7"/>
       <c r="E518" s="5"/>
     </row>
     <row r="519" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A519" s="6"/>
-      <c r="B519" s="5"/>
-      <c r="C519" s="7"/>
+      <c r="A519" s="6">
+        <v>45974</v>
+      </c>
+      <c r="B519" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C519" s="7">
+        <v>76850</v>
+      </c>
       <c r="D519" s="7"/>
       <c r="E519" s="5"/>
     </row>
     <row r="520" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A520" s="6"/>
-      <c r="B520" s="5"/>
-      <c r="C520" s="7"/>
+      <c r="A520" s="6">
+        <v>45975</v>
+      </c>
+      <c r="B520" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C520" s="7">
+        <v>267000</v>
+      </c>
       <c r="D520" s="7"/>
       <c r="E520" s="5"/>
     </row>
     <row r="521" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A521" s="6"/>
-      <c r="B521" s="5"/>
-      <c r="C521" s="7"/>
+      <c r="A521" s="6">
+        <v>45976</v>
+      </c>
+      <c r="B521" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C521" s="7">
+        <v>102640</v>
+      </c>
       <c r="D521" s="7"/>
       <c r="E521" s="5"/>
     </row>
     <row r="522" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A522" s="6"/>
-      <c r="B522" s="5"/>
-      <c r="C522" s="7"/>
+      <c r="A522" s="6">
+        <v>45977</v>
+      </c>
+      <c r="B522" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C522" s="7">
+        <v>157870</v>
+      </c>
       <c r="D522" s="7"/>
       <c r="E522" s="5"/>
     </row>
     <row r="523" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A523" s="6"/>
-      <c r="B523" s="5"/>
-      <c r="C523" s="7"/>
+      <c r="A523" s="6">
+        <v>45978</v>
+      </c>
+      <c r="B523" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C523" s="7">
+        <v>232460</v>
+      </c>
       <c r="D523" s="7"/>
       <c r="E523" s="5"/>
     </row>
     <row r="524" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A524" s="6"/>
-      <c r="B524" s="5"/>
-      <c r="C524" s="7"/>
+      <c r="A524" s="6">
+        <v>45979</v>
+      </c>
+      <c r="B524" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C524" s="7">
+        <v>144140</v>
+      </c>
       <c r="D524" s="7"/>
       <c r="E524" s="5"/>
     </row>
     <row r="525" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A525" s="6"/>
-      <c r="B525" s="5"/>
-      <c r="C525" s="7"/>
+      <c r="A525" s="6">
+        <v>45980</v>
+      </c>
+      <c r="B525" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C525" s="7">
+        <v>254720</v>
+      </c>
       <c r="D525" s="7"/>
       <c r="E525" s="5"/>
     </row>
     <row r="526" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A526" s="6"/>
-      <c r="B526" s="5"/>
-      <c r="C526" s="7"/>
+      <c r="A526" s="6">
+        <v>45981</v>
+      </c>
+      <c r="B526" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C526" s="7">
+        <v>185740</v>
+      </c>
       <c r="D526" s="7"/>
       <c r="E526" s="5"/>
     </row>
     <row r="527" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A527" s="6"/>
-      <c r="B527" s="5"/>
-      <c r="C527" s="7"/>
+      <c r="A527" s="6">
+        <v>45982</v>
+      </c>
+      <c r="B527" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C527" s="7">
+        <v>441520</v>
+      </c>
       <c r="D527" s="7"/>
       <c r="E527" s="5"/>
     </row>
     <row r="528" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A528" s="6"/>
-      <c r="B528" s="5"/>
-      <c r="C528" s="7"/>
+      <c r="A528" s="6">
+        <v>45983</v>
+      </c>
+      <c r="B528" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C528" s="7">
+        <v>126440</v>
+      </c>
       <c r="D528" s="7"/>
       <c r="E528" s="5"/>
     </row>
     <row r="529" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A529" s="6"/>
-      <c r="B529" s="5"/>
-      <c r="C529" s="7"/>
+      <c r="A529" s="6">
+        <v>45984</v>
+      </c>
+      <c r="B529" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C529" s="7">
+        <v>219280</v>
+      </c>
       <c r="D529" s="7"/>
       <c r="E529" s="5"/>
     </row>
     <row r="530" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A530" s="6"/>
-      <c r="B530" s="5"/>
-      <c r="C530" s="7"/>
+      <c r="A530" s="6">
+        <v>45985</v>
+      </c>
+      <c r="B530" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C530" s="7">
+        <v>299150</v>
+      </c>
       <c r="D530" s="7"/>
       <c r="E530" s="5"/>
     </row>
     <row r="531" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A531" s="6"/>
-      <c r="B531" s="5"/>
-      <c r="C531" s="7"/>
+      <c r="A531" s="6">
+        <v>45986</v>
+      </c>
+      <c r="B531" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C531" s="7">
+        <v>178920</v>
+      </c>
       <c r="D531" s="7"/>
       <c r="E531" s="5"/>
     </row>
     <row r="532" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A532" s="6"/>
-      <c r="B532" s="5"/>
-      <c r="C532" s="7"/>
+      <c r="A532" s="6">
+        <v>45987</v>
+      </c>
+      <c r="B532" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C532" s="7">
+        <v>193500</v>
+      </c>
       <c r="D532" s="7"/>
       <c r="E532" s="5"/>
     </row>
     <row r="533" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A533" s="6"/>
-      <c r="B533" s="5"/>
-      <c r="C533" s="7"/>
+      <c r="A533" s="6">
+        <v>45988</v>
+      </c>
+      <c r="B533" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C533" s="7">
+        <v>169700</v>
+      </c>
       <c r="D533" s="7"/>
       <c r="E533" s="5"/>
     </row>
     <row r="534" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A534" s="6"/>
-      <c r="B534" s="5"/>
-      <c r="C534" s="7"/>
+      <c r="A534" s="6">
+        <v>45989</v>
+      </c>
+      <c r="B534" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C534" s="7">
+        <v>146540</v>
+      </c>
       <c r="D534" s="7"/>
       <c r="E534" s="5"/>
     </row>
     <row r="535" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A535" s="6"/>
-      <c r="B535" s="5"/>
-      <c r="C535" s="7"/>
+      <c r="A535" s="6">
+        <v>45990</v>
+      </c>
+      <c r="B535" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C535" s="7">
+        <v>82540</v>
+      </c>
       <c r="D535" s="7"/>
       <c r="E535" s="5"/>
     </row>
     <row r="536" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A536" s="6"/>
-      <c r="B536" s="5"/>
-      <c r="C536" s="7"/>
+      <c r="A536" s="6">
+        <v>45991</v>
+      </c>
+      <c r="B536" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C536" s="7">
+        <v>98580</v>
+      </c>
       <c r="D536" s="7"/>
       <c r="E536" s="5"/>
     </row>
@@ -7436,219 +7394,405 @@
       <c r="E537" s="5"/>
     </row>
     <row r="538" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A538" s="6"/>
-      <c r="B538" s="5"/>
-      <c r="C538" s="7"/>
+      <c r="A538" s="6">
+        <v>45992</v>
+      </c>
+      <c r="B538" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C538" s="7">
+        <v>155060</v>
+      </c>
       <c r="D538" s="7"/>
       <c r="E538" s="5"/>
     </row>
     <row r="539" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A539" s="6"/>
-      <c r="B539" s="5"/>
-      <c r="C539" s="7"/>
+      <c r="A539" s="6">
+        <v>45993</v>
+      </c>
+      <c r="B539" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C539" s="7">
+        <v>619638</v>
+      </c>
       <c r="D539" s="7"/>
       <c r="E539" s="5"/>
     </row>
     <row r="540" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A540" s="6"/>
-      <c r="B540" s="5"/>
-      <c r="C540" s="7"/>
+      <c r="A540" s="6">
+        <v>45994</v>
+      </c>
+      <c r="B540" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C540" s="7">
+        <v>132380</v>
+      </c>
       <c r="D540" s="7"/>
       <c r="E540" s="5"/>
     </row>
     <row r="541" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A541" s="6"/>
-      <c r="B541" s="5"/>
-      <c r="C541" s="7"/>
+      <c r="A541" s="6">
+        <v>45995</v>
+      </c>
+      <c r="B541" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C541" s="7">
+        <v>373160</v>
+      </c>
       <c r="D541" s="7"/>
       <c r="E541" s="5"/>
     </row>
     <row r="542" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A542" s="6"/>
-      <c r="B542" s="5"/>
-      <c r="C542" s="7"/>
+      <c r="A542" s="6">
+        <v>45996</v>
+      </c>
+      <c r="B542" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C542" s="7">
+        <v>527060</v>
+      </c>
       <c r="D542" s="7"/>
       <c r="E542" s="5"/>
     </row>
     <row r="543" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A543" s="6"/>
-      <c r="B543" s="5"/>
-      <c r="C543" s="7"/>
+      <c r="A543" s="6">
+        <v>45997</v>
+      </c>
+      <c r="B543" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C543" s="7">
+        <v>99160</v>
+      </c>
       <c r="D543" s="7"/>
       <c r="E543" s="5"/>
     </row>
     <row r="544" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A544" s="6"/>
-      <c r="B544" s="5"/>
-      <c r="C544" s="7"/>
+      <c r="A544" s="6">
+        <v>45998</v>
+      </c>
+      <c r="B544" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C544" s="7">
+        <v>33880</v>
+      </c>
       <c r="D544" s="7"/>
       <c r="E544" s="5"/>
     </row>
     <row r="545" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A545" s="6"/>
-      <c r="B545" s="5"/>
-      <c r="C545" s="7"/>
+      <c r="A545" s="6">
+        <v>45999</v>
+      </c>
+      <c r="B545" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C545" s="7">
+        <v>152160</v>
+      </c>
       <c r="D545" s="7"/>
       <c r="E545" s="5"/>
     </row>
     <row r="546" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A546" s="6"/>
-      <c r="B546" s="5"/>
-      <c r="C546" s="7"/>
+      <c r="A546" s="6">
+        <v>46000</v>
+      </c>
+      <c r="B546" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C546" s="7">
+        <v>293050</v>
+      </c>
       <c r="D546" s="7"/>
       <c r="E546" s="5"/>
     </row>
     <row r="547" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A547" s="6"/>
-      <c r="B547" s="5"/>
-      <c r="C547" s="7"/>
+      <c r="A547" s="6">
+        <v>46001</v>
+      </c>
+      <c r="B547" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C547" s="7">
+        <v>204900</v>
+      </c>
       <c r="D547" s="7"/>
       <c r="E547" s="5"/>
     </row>
     <row r="548" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A548" s="6"/>
-      <c r="B548" s="5"/>
-      <c r="C548" s="7"/>
+      <c r="A548" s="6">
+        <v>46002</v>
+      </c>
+      <c r="B548" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C548" s="7">
+        <v>569102</v>
+      </c>
       <c r="D548" s="7"/>
       <c r="E548" s="5"/>
     </row>
     <row r="549" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A549" s="6"/>
-      <c r="B549" s="5"/>
-      <c r="C549" s="7"/>
+      <c r="A549" s="6">
+        <v>46003</v>
+      </c>
+      <c r="B549" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C549" s="7">
+        <v>362904</v>
+      </c>
       <c r="D549" s="7"/>
       <c r="E549" s="5"/>
     </row>
     <row r="550" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A550" s="6"/>
-      <c r="B550" s="5"/>
-      <c r="C550" s="7"/>
+      <c r="A550" s="6">
+        <v>46004</v>
+      </c>
+      <c r="B550" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C550" s="7">
+        <v>200280</v>
+      </c>
       <c r="D550" s="7"/>
       <c r="E550" s="5"/>
     </row>
     <row r="551" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A551" s="6"/>
-      <c r="B551" s="5"/>
-      <c r="C551" s="7"/>
+      <c r="A551" s="6">
+        <v>46005</v>
+      </c>
+      <c r="B551" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C551" s="7">
+        <v>56458</v>
+      </c>
       <c r="D551" s="7"/>
       <c r="E551" s="5"/>
     </row>
     <row r="552" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A552" s="6"/>
-      <c r="B552" s="5"/>
-      <c r="C552" s="7"/>
+      <c r="A552" s="6">
+        <v>46006</v>
+      </c>
+      <c r="B552" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C552" s="7">
+        <v>440040</v>
+      </c>
       <c r="D552" s="7"/>
       <c r="E552" s="5"/>
     </row>
     <row r="553" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A553" s="6"/>
-      <c r="B553" s="5"/>
-      <c r="C553" s="7"/>
+      <c r="A553" s="6">
+        <v>46007</v>
+      </c>
+      <c r="B553" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C553" s="7">
+        <v>317760</v>
+      </c>
       <c r="D553" s="7"/>
       <c r="E553" s="5"/>
     </row>
     <row r="554" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A554" s="6"/>
-      <c r="B554" s="5"/>
-      <c r="C554" s="7"/>
+      <c r="A554" s="6">
+        <v>46008</v>
+      </c>
+      <c r="B554" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C554" s="7">
+        <v>222876</v>
+      </c>
       <c r="D554" s="7"/>
       <c r="E554" s="5"/>
     </row>
     <row r="555" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A555" s="6"/>
-      <c r="B555" s="5"/>
-      <c r="C555" s="7"/>
+      <c r="A555" s="6">
+        <v>46009</v>
+      </c>
+      <c r="B555" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C555" s="7">
+        <v>249580</v>
+      </c>
       <c r="D555" s="7"/>
       <c r="E555" s="5"/>
     </row>
     <row r="556" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A556" s="6"/>
-      <c r="B556" s="5"/>
-      <c r="C556" s="7"/>
+      <c r="A556" s="6">
+        <v>46010</v>
+      </c>
+      <c r="B556" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C556" s="7">
+        <v>483230</v>
+      </c>
       <c r="D556" s="7"/>
       <c r="E556" s="5"/>
     </row>
     <row r="557" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A557" s="6"/>
-      <c r="B557" s="5"/>
-      <c r="C557" s="7"/>
+      <c r="A557" s="6">
+        <v>46011</v>
+      </c>
+      <c r="B557" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C557" s="7">
+        <v>464008</v>
+      </c>
       <c r="D557" s="7"/>
       <c r="E557" s="5"/>
     </row>
     <row r="558" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A558" s="6"/>
-      <c r="B558" s="5"/>
-      <c r="C558" s="7"/>
+      <c r="A558" s="6">
+        <v>46012</v>
+      </c>
+      <c r="B558" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C558" s="7">
+        <v>363418</v>
+      </c>
       <c r="D558" s="7"/>
       <c r="E558" s="5"/>
     </row>
     <row r="559" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A559" s="6"/>
-      <c r="B559" s="5"/>
-      <c r="C559" s="7"/>
+      <c r="A559" s="6">
+        <v>46013</v>
+      </c>
+      <c r="B559" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C559" s="7">
+        <v>218138</v>
+      </c>
       <c r="D559" s="7"/>
       <c r="E559" s="5"/>
     </row>
     <row r="560" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A560" s="6"/>
-      <c r="B560" s="5"/>
-      <c r="C560" s="7"/>
+      <c r="A560" s="6">
+        <v>46014</v>
+      </c>
+      <c r="B560" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C560" s="7">
+        <v>202640</v>
+      </c>
       <c r="D560" s="7"/>
       <c r="E560" s="5"/>
     </row>
     <row r="561" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A561" s="6"/>
-      <c r="B561" s="5"/>
-      <c r="C561" s="7"/>
+      <c r="A561" s="6">
+        <v>46015</v>
+      </c>
+      <c r="B561" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C561" s="7">
+        <v>283540</v>
+      </c>
       <c r="D561" s="7"/>
       <c r="E561" s="5"/>
     </row>
     <row r="562" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A562" s="6"/>
-      <c r="B562" s="5"/>
-      <c r="C562" s="7"/>
+      <c r="A562" s="6">
+        <v>46016</v>
+      </c>
+      <c r="B562" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C562" s="7">
+        <v>250380</v>
+      </c>
       <c r="D562" s="7"/>
       <c r="E562" s="5"/>
     </row>
     <row r="563" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A563" s="6"/>
-      <c r="B563" s="5"/>
-      <c r="C563" s="7"/>
+      <c r="A563" s="6">
+        <v>46017</v>
+      </c>
+      <c r="B563" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C563" s="7">
+        <v>633928</v>
+      </c>
       <c r="D563" s="7"/>
       <c r="E563" s="5"/>
     </row>
     <row r="564" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A564" s="6"/>
-      <c r="B564" s="5"/>
-      <c r="C564" s="7"/>
+      <c r="A564" s="6">
+        <v>46018</v>
+      </c>
+      <c r="B564" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C564" s="7">
+        <v>858218</v>
+      </c>
       <c r="D564" s="7"/>
       <c r="E564" s="5"/>
     </row>
     <row r="565" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A565" s="6"/>
-      <c r="B565" s="5"/>
-      <c r="C565" s="7"/>
+      <c r="A565" s="6">
+        <v>46019</v>
+      </c>
+      <c r="B565" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C565" s="7">
+        <v>362272</v>
+      </c>
       <c r="D565" s="7"/>
       <c r="E565" s="5"/>
     </row>
     <row r="566" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A566" s="6"/>
-      <c r="B566" s="5"/>
-      <c r="C566" s="7"/>
+      <c r="A566" s="6">
+        <v>46020</v>
+      </c>
+      <c r="B566" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C566" s="7">
+        <v>531110</v>
+      </c>
       <c r="D566" s="7"/>
       <c r="E566" s="5"/>
     </row>
     <row r="567" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A567" s="6"/>
-      <c r="B567" s="5"/>
-      <c r="C567" s="7"/>
+      <c r="A567" s="6">
+        <v>46021</v>
+      </c>
+      <c r="B567" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C567" s="7">
+        <v>240494</v>
+      </c>
       <c r="D567" s="7"/>
       <c r="E567" s="5"/>
     </row>
     <row r="568" spans="1:5" x14ac:dyDescent="0.15">
-      <c r="A568" s="6"/>
-      <c r="B568" s="5"/>
-      <c r="C568" s="7"/>
+      <c r="A568" s="6">
+        <v>46022</v>
+      </c>
+      <c r="B568" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C568" s="7">
+        <v>365244</v>
+      </c>
       <c r="D568" s="7"/>
       <c r="E568" s="5"/>
     </row>
@@ -9282,6 +9426,678 @@
       <c r="C801" s="7"/>
       <c r="D801" s="7"/>
       <c r="E801" s="5"/>
+    </row>
+    <row r="802" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A802" s="6"/>
+      <c r="B802" s="5"/>
+      <c r="C802" s="7"/>
+      <c r="D802" s="7"/>
+      <c r="E802" s="5"/>
+    </row>
+    <row r="803" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A803" s="6"/>
+      <c r="B803" s="5"/>
+      <c r="C803" s="7"/>
+      <c r="D803" s="7"/>
+      <c r="E803" s="5"/>
+    </row>
+    <row r="804" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A804" s="6"/>
+      <c r="B804" s="5"/>
+      <c r="C804" s="7"/>
+      <c r="D804" s="7"/>
+      <c r="E804" s="5"/>
+    </row>
+    <row r="805" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A805" s="6"/>
+      <c r="B805" s="5"/>
+      <c r="C805" s="7"/>
+      <c r="D805" s="7"/>
+      <c r="E805" s="5"/>
+    </row>
+    <row r="806" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A806" s="6"/>
+      <c r="B806" s="5"/>
+      <c r="C806" s="7"/>
+      <c r="D806" s="7"/>
+      <c r="E806" s="5"/>
+    </row>
+    <row r="807" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A807" s="6"/>
+      <c r="B807" s="5"/>
+      <c r="C807" s="7"/>
+      <c r="D807" s="7"/>
+      <c r="E807" s="5"/>
+    </row>
+    <row r="808" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A808" s="6"/>
+      <c r="B808" s="5"/>
+      <c r="C808" s="7"/>
+      <c r="D808" s="7"/>
+      <c r="E808" s="5"/>
+    </row>
+    <row r="809" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A809" s="6"/>
+      <c r="B809" s="5"/>
+      <c r="C809" s="7"/>
+      <c r="D809" s="7"/>
+      <c r="E809" s="5"/>
+    </row>
+    <row r="810" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A810" s="6"/>
+      <c r="B810" s="5"/>
+      <c r="C810" s="7"/>
+      <c r="D810" s="7"/>
+      <c r="E810" s="5"/>
+    </row>
+    <row r="811" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A811" s="6"/>
+      <c r="B811" s="5"/>
+      <c r="C811" s="7"/>
+      <c r="D811" s="7"/>
+      <c r="E811" s="5"/>
+    </row>
+    <row r="812" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A812" s="6"/>
+      <c r="B812" s="5"/>
+      <c r="C812" s="7"/>
+      <c r="D812" s="7"/>
+      <c r="E812" s="5"/>
+    </row>
+    <row r="813" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A813" s="6"/>
+      <c r="B813" s="5"/>
+      <c r="C813" s="7"/>
+      <c r="D813" s="7"/>
+      <c r="E813" s="5"/>
+    </row>
+    <row r="814" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A814" s="6"/>
+      <c r="B814" s="5"/>
+      <c r="C814" s="7"/>
+      <c r="D814" s="7"/>
+      <c r="E814" s="5"/>
+    </row>
+    <row r="815" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A815" s="6"/>
+      <c r="B815" s="5"/>
+      <c r="C815" s="7"/>
+      <c r="D815" s="7"/>
+      <c r="E815" s="5"/>
+    </row>
+    <row r="816" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A816" s="6"/>
+      <c r="B816" s="5"/>
+      <c r="C816" s="7"/>
+      <c r="D816" s="7"/>
+      <c r="E816" s="5"/>
+    </row>
+    <row r="817" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A817" s="6"/>
+      <c r="B817" s="5"/>
+      <c r="C817" s="7"/>
+      <c r="D817" s="7"/>
+      <c r="E817" s="5"/>
+    </row>
+    <row r="818" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A818" s="6"/>
+      <c r="B818" s="5"/>
+      <c r="C818" s="7"/>
+      <c r="D818" s="7"/>
+      <c r="E818" s="5"/>
+    </row>
+    <row r="819" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A819" s="6"/>
+      <c r="B819" s="5"/>
+      <c r="C819" s="7"/>
+      <c r="D819" s="7"/>
+      <c r="E819" s="5"/>
+    </row>
+    <row r="820" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A820" s="6"/>
+      <c r="B820" s="5"/>
+      <c r="C820" s="7"/>
+      <c r="D820" s="7"/>
+      <c r="E820" s="5"/>
+    </row>
+    <row r="821" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A821" s="6"/>
+      <c r="B821" s="5"/>
+      <c r="C821" s="7"/>
+      <c r="D821" s="7"/>
+      <c r="E821" s="5"/>
+    </row>
+    <row r="822" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A822" s="6"/>
+      <c r="B822" s="5"/>
+      <c r="C822" s="7"/>
+      <c r="D822" s="7"/>
+      <c r="E822" s="5"/>
+    </row>
+    <row r="823" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A823" s="6"/>
+      <c r="B823" s="5"/>
+      <c r="C823" s="7"/>
+      <c r="D823" s="7"/>
+      <c r="E823" s="5"/>
+    </row>
+    <row r="824" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A824" s="6"/>
+      <c r="B824" s="5"/>
+      <c r="C824" s="7"/>
+      <c r="D824" s="7"/>
+      <c r="E824" s="5"/>
+    </row>
+    <row r="825" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A825" s="6"/>
+      <c r="B825" s="5"/>
+      <c r="C825" s="7"/>
+      <c r="D825" s="7"/>
+      <c r="E825" s="5"/>
+    </row>
+    <row r="826" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A826" s="6"/>
+      <c r="B826" s="5"/>
+      <c r="C826" s="7"/>
+      <c r="D826" s="7"/>
+      <c r="E826" s="5"/>
+    </row>
+    <row r="827" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A827" s="6"/>
+      <c r="B827" s="5"/>
+      <c r="C827" s="7"/>
+      <c r="D827" s="7"/>
+      <c r="E827" s="5"/>
+    </row>
+    <row r="828" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A828" s="6"/>
+      <c r="B828" s="5"/>
+      <c r="C828" s="7"/>
+      <c r="D828" s="7"/>
+      <c r="E828" s="5"/>
+    </row>
+    <row r="829" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A829" s="6"/>
+      <c r="B829" s="5"/>
+      <c r="C829" s="7"/>
+      <c r="D829" s="7"/>
+      <c r="E829" s="5"/>
+    </row>
+    <row r="830" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A830" s="6"/>
+      <c r="B830" s="5"/>
+      <c r="C830" s="7"/>
+      <c r="D830" s="7"/>
+      <c r="E830" s="5"/>
+    </row>
+    <row r="831" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A831" s="6"/>
+      <c r="B831" s="5"/>
+      <c r="C831" s="7"/>
+      <c r="D831" s="7"/>
+      <c r="E831" s="5"/>
+    </row>
+    <row r="832" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A832" s="6"/>
+      <c r="B832" s="5"/>
+      <c r="C832" s="7"/>
+      <c r="D832" s="7"/>
+      <c r="E832" s="5"/>
+    </row>
+    <row r="833" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A833" s="6"/>
+      <c r="B833" s="5"/>
+      <c r="C833" s="7"/>
+      <c r="D833" s="7"/>
+      <c r="E833" s="5"/>
+    </row>
+    <row r="834" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A834" s="6"/>
+      <c r="B834" s="5"/>
+      <c r="C834" s="7"/>
+      <c r="D834" s="7"/>
+      <c r="E834" s="5"/>
+    </row>
+    <row r="835" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A835" s="6"/>
+      <c r="B835" s="5"/>
+      <c r="C835" s="7"/>
+      <c r="D835" s="7"/>
+      <c r="E835" s="5"/>
+    </row>
+    <row r="836" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A836" s="6"/>
+      <c r="B836" s="5"/>
+      <c r="C836" s="7"/>
+      <c r="D836" s="7"/>
+      <c r="E836" s="5"/>
+    </row>
+    <row r="837" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A837" s="6"/>
+      <c r="B837" s="5"/>
+      <c r="C837" s="7"/>
+      <c r="D837" s="7"/>
+      <c r="E837" s="5"/>
+    </row>
+    <row r="838" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A838" s="6"/>
+      <c r="B838" s="5"/>
+      <c r="C838" s="7"/>
+      <c r="D838" s="7"/>
+      <c r="E838" s="5"/>
+    </row>
+    <row r="839" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A839" s="6"/>
+      <c r="B839" s="5"/>
+      <c r="C839" s="7"/>
+      <c r="D839" s="7"/>
+      <c r="E839" s="5"/>
+    </row>
+    <row r="840" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A840" s="6"/>
+      <c r="B840" s="5"/>
+      <c r="C840" s="7"/>
+      <c r="D840" s="7"/>
+      <c r="E840" s="5"/>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A841" s="6"/>
+      <c r="B841" s="5"/>
+      <c r="C841" s="7"/>
+      <c r="D841" s="7"/>
+      <c r="E841" s="5"/>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A842" s="6"/>
+      <c r="B842" s="5"/>
+      <c r="C842" s="7"/>
+      <c r="D842" s="7"/>
+      <c r="E842" s="5"/>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A843" s="6"/>
+      <c r="B843" s="5"/>
+      <c r="C843" s="7"/>
+      <c r="D843" s="7"/>
+      <c r="E843" s="5"/>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A844" s="6"/>
+      <c r="B844" s="5"/>
+      <c r="C844" s="7"/>
+      <c r="D844" s="7"/>
+      <c r="E844" s="5"/>
+    </row>
+    <row r="845" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A845" s="6"/>
+      <c r="B845" s="5"/>
+      <c r="C845" s="7"/>
+      <c r="D845" s="7"/>
+      <c r="E845" s="5"/>
+    </row>
+    <row r="846" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A846" s="6"/>
+      <c r="B846" s="5"/>
+      <c r="C846" s="7"/>
+      <c r="D846" s="7"/>
+      <c r="E846" s="5"/>
+    </row>
+    <row r="847" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A847" s="6"/>
+      <c r="B847" s="5"/>
+      <c r="C847" s="7"/>
+      <c r="D847" s="7"/>
+      <c r="E847" s="5"/>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A848" s="6"/>
+      <c r="B848" s="5"/>
+      <c r="C848" s="7"/>
+      <c r="D848" s="7"/>
+      <c r="E848" s="5"/>
+    </row>
+    <row r="849" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A849" s="6"/>
+      <c r="B849" s="5"/>
+      <c r="C849" s="7"/>
+      <c r="D849" s="7"/>
+      <c r="E849" s="5"/>
+    </row>
+    <row r="850" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A850" s="6"/>
+      <c r="B850" s="5"/>
+      <c r="C850" s="7"/>
+      <c r="D850" s="7"/>
+      <c r="E850" s="5"/>
+    </row>
+    <row r="851" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A851" s="6"/>
+      <c r="B851" s="5"/>
+      <c r="C851" s="7"/>
+      <c r="D851" s="7"/>
+      <c r="E851" s="5"/>
+    </row>
+    <row r="852" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A852" s="6"/>
+      <c r="B852" s="5"/>
+      <c r="C852" s="7"/>
+      <c r="D852" s="7"/>
+      <c r="E852" s="5"/>
+    </row>
+    <row r="853" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A853" s="6"/>
+      <c r="B853" s="5"/>
+      <c r="C853" s="7"/>
+      <c r="D853" s="7"/>
+      <c r="E853" s="5"/>
+    </row>
+    <row r="854" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A854" s="6"/>
+      <c r="B854" s="5"/>
+      <c r="C854" s="7"/>
+      <c r="D854" s="7"/>
+      <c r="E854" s="5"/>
+    </row>
+    <row r="855" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A855" s="6"/>
+      <c r="B855" s="5"/>
+      <c r="C855" s="7"/>
+      <c r="D855" s="7"/>
+      <c r="E855" s="5"/>
+    </row>
+    <row r="856" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A856" s="6"/>
+      <c r="B856" s="5"/>
+      <c r="C856" s="7"/>
+      <c r="D856" s="7"/>
+      <c r="E856" s="5"/>
+    </row>
+    <row r="857" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A857" s="6"/>
+      <c r="B857" s="5"/>
+      <c r="C857" s="7"/>
+      <c r="D857" s="7"/>
+      <c r="E857" s="5"/>
+    </row>
+    <row r="858" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A858" s="6"/>
+      <c r="B858" s="5"/>
+      <c r="C858" s="7"/>
+      <c r="D858" s="7"/>
+      <c r="E858" s="5"/>
+    </row>
+    <row r="859" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A859" s="6"/>
+      <c r="B859" s="5"/>
+      <c r="C859" s="7"/>
+      <c r="D859" s="7"/>
+      <c r="E859" s="5"/>
+    </row>
+    <row r="860" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A860" s="6"/>
+      <c r="B860" s="5"/>
+      <c r="C860" s="7"/>
+      <c r="D860" s="7"/>
+      <c r="E860" s="5"/>
+    </row>
+    <row r="861" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A861" s="6"/>
+      <c r="B861" s="5"/>
+      <c r="C861" s="7"/>
+      <c r="D861" s="7"/>
+      <c r="E861" s="5"/>
+    </row>
+    <row r="862" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A862" s="6"/>
+      <c r="B862" s="5"/>
+      <c r="C862" s="7"/>
+      <c r="D862" s="7"/>
+      <c r="E862" s="5"/>
+    </row>
+    <row r="863" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A863" s="6"/>
+      <c r="B863" s="5"/>
+      <c r="C863" s="7"/>
+      <c r="D863" s="7"/>
+      <c r="E863" s="5"/>
+    </row>
+    <row r="864" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A864" s="6"/>
+      <c r="B864" s="5"/>
+      <c r="C864" s="7"/>
+      <c r="D864" s="7"/>
+      <c r="E864" s="5"/>
+    </row>
+    <row r="865" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A865" s="6"/>
+      <c r="B865" s="5"/>
+      <c r="C865" s="7"/>
+      <c r="D865" s="7"/>
+      <c r="E865" s="5"/>
+    </row>
+    <row r="866" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A866" s="6"/>
+      <c r="B866" s="5"/>
+      <c r="C866" s="7"/>
+      <c r="D866" s="7"/>
+      <c r="E866" s="5"/>
+    </row>
+    <row r="867" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A867" s="6"/>
+      <c r="B867" s="5"/>
+      <c r="C867" s="7"/>
+      <c r="D867" s="7"/>
+      <c r="E867" s="5"/>
+    </row>
+    <row r="868" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A868" s="6"/>
+      <c r="B868" s="5"/>
+      <c r="C868" s="7"/>
+      <c r="D868" s="7"/>
+      <c r="E868" s="5"/>
+    </row>
+    <row r="869" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A869" s="6"/>
+      <c r="B869" s="5"/>
+      <c r="C869" s="7"/>
+      <c r="D869" s="7"/>
+      <c r="E869" s="5"/>
+    </row>
+    <row r="870" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A870" s="6"/>
+      <c r="B870" s="5"/>
+      <c r="C870" s="7"/>
+      <c r="D870" s="7"/>
+      <c r="E870" s="5"/>
+    </row>
+    <row r="871" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A871" s="6"/>
+      <c r="B871" s="5"/>
+      <c r="C871" s="7"/>
+      <c r="D871" s="7"/>
+      <c r="E871" s="5"/>
+    </row>
+    <row r="872" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A872" s="6"/>
+      <c r="B872" s="5"/>
+      <c r="C872" s="7"/>
+      <c r="D872" s="7"/>
+      <c r="E872" s="5"/>
+    </row>
+    <row r="873" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A873" s="6"/>
+      <c r="B873" s="5"/>
+      <c r="C873" s="7"/>
+      <c r="D873" s="7"/>
+      <c r="E873" s="5"/>
+    </row>
+    <row r="874" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A874" s="6"/>
+      <c r="B874" s="5"/>
+      <c r="C874" s="7"/>
+      <c r="D874" s="7"/>
+      <c r="E874" s="5"/>
+    </row>
+    <row r="875" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A875" s="6"/>
+      <c r="B875" s="5"/>
+      <c r="C875" s="7"/>
+      <c r="D875" s="7"/>
+      <c r="E875" s="5"/>
+    </row>
+    <row r="876" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A876" s="6"/>
+      <c r="B876" s="5"/>
+      <c r="C876" s="7"/>
+      <c r="D876" s="7"/>
+      <c r="E876" s="5"/>
+    </row>
+    <row r="877" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A877" s="6"/>
+      <c r="B877" s="5"/>
+      <c r="C877" s="7"/>
+      <c r="D877" s="7"/>
+      <c r="E877" s="5"/>
+    </row>
+    <row r="878" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A878" s="6"/>
+      <c r="B878" s="5"/>
+      <c r="C878" s="7"/>
+      <c r="D878" s="7"/>
+      <c r="E878" s="5"/>
+    </row>
+    <row r="879" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A879" s="6"/>
+      <c r="B879" s="5"/>
+      <c r="C879" s="7"/>
+      <c r="D879" s="7"/>
+      <c r="E879" s="5"/>
+    </row>
+    <row r="880" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A880" s="6"/>
+      <c r="B880" s="5"/>
+      <c r="C880" s="7"/>
+      <c r="D880" s="7"/>
+      <c r="E880" s="5"/>
+    </row>
+    <row r="881" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A881" s="6"/>
+      <c r="B881" s="5"/>
+      <c r="C881" s="7"/>
+      <c r="D881" s="7"/>
+      <c r="E881" s="5"/>
+    </row>
+    <row r="882" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A882" s="6"/>
+      <c r="B882" s="5"/>
+      <c r="C882" s="7"/>
+      <c r="D882" s="7"/>
+      <c r="E882" s="5"/>
+    </row>
+    <row r="883" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A883" s="6"/>
+      <c r="B883" s="5"/>
+      <c r="C883" s="7"/>
+      <c r="D883" s="7"/>
+      <c r="E883" s="5"/>
+    </row>
+    <row r="884" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A884" s="6"/>
+      <c r="B884" s="5"/>
+      <c r="C884" s="7"/>
+      <c r="D884" s="7"/>
+      <c r="E884" s="5"/>
+    </row>
+    <row r="885" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A885" s="6"/>
+      <c r="B885" s="5"/>
+      <c r="C885" s="7"/>
+      <c r="D885" s="7"/>
+      <c r="E885" s="5"/>
+    </row>
+    <row r="886" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A886" s="6"/>
+      <c r="B886" s="5"/>
+      <c r="C886" s="7"/>
+      <c r="D886" s="7"/>
+      <c r="E886" s="5"/>
+    </row>
+    <row r="887" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A887" s="6"/>
+      <c r="B887" s="5"/>
+      <c r="C887" s="7"/>
+      <c r="D887" s="7"/>
+      <c r="E887" s="5"/>
+    </row>
+    <row r="888" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A888" s="6"/>
+      <c r="B888" s="5"/>
+      <c r="C888" s="7"/>
+      <c r="D888" s="7"/>
+      <c r="E888" s="5"/>
+    </row>
+    <row r="889" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A889" s="6"/>
+      <c r="B889" s="5"/>
+      <c r="C889" s="7"/>
+      <c r="D889" s="7"/>
+      <c r="E889" s="5"/>
+    </row>
+    <row r="890" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A890" s="6"/>
+      <c r="B890" s="5"/>
+      <c r="C890" s="7"/>
+      <c r="D890" s="7"/>
+      <c r="E890" s="5"/>
+    </row>
+    <row r="891" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A891" s="6"/>
+      <c r="B891" s="5"/>
+      <c r="C891" s="7"/>
+      <c r="D891" s="7"/>
+      <c r="E891" s="5"/>
+    </row>
+    <row r="892" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A892" s="6"/>
+      <c r="B892" s="5"/>
+      <c r="C892" s="7"/>
+      <c r="D892" s="7"/>
+      <c r="E892" s="5"/>
+    </row>
+    <row r="893" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A893" s="6"/>
+      <c r="B893" s="5"/>
+      <c r="C893" s="7"/>
+      <c r="D893" s="7"/>
+      <c r="E893" s="5"/>
+    </row>
+    <row r="894" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A894" s="6"/>
+      <c r="B894" s="5"/>
+      <c r="C894" s="7"/>
+      <c r="D894" s="7"/>
+      <c r="E894" s="5"/>
+    </row>
+    <row r="895" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A895" s="6"/>
+      <c r="B895" s="5"/>
+      <c r="C895" s="7"/>
+      <c r="D895" s="7"/>
+      <c r="E895" s="5"/>
+    </row>
+    <row r="896" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A896" s="6"/>
+      <c r="B896" s="5"/>
+      <c r="C896" s="7"/>
+      <c r="D896" s="7"/>
+      <c r="E896" s="5"/>
+    </row>
+    <row r="897" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A897" s="6"/>
+      <c r="B897" s="5"/>
+      <c r="C897" s="7"/>
+      <c r="D897" s="7"/>
+      <c r="E897" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="5"/>
@@ -9293,7 +10109,7 @@
           <x14:formula1>
             <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
           </x14:formula1>
-          <xm:sqref>B2:B801</xm:sqref>
+          <xm:sqref>B86:B897 B2:B15 B35:B64</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$472</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$473</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,21 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -226,40 +211,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -273,14 +226,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,7 +234,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,7 +257,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -332,6 +278,29 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -340,8 +309,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,48 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -416,7 +374,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,13 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,7 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +470,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,55 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,6 +572,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -588,20 +603,35 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,36 +660,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E473"/>
+  <dimension ref="A1:E474"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7649,9 +7649,20 @@
         <v>555550</v>
       </c>
     </row>
+    <row r="474" spans="1:3">
+      <c r="A474" s="1">
+        <v>46281</v>
+      </c>
+      <c r="B474" t="s">
+        <v>38</v>
+      </c>
+      <c r="C474">
+        <v>516570</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E472">
-    <sortState ref="A1:E472">
+  <autoFilter ref="A1:E473">
+    <sortState ref="A1:E473">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$474</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$475</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,21 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -227,54 +220,28 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -297,7 +264,30 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -311,30 +301,33 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +335,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,7 +422,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,25 +488,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,37 +512,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -512,19 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -624,17 +624,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,17 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E475"/>
+  <dimension ref="A1:E476"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7671,9 +7671,20 @@
         <v>595650</v>
       </c>
     </row>
+    <row r="476" spans="1:3">
+      <c r="A476" s="1">
+        <v>46283</v>
+      </c>
+      <c r="B476" t="s">
+        <v>38</v>
+      </c>
+      <c r="C476">
+        <v>658970</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E474">
-    <sortState ref="A1:E474">
+  <autoFilter ref="A1:E475">
+    <sortState ref="A1:E475">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$475</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$476</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -218,18 +226,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -241,40 +265,16 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -293,19 +293,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,11 +308,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -333,15 +331,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +422,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,19 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,31 +506,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,39 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -589,8 +622,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,73 +668,25 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,19 +695,19 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -716,120 +716,120 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E476"/>
+  <dimension ref="A1:E477"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7682,9 +7682,20 @@
         <v>658970</v>
       </c>
     </row>
+    <row r="477" spans="1:3">
+      <c r="A477" s="1">
+        <v>46284</v>
+      </c>
+      <c r="B477" t="s">
+        <v>38</v>
+      </c>
+      <c r="C477">
+        <v>626120</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E475">
-    <sortState ref="A1:E475">
+  <autoFilter ref="A1:E476">
+    <sortState ref="A1:E476">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$476</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$477</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,36 +205,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -249,8 +219,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -258,14 +236,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,10 +272,27 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -294,15 +305,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -317,13 +327,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -331,17 +340,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,7 +428,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,67 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,19 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,25 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,25 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -589,17 +595,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,9 +621,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,28 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,153 +683,153 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E477"/>
+  <dimension ref="A1:E478"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7693,9 +7693,20 @@
         <v>626120</v>
       </c>
     </row>
+    <row r="478" spans="1:3">
+      <c r="A478" s="1">
+        <v>46285</v>
+      </c>
+      <c r="B478" t="s">
+        <v>38</v>
+      </c>
+      <c r="C478">
+        <v>652800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E476">
-    <sortState ref="A1:E476">
+  <autoFilter ref="A1:E477">
+    <sortState ref="A1:E477">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$477</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$478</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
@@ -205,61 +205,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -280,19 +241,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -311,6 +271,14 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -318,9 +286,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -328,13 +335,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,85 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +380,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +434,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,39 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -621,26 +588,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +618,72 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,144 +692,144 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E478"/>
+  <dimension ref="A1:E479"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7704,9 +7704,20 @@
         <v>652800</v>
       </c>
     </row>
+    <row r="479" spans="1:3">
+      <c r="A479" s="1">
+        <v>46286</v>
+      </c>
+      <c r="B479" t="s">
+        <v>38</v>
+      </c>
+      <c r="C479">
+        <v>628280</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E477">
-    <sortState ref="A1:E477">
+  <autoFilter ref="A1:E478">
+    <sortState ref="A1:E478">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$478</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$479</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,9 +164,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
@@ -203,41 +203,10 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -258,16 +227,39 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -287,7 +279,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,9 +301,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -319,7 +325,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,6 +422,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -398,37 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,19 +464,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +494,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,49 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,32 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -595,17 +621,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -634,26 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E479"/>
+  <dimension ref="A1:E480"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7715,9 +7715,20 @@
         <v>628280</v>
       </c>
     </row>
+    <row r="480" spans="1:3">
+      <c r="A480" s="1">
+        <v>46287</v>
+      </c>
+      <c r="B480" t="s">
+        <v>38</v>
+      </c>
+      <c r="C480">
+        <v>611160</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E478">
-    <sortState ref="A1:E478">
+  <autoFilter ref="A1:E479">
+    <sortState ref="A1:E479">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$479</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$480</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="526" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,7 +219,30 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,14 +257,15 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,14 +273,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -279,15 +303,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,46 +331,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +458,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,121 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,28 +571,32 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -616,7 +620,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,7 +644,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -639,32 +658,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,97 +674,91 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -773,63 +767,69 @@
     <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E480"/>
+  <dimension ref="A1:E481"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7726,9 +7726,20 @@
         <v>611160</v>
       </c>
     </row>
+    <row r="481" spans="1:3">
+      <c r="A481" s="1">
+        <v>46288</v>
+      </c>
+      <c r="B481" t="s">
+        <v>38</v>
+      </c>
+      <c r="C481">
+        <v>519580</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E479">
-    <sortState ref="A1:E479">
+  <autoFilter ref="A1:E480">
+    <sortState ref="A1:E480">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$480</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$481</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="527" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,31 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -212,6 +235,22 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,38 +264,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -271,17 +287,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -295,20 +324,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -316,34 +332,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +446,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,7 +482,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,109 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,17 +571,26 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,26 +610,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,9 +636,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -652,19 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="22" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E481"/>
+  <dimension ref="A1:E482"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7737,9 +7737,20 @@
         <v>519580</v>
       </c>
     </row>
+    <row r="482" spans="1:3">
+      <c r="A482" s="1">
+        <v>46289</v>
+      </c>
+      <c r="B482" t="s">
+        <v>38</v>
+      </c>
+      <c r="C482">
+        <v>564680</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E480">
-    <sortState ref="A1:E480">
+  <autoFilter ref="A1:E481">
+    <sortState ref="A1:E481">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$481</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$482</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,24 +203,22 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,7 +232,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,9 +246,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,15 +261,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -296,23 +294,25 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -326,9 +326,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +416,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,13 +452,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,13 +488,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +524,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,6 +582,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -612,8 +612,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -636,11 +638,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -659,31 +668,22 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,141 +695,141 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E482"/>
+  <dimension ref="A1:E483"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7748,9 +7748,20 @@
         <v>564680</v>
       </c>
     </row>
+    <row r="483" spans="1:3">
+      <c r="A483" s="1">
+        <v>46290</v>
+      </c>
+      <c r="B483" t="s">
+        <v>38</v>
+      </c>
+      <c r="C483">
+        <v>710760</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E481">
-    <sortState ref="A1:E481">
+  <autoFilter ref="A1:E482">
+    <sortState ref="A1:E482">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$482</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$483</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="529" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,15 +210,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,22 +233,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -261,11 +247,26 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -277,22 +278,21 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -309,22 +309,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -334,14 +318,30 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,49 +392,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +410,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,13 +428,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +464,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,7 +518,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -586,11 +595,50 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -620,100 +668,52 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -722,114 +722,114 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E483"/>
+  <dimension ref="A1:E484"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7759,9 +7759,20 @@
         <v>710760</v>
       </c>
     </row>
+    <row r="484" spans="1:3">
+      <c r="A484" s="1">
+        <v>46291</v>
+      </c>
+      <c r="B484" t="s">
+        <v>38</v>
+      </c>
+      <c r="C484">
+        <v>602540</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E482">
-    <sortState ref="A1:E482">
+  <autoFilter ref="A1:E483">
+    <sortState ref="A1:E483">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$483</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$484</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -239,9 +231,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -262,25 +270,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -293,18 +292,19 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -317,8 +317,16 @@
     </font>
     <font>
       <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,14 +342,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,13 +386,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -422,49 +428,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,7 +446,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,13 +476,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,11 +571,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -595,17 +601,46 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,43 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,141 +695,141 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E484"/>
+  <dimension ref="A1:E485"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7770,9 +7770,20 @@
         <v>602540</v>
       </c>
     </row>
+    <row r="485" spans="1:3">
+      <c r="A485" s="1">
+        <v>46292</v>
+      </c>
+      <c r="B485" t="s">
+        <v>38</v>
+      </c>
+      <c r="C485">
+        <v>626500</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E483">
-    <sortState ref="A1:E483">
+  <autoFilter ref="A1:E484">
+    <sortState ref="A1:E484">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$484</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$485</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="531" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,6 +232,44 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -224,15 +277,8 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -247,9 +293,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -258,43 +304,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,31 +319,22 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,25 +410,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,31 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,55 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,7 +476,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,7 +500,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,16 +572,45 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,46 +630,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFB2B2B2"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,144 +692,144 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="16" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E485"/>
+  <dimension ref="A1:E486"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7781,9 +7781,20 @@
         <v>626500</v>
       </c>
     </row>
+    <row r="486" spans="1:3">
+      <c r="A486" s="1">
+        <v>46293</v>
+      </c>
+      <c r="B486" t="s">
+        <v>38</v>
+      </c>
+      <c r="C486">
+        <v>534220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E484">
-    <sortState ref="A1:E484">
+  <autoFilter ref="A1:E485">
+    <sortState ref="A1:E485">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$485</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$486</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,43 +204,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -249,7 +212,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,30 +234,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -310,16 +257,16 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,7 +281,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -342,6 +289,59 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +410,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +488,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,7 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,43 +518,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,73 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,45 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -586,11 +625,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,56 +660,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,162 +674,162 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E486"/>
+  <dimension ref="A1:E487"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7792,9 +7792,20 @@
         <v>534220</v>
       </c>
     </row>
+    <row r="487" spans="1:3">
+      <c r="A487" s="1">
+        <v>46294</v>
+      </c>
+      <c r="B487" t="s">
+        <v>38</v>
+      </c>
+      <c r="C487">
+        <v>597240</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E485">
-    <sortState ref="A1:E485">
+  <autoFilter ref="A1:E486">
+    <sortState ref="A1:E486">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$486</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$487</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,6 +210,50 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -218,8 +262,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -233,24 +299,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -266,82 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,37 +470,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,49 +500,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,19 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,37 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -591,36 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -642,20 +612,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,168 +642,194 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1489,7 +1489,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E487"/>
+  <dimension ref="A1:E488"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7803,9 +7803,17 @@
         <v>597240</v>
       </c>
     </row>
+    <row r="488" spans="1:2">
+      <c r="A488" s="1">
+        <v>46295</v>
+      </c>
+      <c r="B488" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E486">
-    <sortState ref="A1:E486">
+  <autoFilter ref="A1:E487">
+    <sortState ref="A1:E487">
       <sortCondition ref="A2:A897"/>
     </sortState>
     <extLst/>

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C597657-54C4-4129-B3BE-4404CAEFFB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,9 +18,20 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$487</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$488</definedName>
   </definedNames>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -162,15 +179,11 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -183,171 +196,38 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <sz val="6"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <family val="3"/>
+      <charset val="128"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -360,194 +240,8 @@
         <bgColor rgb="FF4E79A7"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -570,253 +264,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -827,10 +279,8 @@
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -841,61 +291,17 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
-    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
-    <cellStyle name="入力" xfId="2" builtinId="20"/>
-    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
-    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
-    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
-    <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
-    <cellStyle name="良い" xfId="13" builtinId="26"/>
-    <cellStyle name="警告文" xfId="14" builtinId="11"/>
-    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
-    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
-    <cellStyle name="説明文" xfId="17" builtinId="53"/>
-    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
-    <cellStyle name="出力" xfId="19" builtinId="21"/>
-    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
-    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
-    <cellStyle name="計算" xfId="22" builtinId="22"/>
-    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
-    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
-    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
-    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
-    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
-    <cellStyle name="集計" xfId="28" builtinId="25"/>
-    <cellStyle name="悪い" xfId="29" builtinId="27"/>
-    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
-    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
-    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
-    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
-    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
-    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
-    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
-    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
-    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
-    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
-    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
-    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
-    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
-    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
-    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
-    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
-    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
-    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1180,317 +586,315 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" spans="1:1">
-      <c r="A1" s="10" t="s">
+    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="11"/>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="11" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" s="9"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="11" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="11"/>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="11" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A5" s="9"/>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="11" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="11" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="11" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="11" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="11"/>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="11" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A12" s="9"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="11" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="11" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="11"/>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="12" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A16" s="9"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="11" t="s">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="11" t="s">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="11" t="s">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="11" t="s">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="11" t="s">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
-      <c r="A23" s="11" t="s">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
-      <c r="A24" s="11" t="s">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A24" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
-      <c r="A25" s="11" t="s">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
-      <c r="A26" s="11" t="s">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A26" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
-      <c r="A27" s="11"/>
-    </row>
-    <row r="28" spans="1:1">
-      <c r="A28" s="12" t="s">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A27" s="9"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
-      <c r="A29" s="11" t="s">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A29" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
-      <c r="A30" s="11" t="s">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
-      <c r="A31" s="11" t="s">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A31" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
-      <c r="A32" s="11" t="s">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A31" s="5"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E488"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -1498,7 +902,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -1515,7 +919,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A2" s="4">
         <v>45809</v>
       </c>
@@ -1528,7 +932,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A3" s="4">
         <v>45810</v>
       </c>
@@ -1541,7 +945,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A4" s="4">
         <v>45811</v>
       </c>
@@ -1554,7 +958,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A5" s="4">
         <v>45812</v>
       </c>
@@ -1567,7 +971,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A6" s="4">
         <v>45813</v>
       </c>
@@ -1580,7 +984,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A7" s="4">
         <v>45814</v>
       </c>
@@ -1593,7 +997,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A8" s="4">
         <v>45815</v>
       </c>
@@ -1606,7 +1010,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A9" s="4">
         <v>45816</v>
       </c>
@@ -1619,7 +1023,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A10" s="4">
         <v>45817</v>
       </c>
@@ -1632,7 +1036,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A11" s="4">
         <v>45818</v>
       </c>
@@ -1645,7 +1049,7 @@
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A12" s="4">
         <v>45819</v>
       </c>
@@ -1658,7 +1062,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A13" s="4">
         <v>45820</v>
       </c>
@@ -1671,7 +1075,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A14" s="4">
         <v>45821</v>
       </c>
@@ -1684,7 +1088,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A15" s="4">
         <v>45822</v>
       </c>
@@ -1697,11 +1101,11 @@
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="8">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A16" s="1">
         <v>45823</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" t="s">
         <v>38</v>
       </c>
       <c r="C16" s="6">
@@ -1710,11 +1114,11 @@
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="8">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="1">
         <v>45824</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="6">
@@ -1723,11 +1127,11 @@
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="8">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="1">
         <v>45825</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="6">
@@ -1736,11 +1140,11 @@
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="8">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="1">
         <v>45826</v>
       </c>
-      <c r="B19" s="9" t="s">
+      <c r="B19" t="s">
         <v>38</v>
       </c>
       <c r="C19" s="6">
@@ -1749,11 +1153,11 @@
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="8">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="1">
         <v>45827</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" t="s">
         <v>38</v>
       </c>
       <c r="C20" s="6">
@@ -1762,11 +1166,11 @@
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="8">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="1">
         <v>45828</v>
       </c>
-      <c r="B21" s="9" t="s">
+      <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" s="6">
@@ -1775,11 +1179,11 @@
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="8">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A22" s="1">
         <v>45829</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" t="s">
         <v>38</v>
       </c>
       <c r="C22" s="6">
@@ -1788,11 +1192,11 @@
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="8">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A23" s="1">
         <v>45830</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" t="s">
         <v>38</v>
       </c>
       <c r="C23" s="6">
@@ -1801,11 +1205,11 @@
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="8">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A24" s="1">
         <v>45831</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" t="s">
         <v>38</v>
       </c>
       <c r="C24" s="6">
@@ -1814,11 +1218,11 @@
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="8">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A25" s="1">
         <v>45832</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" t="s">
         <v>38</v>
       </c>
       <c r="C25" s="6">
@@ -1827,11 +1231,11 @@
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="8">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A26" s="1">
         <v>45833</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" t="s">
         <v>38</v>
       </c>
       <c r="C26" s="6">
@@ -1840,11 +1244,11 @@
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="8">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A27" s="1">
         <v>45834</v>
       </c>
-      <c r="B27" s="9" t="s">
+      <c r="B27" t="s">
         <v>38</v>
       </c>
       <c r="C27" s="6">
@@ -1853,11 +1257,11 @@
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="8">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A28" s="1">
         <v>45835</v>
       </c>
-      <c r="B28" s="9" t="s">
+      <c r="B28" t="s">
         <v>38</v>
       </c>
       <c r="C28" s="6">
@@ -1866,11 +1270,11 @@
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="8">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A29" s="1">
         <v>45836</v>
       </c>
-      <c r="B29" s="9" t="s">
+      <c r="B29" t="s">
         <v>38</v>
       </c>
       <c r="C29" s="6">
@@ -1879,11 +1283,11 @@
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="8">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A30" s="1">
         <v>45837</v>
       </c>
-      <c r="B30" s="9" t="s">
+      <c r="B30" t="s">
         <v>38</v>
       </c>
       <c r="C30" s="6">
@@ -1892,11 +1296,11 @@
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="8">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A31" s="1">
         <v>45838</v>
       </c>
-      <c r="B31" s="9" t="s">
+      <c r="B31" t="s">
         <v>38</v>
       </c>
       <c r="C31" s="6">
@@ -1905,11 +1309,11 @@
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="8">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A32" s="1">
         <v>45839</v>
       </c>
-      <c r="B32" s="9" t="s">
+      <c r="B32" t="s">
         <v>38</v>
       </c>
       <c r="C32" s="6">
@@ -1918,11 +1322,11 @@
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="8">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
         <v>45840</v>
       </c>
-      <c r="B33" s="9" t="s">
+      <c r="B33" t="s">
         <v>38</v>
       </c>
       <c r="C33" s="6">
@@ -1931,11 +1335,11 @@
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="8">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A34" s="1">
         <v>45841</v>
       </c>
-      <c r="B34" s="9" t="s">
+      <c r="B34" t="s">
         <v>38</v>
       </c>
       <c r="C34" s="6">
@@ -1944,7 +1348,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A35" s="4">
         <v>45842</v>
       </c>
@@ -1957,7 +1361,7 @@
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A36" s="4">
         <v>45843</v>
       </c>
@@ -1970,7 +1374,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A37" s="4">
         <v>45844</v>
       </c>
@@ -1983,7 +1387,7 @@
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A38" s="4">
         <v>45845</v>
       </c>
@@ -1996,7 +1400,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A39" s="4">
         <v>45846</v>
       </c>
@@ -2009,7 +1413,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A40" s="4">
         <v>45847</v>
       </c>
@@ -2022,7 +1426,7 @@
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A41" s="4">
         <v>45848</v>
       </c>
@@ -2035,7 +1439,7 @@
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A42" s="4">
         <v>45849</v>
       </c>
@@ -2048,7 +1452,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A43" s="4">
         <v>45850</v>
       </c>
@@ -2061,7 +1465,7 @@
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A44" s="4">
         <v>45851</v>
       </c>
@@ -2074,7 +1478,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A45" s="4">
         <v>45852</v>
       </c>
@@ -2087,7 +1491,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A46" s="4">
         <v>45853</v>
       </c>
@@ -2100,7 +1504,7 @@
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A47" s="4">
         <v>45854</v>
       </c>
@@ -2113,7 +1517,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A48" s="4">
         <v>45855</v>
       </c>
@@ -2126,7 +1530,7 @@
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A49" s="4">
         <v>45856</v>
       </c>
@@ -2139,7 +1543,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A50" s="4">
         <v>45857</v>
       </c>
@@ -2152,7 +1556,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A51" s="4">
         <v>45858</v>
       </c>
@@ -2165,7 +1569,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A52" s="4">
         <v>45859</v>
       </c>
@@ -2178,7 +1582,7 @@
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A53" s="4">
         <v>45860</v>
       </c>
@@ -2191,7 +1595,7 @@
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A54" s="4">
         <v>45861</v>
       </c>
@@ -2204,7 +1608,7 @@
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A55" s="4">
         <v>45862</v>
       </c>
@@ -2217,7 +1621,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A56" s="4">
         <v>45863</v>
       </c>
@@ -2230,7 +1634,7 @@
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A57" s="4">
         <v>45864</v>
       </c>
@@ -2243,7 +1647,7 @@
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A58" s="4">
         <v>45865</v>
       </c>
@@ -2256,7 +1660,7 @@
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A59" s="4">
         <v>45866</v>
       </c>
@@ -2269,7 +1673,7 @@
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A60" s="4">
         <v>45867</v>
       </c>
@@ -2282,7 +1686,7 @@
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A61" s="4">
         <v>45868</v>
       </c>
@@ -2295,7 +1699,7 @@
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A62" s="4">
         <v>45869</v>
       </c>
@@ -2308,7 +1712,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A63" s="4">
         <v>45870</v>
       </c>
@@ -2321,7 +1725,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A64" s="4">
         <v>45871</v>
       </c>
@@ -2334,11 +1738,11 @@
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5">
-      <c r="A65" s="8">
+    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A65" s="1">
         <v>45872</v>
       </c>
-      <c r="B65" s="9" t="s">
+      <c r="B65" t="s">
         <v>38</v>
       </c>
       <c r="C65" s="6">
@@ -2347,11 +1751,11 @@
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66" s="8">
+    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A66" s="1">
         <v>45873</v>
       </c>
-      <c r="B66" s="9" t="s">
+      <c r="B66" t="s">
         <v>38</v>
       </c>
       <c r="C66" s="6">
@@ -2360,11 +1764,11 @@
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67" s="8">
+    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A67" s="1">
         <v>45874</v>
       </c>
-      <c r="B67" s="9" t="s">
+      <c r="B67" t="s">
         <v>38</v>
       </c>
       <c r="C67" s="6">
@@ -2373,11 +1777,11 @@
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5">
-      <c r="A68" s="8">
+    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A68" s="1">
         <v>45875</v>
       </c>
-      <c r="B68" s="9" t="s">
+      <c r="B68" t="s">
         <v>38</v>
       </c>
       <c r="C68" s="6">
@@ -2386,11 +1790,11 @@
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5">
-      <c r="A69" s="8">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A69" s="1">
         <v>45876</v>
       </c>
-      <c r="B69" s="9" t="s">
+      <c r="B69" t="s">
         <v>38</v>
       </c>
       <c r="C69" s="6">
@@ -2399,11 +1803,11 @@
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5">
-      <c r="A70" s="8">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A70" s="1">
         <v>45877</v>
       </c>
-      <c r="B70" s="9" t="s">
+      <c r="B70" t="s">
         <v>38</v>
       </c>
       <c r="C70" s="6">
@@ -2412,11 +1816,11 @@
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5">
-      <c r="A71" s="8">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A71" s="1">
         <v>45878</v>
       </c>
-      <c r="B71" s="9" t="s">
+      <c r="B71" t="s">
         <v>38</v>
       </c>
       <c r="C71" s="6">
@@ -2425,11 +1829,11 @@
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72" s="8">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A72" s="1">
         <v>45879</v>
       </c>
-      <c r="B72" s="9" t="s">
+      <c r="B72" t="s">
         <v>38</v>
       </c>
       <c r="C72" s="6">
@@ -2438,11 +1842,11 @@
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5">
-      <c r="A73" s="8">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A73" s="1">
         <v>45880</v>
       </c>
-      <c r="B73" s="9" t="s">
+      <c r="B73" t="s">
         <v>38</v>
       </c>
       <c r="C73" s="6">
@@ -2451,11 +1855,11 @@
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5">
-      <c r="A74" s="8">
+    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A74" s="1">
         <v>45881</v>
       </c>
-      <c r="B74" s="9" t="s">
+      <c r="B74" t="s">
         <v>38</v>
       </c>
       <c r="C74" s="6">
@@ -2464,11 +1868,11 @@
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5">
-      <c r="A75" s="8">
+    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A75" s="1">
         <v>45882</v>
       </c>
-      <c r="B75" s="9" t="s">
+      <c r="B75" t="s">
         <v>38</v>
       </c>
       <c r="C75" s="6">
@@ -2477,11 +1881,11 @@
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5">
-      <c r="A76" s="8">
+    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A76" s="1">
         <v>45883</v>
       </c>
-      <c r="B76" s="9" t="s">
+      <c r="B76" t="s">
         <v>38</v>
       </c>
       <c r="C76" s="6">
@@ -2490,11 +1894,11 @@
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5">
-      <c r="A77" s="8">
+    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A77" s="1">
         <v>45884</v>
       </c>
-      <c r="B77" s="9" t="s">
+      <c r="B77" t="s">
         <v>38</v>
       </c>
       <c r="C77" s="6">
@@ -2503,11 +1907,11 @@
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5">
-      <c r="A78" s="8">
+    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A78" s="1">
         <v>45885</v>
       </c>
-      <c r="B78" s="9" t="s">
+      <c r="B78" t="s">
         <v>38</v>
       </c>
       <c r="C78" s="6">
@@ -2516,11 +1920,11 @@
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5">
-      <c r="A79" s="8">
+    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A79" s="1">
         <v>45886</v>
       </c>
-      <c r="B79" s="9" t="s">
+      <c r="B79" t="s">
         <v>38</v>
       </c>
       <c r="C79" s="6">
@@ -2529,11 +1933,11 @@
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5">
-      <c r="A80" s="8">
+    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A80" s="1">
         <v>45887</v>
       </c>
-      <c r="B80" s="9" t="s">
+      <c r="B80" t="s">
         <v>38</v>
       </c>
       <c r="C80" s="6">
@@ -2542,11 +1946,11 @@
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5">
-      <c r="A81" s="8">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A81" s="1">
         <v>45888</v>
       </c>
-      <c r="B81" s="9" t="s">
+      <c r="B81" t="s">
         <v>38</v>
       </c>
       <c r="C81" s="6">
@@ -2555,11 +1959,11 @@
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="1:5">
-      <c r="A82" s="8">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A82" s="1">
         <v>45889</v>
       </c>
-      <c r="B82" s="9" t="s">
+      <c r="B82" t="s">
         <v>38</v>
       </c>
       <c r="C82" s="6">
@@ -2568,11 +1972,11 @@
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="1:5">
-      <c r="A83" s="8">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A83" s="1">
         <v>45890</v>
       </c>
-      <c r="B83" s="9" t="s">
+      <c r="B83" t="s">
         <v>38</v>
       </c>
       <c r="C83" s="6">
@@ -2581,11 +1985,11 @@
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5">
-      <c r="A84" s="8">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A84" s="1">
         <v>45891</v>
       </c>
-      <c r="B84" s="9" t="s">
+      <c r="B84" t="s">
         <v>38</v>
       </c>
       <c r="C84" s="6">
@@ -2594,11 +1998,11 @@
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5">
-      <c r="A85" s="8">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A85" s="1">
         <v>45892</v>
       </c>
-      <c r="B85" s="9" t="s">
+      <c r="B85" t="s">
         <v>38</v>
       </c>
       <c r="C85" s="6">
@@ -2607,7 +2011,7 @@
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A86" s="4">
         <v>45893</v>
       </c>
@@ -2620,7 +2024,7 @@
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A87" s="4">
         <v>45894</v>
       </c>
@@ -2633,7 +2037,7 @@
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A88" s="4">
         <v>45895</v>
       </c>
@@ -2646,7 +2050,7 @@
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A89" s="4">
         <v>45896</v>
       </c>
@@ -2659,7 +2063,7 @@
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A90" s="4">
         <v>45897</v>
       </c>
@@ -2672,7 +2076,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A91" s="4">
         <v>45898</v>
       </c>
@@ -2685,7 +2089,7 @@
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A92" s="4">
         <v>45899</v>
       </c>
@@ -2698,7 +2102,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A93" s="4">
         <v>45900</v>
       </c>
@@ -2711,7 +2115,7 @@
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A94" s="4">
         <v>45901</v>
       </c>
@@ -2724,7 +2128,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A95" s="4">
         <v>45902</v>
       </c>
@@ -2737,7 +2141,7 @@
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A96" s="4">
         <v>45903</v>
       </c>
@@ -2750,7 +2154,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A97" s="4">
         <v>45904</v>
       </c>
@@ -2763,7 +2167,7 @@
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A98" s="4">
         <v>45905</v>
       </c>
@@ -2776,7 +2180,7 @@
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A99" s="4">
         <v>45906</v>
       </c>
@@ -2789,7 +2193,7 @@
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A100" s="4">
         <v>45907</v>
       </c>
@@ -2802,7 +2206,7 @@
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A101" s="4">
         <v>45908</v>
       </c>
@@ -2815,7 +2219,7 @@
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A102" s="4">
         <v>45909</v>
       </c>
@@ -2828,7 +2232,7 @@
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A103" s="4">
         <v>45910</v>
       </c>
@@ -2841,7 +2245,7 @@
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A104" s="4">
         <v>45911</v>
       </c>
@@ -2854,7 +2258,7 @@
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A105" s="4">
         <v>45912</v>
       </c>
@@ -2867,7 +2271,7 @@
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A106" s="4">
         <v>45913</v>
       </c>
@@ -2880,7 +2284,7 @@
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A107" s="4">
         <v>45914</v>
       </c>
@@ -2893,7 +2297,7 @@
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A108" s="4">
         <v>45915</v>
       </c>
@@ -2906,7 +2310,7 @@
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A109" s="4">
         <v>45916</v>
       </c>
@@ -2919,7 +2323,7 @@
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A110" s="4">
         <v>45917</v>
       </c>
@@ -2932,7 +2336,7 @@
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A111" s="4">
         <v>45918</v>
       </c>
@@ -2945,7 +2349,7 @@
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A112" s="4">
         <v>45919</v>
       </c>
@@ -2958,7 +2362,7 @@
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A113" s="4">
         <v>45920</v>
       </c>
@@ -2971,7 +2375,7 @@
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A114" s="4">
         <v>45921</v>
       </c>
@@ -2984,7 +2388,7 @@
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A115" s="4">
         <v>45922</v>
       </c>
@@ -2997,7 +2401,7 @@
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A116" s="4">
         <v>45923</v>
       </c>
@@ -3010,7 +2414,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A117" s="4">
         <v>45924</v>
       </c>
@@ -3023,7 +2427,7 @@
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A118" s="4">
         <v>45925</v>
       </c>
@@ -3036,7 +2440,7 @@
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A119" s="4">
         <v>45926</v>
       </c>
@@ -3049,7 +2453,7 @@
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A120" s="4">
         <v>45927</v>
       </c>
@@ -3062,7 +2466,7 @@
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A121" s="4">
         <v>45928</v>
       </c>
@@ -3075,7 +2479,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
-    <row r="122" spans="1:5">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A122" s="4">
         <v>45929</v>
       </c>
@@ -3088,7 +2492,7 @@
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
-    <row r="123" spans="1:5">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A123" s="4">
         <v>45930</v>
       </c>
@@ -3101,7 +2505,7 @@
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
-    <row r="124" spans="1:5">
+    <row r="124" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A124" s="4">
         <v>45931</v>
       </c>
@@ -3114,7 +2518,7 @@
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
-    <row r="125" spans="1:5">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A125" s="4">
         <v>45932</v>
       </c>
@@ -3127,7 +2531,7 @@
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
-    <row r="126" spans="1:5">
+    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A126" s="4">
         <v>45933</v>
       </c>
@@ -3140,7 +2544,7 @@
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
-    <row r="127" spans="1:5">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A127" s="4">
         <v>45934</v>
       </c>
@@ -3153,7 +2557,7 @@
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
-    <row r="128" spans="1:5">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A128" s="4">
         <v>45935</v>
       </c>
@@ -3166,7 +2570,7 @@
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
-    <row r="129" spans="1:5">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A129" s="4">
         <v>45936</v>
       </c>
@@ -3179,7 +2583,7 @@
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
-    <row r="130" spans="1:5">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A130" s="4">
         <v>45937</v>
       </c>
@@ -3192,7 +2596,7 @@
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
-    <row r="131" spans="1:5">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A131" s="4">
         <v>45938</v>
       </c>
@@ -3205,7 +2609,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
-    <row r="132" spans="1:5">
+    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A132" s="4">
         <v>45939</v>
       </c>
@@ -3218,7 +2622,7 @@
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
-    <row r="133" spans="1:5">
+    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A133" s="4">
         <v>45940</v>
       </c>
@@ -3231,7 +2635,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
-    <row r="134" spans="1:5">
+    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A134" s="4">
         <v>45941</v>
       </c>
@@ -3244,7 +2648,7 @@
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
-    <row r="135" spans="1:5">
+    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A135" s="4">
         <v>45942</v>
       </c>
@@ -3257,7 +2661,7 @@
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
-    <row r="136" spans="1:5">
+    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A136" s="4">
         <v>45943</v>
       </c>
@@ -3270,7 +2674,7 @@
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
-    <row r="137" spans="1:5">
+    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A137" s="4">
         <v>45944</v>
       </c>
@@ -3283,7 +2687,7 @@
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
-    <row r="138" spans="1:5">
+    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A138" s="4">
         <v>45945</v>
       </c>
@@ -3296,7 +2700,7 @@
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
-    <row r="139" spans="1:5">
+    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A139" s="4">
         <v>45946</v>
       </c>
@@ -3309,7 +2713,7 @@
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
-    <row r="140" spans="1:5">
+    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A140" s="4">
         <v>45947</v>
       </c>
@@ -3322,7 +2726,7 @@
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
-    <row r="141" spans="1:5">
+    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A141" s="4">
         <v>45948</v>
       </c>
@@ -3335,7 +2739,7 @@
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
-    <row r="142" spans="1:5">
+    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A142" s="4">
         <v>45949</v>
       </c>
@@ -3348,7 +2752,7 @@
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
-    <row r="143" spans="1:5">
+    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A143" s="4">
         <v>45950</v>
       </c>
@@ -3361,7 +2765,7 @@
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
-    <row r="144" spans="1:5">
+    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A144" s="4">
         <v>45951</v>
       </c>
@@ -3374,7 +2778,7 @@
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
-    <row r="145" spans="1:5">
+    <row r="145" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A145" s="4">
         <v>45952</v>
       </c>
@@ -3387,7 +2791,7 @@
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
-    <row r="146" spans="1:5">
+    <row r="146" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A146" s="4">
         <v>45953</v>
       </c>
@@ -3400,7 +2804,7 @@
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
-    <row r="147" spans="1:5">
+    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A147" s="4">
         <v>45954</v>
       </c>
@@ -3413,7 +2817,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
-    <row r="148" spans="1:5">
+    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A148" s="4">
         <v>45955</v>
       </c>
@@ -3426,7 +2830,7 @@
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
-    <row r="149" spans="1:5">
+    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A149" s="4">
         <v>45956</v>
       </c>
@@ -3439,7 +2843,7 @@
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
-    <row r="150" spans="1:5">
+    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A150" s="4">
         <v>45957</v>
       </c>
@@ -3452,7 +2856,7 @@
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
-    <row r="151" spans="1:5">
+    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A151" s="4">
         <v>45958</v>
       </c>
@@ -3465,7 +2869,7 @@
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
-    <row r="152" spans="1:5">
+    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A152" s="4">
         <v>45959</v>
       </c>
@@ -3478,7 +2882,7 @@
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
-    <row r="153" spans="1:5">
+    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A153" s="4">
         <v>45960</v>
       </c>
@@ -3491,7 +2895,7 @@
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
-    <row r="154" spans="1:5">
+    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A154" s="4">
         <v>45961</v>
       </c>
@@ -3504,7 +2908,7 @@
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
-    <row r="155" spans="1:5">
+    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A155" s="4">
         <v>45962</v>
       </c>
@@ -3517,7 +2921,7 @@
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
-    <row r="156" spans="1:5">
+    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A156" s="4">
         <v>45963</v>
       </c>
@@ -3530,7 +2934,7 @@
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
-    <row r="157" spans="1:5">
+    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A157" s="4">
         <v>45964</v>
       </c>
@@ -3543,7 +2947,7 @@
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
-    <row r="158" spans="1:5">
+    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A158" s="4">
         <v>45965</v>
       </c>
@@ -3556,7 +2960,7 @@
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
-    <row r="159" spans="1:5">
+    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A159" s="4">
         <v>45966</v>
       </c>
@@ -3569,7 +2973,7 @@
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
-    <row r="160" spans="1:5">
+    <row r="160" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A160" s="4">
         <v>45967</v>
       </c>
@@ -3582,7 +2986,7 @@
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
-    <row r="161" spans="1:5">
+    <row r="161" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A161" s="4">
         <v>45968</v>
       </c>
@@ -3595,7 +2999,7 @@
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
-    <row r="162" spans="1:5">
+    <row r="162" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A162" s="4">
         <v>45969</v>
       </c>
@@ -3608,7 +3012,7 @@
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
-    <row r="163" spans="1:5">
+    <row r="163" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A163" s="4">
         <v>45970</v>
       </c>
@@ -3621,7 +3025,7 @@
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
-    <row r="164" spans="1:5">
+    <row r="164" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A164" s="4">
         <v>45971</v>
       </c>
@@ -3634,7 +3038,7 @@
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
-    <row r="165" spans="1:5">
+    <row r="165" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A165" s="4">
         <v>45972</v>
       </c>
@@ -3647,7 +3051,7 @@
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
-    <row r="166" spans="1:5">
+    <row r="166" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A166" s="4">
         <v>45973</v>
       </c>
@@ -3660,7 +3064,7 @@
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
-    <row r="167" spans="1:5">
+    <row r="167" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A167" s="4">
         <v>45974</v>
       </c>
@@ -3673,7 +3077,7 @@
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
-    <row r="168" spans="1:5">
+    <row r="168" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A168" s="4">
         <v>45975</v>
       </c>
@@ -3686,7 +3090,7 @@
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
-    <row r="169" spans="1:5">
+    <row r="169" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A169" s="4">
         <v>45976</v>
       </c>
@@ -3699,7 +3103,7 @@
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
-    <row r="170" spans="1:5">
+    <row r="170" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A170" s="4">
         <v>45977</v>
       </c>
@@ -3712,7 +3116,7 @@
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
-    <row r="171" spans="1:5">
+    <row r="171" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A171" s="4">
         <v>45978</v>
       </c>
@@ -3725,7 +3129,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
-    <row r="172" spans="1:5">
+    <row r="172" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A172" s="4">
         <v>45979</v>
       </c>
@@ -3738,7 +3142,7 @@
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
-    <row r="173" spans="1:5">
+    <row r="173" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A173" s="4">
         <v>45980</v>
       </c>
@@ -3751,7 +3155,7 @@
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
-    <row r="174" spans="1:5">
+    <row r="174" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A174" s="4">
         <v>45981</v>
       </c>
@@ -3764,7 +3168,7 @@
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
-    <row r="175" spans="1:5">
+    <row r="175" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A175" s="4">
         <v>45982</v>
       </c>
@@ -3777,7 +3181,7 @@
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
-    <row r="176" spans="1:5">
+    <row r="176" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A176" s="4">
         <v>45983</v>
       </c>
@@ -3790,7 +3194,7 @@
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
-    <row r="177" spans="1:5">
+    <row r="177" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A177" s="4">
         <v>45984</v>
       </c>
@@ -3803,7 +3207,7 @@
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
-    <row r="178" spans="1:5">
+    <row r="178" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A178" s="4">
         <v>45985</v>
       </c>
@@ -3816,7 +3220,7 @@
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
-    <row r="179" spans="1:5">
+    <row r="179" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A179" s="4">
         <v>45986</v>
       </c>
@@ -3829,7 +3233,7 @@
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
-    <row r="180" spans="1:5">
+    <row r="180" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A180" s="4">
         <v>45987</v>
       </c>
@@ -3842,7 +3246,7 @@
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
-    <row r="181" spans="1:5">
+    <row r="181" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A181" s="4">
         <v>45988</v>
       </c>
@@ -3855,7 +3259,7 @@
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
-    <row r="182" spans="1:5">
+    <row r="182" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A182" s="4">
         <v>45989</v>
       </c>
@@ -3868,7 +3272,7 @@
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
-    <row r="183" spans="1:5">
+    <row r="183" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A183" s="4">
         <v>45990</v>
       </c>
@@ -3881,7 +3285,7 @@
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
-    <row r="184" spans="1:5">
+    <row r="184" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A184" s="4">
         <v>45991</v>
       </c>
@@ -3894,7 +3298,7 @@
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
-    <row r="185" spans="1:5">
+    <row r="185" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A185" s="4">
         <v>45992</v>
       </c>
@@ -3907,7 +3311,7 @@
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
-    <row r="186" spans="1:5">
+    <row r="186" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A186" s="4">
         <v>45993</v>
       </c>
@@ -3920,7 +3324,7 @@
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
-    <row r="187" spans="1:5">
+    <row r="187" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A187" s="4">
         <v>45994</v>
       </c>
@@ -3933,7 +3337,7 @@
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
-    <row r="188" spans="1:5">
+    <row r="188" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A188" s="4">
         <v>45995</v>
       </c>
@@ -3946,7 +3350,7 @@
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
-    <row r="189" spans="1:5">
+    <row r="189" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A189" s="4">
         <v>45996</v>
       </c>
@@ -3959,7 +3363,7 @@
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
-    <row r="190" spans="1:5">
+    <row r="190" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A190" s="4">
         <v>45997</v>
       </c>
@@ -3972,7 +3376,7 @@
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
-    <row r="191" spans="1:5">
+    <row r="191" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A191" s="4">
         <v>45998</v>
       </c>
@@ -3985,7 +3389,7 @@
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
-    <row r="192" spans="1:5">
+    <row r="192" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A192" s="4">
         <v>45999</v>
       </c>
@@ -3998,7 +3402,7 @@
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
-    <row r="193" spans="1:5">
+    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A193" s="4">
         <v>46000</v>
       </c>
@@ -4011,7 +3415,7 @@
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
-    <row r="194" spans="1:5">
+    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A194" s="4">
         <v>46001</v>
       </c>
@@ -4024,7 +3428,7 @@
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
-    <row r="195" spans="1:5">
+    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A195" s="4">
         <v>46002</v>
       </c>
@@ -4037,7 +3441,7 @@
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
-    <row r="196" spans="1:5">
+    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A196" s="4">
         <v>46003</v>
       </c>
@@ -4050,7 +3454,7 @@
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
-    <row r="197" spans="1:5">
+    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A197" s="4">
         <v>46004</v>
       </c>
@@ -4063,7 +3467,7 @@
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
-    <row r="198" spans="1:5">
+    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A198" s="4">
         <v>46005</v>
       </c>
@@ -4076,7 +3480,7 @@
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
-    <row r="199" spans="1:5">
+    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A199" s="4">
         <v>46006</v>
       </c>
@@ -4089,7 +3493,7 @@
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
-    <row r="200" spans="1:5">
+    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A200" s="4">
         <v>46007</v>
       </c>
@@ -4102,7 +3506,7 @@
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
-    <row r="201" spans="1:5">
+    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A201" s="4">
         <v>46008</v>
       </c>
@@ -4115,7 +3519,7 @@
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
-    <row r="202" spans="1:5">
+    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A202" s="4">
         <v>46009</v>
       </c>
@@ -4128,7 +3532,7 @@
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
-    <row r="203" spans="1:5">
+    <row r="203" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A203" s="4">
         <v>46010</v>
       </c>
@@ -4141,7 +3545,7 @@
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
-    <row r="204" spans="1:5">
+    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A204" s="4">
         <v>46011</v>
       </c>
@@ -4154,7 +3558,7 @@
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
-    <row r="205" spans="1:5">
+    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A205" s="4">
         <v>46012</v>
       </c>
@@ -4167,7 +3571,7 @@
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
-    <row r="206" spans="1:5">
+    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A206" s="4">
         <v>46013</v>
       </c>
@@ -4180,7 +3584,7 @@
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
-    <row r="207" spans="1:5">
+    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A207" s="4">
         <v>46014</v>
       </c>
@@ -4193,7 +3597,7 @@
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
-    <row r="208" spans="1:5">
+    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A208" s="4">
         <v>46015</v>
       </c>
@@ -4206,7 +3610,7 @@
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
-    <row r="209" spans="1:5">
+    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A209" s="4">
         <v>46016</v>
       </c>
@@ -4219,7 +3623,7 @@
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
-    <row r="210" spans="1:5">
+    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A210" s="4">
         <v>46017</v>
       </c>
@@ -4232,7 +3636,7 @@
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
-    <row r="211" spans="1:5">
+    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A211" s="4">
         <v>46018</v>
       </c>
@@ -4245,7 +3649,7 @@
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
-    <row r="212" spans="1:5">
+    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A212" s="4">
         <v>46019</v>
       </c>
@@ -4258,7 +3662,7 @@
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
-    <row r="213" spans="1:5">
+    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A213" s="4">
         <v>46020</v>
       </c>
@@ -4271,7 +3675,7 @@
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
-    <row r="214" spans="1:5">
+    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A214" s="4">
         <v>46021</v>
       </c>
@@ -4284,7 +3688,7 @@
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
-    <row r="215" spans="1:5">
+    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A215" s="4">
         <v>46022</v>
       </c>
@@ -4297,7 +3701,7 @@
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
-    <row r="216" spans="1:5">
+    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A216" s="4">
         <v>46023</v>
       </c>
@@ -4310,7 +3714,7 @@
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
-    <row r="217" spans="1:5">
+    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A217" s="4">
         <v>46024</v>
       </c>
@@ -4323,7 +3727,7 @@
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
-    <row r="218" spans="1:5">
+    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A218" s="4">
         <v>46025</v>
       </c>
@@ -4336,7 +3740,7 @@
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
-    <row r="219" spans="1:5">
+    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A219" s="4">
         <v>46026</v>
       </c>
@@ -4349,7 +3753,7 @@
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
-    <row r="220" spans="1:5">
+    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A220" s="4">
         <v>46027</v>
       </c>
@@ -4362,7 +3766,7 @@
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
-    <row r="221" spans="1:5">
+    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A221" s="4">
         <v>46028</v>
       </c>
@@ -4375,7 +3779,7 @@
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
-    <row r="222" spans="1:5">
+    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A222" s="4">
         <v>46029</v>
       </c>
@@ -4388,7 +3792,7 @@
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
-    <row r="223" spans="1:5">
+    <row r="223" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A223" s="4">
         <v>46030</v>
       </c>
@@ -4401,7 +3805,7 @@
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
-    <row r="224" spans="1:5">
+    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A224" s="4">
         <v>46031</v>
       </c>
@@ -4414,7 +3818,7 @@
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
-    <row r="225" spans="1:5">
+    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A225" s="4">
         <v>46032</v>
       </c>
@@ -4427,7 +3831,7 @@
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
-    <row r="226" spans="1:5">
+    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A226" s="4">
         <v>46033</v>
       </c>
@@ -4440,7 +3844,7 @@
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
-    <row r="227" spans="1:5">
+    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A227" s="4">
         <v>46034</v>
       </c>
@@ -4453,7 +3857,7 @@
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
-    <row r="228" spans="1:5">
+    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A228" s="4">
         <v>46035</v>
       </c>
@@ -4466,7 +3870,7 @@
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
-    <row r="229" spans="1:5">
+    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A229" s="4">
         <v>46036</v>
       </c>
@@ -4479,7 +3883,7 @@
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
-    <row r="230" spans="1:5">
+    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A230" s="4">
         <v>46037</v>
       </c>
@@ -4492,7 +3896,7 @@
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
-    <row r="231" spans="1:5">
+    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A231" s="4">
         <v>46038</v>
       </c>
@@ -4505,7 +3909,7 @@
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
-    <row r="232" spans="1:5">
+    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A232" s="4">
         <v>46039</v>
       </c>
@@ -4518,7 +3922,7 @@
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
-    <row r="233" spans="1:5">
+    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A233" s="4">
         <v>46040</v>
       </c>
@@ -4531,7 +3935,7 @@
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
-    <row r="234" spans="1:5">
+    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A234" s="4">
         <v>46041</v>
       </c>
@@ -4544,7 +3948,7 @@
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
-    <row r="235" spans="1:5">
+    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A235" s="4">
         <v>46042</v>
       </c>
@@ -4557,7 +3961,7 @@
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
-    <row r="236" spans="1:5">
+    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A236" s="4">
         <v>46043</v>
       </c>
@@ -4570,7 +3974,7 @@
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
-    <row r="237" spans="1:5">
+    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A237" s="4">
         <v>46044</v>
       </c>
@@ -4583,7 +3987,7 @@
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
-    <row r="238" spans="1:5">
+    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A238" s="4">
         <v>46045</v>
       </c>
@@ -4596,7 +4000,7 @@
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
-    <row r="239" spans="1:5">
+    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A239" s="4">
         <v>46046</v>
       </c>
@@ -4609,7 +4013,7 @@
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
-    <row r="240" spans="1:5">
+    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A240" s="4">
         <v>46047</v>
       </c>
@@ -4622,7 +4026,7 @@
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
-    <row r="241" spans="1:5">
+    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A241" s="4">
         <v>46048</v>
       </c>
@@ -4635,7 +4039,7 @@
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
-    <row r="242" spans="1:5">
+    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A242" s="4">
         <v>46049</v>
       </c>
@@ -4648,7 +4052,7 @@
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
-    <row r="243" spans="1:5">
+    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A243" s="4">
         <v>46050</v>
       </c>
@@ -4661,7 +4065,7 @@
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
-    <row r="244" spans="1:5">
+    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A244" s="4">
         <v>46051</v>
       </c>
@@ -4674,7 +4078,7 @@
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
-    <row r="245" spans="1:5">
+    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A245" s="4">
         <v>46052</v>
       </c>
@@ -4687,7 +4091,7 @@
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
-    <row r="246" spans="1:5">
+    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A246" s="4">
         <v>46053</v>
       </c>
@@ -4700,7 +4104,7 @@
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
-    <row r="247" spans="1:5">
+    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A247" s="4">
         <v>46054</v>
       </c>
@@ -4713,7 +4117,7 @@
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
-    <row r="248" spans="1:5">
+    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A248" s="4">
         <v>46055</v>
       </c>
@@ -4726,7 +4130,7 @@
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
-    <row r="249" spans="1:5">
+    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A249" s="4">
         <v>46056</v>
       </c>
@@ -4739,7 +4143,7 @@
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
-    <row r="250" spans="1:5">
+    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A250" s="4">
         <v>46057</v>
       </c>
@@ -4752,7 +4156,7 @@
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
-    <row r="251" spans="1:5">
+    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A251" s="4">
         <v>46058</v>
       </c>
@@ -4765,7 +4169,7 @@
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
-    <row r="252" spans="1:5">
+    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A252" s="4">
         <v>46059</v>
       </c>
@@ -4778,7 +4182,7 @@
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
-    <row r="253" spans="1:5">
+    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A253" s="4">
         <v>46060</v>
       </c>
@@ -4791,7 +4195,7 @@
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
-    <row r="254" spans="1:5">
+    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A254" s="4">
         <v>46061</v>
       </c>
@@ -4804,7 +4208,7 @@
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
-    <row r="255" spans="1:5">
+    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A255" s="4">
         <v>46062</v>
       </c>
@@ -4817,7 +4221,7 @@
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
-    <row r="256" spans="1:5">
+    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A256" s="4">
         <v>46063</v>
       </c>
@@ -4830,7 +4234,7 @@
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
-    <row r="257" spans="1:5">
+    <row r="257" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A257" s="4">
         <v>46064</v>
       </c>
@@ -4843,7 +4247,7 @@
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
-    <row r="258" spans="1:5">
+    <row r="258" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A258" s="4">
         <v>46065</v>
       </c>
@@ -4856,7 +4260,7 @@
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
-    <row r="259" spans="1:5">
+    <row r="259" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A259" s="4">
         <v>46066</v>
       </c>
@@ -4869,7 +4273,7 @@
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
-    <row r="260" spans="1:5">
+    <row r="260" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A260" s="4">
         <v>46067</v>
       </c>
@@ -4882,7 +4286,7 @@
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
-    <row r="261" spans="1:5">
+    <row r="261" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A261" s="4">
         <v>46068</v>
       </c>
@@ -4895,7 +4299,7 @@
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
-    <row r="262" spans="1:5">
+    <row r="262" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A262" s="4">
         <v>46069</v>
       </c>
@@ -4908,7 +4312,7 @@
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
-    <row r="263" spans="1:5">
+    <row r="263" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A263" s="4">
         <v>46070</v>
       </c>
@@ -4921,7 +4325,7 @@
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
-    <row r="264" spans="1:5">
+    <row r="264" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A264" s="4">
         <v>46071</v>
       </c>
@@ -4934,7 +4338,7 @@
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
-    <row r="265" spans="1:5">
+    <row r="265" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A265" s="4">
         <v>46072</v>
       </c>
@@ -4947,7 +4351,7 @@
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
-    <row r="266" spans="1:5">
+    <row r="266" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A266" s="4">
         <v>46073</v>
       </c>
@@ -4960,7 +4364,7 @@
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
-    <row r="267" spans="1:5">
+    <row r="267" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A267" s="4">
         <v>46074</v>
       </c>
@@ -4973,7 +4377,7 @@
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
-    <row r="268" spans="1:5">
+    <row r="268" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A268" s="4">
         <v>46075</v>
       </c>
@@ -4986,7 +4390,7 @@
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
-    <row r="269" spans="1:5">
+    <row r="269" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A269" s="4">
         <v>46076</v>
       </c>
@@ -4999,7 +4403,7 @@
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
-    <row r="270" spans="1:5">
+    <row r="270" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A270" s="4">
         <v>46077</v>
       </c>
@@ -5012,7 +4416,7 @@
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
-    <row r="271" spans="1:5">
+    <row r="271" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A271" s="4">
         <v>46078</v>
       </c>
@@ -5025,7 +4429,7 @@
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
-    <row r="272" spans="1:5">
+    <row r="272" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A272" s="4">
         <v>46079</v>
       </c>
@@ -5038,7 +4442,7 @@
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
-    <row r="273" spans="1:5">
+    <row r="273" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A273" s="4">
         <v>46080</v>
       </c>
@@ -5051,7 +4455,7 @@
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
-    <row r="274" spans="1:5">
+    <row r="274" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A274" s="4">
         <v>46081</v>
       </c>
@@ -5064,7 +4468,7 @@
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
-    <row r="275" spans="1:5">
+    <row r="275" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A275" s="4">
         <v>46082</v>
       </c>
@@ -5077,7 +4481,7 @@
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
-    <row r="276" spans="1:5">
+    <row r="276" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A276" s="4">
         <v>46083</v>
       </c>
@@ -5090,7 +4494,7 @@
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
-    <row r="277" spans="1:5">
+    <row r="277" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A277" s="4">
         <v>46084</v>
       </c>
@@ -5103,7 +4507,7 @@
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
-    <row r="278" spans="1:5">
+    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A278" s="4">
         <v>46085</v>
       </c>
@@ -5116,7 +4520,7 @@
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
-    <row r="279" spans="1:5">
+    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A279" s="4">
         <v>46086</v>
       </c>
@@ -5129,7 +4533,7 @@
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
-    <row r="280" spans="1:5">
+    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A280" s="4">
         <v>46087</v>
       </c>
@@ -5142,7 +4546,7 @@
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
-    <row r="281" spans="1:5">
+    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A281" s="4">
         <v>46088</v>
       </c>
@@ -5155,7 +4559,7 @@
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
-    <row r="282" spans="1:5">
+    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A282" s="4">
         <v>46089</v>
       </c>
@@ -5168,7 +4572,7 @@
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
-    <row r="283" spans="1:5">
+    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A283" s="4">
         <v>46090</v>
       </c>
@@ -5181,7 +4585,7 @@
       <c r="D283" s="7"/>
       <c r="E283" s="5"/>
     </row>
-    <row r="284" spans="1:5">
+    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A284" s="4">
         <v>46091</v>
       </c>
@@ -5194,7 +4598,7 @@
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
-    <row r="285" spans="1:5">
+    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A285" s="4">
         <v>46092</v>
       </c>
@@ -5207,7 +4611,7 @@
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
-    <row r="286" spans="1:5">
+    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A286" s="4">
         <v>46093</v>
       </c>
@@ -5220,7 +4624,7 @@
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
-    <row r="287" spans="1:5">
+    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A287" s="4">
         <v>46094</v>
       </c>
@@ -5233,7 +4637,7 @@
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
-    <row r="288" spans="1:5">
+    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A288" s="4">
         <v>46095</v>
       </c>
@@ -5246,7 +4650,7 @@
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
-    <row r="289" spans="1:5">
+    <row r="289" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A289" s="4">
         <v>46096</v>
       </c>
@@ -5259,7 +4663,7 @@
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
-    <row r="290" spans="1:5">
+    <row r="290" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A290" s="4">
         <v>46097</v>
       </c>
@@ -5272,7 +4676,7 @@
       <c r="D290" s="7"/>
       <c r="E290" s="5"/>
     </row>
-    <row r="291" spans="1:5">
+    <row r="291" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A291" s="4">
         <v>46098</v>
       </c>
@@ -5285,7 +4689,7 @@
       <c r="D291" s="7"/>
       <c r="E291" s="5"/>
     </row>
-    <row r="292" spans="1:5">
+    <row r="292" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A292" s="4">
         <v>46099</v>
       </c>
@@ -5298,7 +4702,7 @@
       <c r="D292" s="7"/>
       <c r="E292" s="5"/>
     </row>
-    <row r="293" spans="1:5">
+    <row r="293" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A293" s="4">
         <v>46100</v>
       </c>
@@ -5311,7 +4715,7 @@
       <c r="D293" s="7"/>
       <c r="E293" s="5"/>
     </row>
-    <row r="294" spans="1:5">
+    <row r="294" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A294" s="4">
         <v>46101</v>
       </c>
@@ -5324,7 +4728,7 @@
       <c r="D294" s="7"/>
       <c r="E294" s="5"/>
     </row>
-    <row r="295" spans="1:5">
+    <row r="295" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A295" s="4">
         <v>46102</v>
       </c>
@@ -5337,7 +4741,7 @@
       <c r="D295" s="7"/>
       <c r="E295" s="5"/>
     </row>
-    <row r="296" spans="1:5">
+    <row r="296" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A296" s="4">
         <v>46103</v>
       </c>
@@ -5350,7 +4754,7 @@
       <c r="D296" s="7"/>
       <c r="E296" s="5"/>
     </row>
-    <row r="297" spans="1:5">
+    <row r="297" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A297" s="4">
         <v>46104</v>
       </c>
@@ -5363,7 +4767,7 @@
       <c r="D297" s="7"/>
       <c r="E297" s="5"/>
     </row>
-    <row r="298" spans="1:5">
+    <row r="298" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A298" s="4">
         <v>46105</v>
       </c>
@@ -5376,7 +4780,7 @@
       <c r="D298" s="7"/>
       <c r="E298" s="5"/>
     </row>
-    <row r="299" spans="1:5">
+    <row r="299" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A299" s="4">
         <v>46106</v>
       </c>
@@ -5389,7 +4793,7 @@
       <c r="D299" s="7"/>
       <c r="E299" s="5"/>
     </row>
-    <row r="300" spans="1:5">
+    <row r="300" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A300" s="4">
         <v>46107</v>
       </c>
@@ -5402,7 +4806,7 @@
       <c r="D300" s="7"/>
       <c r="E300" s="5"/>
     </row>
-    <row r="301" spans="1:5">
+    <row r="301" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A301" s="4">
         <v>46108</v>
       </c>
@@ -5415,7 +4819,7 @@
       <c r="D301" s="7"/>
       <c r="E301" s="5"/>
     </row>
-    <row r="302" spans="1:5">
+    <row r="302" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A302" s="4">
         <v>46109</v>
       </c>
@@ -5428,7 +4832,7 @@
       <c r="D302" s="7"/>
       <c r="E302" s="5"/>
     </row>
-    <row r="303" spans="1:5">
+    <row r="303" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A303" s="4">
         <v>46110</v>
       </c>
@@ -5441,7 +4845,7 @@
       <c r="D303" s="7"/>
       <c r="E303" s="5"/>
     </row>
-    <row r="304" spans="1:5">
+    <row r="304" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A304" s="4">
         <v>46111</v>
       </c>
@@ -5454,7 +4858,7 @@
       <c r="D304" s="7"/>
       <c r="E304" s="5"/>
     </row>
-    <row r="305" spans="1:5">
+    <row r="305" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A305" s="4">
         <v>46112</v>
       </c>
@@ -5467,7 +4871,7 @@
       <c r="D305" s="7"/>
       <c r="E305" s="5"/>
     </row>
-    <row r="306" spans="1:5">
+    <row r="306" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A306" s="4">
         <v>46113</v>
       </c>
@@ -5480,7 +4884,7 @@
       <c r="D306" s="7"/>
       <c r="E306" s="5"/>
     </row>
-    <row r="307" spans="1:5">
+    <row r="307" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A307" s="4">
         <v>46114</v>
       </c>
@@ -5493,7 +4897,7 @@
       <c r="D307" s="7"/>
       <c r="E307" s="5"/>
     </row>
-    <row r="308" spans="1:5">
+    <row r="308" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A308" s="4">
         <v>46115</v>
       </c>
@@ -5506,7 +4910,7 @@
       <c r="D308" s="7"/>
       <c r="E308" s="5"/>
     </row>
-    <row r="309" spans="1:5">
+    <row r="309" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A309" s="4">
         <v>46116</v>
       </c>
@@ -5519,7 +4923,7 @@
       <c r="D309" s="7"/>
       <c r="E309" s="5"/>
     </row>
-    <row r="310" spans="1:5">
+    <row r="310" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A310" s="4">
         <v>46117</v>
       </c>
@@ -5532,7 +4936,7 @@
       <c r="D310" s="7"/>
       <c r="E310" s="5"/>
     </row>
-    <row r="311" spans="1:5">
+    <row r="311" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A311" s="4">
         <v>46118</v>
       </c>
@@ -5545,7 +4949,7 @@
       <c r="D311" s="7"/>
       <c r="E311" s="5"/>
     </row>
-    <row r="312" spans="1:5">
+    <row r="312" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A312" s="4">
         <v>46119</v>
       </c>
@@ -5558,7 +4962,7 @@
       <c r="D312" s="7"/>
       <c r="E312" s="5"/>
     </row>
-    <row r="313" spans="1:5">
+    <row r="313" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A313" s="4">
         <v>46120</v>
       </c>
@@ -5571,7 +4975,7 @@
       <c r="D313" s="7"/>
       <c r="E313" s="5"/>
     </row>
-    <row r="314" spans="1:5">
+    <row r="314" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A314" s="4">
         <v>46121</v>
       </c>
@@ -5584,7 +4988,7 @@
       <c r="D314" s="7"/>
       <c r="E314" s="5"/>
     </row>
-    <row r="315" spans="1:5">
+    <row r="315" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A315" s="4">
         <v>46122</v>
       </c>
@@ -5597,7 +5001,7 @@
       <c r="D315" s="7"/>
       <c r="E315" s="5"/>
     </row>
-    <row r="316" spans="1:5">
+    <row r="316" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A316" s="4">
         <v>46123</v>
       </c>
@@ -5610,7 +5014,7 @@
       <c r="D316" s="7"/>
       <c r="E316" s="5"/>
     </row>
-    <row r="317" spans="1:5">
+    <row r="317" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A317" s="4">
         <v>46124</v>
       </c>
@@ -5623,7 +5027,7 @@
       <c r="D317" s="7"/>
       <c r="E317" s="5"/>
     </row>
-    <row r="318" spans="1:5">
+    <row r="318" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A318" s="4">
         <v>46125</v>
       </c>
@@ -5636,7 +5040,7 @@
       <c r="D318" s="7"/>
       <c r="E318" s="5"/>
     </row>
-    <row r="319" spans="1:5">
+    <row r="319" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A319" s="4">
         <v>46126</v>
       </c>
@@ -5649,7 +5053,7 @@
       <c r="D319" s="7"/>
       <c r="E319" s="5"/>
     </row>
-    <row r="320" spans="1:5">
+    <row r="320" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A320" s="4">
         <v>46127</v>
       </c>
@@ -5662,7 +5066,7 @@
       <c r="D320" s="7"/>
       <c r="E320" s="5"/>
     </row>
-    <row r="321" spans="1:5">
+    <row r="321" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A321" s="4">
         <v>46128</v>
       </c>
@@ -5675,7 +5079,7 @@
       <c r="D321" s="7"/>
       <c r="E321" s="5"/>
     </row>
-    <row r="322" spans="1:5">
+    <row r="322" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A322" s="4">
         <v>46129</v>
       </c>
@@ -5688,7 +5092,7 @@
       <c r="D322" s="7"/>
       <c r="E322" s="5"/>
     </row>
-    <row r="323" spans="1:5">
+    <row r="323" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A323" s="4">
         <v>46130</v>
       </c>
@@ -5701,7 +5105,7 @@
       <c r="D323" s="7"/>
       <c r="E323" s="5"/>
     </row>
-    <row r="324" spans="1:5">
+    <row r="324" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A324" s="4">
         <v>46131</v>
       </c>
@@ -5714,7 +5118,7 @@
       <c r="D324" s="7"/>
       <c r="E324" s="5"/>
     </row>
-    <row r="325" spans="1:5">
+    <row r="325" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A325" s="4">
         <v>46132</v>
       </c>
@@ -5727,7 +5131,7 @@
       <c r="D325" s="7"/>
       <c r="E325" s="5"/>
     </row>
-    <row r="326" spans="1:5">
+    <row r="326" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A326" s="4">
         <v>46133</v>
       </c>
@@ -5740,7 +5144,7 @@
       <c r="D326" s="7"/>
       <c r="E326" s="5"/>
     </row>
-    <row r="327" spans="1:5">
+    <row r="327" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A327" s="4">
         <v>46134</v>
       </c>
@@ -5753,7 +5157,7 @@
       <c r="D327" s="7"/>
       <c r="E327" s="5"/>
     </row>
-    <row r="328" spans="1:5">
+    <row r="328" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A328" s="4">
         <v>46135</v>
       </c>
@@ -5766,7 +5170,7 @@
       <c r="D328" s="7"/>
       <c r="E328" s="5"/>
     </row>
-    <row r="329" spans="1:5">
+    <row r="329" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A329" s="4">
         <v>46136</v>
       </c>
@@ -5779,7 +5183,7 @@
       <c r="D329" s="7"/>
       <c r="E329" s="5"/>
     </row>
-    <row r="330" spans="1:5">
+    <row r="330" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A330" s="4">
         <v>46137</v>
       </c>
@@ -5792,7 +5196,7 @@
       <c r="D330" s="7"/>
       <c r="E330" s="5"/>
     </row>
-    <row r="331" spans="1:5">
+    <row r="331" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A331" s="4">
         <v>46138</v>
       </c>
@@ -5805,7 +5209,7 @@
       <c r="D331" s="7"/>
       <c r="E331" s="5"/>
     </row>
-    <row r="332" spans="1:5">
+    <row r="332" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A332" s="4">
         <v>46139</v>
       </c>
@@ -5818,7 +5222,7 @@
       <c r="D332" s="7"/>
       <c r="E332" s="5"/>
     </row>
-    <row r="333" spans="1:5">
+    <row r="333" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A333" s="4">
         <v>46140</v>
       </c>
@@ -5831,7 +5235,7 @@
       <c r="D333" s="7"/>
       <c r="E333" s="5"/>
     </row>
-    <row r="334" spans="1:5">
+    <row r="334" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A334" s="4">
         <v>46141</v>
       </c>
@@ -5844,7 +5248,7 @@
       <c r="D334" s="7"/>
       <c r="E334" s="5"/>
     </row>
-    <row r="335" spans="1:5">
+    <row r="335" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A335" s="4">
         <v>46142</v>
       </c>
@@ -5857,7 +5261,7 @@
       <c r="D335" s="7"/>
       <c r="E335" s="5"/>
     </row>
-    <row r="336" spans="1:5">
+    <row r="336" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A336" s="4">
         <v>46143</v>
       </c>
@@ -5870,7 +5274,7 @@
       <c r="D336" s="7"/>
       <c r="E336" s="5"/>
     </row>
-    <row r="337" spans="1:5">
+    <row r="337" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A337" s="4">
         <v>46144</v>
       </c>
@@ -5883,7 +5287,7 @@
       <c r="D337" s="7"/>
       <c r="E337" s="5"/>
     </row>
-    <row r="338" spans="1:5">
+    <row r="338" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A338" s="4">
         <v>46145</v>
       </c>
@@ -5896,7 +5300,7 @@
       <c r="D338" s="7"/>
       <c r="E338" s="5"/>
     </row>
-    <row r="339" spans="1:5">
+    <row r="339" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A339" s="4">
         <v>46146</v>
       </c>
@@ -5909,7 +5313,7 @@
       <c r="D339" s="7"/>
       <c r="E339" s="5"/>
     </row>
-    <row r="340" spans="1:5">
+    <row r="340" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A340" s="4">
         <v>46147</v>
       </c>
@@ -5922,7 +5326,7 @@
       <c r="D340" s="7"/>
       <c r="E340" s="5"/>
     </row>
-    <row r="341" spans="1:5">
+    <row r="341" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A341" s="4">
         <v>46148</v>
       </c>
@@ -5935,7 +5339,7 @@
       <c r="D341" s="7"/>
       <c r="E341" s="5"/>
     </row>
-    <row r="342" spans="1:5">
+    <row r="342" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A342" s="4">
         <v>46149</v>
       </c>
@@ -5948,7 +5352,7 @@
       <c r="D342" s="7"/>
       <c r="E342" s="5"/>
     </row>
-    <row r="343" spans="1:5">
+    <row r="343" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A343" s="4">
         <v>46150</v>
       </c>
@@ -5961,7 +5365,7 @@
       <c r="D343" s="7"/>
       <c r="E343" s="5"/>
     </row>
-    <row r="344" spans="1:5">
+    <row r="344" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A344" s="4">
         <v>46151</v>
       </c>
@@ -5974,7 +5378,7 @@
       <c r="D344" s="7"/>
       <c r="E344" s="5"/>
     </row>
-    <row r="345" spans="1:5">
+    <row r="345" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A345" s="4">
         <v>46152</v>
       </c>
@@ -5987,7 +5391,7 @@
       <c r="D345" s="7"/>
       <c r="E345" s="5"/>
     </row>
-    <row r="346" spans="1:5">
+    <row r="346" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A346" s="4">
         <v>46153</v>
       </c>
@@ -6000,7 +5404,7 @@
       <c r="D346" s="7"/>
       <c r="E346" s="5"/>
     </row>
-    <row r="347" spans="1:5">
+    <row r="347" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A347" s="4">
         <v>46154</v>
       </c>
@@ -6013,7 +5417,7 @@
       <c r="D347" s="7"/>
       <c r="E347" s="5"/>
     </row>
-    <row r="348" spans="1:5">
+    <row r="348" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A348" s="4">
         <v>46155</v>
       </c>
@@ -6026,7 +5430,7 @@
       <c r="D348" s="7"/>
       <c r="E348" s="5"/>
     </row>
-    <row r="349" spans="1:5">
+    <row r="349" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A349" s="4">
         <v>46156</v>
       </c>
@@ -6039,7 +5443,7 @@
       <c r="D349" s="7"/>
       <c r="E349" s="5"/>
     </row>
-    <row r="350" spans="1:5">
+    <row r="350" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A350" s="4">
         <v>46157</v>
       </c>
@@ -6052,7 +5456,7 @@
       <c r="D350" s="7"/>
       <c r="E350" s="5"/>
     </row>
-    <row r="351" spans="1:5">
+    <row r="351" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A351" s="4">
         <v>46158</v>
       </c>
@@ -6065,7 +5469,7 @@
       <c r="D351" s="7"/>
       <c r="E351" s="5"/>
     </row>
-    <row r="352" spans="1:5">
+    <row r="352" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A352" s="4">
         <v>46159</v>
       </c>
@@ -6078,7 +5482,7 @@
       <c r="D352" s="7"/>
       <c r="E352" s="5"/>
     </row>
-    <row r="353" spans="1:5">
+    <row r="353" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A353" s="4">
         <v>46160</v>
       </c>
@@ -6091,7 +5495,7 @@
       <c r="D353" s="7"/>
       <c r="E353" s="5"/>
     </row>
-    <row r="354" spans="1:5">
+    <row r="354" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A354" s="4">
         <v>46161</v>
       </c>
@@ -6104,7 +5508,7 @@
       <c r="D354" s="7"/>
       <c r="E354" s="5"/>
     </row>
-    <row r="355" spans="1:5">
+    <row r="355" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A355" s="4">
         <v>46162</v>
       </c>
@@ -6117,7 +5521,7 @@
       <c r="D355" s="7"/>
       <c r="E355" s="5"/>
     </row>
-    <row r="356" spans="1:5">
+    <row r="356" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A356" s="4">
         <v>46163</v>
       </c>
@@ -6130,7 +5534,7 @@
       <c r="D356" s="7"/>
       <c r="E356" s="5"/>
     </row>
-    <row r="357" spans="1:5">
+    <row r="357" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A357" s="4">
         <v>46164</v>
       </c>
@@ -6143,7 +5547,7 @@
       <c r="D357" s="7"/>
       <c r="E357" s="5"/>
     </row>
-    <row r="358" spans="1:5">
+    <row r="358" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A358" s="4">
         <v>46165</v>
       </c>
@@ -6156,7 +5560,7 @@
       <c r="D358" s="7"/>
       <c r="E358" s="5"/>
     </row>
-    <row r="359" spans="1:5">
+    <row r="359" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A359" s="4">
         <v>46166</v>
       </c>
@@ -6169,7 +5573,7 @@
       <c r="D359" s="7"/>
       <c r="E359" s="5"/>
     </row>
-    <row r="360" spans="1:5">
+    <row r="360" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A360" s="4">
         <v>46167</v>
       </c>
@@ -6182,7 +5586,7 @@
       <c r="D360" s="7"/>
       <c r="E360" s="5"/>
     </row>
-    <row r="361" spans="1:5">
+    <row r="361" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A361" s="4">
         <v>46168</v>
       </c>
@@ -6195,7 +5599,7 @@
       <c r="D361" s="7"/>
       <c r="E361" s="5"/>
     </row>
-    <row r="362" spans="1:5">
+    <row r="362" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A362" s="4">
         <v>46169</v>
       </c>
@@ -6208,7 +5612,7 @@
       <c r="D362" s="7"/>
       <c r="E362" s="5"/>
     </row>
-    <row r="363" spans="1:5">
+    <row r="363" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A363" s="4">
         <v>46170</v>
       </c>
@@ -6221,7 +5625,7 @@
       <c r="D363" s="7"/>
       <c r="E363" s="5"/>
     </row>
-    <row r="364" spans="1:5">
+    <row r="364" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A364" s="4">
         <v>46171</v>
       </c>
@@ -6234,7 +5638,7 @@
       <c r="D364" s="7"/>
       <c r="E364" s="5"/>
     </row>
-    <row r="365" spans="1:5">
+    <row r="365" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A365" s="4">
         <v>46172</v>
       </c>
@@ -6247,7 +5651,7 @@
       <c r="D365" s="7"/>
       <c r="E365" s="5"/>
     </row>
-    <row r="366" spans="1:5">
+    <row r="366" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A366" s="4">
         <v>46173</v>
       </c>
@@ -6260,7 +5664,7 @@
       <c r="D366" s="7"/>
       <c r="E366" s="5"/>
     </row>
-    <row r="367" spans="1:5">
+    <row r="367" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A367" s="4">
         <v>46174</v>
       </c>
@@ -6273,7 +5677,7 @@
       <c r="D367" s="7"/>
       <c r="E367" s="5"/>
     </row>
-    <row r="368" spans="1:5">
+    <row r="368" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A368" s="4">
         <v>46175</v>
       </c>
@@ -6286,7 +5690,7 @@
       <c r="D368" s="7"/>
       <c r="E368" s="5"/>
     </row>
-    <row r="369" spans="1:5">
+    <row r="369" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A369" s="4">
         <v>46176</v>
       </c>
@@ -6299,7 +5703,7 @@
       <c r="D369" s="7"/>
       <c r="E369" s="5"/>
     </row>
-    <row r="370" spans="1:5">
+    <row r="370" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A370" s="4">
         <v>46177</v>
       </c>
@@ -6312,7 +5716,7 @@
       <c r="D370" s="7"/>
       <c r="E370" s="5"/>
     </row>
-    <row r="371" spans="1:5">
+    <row r="371" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A371" s="4">
         <v>46178</v>
       </c>
@@ -6325,7 +5729,7 @@
       <c r="D371" s="7"/>
       <c r="E371" s="5"/>
     </row>
-    <row r="372" spans="1:5">
+    <row r="372" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A372" s="4">
         <v>46179</v>
       </c>
@@ -6338,7 +5742,7 @@
       <c r="D372" s="7"/>
       <c r="E372" s="5"/>
     </row>
-    <row r="373" spans="1:5">
+    <row r="373" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A373" s="4">
         <v>46180</v>
       </c>
@@ -6351,7 +5755,7 @@
       <c r="D373" s="7"/>
       <c r="E373" s="5"/>
     </row>
-    <row r="374" spans="1:5">
+    <row r="374" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A374" s="4">
         <v>46181</v>
       </c>
@@ -6364,7 +5768,7 @@
       <c r="D374" s="7"/>
       <c r="E374" s="5"/>
     </row>
-    <row r="375" spans="1:5">
+    <row r="375" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A375" s="4">
         <v>46182</v>
       </c>
@@ -6377,7 +5781,7 @@
       <c r="D375" s="7"/>
       <c r="E375" s="5"/>
     </row>
-    <row r="376" spans="1:5">
+    <row r="376" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A376" s="4">
         <v>46183</v>
       </c>
@@ -6390,7 +5794,7 @@
       <c r="D376" s="7"/>
       <c r="E376" s="5"/>
     </row>
-    <row r="377" spans="1:5">
+    <row r="377" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A377" s="4">
         <v>46184</v>
       </c>
@@ -6403,7 +5807,7 @@
       <c r="D377" s="7"/>
       <c r="E377" s="5"/>
     </row>
-    <row r="378" spans="1:5">
+    <row r="378" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A378" s="4">
         <v>46185</v>
       </c>
@@ -6416,7 +5820,7 @@
       <c r="D378" s="7"/>
       <c r="E378" s="5"/>
     </row>
-    <row r="379" spans="1:5">
+    <row r="379" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A379" s="4">
         <v>46186</v>
       </c>
@@ -6429,7 +5833,7 @@
       <c r="D379" s="7"/>
       <c r="E379" s="5"/>
     </row>
-    <row r="380" spans="1:5">
+    <row r="380" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A380" s="4">
         <v>46187</v>
       </c>
@@ -6442,7 +5846,7 @@
       <c r="D380" s="7"/>
       <c r="E380" s="5"/>
     </row>
-    <row r="381" spans="1:5">
+    <row r="381" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A381" s="4">
         <v>46188</v>
       </c>
@@ -6455,7 +5859,7 @@
       <c r="D381" s="7"/>
       <c r="E381" s="5"/>
     </row>
-    <row r="382" spans="1:5">
+    <row r="382" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A382" s="4">
         <v>46189</v>
       </c>
@@ -6468,7 +5872,7 @@
       <c r="D382" s="7"/>
       <c r="E382" s="5"/>
     </row>
-    <row r="383" spans="1:5">
+    <row r="383" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A383" s="4">
         <v>46190</v>
       </c>
@@ -6481,7 +5885,7 @@
       <c r="D383" s="7"/>
       <c r="E383" s="5"/>
     </row>
-    <row r="384" spans="1:5">
+    <row r="384" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A384" s="4">
         <v>46191</v>
       </c>
@@ -6494,7 +5898,7 @@
       <c r="D384" s="7"/>
       <c r="E384" s="5"/>
     </row>
-    <row r="385" spans="1:5">
+    <row r="385" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A385" s="4">
         <v>46192</v>
       </c>
@@ -6507,7 +5911,7 @@
       <c r="D385" s="7"/>
       <c r="E385" s="5"/>
     </row>
-    <row r="386" spans="1:5">
+    <row r="386" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A386" s="4">
         <v>46193</v>
       </c>
@@ -6520,7 +5924,7 @@
       <c r="D386" s="7"/>
       <c r="E386" s="5"/>
     </row>
-    <row r="387" spans="1:5">
+    <row r="387" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A387" s="4">
         <v>46194</v>
       </c>
@@ -6533,7 +5937,7 @@
       <c r="D387" s="7"/>
       <c r="E387" s="5"/>
     </row>
-    <row r="388" spans="1:5">
+    <row r="388" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A388" s="4">
         <v>46195</v>
       </c>
@@ -6546,7 +5950,7 @@
       <c r="D388" s="7"/>
       <c r="E388" s="5"/>
     </row>
-    <row r="389" spans="1:5">
+    <row r="389" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A389" s="4">
         <v>46196</v>
       </c>
@@ -6559,7 +5963,7 @@
       <c r="D389" s="7"/>
       <c r="E389" s="5"/>
     </row>
-    <row r="390" spans="1:5">
+    <row r="390" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A390" s="4">
         <v>46197</v>
       </c>
@@ -6572,7 +5976,7 @@
       <c r="D390" s="7"/>
       <c r="E390" s="5"/>
     </row>
-    <row r="391" spans="1:5">
+    <row r="391" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A391" s="4">
         <v>46198</v>
       </c>
@@ -6585,7 +5989,7 @@
       <c r="D391" s="7"/>
       <c r="E391" s="5"/>
     </row>
-    <row r="392" spans="1:5">
+    <row r="392" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A392" s="4">
         <v>46199</v>
       </c>
@@ -6598,7 +6002,7 @@
       <c r="D392" s="7"/>
       <c r="E392" s="5"/>
     </row>
-    <row r="393" spans="1:5">
+    <row r="393" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A393" s="4">
         <v>46200</v>
       </c>
@@ -6611,7 +6015,7 @@
       <c r="D393" s="7"/>
       <c r="E393" s="5"/>
     </row>
-    <row r="394" spans="1:5">
+    <row r="394" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A394" s="4">
         <v>46201</v>
       </c>
@@ -6624,7 +6028,7 @@
       <c r="D394" s="7"/>
       <c r="E394" s="5"/>
     </row>
-    <row r="395" spans="1:5">
+    <row r="395" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A395" s="4">
         <v>46202</v>
       </c>
@@ -6637,7 +6041,7 @@
       <c r="D395" s="7"/>
       <c r="E395" s="5"/>
     </row>
-    <row r="396" spans="1:5">
+    <row r="396" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A396" s="4">
         <v>46203</v>
       </c>
@@ -6650,7 +6054,7 @@
       <c r="D396" s="7"/>
       <c r="E396" s="5"/>
     </row>
-    <row r="397" spans="1:5">
+    <row r="397" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A397" s="4">
         <v>46204</v>
       </c>
@@ -6663,7 +6067,7 @@
       <c r="D397" s="7"/>
       <c r="E397" s="5"/>
     </row>
-    <row r="398" spans="1:5">
+    <row r="398" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A398" s="4">
         <v>46205</v>
       </c>
@@ -6676,7 +6080,7 @@
       <c r="D398" s="7"/>
       <c r="E398" s="5"/>
     </row>
-    <row r="399" spans="1:5">
+    <row r="399" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A399" s="4">
         <v>46206</v>
       </c>
@@ -6689,7 +6093,7 @@
       <c r="D399" s="7"/>
       <c r="E399" s="5"/>
     </row>
-    <row r="400" spans="1:5">
+    <row r="400" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A400" s="4">
         <v>46207</v>
       </c>
@@ -6702,7 +6106,7 @@
       <c r="D400" s="7"/>
       <c r="E400" s="5"/>
     </row>
-    <row r="401" spans="1:5">
+    <row r="401" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A401" s="4">
         <v>46208</v>
       </c>
@@ -6715,7 +6119,7 @@
       <c r="D401" s="7"/>
       <c r="E401" s="5"/>
     </row>
-    <row r="402" spans="1:5">
+    <row r="402" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A402" s="4">
         <v>46209</v>
       </c>
@@ -6728,7 +6132,7 @@
       <c r="D402" s="7"/>
       <c r="E402" s="5"/>
     </row>
-    <row r="403" spans="1:5">
+    <row r="403" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A403" s="4">
         <v>46210</v>
       </c>
@@ -6741,7 +6145,7 @@
       <c r="D403" s="7"/>
       <c r="E403" s="5"/>
     </row>
-    <row r="404" spans="1:5">
+    <row r="404" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A404" s="4">
         <v>46211</v>
       </c>
@@ -6754,7 +6158,7 @@
       <c r="D404" s="7"/>
       <c r="E404" s="5"/>
     </row>
-    <row r="405" spans="1:5">
+    <row r="405" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A405" s="4">
         <v>46212</v>
       </c>
@@ -6767,7 +6171,7 @@
       <c r="D405" s="7"/>
       <c r="E405" s="5"/>
     </row>
-    <row r="406" spans="1:5">
+    <row r="406" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A406" s="4">
         <v>46213</v>
       </c>
@@ -6780,7 +6184,7 @@
       <c r="D406" s="7"/>
       <c r="E406" s="5"/>
     </row>
-    <row r="407" spans="1:5">
+    <row r="407" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A407" s="4">
         <v>46214</v>
       </c>
@@ -6793,7 +6197,7 @@
       <c r="D407" s="7"/>
       <c r="E407" s="5"/>
     </row>
-    <row r="408" spans="1:5">
+    <row r="408" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A408" s="4">
         <v>46215</v>
       </c>
@@ -6806,7 +6210,7 @@
       <c r="D408" s="7"/>
       <c r="E408" s="5"/>
     </row>
-    <row r="409" spans="1:5">
+    <row r="409" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A409" s="4">
         <v>46216</v>
       </c>
@@ -6819,7 +6223,7 @@
       <c r="D409" s="7"/>
       <c r="E409" s="5"/>
     </row>
-    <row r="410" spans="1:5">
+    <row r="410" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A410" s="4">
         <v>46217</v>
       </c>
@@ -6832,7 +6236,7 @@
       <c r="D410" s="7"/>
       <c r="E410" s="5"/>
     </row>
-    <row r="411" spans="1:5">
+    <row r="411" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A411" s="4">
         <v>46218</v>
       </c>
@@ -6845,7 +6249,7 @@
       <c r="D411" s="7"/>
       <c r="E411" s="5"/>
     </row>
-    <row r="412" spans="1:5">
+    <row r="412" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A412" s="4">
         <v>46219</v>
       </c>
@@ -6858,7 +6262,7 @@
       <c r="D412" s="7"/>
       <c r="E412" s="5"/>
     </row>
-    <row r="413" spans="1:5">
+    <row r="413" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A413" s="4">
         <v>46220</v>
       </c>
@@ -6871,7 +6275,7 @@
       <c r="D413" s="7"/>
       <c r="E413" s="5"/>
     </row>
-    <row r="414" spans="1:5">
+    <row r="414" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A414" s="4">
         <v>46221</v>
       </c>
@@ -6884,7 +6288,7 @@
       <c r="D414" s="7"/>
       <c r="E414" s="5"/>
     </row>
-    <row r="415" spans="1:5">
+    <row r="415" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A415" s="4">
         <v>46222</v>
       </c>
@@ -6897,7 +6301,7 @@
       <c r="D415" s="7"/>
       <c r="E415" s="5"/>
     </row>
-    <row r="416" spans="1:5">
+    <row r="416" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A416" s="4">
         <v>46223</v>
       </c>
@@ -6910,7 +6314,7 @@
       <c r="D416" s="7"/>
       <c r="E416" s="5"/>
     </row>
-    <row r="417" spans="1:5">
+    <row r="417" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A417" s="4">
         <v>46224</v>
       </c>
@@ -6923,7 +6327,7 @@
       <c r="D417" s="7"/>
       <c r="E417" s="5"/>
     </row>
-    <row r="418" spans="1:5">
+    <row r="418" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A418" s="4">
         <v>46225</v>
       </c>
@@ -6936,7 +6340,7 @@
       <c r="D418" s="7"/>
       <c r="E418" s="5"/>
     </row>
-    <row r="419" spans="1:5">
+    <row r="419" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A419" s="4">
         <v>46226</v>
       </c>
@@ -6949,7 +6353,7 @@
       <c r="D419" s="7"/>
       <c r="E419" s="5"/>
     </row>
-    <row r="420" spans="1:5">
+    <row r="420" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A420" s="4">
         <v>46227</v>
       </c>
@@ -6962,7 +6366,7 @@
       <c r="D420" s="7"/>
       <c r="E420" s="5"/>
     </row>
-    <row r="421" spans="1:5">
+    <row r="421" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A421" s="4">
         <v>46228</v>
       </c>
@@ -6975,7 +6379,7 @@
       <c r="D421" s="7"/>
       <c r="E421" s="5"/>
     </row>
-    <row r="422" spans="1:5">
+    <row r="422" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A422" s="4">
         <v>46229</v>
       </c>
@@ -6988,7 +6392,7 @@
       <c r="D422" s="7"/>
       <c r="E422" s="5"/>
     </row>
-    <row r="423" spans="1:5">
+    <row r="423" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A423" s="4">
         <v>46230</v>
       </c>
@@ -7001,7 +6405,7 @@
       <c r="D423" s="7"/>
       <c r="E423" s="5"/>
     </row>
-    <row r="424" spans="1:5">
+    <row r="424" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A424" s="4">
         <v>46231</v>
       </c>
@@ -7014,7 +6418,7 @@
       <c r="D424" s="7"/>
       <c r="E424" s="5"/>
     </row>
-    <row r="425" spans="1:5">
+    <row r="425" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A425" s="4">
         <v>46232</v>
       </c>
@@ -7027,7 +6431,7 @@
       <c r="D425" s="7"/>
       <c r="E425" s="5"/>
     </row>
-    <row r="426" spans="1:5">
+    <row r="426" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A426" s="4">
         <v>46233</v>
       </c>
@@ -7040,7 +6444,7 @@
       <c r="D426" s="7"/>
       <c r="E426" s="5"/>
     </row>
-    <row r="427" spans="1:5">
+    <row r="427" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A427" s="4">
         <v>46234</v>
       </c>
@@ -7053,7 +6457,7 @@
       <c r="D427" s="7"/>
       <c r="E427" s="5"/>
     </row>
-    <row r="428" spans="1:5">
+    <row r="428" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A428" s="4">
         <v>46235</v>
       </c>
@@ -7066,7 +6470,7 @@
       <c r="D428" s="7"/>
       <c r="E428" s="5"/>
     </row>
-    <row r="429" spans="1:5">
+    <row r="429" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A429" s="4">
         <v>46236</v>
       </c>
@@ -7079,7 +6483,7 @@
       <c r="D429" s="7"/>
       <c r="E429" s="5"/>
     </row>
-    <row r="430" spans="1:5">
+    <row r="430" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A430" s="4">
         <v>46237</v>
       </c>
@@ -7092,7 +6496,7 @@
       <c r="D430" s="7"/>
       <c r="E430" s="5"/>
     </row>
-    <row r="431" spans="1:5">
+    <row r="431" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A431" s="4">
         <v>46238</v>
       </c>
@@ -7105,7 +6509,7 @@
       <c r="D431" s="7"/>
       <c r="E431" s="5"/>
     </row>
-    <row r="432" spans="1:5">
+    <row r="432" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A432" s="4">
         <v>46239</v>
       </c>
@@ -7118,7 +6522,7 @@
       <c r="D432" s="7"/>
       <c r="E432" s="5"/>
     </row>
-    <row r="433" spans="1:5">
+    <row r="433" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A433" s="4">
         <v>46240</v>
       </c>
@@ -7131,7 +6535,7 @@
       <c r="D433" s="7"/>
       <c r="E433" s="5"/>
     </row>
-    <row r="434" spans="1:5">
+    <row r="434" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A434" s="4">
         <v>46241</v>
       </c>
@@ -7144,7 +6548,7 @@
       <c r="D434" s="7"/>
       <c r="E434" s="5"/>
     </row>
-    <row r="435" spans="1:5">
+    <row r="435" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A435" s="4">
         <v>46242</v>
       </c>
@@ -7157,7 +6561,7 @@
       <c r="D435" s="7"/>
       <c r="E435" s="5"/>
     </row>
-    <row r="436" spans="1:5">
+    <row r="436" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A436" s="4">
         <v>46243</v>
       </c>
@@ -7170,7 +6574,7 @@
       <c r="D436" s="7"/>
       <c r="E436" s="5"/>
     </row>
-    <row r="437" spans="1:5">
+    <row r="437" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A437" s="4">
         <v>46244</v>
       </c>
@@ -7183,7 +6587,7 @@
       <c r="D437" s="7"/>
       <c r="E437" s="5"/>
     </row>
-    <row r="438" spans="1:5">
+    <row r="438" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A438" s="4">
         <v>46245</v>
       </c>
@@ -7196,7 +6600,7 @@
       <c r="D438" s="7"/>
       <c r="E438" s="5"/>
     </row>
-    <row r="439" spans="1:5">
+    <row r="439" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A439" s="4">
         <v>46246</v>
       </c>
@@ -7209,7 +6613,7 @@
       <c r="D439" s="7"/>
       <c r="E439" s="5"/>
     </row>
-    <row r="440" spans="1:5">
+    <row r="440" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A440" s="4">
         <v>46247</v>
       </c>
@@ -7222,7 +6626,7 @@
       <c r="D440" s="7"/>
       <c r="E440" s="5"/>
     </row>
-    <row r="441" spans="1:5">
+    <row r="441" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A441" s="4">
         <v>46248</v>
       </c>
@@ -7235,7 +6639,7 @@
       <c r="D441" s="7"/>
       <c r="E441" s="5"/>
     </row>
-    <row r="442" spans="1:5">
+    <row r="442" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A442" s="4">
         <v>46249</v>
       </c>
@@ -7248,7 +6652,7 @@
       <c r="D442" s="7"/>
       <c r="E442" s="5"/>
     </row>
-    <row r="443" spans="1:5">
+    <row r="443" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A443" s="4">
         <v>46250</v>
       </c>
@@ -7261,7 +6665,7 @@
       <c r="D443" s="7"/>
       <c r="E443" s="5"/>
     </row>
-    <row r="444" spans="1:5">
+    <row r="444" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A444" s="4">
         <v>46251</v>
       </c>
@@ -7274,7 +6678,7 @@
       <c r="D444" s="7"/>
       <c r="E444" s="5"/>
     </row>
-    <row r="445" spans="1:5">
+    <row r="445" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A445" s="4">
         <v>46252</v>
       </c>
@@ -7287,7 +6691,7 @@
       <c r="D445" s="7"/>
       <c r="E445" s="5"/>
     </row>
-    <row r="446" spans="1:5">
+    <row r="446" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A446" s="4">
         <v>46253</v>
       </c>
@@ -7300,7 +6704,7 @@
       <c r="D446" s="7"/>
       <c r="E446" s="5"/>
     </row>
-    <row r="447" spans="1:5">
+    <row r="447" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A447" s="4">
         <v>46254</v>
       </c>
@@ -7313,7 +6717,7 @@
       <c r="D447" s="7"/>
       <c r="E447" s="5"/>
     </row>
-    <row r="448" spans="1:5">
+    <row r="448" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A448" s="4">
         <v>46255</v>
       </c>
@@ -7326,7 +6730,7 @@
       <c r="D448" s="7"/>
       <c r="E448" s="5"/>
     </row>
-    <row r="449" spans="1:5">
+    <row r="449" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A449" s="4">
         <v>46256</v>
       </c>
@@ -7339,7 +6743,7 @@
       <c r="D449" s="7"/>
       <c r="E449" s="5"/>
     </row>
-    <row r="450" spans="1:5">
+    <row r="450" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A450" s="4">
         <v>46257</v>
       </c>
@@ -7352,7 +6756,7 @@
       <c r="D450" s="7"/>
       <c r="E450" s="5"/>
     </row>
-    <row r="451" spans="1:5">
+    <row r="451" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A451" s="4">
         <v>46258</v>
       </c>
@@ -7365,7 +6769,7 @@
       <c r="D451" s="7"/>
       <c r="E451" s="5"/>
     </row>
-    <row r="452" spans="1:5">
+    <row r="452" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A452" s="4">
         <v>46259</v>
       </c>
@@ -7378,7 +6782,7 @@
       <c r="D452" s="7"/>
       <c r="E452" s="5"/>
     </row>
-    <row r="453" spans="1:5">
+    <row r="453" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A453" s="4">
         <v>46260</v>
       </c>
@@ -7391,7 +6795,7 @@
       <c r="D453" s="7"/>
       <c r="E453" s="5"/>
     </row>
-    <row r="454" spans="1:5">
+    <row r="454" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A454" s="4">
         <v>46261</v>
       </c>
@@ -7404,7 +6808,7 @@
       <c r="D454" s="7"/>
       <c r="E454" s="5"/>
     </row>
-    <row r="455" spans="1:5">
+    <row r="455" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A455" s="4">
         <v>46262</v>
       </c>
@@ -7417,7 +6821,7 @@
       <c r="D455" s="7"/>
       <c r="E455" s="5"/>
     </row>
-    <row r="456" spans="1:5">
+    <row r="456" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A456" s="4">
         <v>46263</v>
       </c>
@@ -7430,7 +6834,7 @@
       <c r="D456" s="7"/>
       <c r="E456" s="5"/>
     </row>
-    <row r="457" spans="1:5">
+    <row r="457" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A457" s="4">
         <v>46264</v>
       </c>
@@ -7443,7 +6847,7 @@
       <c r="D457" s="7"/>
       <c r="E457" s="5"/>
     </row>
-    <row r="458" spans="1:5">
+    <row r="458" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A458" s="4">
         <v>46265</v>
       </c>
@@ -7456,7 +6860,7 @@
       <c r="D458" s="7"/>
       <c r="E458" s="5"/>
     </row>
-    <row r="459" spans="1:5">
+    <row r="459" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A459" s="4">
         <v>46266</v>
       </c>
@@ -7469,7 +6873,7 @@
       <c r="D459" s="7"/>
       <c r="E459" s="5"/>
     </row>
-    <row r="460" spans="1:5">
+    <row r="460" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A460" s="4">
         <v>46267</v>
       </c>
@@ -7482,7 +6886,7 @@
       <c r="D460" s="7"/>
       <c r="E460" s="5"/>
     </row>
-    <row r="461" spans="1:5">
+    <row r="461" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A461" s="4">
         <v>46268</v>
       </c>
@@ -7495,7 +6899,7 @@
       <c r="D461" s="7"/>
       <c r="E461" s="5"/>
     </row>
-    <row r="462" spans="1:5">
+    <row r="462" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A462" s="4">
         <v>46269</v>
       </c>
@@ -7508,7 +6912,7 @@
       <c r="D462" s="7"/>
       <c r="E462" s="5"/>
     </row>
-    <row r="463" spans="1:5">
+    <row r="463" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A463" s="4">
         <v>46270</v>
       </c>
@@ -7521,7 +6925,7 @@
       <c r="D463" s="7"/>
       <c r="E463" s="5"/>
     </row>
-    <row r="464" spans="1:5">
+    <row r="464" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A464" s="4">
         <v>46271</v>
       </c>
@@ -7534,7 +6938,7 @@
       <c r="D464" s="7"/>
       <c r="E464" s="5"/>
     </row>
-    <row r="465" spans="1:5">
+    <row r="465" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A465" s="4">
         <v>46272</v>
       </c>
@@ -7547,7 +6951,7 @@
       <c r="D465" s="7"/>
       <c r="E465" s="5"/>
     </row>
-    <row r="466" spans="1:5">
+    <row r="466" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A466" s="4">
         <v>46273</v>
       </c>
@@ -7560,7 +6964,7 @@
       <c r="D466" s="7"/>
       <c r="E466" s="5"/>
     </row>
-    <row r="467" spans="1:5">
+    <row r="467" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A467" s="4">
         <v>46274</v>
       </c>
@@ -7573,7 +6977,7 @@
       <c r="D467" s="7"/>
       <c r="E467" s="5"/>
     </row>
-    <row r="468" spans="1:5">
+    <row r="468" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A468" s="4">
         <v>46275</v>
       </c>
@@ -7586,7 +6990,7 @@
       <c r="D468" s="7"/>
       <c r="E468" s="5"/>
     </row>
-    <row r="469" spans="1:5">
+    <row r="469" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A469" s="4">
         <v>46276</v>
       </c>
@@ -7599,7 +7003,7 @@
       <c r="D469" s="7"/>
       <c r="E469" s="5"/>
     </row>
-    <row r="470" spans="1:5">
+    <row r="470" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A470" s="4">
         <v>46277</v>
       </c>
@@ -7612,7 +7016,7 @@
       <c r="D470" s="7"/>
       <c r="E470" s="5"/>
     </row>
-    <row r="471" spans="1:5">
+    <row r="471" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A471" s="4">
         <v>46278</v>
       </c>
@@ -7625,7 +7029,7 @@
       <c r="D471" s="7"/>
       <c r="E471" s="5"/>
     </row>
-    <row r="472" spans="1:5">
+    <row r="472" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A472" s="4">
         <v>46279</v>
       </c>
@@ -7638,7 +7042,7 @@
       <c r="D472" s="7"/>
       <c r="E472" s="5"/>
     </row>
-    <row r="473" spans="1:3">
+    <row r="473" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A473" s="1">
         <v>46280</v>
       </c>
@@ -7649,7 +7053,7 @@
         <v>555550</v>
       </c>
     </row>
-    <row r="474" spans="1:3">
+    <row r="474" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A474" s="1">
         <v>46281</v>
       </c>
@@ -7660,7 +7064,7 @@
         <v>516570</v>
       </c>
     </row>
-    <row r="475" spans="1:3">
+    <row r="475" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A475" s="1">
         <v>46282</v>
       </c>
@@ -7671,7 +7075,7 @@
         <v>595650</v>
       </c>
     </row>
-    <row r="476" spans="1:3">
+    <row r="476" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A476" s="1">
         <v>46283</v>
       </c>
@@ -7682,7 +7086,7 @@
         <v>658970</v>
       </c>
     </row>
-    <row r="477" spans="1:3">
+    <row r="477" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A477" s="1">
         <v>46284</v>
       </c>
@@ -7693,7 +7097,7 @@
         <v>626120</v>
       </c>
     </row>
-    <row r="478" spans="1:3">
+    <row r="478" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A478" s="1">
         <v>46285</v>
       </c>
@@ -7704,7 +7108,7 @@
         <v>652800</v>
       </c>
     </row>
-    <row r="479" spans="1:3">
+    <row r="479" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A479" s="1">
         <v>46286</v>
       </c>
@@ -7715,7 +7119,7 @@
         <v>628280</v>
       </c>
     </row>
-    <row r="480" spans="1:3">
+    <row r="480" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A480" s="1">
         <v>46287</v>
       </c>
@@ -7726,7 +7130,7 @@
         <v>611160</v>
       </c>
     </row>
-    <row r="481" spans="1:3">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A481" s="1">
         <v>46288</v>
       </c>
@@ -7737,7 +7141,7 @@
         <v>519580</v>
       </c>
     </row>
-    <row r="482" spans="1:3">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A482" s="1">
         <v>46289</v>
       </c>
@@ -7748,7 +7152,7 @@
         <v>564680</v>
       </c>
     </row>
-    <row r="483" spans="1:3">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A483" s="1">
         <v>46290</v>
       </c>
@@ -7759,7 +7163,7 @@
         <v>710760</v>
       </c>
     </row>
-    <row r="484" spans="1:3">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A484" s="1">
         <v>46291</v>
       </c>
@@ -7770,7 +7174,7 @@
         <v>602540</v>
       </c>
     </row>
-    <row r="485" spans="1:3">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A485" s="1">
         <v>46292</v>
       </c>
@@ -7781,7 +7185,7 @@
         <v>626500</v>
       </c>
     </row>
-    <row r="486" spans="1:3">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A486" s="1">
         <v>46293</v>
       </c>
@@ -7792,7 +7196,7 @@
         <v>534220</v>
       </c>
     </row>
-    <row r="487" spans="1:3">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A487" s="1">
         <v>46294</v>
       </c>
@@ -7803,27 +7207,32 @@
         <v>597240</v>
       </c>
     </row>
-    <row r="488" spans="1:2">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A488" s="1">
         <v>46295</v>
       </c>
       <c r="B488" t="s">
         <v>38</v>
       </c>
+      <c r="C488">
+        <v>646720</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E487">
-    <sortState ref="A1:E487">
-      <sortCondition ref="A2:A897"/>
-    </sortState>
-    <extLst/>
-  </autoFilter>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B15 B35:B64 B86:B472">
-      <formula1>店舗マスタ!$A$2:$A$31</formula1>
-    </dataValidation>
-  </dataValidations>
+  <autoFilter ref="A1:E488" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
+  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" xr:uid="{00000000-0002-0000-0200-000000000000}">
+          <x14:formula1>
+            <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
+          </x14:formula1>
+          <xm:sqref>B2:B15 B35:B64 B86:B472</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\KYOYU-PC\Users\ビッグボス画像共有フォルダ\【迷惑メール】開いたら危険！\incoming\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C597657-54C4-4129-B3BE-4404CAEFFB9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -20,23 +14,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$488</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -179,11 +162,15 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -196,38 +183,171 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
       <charset val="128"/>
     </font>
     <font>
-      <sz val="6"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -240,8 +360,194 @@
         <bgColor rgb="FF4E79A7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -264,9 +570,251 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -291,17 +839,61 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="桁区切り[0]" xfId="1" builtinId="6"/>
+    <cellStyle name="入力" xfId="2" builtinId="20"/>
+    <cellStyle name="桁区切り" xfId="3" builtinId="3"/>
+    <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
+    <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
+    <cellStyle name="通貨" xfId="6" builtinId="4"/>
+    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
+    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
+    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="良い" xfId="13" builtinId="26"/>
+    <cellStyle name="警告文" xfId="14" builtinId="11"/>
+    <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
+    <cellStyle name="タイトル" xfId="16" builtinId="15"/>
+    <cellStyle name="説明文" xfId="17" builtinId="53"/>
+    <cellStyle name="アクセント 6" xfId="18" builtinId="49"/>
+    <cellStyle name="出力" xfId="19" builtinId="21"/>
+    <cellStyle name="見出し 1" xfId="20" builtinId="16"/>
+    <cellStyle name="見出し 2" xfId="21" builtinId="17"/>
+    <cellStyle name="計算" xfId="22" builtinId="22"/>
+    <cellStyle name="見出し 3" xfId="23" builtinId="18"/>
+    <cellStyle name="見出し 4" xfId="24" builtinId="19"/>
+    <cellStyle name="60% - アクセント 5" xfId="25" builtinId="48"/>
+    <cellStyle name="チェックセル" xfId="26" builtinId="23"/>
+    <cellStyle name="40% - アクセント 1" xfId="27" builtinId="31"/>
+    <cellStyle name="集計" xfId="28" builtinId="25"/>
+    <cellStyle name="悪い" xfId="29" builtinId="27"/>
+    <cellStyle name="どちらでもない" xfId="30" builtinId="28"/>
+    <cellStyle name="アクセント 1" xfId="31" builtinId="29"/>
+    <cellStyle name="20% - アクセント 1" xfId="32" builtinId="30"/>
+    <cellStyle name="20% - アクセント 5" xfId="33" builtinId="46"/>
+    <cellStyle name="60% - アクセント 1" xfId="34" builtinId="32"/>
+    <cellStyle name="20% - アクセント 2" xfId="35" builtinId="34"/>
+    <cellStyle name="40% - アクセント 2" xfId="36" builtinId="35"/>
+    <cellStyle name="20% - アクセント 6" xfId="37" builtinId="50"/>
+    <cellStyle name="60% - アクセント 2" xfId="38" builtinId="36"/>
+    <cellStyle name="アクセント 3" xfId="39" builtinId="37"/>
+    <cellStyle name="20% - アクセント 3" xfId="40" builtinId="38"/>
+    <cellStyle name="40% - アクセント 3" xfId="41" builtinId="39"/>
+    <cellStyle name="60% - アクセント 3" xfId="42" builtinId="40"/>
+    <cellStyle name="アクセント 4" xfId="43" builtinId="41"/>
+    <cellStyle name="40% - アクセント 4" xfId="44" builtinId="43"/>
+    <cellStyle name="60% - アクセント 4" xfId="45" builtinId="44"/>
+    <cellStyle name="アクセント 5" xfId="46" builtinId="45"/>
+    <cellStyle name="40% - アクセント 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - アクセント 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -586,315 +1178,317 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="17.25" x14ac:dyDescent="0.15">
+    <row r="1" ht="17.25" spans="1:1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="9"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="9" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="9"/>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="9" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="9" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="9" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="9"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="9" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="9" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="9"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="10" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="9" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="9" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="9" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="9" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="9" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="9"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="9" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="9" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:1">
       <c r="A32" s="9" t="s">
         <v>26</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A31"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:1">
       <c r="A1" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:1">
       <c r="A2" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:1">
       <c r="A3" s="5" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:1">
       <c r="A4" s="5" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:1">
       <c r="A5" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:1">
       <c r="A6" s="5" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:1">
       <c r="A7" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:1">
       <c r="A8" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:1">
       <c r="A9" s="5" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:1">
       <c r="A10" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:1">
       <c r="A11" s="5" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:1">
       <c r="A12" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:1">
       <c r="A13" s="5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:1">
       <c r="A14" s="5" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:1">
       <c r="A15" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:1">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:1">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:1">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:1">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:1">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:1">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:1">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:1">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:1">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:1">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:1">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:1">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:1">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:1">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:1">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:1">
       <c r="A31" s="5"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:E488"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E489"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
     <col min="2" max="3" width="16" customWidth="1"/>
@@ -902,7 +1496,7 @@
     <col min="5" max="5" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -919,7 +1513,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:5">
       <c r="A2" s="4">
         <v>45809</v>
       </c>
@@ -932,7 +1526,7 @@
       <c r="D2" s="7"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:5">
       <c r="A3" s="4">
         <v>45810</v>
       </c>
@@ -945,7 +1539,7 @@
       <c r="D3" s="7"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:5">
       <c r="A4" s="4">
         <v>45811</v>
       </c>
@@ -958,7 +1552,7 @@
       <c r="D4" s="7"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:5">
       <c r="A5" s="4">
         <v>45812</v>
       </c>
@@ -971,7 +1565,7 @@
       <c r="D5" s="7"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:5">
       <c r="A6" s="4">
         <v>45813</v>
       </c>
@@ -984,7 +1578,7 @@
       <c r="D6" s="7"/>
       <c r="E6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:5">
       <c r="A7" s="4">
         <v>45814</v>
       </c>
@@ -997,7 +1591,7 @@
       <c r="D7" s="7"/>
       <c r="E7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:5">
       <c r="A8" s="4">
         <v>45815</v>
       </c>
@@ -1010,7 +1604,7 @@
       <c r="D8" s="7"/>
       <c r="E8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:5">
       <c r="A9" s="4">
         <v>45816</v>
       </c>
@@ -1023,7 +1617,7 @@
       <c r="D9" s="7"/>
       <c r="E9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:5">
       <c r="A10" s="4">
         <v>45817</v>
       </c>
@@ -1036,7 +1630,7 @@
       <c r="D10" s="7"/>
       <c r="E10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:5">
       <c r="A11" s="4">
         <v>45818</v>
       </c>
@@ -1049,7 +1643,7 @@
       <c r="D11" s="7"/>
       <c r="E11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:5">
       <c r="A12" s="4">
         <v>45819</v>
       </c>
@@ -1062,7 +1656,7 @@
       <c r="D12" s="7"/>
       <c r="E12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:5">
       <c r="A13" s="4">
         <v>45820</v>
       </c>
@@ -1075,7 +1669,7 @@
       <c r="D13" s="7"/>
       <c r="E13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:5">
       <c r="A14" s="4">
         <v>45821</v>
       </c>
@@ -1088,7 +1682,7 @@
       <c r="D14" s="7"/>
       <c r="E14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:5">
       <c r="A15" s="4">
         <v>45822</v>
       </c>
@@ -1101,7 +1695,7 @@
       <c r="D15" s="7"/>
       <c r="E15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:5">
       <c r="A16" s="1">
         <v>45823</v>
       </c>
@@ -1114,7 +1708,7 @@
       <c r="D16" s="7"/>
       <c r="E16" s="5"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:5">
       <c r="A17" s="1">
         <v>45824</v>
       </c>
@@ -1127,7 +1721,7 @@
       <c r="D17" s="7"/>
       <c r="E17" s="5"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:5">
       <c r="A18" s="1">
         <v>45825</v>
       </c>
@@ -1140,7 +1734,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="5"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:5">
       <c r="A19" s="1">
         <v>45826</v>
       </c>
@@ -1153,7 +1747,7 @@
       <c r="D19" s="7"/>
       <c r="E19" s="5"/>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:5">
       <c r="A20" s="1">
         <v>45827</v>
       </c>
@@ -1166,7 +1760,7 @@
       <c r="D20" s="7"/>
       <c r="E20" s="5"/>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:5">
       <c r="A21" s="1">
         <v>45828</v>
       </c>
@@ -1179,7 +1773,7 @@
       <c r="D21" s="7"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:5">
       <c r="A22" s="1">
         <v>45829</v>
       </c>
@@ -1192,7 +1786,7 @@
       <c r="D22" s="7"/>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:5">
       <c r="A23" s="1">
         <v>45830</v>
       </c>
@@ -1205,7 +1799,7 @@
       <c r="D23" s="7"/>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:5">
       <c r="A24" s="1">
         <v>45831</v>
       </c>
@@ -1218,7 +1812,7 @@
       <c r="D24" s="7"/>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:5">
       <c r="A25" s="1">
         <v>45832</v>
       </c>
@@ -1231,7 +1825,7 @@
       <c r="D25" s="7"/>
       <c r="E25" s="5"/>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:5">
       <c r="A26" s="1">
         <v>45833</v>
       </c>
@@ -1244,7 +1838,7 @@
       <c r="D26" s="7"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:5">
       <c r="A27" s="1">
         <v>45834</v>
       </c>
@@ -1257,7 +1851,7 @@
       <c r="D27" s="7"/>
       <c r="E27" s="5"/>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:5">
       <c r="A28" s="1">
         <v>45835</v>
       </c>
@@ -1270,7 +1864,7 @@
       <c r="D28" s="7"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:5">
       <c r="A29" s="1">
         <v>45836</v>
       </c>
@@ -1283,7 +1877,7 @@
       <c r="D29" s="7"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:5">
       <c r="A30" s="1">
         <v>45837</v>
       </c>
@@ -1296,7 +1890,7 @@
       <c r="D30" s="7"/>
       <c r="E30" s="5"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:5">
       <c r="A31" s="1">
         <v>45838</v>
       </c>
@@ -1309,7 +1903,7 @@
       <c r="D31" s="7"/>
       <c r="E31" s="5"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:5">
       <c r="A32" s="1">
         <v>45839</v>
       </c>
@@ -1322,7 +1916,7 @@
       <c r="D32" s="7"/>
       <c r="E32" s="5"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:5">
       <c r="A33" s="1">
         <v>45840</v>
       </c>
@@ -1335,7 +1929,7 @@
       <c r="D33" s="7"/>
       <c r="E33" s="5"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:5">
       <c r="A34" s="1">
         <v>45841</v>
       </c>
@@ -1348,7 +1942,7 @@
       <c r="D34" s="7"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:5">
       <c r="A35" s="4">
         <v>45842</v>
       </c>
@@ -1361,7 +1955,7 @@
       <c r="D35" s="7"/>
       <c r="E35" s="5"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:5">
       <c r="A36" s="4">
         <v>45843</v>
       </c>
@@ -1374,7 +1968,7 @@
       <c r="D36" s="7"/>
       <c r="E36" s="5"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:5">
       <c r="A37" s="4">
         <v>45844</v>
       </c>
@@ -1387,7 +1981,7 @@
       <c r="D37" s="7"/>
       <c r="E37" s="5"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:5">
       <c r="A38" s="4">
         <v>45845</v>
       </c>
@@ -1400,7 +1994,7 @@
       <c r="D38" s="7"/>
       <c r="E38" s="5"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:5">
       <c r="A39" s="4">
         <v>45846</v>
       </c>
@@ -1413,7 +2007,7 @@
       <c r="D39" s="7"/>
       <c r="E39" s="5"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:5">
       <c r="A40" s="4">
         <v>45847</v>
       </c>
@@ -1426,7 +2020,7 @@
       <c r="D40" s="7"/>
       <c r="E40" s="5"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:5">
       <c r="A41" s="4">
         <v>45848</v>
       </c>
@@ -1439,7 +2033,7 @@
       <c r="D41" s="7"/>
       <c r="E41" s="5"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:5">
       <c r="A42" s="4">
         <v>45849</v>
       </c>
@@ -1452,7 +2046,7 @@
       <c r="D42" s="7"/>
       <c r="E42" s="5"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:5">
       <c r="A43" s="4">
         <v>45850</v>
       </c>
@@ -1465,7 +2059,7 @@
       <c r="D43" s="7"/>
       <c r="E43" s="5"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:5">
       <c r="A44" s="4">
         <v>45851</v>
       </c>
@@ -1478,7 +2072,7 @@
       <c r="D44" s="7"/>
       <c r="E44" s="5"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:5">
       <c r="A45" s="4">
         <v>45852</v>
       </c>
@@ -1491,7 +2085,7 @@
       <c r="D45" s="7"/>
       <c r="E45" s="5"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:5">
       <c r="A46" s="4">
         <v>45853</v>
       </c>
@@ -1504,7 +2098,7 @@
       <c r="D46" s="7"/>
       <c r="E46" s="5"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:5">
       <c r="A47" s="4">
         <v>45854</v>
       </c>
@@ -1517,7 +2111,7 @@
       <c r="D47" s="7"/>
       <c r="E47" s="5"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:5">
       <c r="A48" s="4">
         <v>45855</v>
       </c>
@@ -1530,7 +2124,7 @@
       <c r="D48" s="7"/>
       <c r="E48" s="5"/>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:5">
       <c r="A49" s="4">
         <v>45856</v>
       </c>
@@ -1543,7 +2137,7 @@
       <c r="D49" s="7"/>
       <c r="E49" s="5"/>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:5">
       <c r="A50" s="4">
         <v>45857</v>
       </c>
@@ -1556,7 +2150,7 @@
       <c r="D50" s="7"/>
       <c r="E50" s="5"/>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:5">
       <c r="A51" s="4">
         <v>45858</v>
       </c>
@@ -1569,7 +2163,7 @@
       <c r="D51" s="7"/>
       <c r="E51" s="5"/>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:5">
       <c r="A52" s="4">
         <v>45859</v>
       </c>
@@ -1582,7 +2176,7 @@
       <c r="D52" s="7"/>
       <c r="E52" s="5"/>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:5">
       <c r="A53" s="4">
         <v>45860</v>
       </c>
@@ -1595,7 +2189,7 @@
       <c r="D53" s="7"/>
       <c r="E53" s="5"/>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:5">
       <c r="A54" s="4">
         <v>45861</v>
       </c>
@@ -1608,7 +2202,7 @@
       <c r="D54" s="7"/>
       <c r="E54" s="5"/>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:5">
       <c r="A55" s="4">
         <v>45862</v>
       </c>
@@ -1621,7 +2215,7 @@
       <c r="D55" s="7"/>
       <c r="E55" s="5"/>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:5">
       <c r="A56" s="4">
         <v>45863</v>
       </c>
@@ -1634,7 +2228,7 @@
       <c r="D56" s="7"/>
       <c r="E56" s="5"/>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:5">
       <c r="A57" s="4">
         <v>45864</v>
       </c>
@@ -1647,7 +2241,7 @@
       <c r="D57" s="7"/>
       <c r="E57" s="5"/>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:5">
       <c r="A58" s="4">
         <v>45865</v>
       </c>
@@ -1660,7 +2254,7 @@
       <c r="D58" s="7"/>
       <c r="E58" s="5"/>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:5">
       <c r="A59" s="4">
         <v>45866</v>
       </c>
@@ -1673,7 +2267,7 @@
       <c r="D59" s="7"/>
       <c r="E59" s="5"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:5">
       <c r="A60" s="4">
         <v>45867</v>
       </c>
@@ -1686,7 +2280,7 @@
       <c r="D60" s="7"/>
       <c r="E60" s="5"/>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:5">
       <c r="A61" s="4">
         <v>45868</v>
       </c>
@@ -1699,7 +2293,7 @@
       <c r="D61" s="7"/>
       <c r="E61" s="5"/>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:5">
       <c r="A62" s="4">
         <v>45869</v>
       </c>
@@ -1712,7 +2306,7 @@
       <c r="D62" s="7"/>
       <c r="E62" s="5"/>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:5">
       <c r="A63" s="4">
         <v>45870</v>
       </c>
@@ -1725,7 +2319,7 @@
       <c r="D63" s="7"/>
       <c r="E63" s="5"/>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:5">
       <c r="A64" s="4">
         <v>45871</v>
       </c>
@@ -1738,7 +2332,7 @@
       <c r="D64" s="7"/>
       <c r="E64" s="5"/>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:5">
       <c r="A65" s="1">
         <v>45872</v>
       </c>
@@ -1751,7 +2345,7 @@
       <c r="D65" s="7"/>
       <c r="E65" s="5"/>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:5">
       <c r="A66" s="1">
         <v>45873</v>
       </c>
@@ -1764,7 +2358,7 @@
       <c r="D66" s="7"/>
       <c r="E66" s="5"/>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:5">
       <c r="A67" s="1">
         <v>45874</v>
       </c>
@@ -1777,7 +2371,7 @@
       <c r="D67" s="7"/>
       <c r="E67" s="5"/>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:5">
       <c r="A68" s="1">
         <v>45875</v>
       </c>
@@ -1790,7 +2384,7 @@
       <c r="D68" s="7"/>
       <c r="E68" s="5"/>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:5">
       <c r="A69" s="1">
         <v>45876</v>
       </c>
@@ -1803,7 +2397,7 @@
       <c r="D69" s="7"/>
       <c r="E69" s="5"/>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:5">
       <c r="A70" s="1">
         <v>45877</v>
       </c>
@@ -1816,7 +2410,7 @@
       <c r="D70" s="7"/>
       <c r="E70" s="5"/>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:5">
       <c r="A71" s="1">
         <v>45878</v>
       </c>
@@ -1829,7 +2423,7 @@
       <c r="D71" s="7"/>
       <c r="E71" s="5"/>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:5">
       <c r="A72" s="1">
         <v>45879</v>
       </c>
@@ -1842,7 +2436,7 @@
       <c r="D72" s="7"/>
       <c r="E72" s="5"/>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:5">
       <c r="A73" s="1">
         <v>45880</v>
       </c>
@@ -1855,7 +2449,7 @@
       <c r="D73" s="7"/>
       <c r="E73" s="5"/>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:5">
       <c r="A74" s="1">
         <v>45881</v>
       </c>
@@ -1868,7 +2462,7 @@
       <c r="D74" s="7"/>
       <c r="E74" s="5"/>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:5">
       <c r="A75" s="1">
         <v>45882</v>
       </c>
@@ -1881,7 +2475,7 @@
       <c r="D75" s="7"/>
       <c r="E75" s="5"/>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:5">
       <c r="A76" s="1">
         <v>45883</v>
       </c>
@@ -1894,7 +2488,7 @@
       <c r="D76" s="7"/>
       <c r="E76" s="5"/>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:5">
       <c r="A77" s="1">
         <v>45884</v>
       </c>
@@ -1907,7 +2501,7 @@
       <c r="D77" s="7"/>
       <c r="E77" s="5"/>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:5">
       <c r="A78" s="1">
         <v>45885</v>
       </c>
@@ -1920,7 +2514,7 @@
       <c r="D78" s="7"/>
       <c r="E78" s="5"/>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:5">
       <c r="A79" s="1">
         <v>45886</v>
       </c>
@@ -1933,7 +2527,7 @@
       <c r="D79" s="7"/>
       <c r="E79" s="5"/>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:5">
       <c r="A80" s="1">
         <v>45887</v>
       </c>
@@ -1946,7 +2540,7 @@
       <c r="D80" s="7"/>
       <c r="E80" s="5"/>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:5">
       <c r="A81" s="1">
         <v>45888</v>
       </c>
@@ -1959,7 +2553,7 @@
       <c r="D81" s="7"/>
       <c r="E81" s="5"/>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:5">
       <c r="A82" s="1">
         <v>45889</v>
       </c>
@@ -1972,7 +2566,7 @@
       <c r="D82" s="7"/>
       <c r="E82" s="5"/>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:5">
       <c r="A83" s="1">
         <v>45890</v>
       </c>
@@ -1985,7 +2579,7 @@
       <c r="D83" s="7"/>
       <c r="E83" s="5"/>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:5">
       <c r="A84" s="1">
         <v>45891</v>
       </c>
@@ -1998,7 +2592,7 @@
       <c r="D84" s="7"/>
       <c r="E84" s="5"/>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:5">
       <c r="A85" s="1">
         <v>45892</v>
       </c>
@@ -2011,7 +2605,7 @@
       <c r="D85" s="7"/>
       <c r="E85" s="5"/>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:5">
       <c r="A86" s="4">
         <v>45893</v>
       </c>
@@ -2024,7 +2618,7 @@
       <c r="D86" s="7"/>
       <c r="E86" s="5"/>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:5">
       <c r="A87" s="4">
         <v>45894</v>
       </c>
@@ -2037,7 +2631,7 @@
       <c r="D87" s="7"/>
       <c r="E87" s="5"/>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:5">
       <c r="A88" s="4">
         <v>45895</v>
       </c>
@@ -2050,7 +2644,7 @@
       <c r="D88" s="7"/>
       <c r="E88" s="5"/>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:5">
       <c r="A89" s="4">
         <v>45896</v>
       </c>
@@ -2063,7 +2657,7 @@
       <c r="D89" s="7"/>
       <c r="E89" s="5"/>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:5">
       <c r="A90" s="4">
         <v>45897</v>
       </c>
@@ -2076,7 +2670,7 @@
       <c r="D90" s="7"/>
       <c r="E90" s="5"/>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:5">
       <c r="A91" s="4">
         <v>45898</v>
       </c>
@@ -2089,7 +2683,7 @@
       <c r="D91" s="7"/>
       <c r="E91" s="5"/>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:5">
       <c r="A92" s="4">
         <v>45899</v>
       </c>
@@ -2102,7 +2696,7 @@
       <c r="D92" s="7"/>
       <c r="E92" s="5"/>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:5">
       <c r="A93" s="4">
         <v>45900</v>
       </c>
@@ -2115,7 +2709,7 @@
       <c r="D93" s="7"/>
       <c r="E93" s="5"/>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:5">
       <c r="A94" s="4">
         <v>45901</v>
       </c>
@@ -2128,7 +2722,7 @@
       <c r="D94" s="7"/>
       <c r="E94" s="5"/>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:5">
       <c r="A95" s="4">
         <v>45902</v>
       </c>
@@ -2141,7 +2735,7 @@
       <c r="D95" s="7"/>
       <c r="E95" s="5"/>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:5">
       <c r="A96" s="4">
         <v>45903</v>
       </c>
@@ -2154,7 +2748,7 @@
       <c r="D96" s="7"/>
       <c r="E96" s="5"/>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:5">
       <c r="A97" s="4">
         <v>45904</v>
       </c>
@@ -2167,7 +2761,7 @@
       <c r="D97" s="7"/>
       <c r="E97" s="5"/>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:5">
       <c r="A98" s="4">
         <v>45905</v>
       </c>
@@ -2180,7 +2774,7 @@
       <c r="D98" s="7"/>
       <c r="E98" s="5"/>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:5">
       <c r="A99" s="4">
         <v>45906</v>
       </c>
@@ -2193,7 +2787,7 @@
       <c r="D99" s="7"/>
       <c r="E99" s="5"/>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:5">
       <c r="A100" s="4">
         <v>45907</v>
       </c>
@@ -2206,7 +2800,7 @@
       <c r="D100" s="7"/>
       <c r="E100" s="5"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:5">
       <c r="A101" s="4">
         <v>45908</v>
       </c>
@@ -2219,7 +2813,7 @@
       <c r="D101" s="7"/>
       <c r="E101" s="5"/>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:5">
       <c r="A102" s="4">
         <v>45909</v>
       </c>
@@ -2232,7 +2826,7 @@
       <c r="D102" s="7"/>
       <c r="E102" s="5"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:5">
       <c r="A103" s="4">
         <v>45910</v>
       </c>
@@ -2245,7 +2839,7 @@
       <c r="D103" s="7"/>
       <c r="E103" s="5"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:5">
       <c r="A104" s="4">
         <v>45911</v>
       </c>
@@ -2258,7 +2852,7 @@
       <c r="D104" s="7"/>
       <c r="E104" s="5"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:5">
       <c r="A105" s="4">
         <v>45912</v>
       </c>
@@ -2271,7 +2865,7 @@
       <c r="D105" s="7"/>
       <c r="E105" s="5"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:5">
       <c r="A106" s="4">
         <v>45913</v>
       </c>
@@ -2284,7 +2878,7 @@
       <c r="D106" s="7"/>
       <c r="E106" s="5"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:5">
       <c r="A107" s="4">
         <v>45914</v>
       </c>
@@ -2297,7 +2891,7 @@
       <c r="D107" s="7"/>
       <c r="E107" s="5"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:5">
       <c r="A108" s="4">
         <v>45915</v>
       </c>
@@ -2310,7 +2904,7 @@
       <c r="D108" s="7"/>
       <c r="E108" s="5"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:5">
       <c r="A109" s="4">
         <v>45916</v>
       </c>
@@ -2323,7 +2917,7 @@
       <c r="D109" s="7"/>
       <c r="E109" s="5"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:5">
       <c r="A110" s="4">
         <v>45917</v>
       </c>
@@ -2336,7 +2930,7 @@
       <c r="D110" s="7"/>
       <c r="E110" s="5"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:5">
       <c r="A111" s="4">
         <v>45918</v>
       </c>
@@ -2349,7 +2943,7 @@
       <c r="D111" s="7"/>
       <c r="E111" s="5"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:5">
       <c r="A112" s="4">
         <v>45919</v>
       </c>
@@ -2362,7 +2956,7 @@
       <c r="D112" s="7"/>
       <c r="E112" s="5"/>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="113" spans="1:5">
       <c r="A113" s="4">
         <v>45920</v>
       </c>
@@ -2375,7 +2969,7 @@
       <c r="D113" s="7"/>
       <c r="E113" s="5"/>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="114" spans="1:5">
       <c r="A114" s="4">
         <v>45921</v>
       </c>
@@ -2388,7 +2982,7 @@
       <c r="D114" s="7"/>
       <c r="E114" s="5"/>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="115" spans="1:5">
       <c r="A115" s="4">
         <v>45922</v>
       </c>
@@ -2401,7 +2995,7 @@
       <c r="D115" s="7"/>
       <c r="E115" s="5"/>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="116" spans="1:5">
       <c r="A116" s="4">
         <v>45923</v>
       </c>
@@ -2414,7 +3008,7 @@
       <c r="D116" s="7"/>
       <c r="E116" s="5"/>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="117" spans="1:5">
       <c r="A117" s="4">
         <v>45924</v>
       </c>
@@ -2427,7 +3021,7 @@
       <c r="D117" s="7"/>
       <c r="E117" s="5"/>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="118" spans="1:5">
       <c r="A118" s="4">
         <v>45925</v>
       </c>
@@ -2440,7 +3034,7 @@
       <c r="D118" s="7"/>
       <c r="E118" s="5"/>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="119" spans="1:5">
       <c r="A119" s="4">
         <v>45926</v>
       </c>
@@ -2453,7 +3047,7 @@
       <c r="D119" s="7"/>
       <c r="E119" s="5"/>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="120" spans="1:5">
       <c r="A120" s="4">
         <v>45927</v>
       </c>
@@ -2466,7 +3060,7 @@
       <c r="D120" s="7"/>
       <c r="E120" s="5"/>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="121" spans="1:5">
       <c r="A121" s="4">
         <v>45928</v>
       </c>
@@ -2479,7 +3073,7 @@
       <c r="D121" s="7"/>
       <c r="E121" s="5"/>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="122" spans="1:5">
       <c r="A122" s="4">
         <v>45929</v>
       </c>
@@ -2492,7 +3086,7 @@
       <c r="D122" s="7"/>
       <c r="E122" s="5"/>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="123" spans="1:5">
       <c r="A123" s="4">
         <v>45930</v>
       </c>
@@ -2505,7 +3099,7 @@
       <c r="D123" s="7"/>
       <c r="E123" s="5"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="124" spans="1:5">
       <c r="A124" s="4">
         <v>45931</v>
       </c>
@@ -2518,7 +3112,7 @@
       <c r="D124" s="7"/>
       <c r="E124" s="5"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="125" spans="1:5">
       <c r="A125" s="4">
         <v>45932</v>
       </c>
@@ -2531,7 +3125,7 @@
       <c r="D125" s="7"/>
       <c r="E125" s="5"/>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="126" spans="1:5">
       <c r="A126" s="4">
         <v>45933</v>
       </c>
@@ -2544,7 +3138,7 @@
       <c r="D126" s="7"/>
       <c r="E126" s="5"/>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="127" spans="1:5">
       <c r="A127" s="4">
         <v>45934</v>
       </c>
@@ -2557,7 +3151,7 @@
       <c r="D127" s="7"/>
       <c r="E127" s="5"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="128" spans="1:5">
       <c r="A128" s="4">
         <v>45935</v>
       </c>
@@ -2570,7 +3164,7 @@
       <c r="D128" s="7"/>
       <c r="E128" s="5"/>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="129" spans="1:5">
       <c r="A129" s="4">
         <v>45936</v>
       </c>
@@ -2583,7 +3177,7 @@
       <c r="D129" s="7"/>
       <c r="E129" s="5"/>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="130" spans="1:5">
       <c r="A130" s="4">
         <v>45937</v>
       </c>
@@ -2596,7 +3190,7 @@
       <c r="D130" s="7"/>
       <c r="E130" s="5"/>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="131" spans="1:5">
       <c r="A131" s="4">
         <v>45938</v>
       </c>
@@ -2609,7 +3203,7 @@
       <c r="D131" s="7"/>
       <c r="E131" s="5"/>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="132" spans="1:5">
       <c r="A132" s="4">
         <v>45939</v>
       </c>
@@ -2622,7 +3216,7 @@
       <c r="D132" s="7"/>
       <c r="E132" s="5"/>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="133" spans="1:5">
       <c r="A133" s="4">
         <v>45940</v>
       </c>
@@ -2635,7 +3229,7 @@
       <c r="D133" s="7"/>
       <c r="E133" s="5"/>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="134" spans="1:5">
       <c r="A134" s="4">
         <v>45941</v>
       </c>
@@ -2648,7 +3242,7 @@
       <c r="D134" s="7"/>
       <c r="E134" s="5"/>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="135" spans="1:5">
       <c r="A135" s="4">
         <v>45942</v>
       </c>
@@ -2661,7 +3255,7 @@
       <c r="D135" s="7"/>
       <c r="E135" s="5"/>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="136" spans="1:5">
       <c r="A136" s="4">
         <v>45943</v>
       </c>
@@ -2674,7 +3268,7 @@
       <c r="D136" s="7"/>
       <c r="E136" s="5"/>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="137" spans="1:5">
       <c r="A137" s="4">
         <v>45944</v>
       </c>
@@ -2687,7 +3281,7 @@
       <c r="D137" s="7"/>
       <c r="E137" s="5"/>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="138" spans="1:5">
       <c r="A138" s="4">
         <v>45945</v>
       </c>
@@ -2700,7 +3294,7 @@
       <c r="D138" s="7"/>
       <c r="E138" s="5"/>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="139" spans="1:5">
       <c r="A139" s="4">
         <v>45946</v>
       </c>
@@ -2713,7 +3307,7 @@
       <c r="D139" s="7"/>
       <c r="E139" s="5"/>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="140" spans="1:5">
       <c r="A140" s="4">
         <v>45947</v>
       </c>
@@ -2726,7 +3320,7 @@
       <c r="D140" s="7"/>
       <c r="E140" s="5"/>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="141" spans="1:5">
       <c r="A141" s="4">
         <v>45948</v>
       </c>
@@ -2739,7 +3333,7 @@
       <c r="D141" s="7"/>
       <c r="E141" s="5"/>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="142" spans="1:5">
       <c r="A142" s="4">
         <v>45949</v>
       </c>
@@ -2752,7 +3346,7 @@
       <c r="D142" s="7"/>
       <c r="E142" s="5"/>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="143" spans="1:5">
       <c r="A143" s="4">
         <v>45950</v>
       </c>
@@ -2765,7 +3359,7 @@
       <c r="D143" s="7"/>
       <c r="E143" s="5"/>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="144" spans="1:5">
       <c r="A144" s="4">
         <v>45951</v>
       </c>
@@ -2778,7 +3372,7 @@
       <c r="D144" s="7"/>
       <c r="E144" s="5"/>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="145" spans="1:5">
       <c r="A145" s="4">
         <v>45952</v>
       </c>
@@ -2791,7 +3385,7 @@
       <c r="D145" s="7"/>
       <c r="E145" s="5"/>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="146" spans="1:5">
       <c r="A146" s="4">
         <v>45953</v>
       </c>
@@ -2804,7 +3398,7 @@
       <c r="D146" s="7"/>
       <c r="E146" s="5"/>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="147" spans="1:5">
       <c r="A147" s="4">
         <v>45954</v>
       </c>
@@ -2817,7 +3411,7 @@
       <c r="D147" s="7"/>
       <c r="E147" s="5"/>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="148" spans="1:5">
       <c r="A148" s="4">
         <v>45955</v>
       </c>
@@ -2830,7 +3424,7 @@
       <c r="D148" s="7"/>
       <c r="E148" s="5"/>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="149" spans="1:5">
       <c r="A149" s="4">
         <v>45956</v>
       </c>
@@ -2843,7 +3437,7 @@
       <c r="D149" s="7"/>
       <c r="E149" s="5"/>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="150" spans="1:5">
       <c r="A150" s="4">
         <v>45957</v>
       </c>
@@ -2856,7 +3450,7 @@
       <c r="D150" s="7"/>
       <c r="E150" s="5"/>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="151" spans="1:5">
       <c r="A151" s="4">
         <v>45958</v>
       </c>
@@ -2869,7 +3463,7 @@
       <c r="D151" s="7"/>
       <c r="E151" s="5"/>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="152" spans="1:5">
       <c r="A152" s="4">
         <v>45959</v>
       </c>
@@ -2882,7 +3476,7 @@
       <c r="D152" s="7"/>
       <c r="E152" s="5"/>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="153" spans="1:5">
       <c r="A153" s="4">
         <v>45960</v>
       </c>
@@ -2895,7 +3489,7 @@
       <c r="D153" s="7"/>
       <c r="E153" s="5"/>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="154" spans="1:5">
       <c r="A154" s="4">
         <v>45961</v>
       </c>
@@ -2908,7 +3502,7 @@
       <c r="D154" s="7"/>
       <c r="E154" s="5"/>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="155" spans="1:5">
       <c r="A155" s="4">
         <v>45962</v>
       </c>
@@ -2921,7 +3515,7 @@
       <c r="D155" s="7"/>
       <c r="E155" s="5"/>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="156" spans="1:5">
       <c r="A156" s="4">
         <v>45963</v>
       </c>
@@ -2934,7 +3528,7 @@
       <c r="D156" s="7"/>
       <c r="E156" s="5"/>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="157" spans="1:5">
       <c r="A157" s="4">
         <v>45964</v>
       </c>
@@ -2947,7 +3541,7 @@
       <c r="D157" s="7"/>
       <c r="E157" s="5"/>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="158" spans="1:5">
       <c r="A158" s="4">
         <v>45965</v>
       </c>
@@ -2960,7 +3554,7 @@
       <c r="D158" s="7"/>
       <c r="E158" s="5"/>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="159" spans="1:5">
       <c r="A159" s="4">
         <v>45966</v>
       </c>
@@ -2973,7 +3567,7 @@
       <c r="D159" s="7"/>
       <c r="E159" s="5"/>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="160" spans="1:5">
       <c r="A160" s="4">
         <v>45967</v>
       </c>
@@ -2986,7 +3580,7 @@
       <c r="D160" s="7"/>
       <c r="E160" s="5"/>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="161" spans="1:5">
       <c r="A161" s="4">
         <v>45968</v>
       </c>
@@ -2999,7 +3593,7 @@
       <c r="D161" s="7"/>
       <c r="E161" s="5"/>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="162" spans="1:5">
       <c r="A162" s="4">
         <v>45969</v>
       </c>
@@ -3012,7 +3606,7 @@
       <c r="D162" s="7"/>
       <c r="E162" s="5"/>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="163" spans="1:5">
       <c r="A163" s="4">
         <v>45970</v>
       </c>
@@ -3025,7 +3619,7 @@
       <c r="D163" s="7"/>
       <c r="E163" s="5"/>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="164" spans="1:5">
       <c r="A164" s="4">
         <v>45971</v>
       </c>
@@ -3038,7 +3632,7 @@
       <c r="D164" s="7"/>
       <c r="E164" s="5"/>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="165" spans="1:5">
       <c r="A165" s="4">
         <v>45972</v>
       </c>
@@ -3051,7 +3645,7 @@
       <c r="D165" s="7"/>
       <c r="E165" s="5"/>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="166" spans="1:5">
       <c r="A166" s="4">
         <v>45973</v>
       </c>
@@ -3064,7 +3658,7 @@
       <c r="D166" s="7"/>
       <c r="E166" s="5"/>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="167" spans="1:5">
       <c r="A167" s="4">
         <v>45974</v>
       </c>
@@ -3077,7 +3671,7 @@
       <c r="D167" s="7"/>
       <c r="E167" s="5"/>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="168" spans="1:5">
       <c r="A168" s="4">
         <v>45975</v>
       </c>
@@ -3090,7 +3684,7 @@
       <c r="D168" s="7"/>
       <c r="E168" s="5"/>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="169" spans="1:5">
       <c r="A169" s="4">
         <v>45976</v>
       </c>
@@ -3103,7 +3697,7 @@
       <c r="D169" s="7"/>
       <c r="E169" s="5"/>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="170" spans="1:5">
       <c r="A170" s="4">
         <v>45977</v>
       </c>
@@ -3116,7 +3710,7 @@
       <c r="D170" s="7"/>
       <c r="E170" s="5"/>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="171" spans="1:5">
       <c r="A171" s="4">
         <v>45978</v>
       </c>
@@ -3129,7 +3723,7 @@
       <c r="D171" s="7"/>
       <c r="E171" s="5"/>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="172" spans="1:5">
       <c r="A172" s="4">
         <v>45979</v>
       </c>
@@ -3142,7 +3736,7 @@
       <c r="D172" s="7"/>
       <c r="E172" s="5"/>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="173" spans="1:5">
       <c r="A173" s="4">
         <v>45980</v>
       </c>
@@ -3155,7 +3749,7 @@
       <c r="D173" s="7"/>
       <c r="E173" s="5"/>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="174" spans="1:5">
       <c r="A174" s="4">
         <v>45981</v>
       </c>
@@ -3168,7 +3762,7 @@
       <c r="D174" s="7"/>
       <c r="E174" s="5"/>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="175" spans="1:5">
       <c r="A175" s="4">
         <v>45982</v>
       </c>
@@ -3181,7 +3775,7 @@
       <c r="D175" s="7"/>
       <c r="E175" s="5"/>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="176" spans="1:5">
       <c r="A176" s="4">
         <v>45983</v>
       </c>
@@ -3194,7 +3788,7 @@
       <c r="D176" s="7"/>
       <c r="E176" s="5"/>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="177" spans="1:5">
       <c r="A177" s="4">
         <v>45984</v>
       </c>
@@ -3207,7 +3801,7 @@
       <c r="D177" s="7"/>
       <c r="E177" s="5"/>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="178" spans="1:5">
       <c r="A178" s="4">
         <v>45985</v>
       </c>
@@ -3220,7 +3814,7 @@
       <c r="D178" s="7"/>
       <c r="E178" s="5"/>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="179" spans="1:5">
       <c r="A179" s="4">
         <v>45986</v>
       </c>
@@ -3233,7 +3827,7 @@
       <c r="D179" s="7"/>
       <c r="E179" s="5"/>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="180" spans="1:5">
       <c r="A180" s="4">
         <v>45987</v>
       </c>
@@ -3246,7 +3840,7 @@
       <c r="D180" s="7"/>
       <c r="E180" s="5"/>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="181" spans="1:5">
       <c r="A181" s="4">
         <v>45988</v>
       </c>
@@ -3259,7 +3853,7 @@
       <c r="D181" s="7"/>
       <c r="E181" s="5"/>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="182" spans="1:5">
       <c r="A182" s="4">
         <v>45989</v>
       </c>
@@ -3272,7 +3866,7 @@
       <c r="D182" s="7"/>
       <c r="E182" s="5"/>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="183" spans="1:5">
       <c r="A183" s="4">
         <v>45990</v>
       </c>
@@ -3285,7 +3879,7 @@
       <c r="D183" s="7"/>
       <c r="E183" s="5"/>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="184" spans="1:5">
       <c r="A184" s="4">
         <v>45991</v>
       </c>
@@ -3298,7 +3892,7 @@
       <c r="D184" s="7"/>
       <c r="E184" s="5"/>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="185" spans="1:5">
       <c r="A185" s="4">
         <v>45992</v>
       </c>
@@ -3311,7 +3905,7 @@
       <c r="D185" s="7"/>
       <c r="E185" s="5"/>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="186" spans="1:5">
       <c r="A186" s="4">
         <v>45993</v>
       </c>
@@ -3324,7 +3918,7 @@
       <c r="D186" s="7"/>
       <c r="E186" s="5"/>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="187" spans="1:5">
       <c r="A187" s="4">
         <v>45994</v>
       </c>
@@ -3337,7 +3931,7 @@
       <c r="D187" s="7"/>
       <c r="E187" s="5"/>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="188" spans="1:5">
       <c r="A188" s="4">
         <v>45995</v>
       </c>
@@ -3350,7 +3944,7 @@
       <c r="D188" s="7"/>
       <c r="E188" s="5"/>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="189" spans="1:5">
       <c r="A189" s="4">
         <v>45996</v>
       </c>
@@ -3363,7 +3957,7 @@
       <c r="D189" s="7"/>
       <c r="E189" s="5"/>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="190" spans="1:5">
       <c r="A190" s="4">
         <v>45997</v>
       </c>
@@ -3376,7 +3970,7 @@
       <c r="D190" s="7"/>
       <c r="E190" s="5"/>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="191" spans="1:5">
       <c r="A191" s="4">
         <v>45998</v>
       </c>
@@ -3389,7 +3983,7 @@
       <c r="D191" s="7"/>
       <c r="E191" s="5"/>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="192" spans="1:5">
       <c r="A192" s="4">
         <v>45999</v>
       </c>
@@ -3402,7 +3996,7 @@
       <c r="D192" s="7"/>
       <c r="E192" s="5"/>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="193" spans="1:5">
       <c r="A193" s="4">
         <v>46000</v>
       </c>
@@ -3415,7 +4009,7 @@
       <c r="D193" s="7"/>
       <c r="E193" s="5"/>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="194" spans="1:5">
       <c r="A194" s="4">
         <v>46001</v>
       </c>
@@ -3428,7 +4022,7 @@
       <c r="D194" s="7"/>
       <c r="E194" s="5"/>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="195" spans="1:5">
       <c r="A195" s="4">
         <v>46002</v>
       </c>
@@ -3441,7 +4035,7 @@
       <c r="D195" s="7"/>
       <c r="E195" s="5"/>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="196" spans="1:5">
       <c r="A196" s="4">
         <v>46003</v>
       </c>
@@ -3454,7 +4048,7 @@
       <c r="D196" s="7"/>
       <c r="E196" s="5"/>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="197" spans="1:5">
       <c r="A197" s="4">
         <v>46004</v>
       </c>
@@ -3467,7 +4061,7 @@
       <c r="D197" s="7"/>
       <c r="E197" s="5"/>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="198" spans="1:5">
       <c r="A198" s="4">
         <v>46005</v>
       </c>
@@ -3480,7 +4074,7 @@
       <c r="D198" s="7"/>
       <c r="E198" s="5"/>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="199" spans="1:5">
       <c r="A199" s="4">
         <v>46006</v>
       </c>
@@ -3493,7 +4087,7 @@
       <c r="D199" s="7"/>
       <c r="E199" s="5"/>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="200" spans="1:5">
       <c r="A200" s="4">
         <v>46007</v>
       </c>
@@ -3506,7 +4100,7 @@
       <c r="D200" s="7"/>
       <c r="E200" s="5"/>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="201" spans="1:5">
       <c r="A201" s="4">
         <v>46008</v>
       </c>
@@ -3519,7 +4113,7 @@
       <c r="D201" s="7"/>
       <c r="E201" s="5"/>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="202" spans="1:5">
       <c r="A202" s="4">
         <v>46009</v>
       </c>
@@ -3532,7 +4126,7 @@
       <c r="D202" s="7"/>
       <c r="E202" s="5"/>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="203" spans="1:5">
       <c r="A203" s="4">
         <v>46010</v>
       </c>
@@ -3545,7 +4139,7 @@
       <c r="D203" s="7"/>
       <c r="E203" s="5"/>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="204" spans="1:5">
       <c r="A204" s="4">
         <v>46011</v>
       </c>
@@ -3558,7 +4152,7 @@
       <c r="D204" s="7"/>
       <c r="E204" s="5"/>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="205" spans="1:5">
       <c r="A205" s="4">
         <v>46012</v>
       </c>
@@ -3571,7 +4165,7 @@
       <c r="D205" s="7"/>
       <c r="E205" s="5"/>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="206" spans="1:5">
       <c r="A206" s="4">
         <v>46013</v>
       </c>
@@ -3584,7 +4178,7 @@
       <c r="D206" s="7"/>
       <c r="E206" s="5"/>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="207" spans="1:5">
       <c r="A207" s="4">
         <v>46014</v>
       </c>
@@ -3597,7 +4191,7 @@
       <c r="D207" s="7"/>
       <c r="E207" s="5"/>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="208" spans="1:5">
       <c r="A208" s="4">
         <v>46015</v>
       </c>
@@ -3610,7 +4204,7 @@
       <c r="D208" s="7"/>
       <c r="E208" s="5"/>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="209" spans="1:5">
       <c r="A209" s="4">
         <v>46016</v>
       </c>
@@ -3623,7 +4217,7 @@
       <c r="D209" s="7"/>
       <c r="E209" s="5"/>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="210" spans="1:5">
       <c r="A210" s="4">
         <v>46017</v>
       </c>
@@ -3636,7 +4230,7 @@
       <c r="D210" s="7"/>
       <c r="E210" s="5"/>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="211" spans="1:5">
       <c r="A211" s="4">
         <v>46018</v>
       </c>
@@ -3649,7 +4243,7 @@
       <c r="D211" s="7"/>
       <c r="E211" s="5"/>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="212" spans="1:5">
       <c r="A212" s="4">
         <v>46019</v>
       </c>
@@ -3662,7 +4256,7 @@
       <c r="D212" s="7"/>
       <c r="E212" s="5"/>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="213" spans="1:5">
       <c r="A213" s="4">
         <v>46020</v>
       </c>
@@ -3675,7 +4269,7 @@
       <c r="D213" s="7"/>
       <c r="E213" s="5"/>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="214" spans="1:5">
       <c r="A214" s="4">
         <v>46021</v>
       </c>
@@ -3688,7 +4282,7 @@
       <c r="D214" s="7"/>
       <c r="E214" s="5"/>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="215" spans="1:5">
       <c r="A215" s="4">
         <v>46022</v>
       </c>
@@ -3701,7 +4295,7 @@
       <c r="D215" s="7"/>
       <c r="E215" s="5"/>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="216" spans="1:5">
       <c r="A216" s="4">
         <v>46023</v>
       </c>
@@ -3714,7 +4308,7 @@
       <c r="D216" s="7"/>
       <c r="E216" s="5"/>
     </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="217" spans="1:5">
       <c r="A217" s="4">
         <v>46024</v>
       </c>
@@ -3727,7 +4321,7 @@
       <c r="D217" s="7"/>
       <c r="E217" s="5"/>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="218" spans="1:5">
       <c r="A218" s="4">
         <v>46025</v>
       </c>
@@ -3740,7 +4334,7 @@
       <c r="D218" s="7"/>
       <c r="E218" s="5"/>
     </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="219" spans="1:5">
       <c r="A219" s="4">
         <v>46026</v>
       </c>
@@ -3753,7 +4347,7 @@
       <c r="D219" s="7"/>
       <c r="E219" s="5"/>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="220" spans="1:5">
       <c r="A220" s="4">
         <v>46027</v>
       </c>
@@ -3766,7 +4360,7 @@
       <c r="D220" s="7"/>
       <c r="E220" s="5"/>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="221" spans="1:5">
       <c r="A221" s="4">
         <v>46028</v>
       </c>
@@ -3779,7 +4373,7 @@
       <c r="D221" s="7"/>
       <c r="E221" s="5"/>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="222" spans="1:5">
       <c r="A222" s="4">
         <v>46029</v>
       </c>
@@ -3792,7 +4386,7 @@
       <c r="D222" s="7"/>
       <c r="E222" s="5"/>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="223" spans="1:5">
       <c r="A223" s="4">
         <v>46030</v>
       </c>
@@ -3805,7 +4399,7 @@
       <c r="D223" s="7"/>
       <c r="E223" s="5"/>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="224" spans="1:5">
       <c r="A224" s="4">
         <v>46031</v>
       </c>
@@ -3818,7 +4412,7 @@
       <c r="D224" s="7"/>
       <c r="E224" s="5"/>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="225" spans="1:5">
       <c r="A225" s="4">
         <v>46032</v>
       </c>
@@ -3831,7 +4425,7 @@
       <c r="D225" s="7"/>
       <c r="E225" s="5"/>
     </row>
-    <row r="226" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="226" spans="1:5">
       <c r="A226" s="4">
         <v>46033</v>
       </c>
@@ -3844,7 +4438,7 @@
       <c r="D226" s="7"/>
       <c r="E226" s="5"/>
     </row>
-    <row r="227" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="227" spans="1:5">
       <c r="A227" s="4">
         <v>46034</v>
       </c>
@@ -3857,7 +4451,7 @@
       <c r="D227" s="7"/>
       <c r="E227" s="5"/>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="228" spans="1:5">
       <c r="A228" s="4">
         <v>46035</v>
       </c>
@@ -3870,7 +4464,7 @@
       <c r="D228" s="7"/>
       <c r="E228" s="5"/>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="229" spans="1:5">
       <c r="A229" s="4">
         <v>46036</v>
       </c>
@@ -3883,7 +4477,7 @@
       <c r="D229" s="7"/>
       <c r="E229" s="5"/>
     </row>
-    <row r="230" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="230" spans="1:5">
       <c r="A230" s="4">
         <v>46037</v>
       </c>
@@ -3896,7 +4490,7 @@
       <c r="D230" s="7"/>
       <c r="E230" s="5"/>
     </row>
-    <row r="231" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="231" spans="1:5">
       <c r="A231" s="4">
         <v>46038</v>
       </c>
@@ -3909,7 +4503,7 @@
       <c r="D231" s="7"/>
       <c r="E231" s="5"/>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="232" spans="1:5">
       <c r="A232" s="4">
         <v>46039</v>
       </c>
@@ -3922,7 +4516,7 @@
       <c r="D232" s="7"/>
       <c r="E232" s="5"/>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="233" spans="1:5">
       <c r="A233" s="4">
         <v>46040</v>
       </c>
@@ -3935,7 +4529,7 @@
       <c r="D233" s="7"/>
       <c r="E233" s="5"/>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="234" spans="1:5">
       <c r="A234" s="4">
         <v>46041</v>
       </c>
@@ -3948,7 +4542,7 @@
       <c r="D234" s="7"/>
       <c r="E234" s="5"/>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="235" spans="1:5">
       <c r="A235" s="4">
         <v>46042</v>
       </c>
@@ -3961,7 +4555,7 @@
       <c r="D235" s="7"/>
       <c r="E235" s="5"/>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="236" spans="1:5">
       <c r="A236" s="4">
         <v>46043</v>
       </c>
@@ -3974,7 +4568,7 @@
       <c r="D236" s="7"/>
       <c r="E236" s="5"/>
     </row>
-    <row r="237" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="237" spans="1:5">
       <c r="A237" s="4">
         <v>46044</v>
       </c>
@@ -3987,7 +4581,7 @@
       <c r="D237" s="7"/>
       <c r="E237" s="5"/>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="238" spans="1:5">
       <c r="A238" s="4">
         <v>46045</v>
       </c>
@@ -4000,7 +4594,7 @@
       <c r="D238" s="7"/>
       <c r="E238" s="5"/>
     </row>
-    <row r="239" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="239" spans="1:5">
       <c r="A239" s="4">
         <v>46046</v>
       </c>
@@ -4013,7 +4607,7 @@
       <c r="D239" s="7"/>
       <c r="E239" s="5"/>
     </row>
-    <row r="240" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="240" spans="1:5">
       <c r="A240" s="4">
         <v>46047</v>
       </c>
@@ -4026,7 +4620,7 @@
       <c r="D240" s="7"/>
       <c r="E240" s="5"/>
     </row>
-    <row r="241" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="241" spans="1:5">
       <c r="A241" s="4">
         <v>46048</v>
       </c>
@@ -4039,7 +4633,7 @@
       <c r="D241" s="7"/>
       <c r="E241" s="5"/>
     </row>
-    <row r="242" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="242" spans="1:5">
       <c r="A242" s="4">
         <v>46049</v>
       </c>
@@ -4052,7 +4646,7 @@
       <c r="D242" s="7"/>
       <c r="E242" s="5"/>
     </row>
-    <row r="243" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="243" spans="1:5">
       <c r="A243" s="4">
         <v>46050</v>
       </c>
@@ -4065,7 +4659,7 @@
       <c r="D243" s="7"/>
       <c r="E243" s="5"/>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="244" spans="1:5">
       <c r="A244" s="4">
         <v>46051</v>
       </c>
@@ -4078,7 +4672,7 @@
       <c r="D244" s="7"/>
       <c r="E244" s="5"/>
     </row>
-    <row r="245" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="245" spans="1:5">
       <c r="A245" s="4">
         <v>46052</v>
       </c>
@@ -4091,7 +4685,7 @@
       <c r="D245" s="7"/>
       <c r="E245" s="5"/>
     </row>
-    <row r="246" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="246" spans="1:5">
       <c r="A246" s="4">
         <v>46053</v>
       </c>
@@ -4104,7 +4698,7 @@
       <c r="D246" s="7"/>
       <c r="E246" s="5"/>
     </row>
-    <row r="247" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="247" spans="1:5">
       <c r="A247" s="4">
         <v>46054</v>
       </c>
@@ -4117,7 +4711,7 @@
       <c r="D247" s="7"/>
       <c r="E247" s="5"/>
     </row>
-    <row r="248" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="248" spans="1:5">
       <c r="A248" s="4">
         <v>46055</v>
       </c>
@@ -4130,7 +4724,7 @@
       <c r="D248" s="7"/>
       <c r="E248" s="5"/>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="249" spans="1:5">
       <c r="A249" s="4">
         <v>46056</v>
       </c>
@@ -4143,7 +4737,7 @@
       <c r="D249" s="7"/>
       <c r="E249" s="5"/>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="250" spans="1:5">
       <c r="A250" s="4">
         <v>46057</v>
       </c>
@@ -4156,7 +4750,7 @@
       <c r="D250" s="7"/>
       <c r="E250" s="5"/>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="251" spans="1:5">
       <c r="A251" s="4">
         <v>46058</v>
       </c>
@@ -4169,7 +4763,7 @@
       <c r="D251" s="7"/>
       <c r="E251" s="5"/>
     </row>
-    <row r="252" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="252" spans="1:5">
       <c r="A252" s="4">
         <v>46059</v>
       </c>
@@ -4182,7 +4776,7 @@
       <c r="D252" s="7"/>
       <c r="E252" s="5"/>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="253" spans="1:5">
       <c r="A253" s="4">
         <v>46060</v>
       </c>
@@ -4195,7 +4789,7 @@
       <c r="D253" s="7"/>
       <c r="E253" s="5"/>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="254" spans="1:5">
       <c r="A254" s="4">
         <v>46061</v>
       </c>
@@ -4208,7 +4802,7 @@
       <c r="D254" s="7"/>
       <c r="E254" s="5"/>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="255" spans="1:5">
       <c r="A255" s="4">
         <v>46062</v>
       </c>
@@ -4221,7 +4815,7 @@
       <c r="D255" s="7"/>
       <c r="E255" s="5"/>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="256" spans="1:5">
       <c r="A256" s="4">
         <v>46063</v>
       </c>
@@ -4234,7 +4828,7 @@
       <c r="D256" s="7"/>
       <c r="E256" s="5"/>
     </row>
-    <row r="257" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="257" spans="1:5">
       <c r="A257" s="4">
         <v>46064</v>
       </c>
@@ -4247,7 +4841,7 @@
       <c r="D257" s="7"/>
       <c r="E257" s="5"/>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="258" spans="1:5">
       <c r="A258" s="4">
         <v>46065</v>
       </c>
@@ -4260,7 +4854,7 @@
       <c r="D258" s="7"/>
       <c r="E258" s="5"/>
     </row>
-    <row r="259" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="259" spans="1:5">
       <c r="A259" s="4">
         <v>46066</v>
       </c>
@@ -4273,7 +4867,7 @@
       <c r="D259" s="7"/>
       <c r="E259" s="5"/>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="260" spans="1:5">
       <c r="A260" s="4">
         <v>46067</v>
       </c>
@@ -4286,7 +4880,7 @@
       <c r="D260" s="7"/>
       <c r="E260" s="5"/>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="261" spans="1:5">
       <c r="A261" s="4">
         <v>46068</v>
       </c>
@@ -4299,7 +4893,7 @@
       <c r="D261" s="7"/>
       <c r="E261" s="5"/>
     </row>
-    <row r="262" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="262" spans="1:5">
       <c r="A262" s="4">
         <v>46069</v>
       </c>
@@ -4312,7 +4906,7 @@
       <c r="D262" s="7"/>
       <c r="E262" s="5"/>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="263" spans="1:5">
       <c r="A263" s="4">
         <v>46070</v>
       </c>
@@ -4325,7 +4919,7 @@
       <c r="D263" s="7"/>
       <c r="E263" s="5"/>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="264" spans="1:5">
       <c r="A264" s="4">
         <v>46071</v>
       </c>
@@ -4338,7 +4932,7 @@
       <c r="D264" s="7"/>
       <c r="E264" s="5"/>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="265" spans="1:5">
       <c r="A265" s="4">
         <v>46072</v>
       </c>
@@ -4351,7 +4945,7 @@
       <c r="D265" s="7"/>
       <c r="E265" s="5"/>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="266" spans="1:5">
       <c r="A266" s="4">
         <v>46073</v>
       </c>
@@ -4364,7 +4958,7 @@
       <c r="D266" s="7"/>
       <c r="E266" s="5"/>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="267" spans="1:5">
       <c r="A267" s="4">
         <v>46074</v>
       </c>
@@ -4377,7 +4971,7 @@
       <c r="D267" s="7"/>
       <c r="E267" s="5"/>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="268" spans="1:5">
       <c r="A268" s="4">
         <v>46075</v>
       </c>
@@ -4390,7 +4984,7 @@
       <c r="D268" s="7"/>
       <c r="E268" s="5"/>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="269" spans="1:5">
       <c r="A269" s="4">
         <v>46076</v>
       </c>
@@ -4403,7 +4997,7 @@
       <c r="D269" s="7"/>
       <c r="E269" s="5"/>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="270" spans="1:5">
       <c r="A270" s="4">
         <v>46077</v>
       </c>
@@ -4416,7 +5010,7 @@
       <c r="D270" s="7"/>
       <c r="E270" s="5"/>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="271" spans="1:5">
       <c r="A271" s="4">
         <v>46078</v>
       </c>
@@ -4429,7 +5023,7 @@
       <c r="D271" s="7"/>
       <c r="E271" s="5"/>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="272" spans="1:5">
       <c r="A272" s="4">
         <v>46079</v>
       </c>
@@ -4442,7 +5036,7 @@
       <c r="D272" s="7"/>
       <c r="E272" s="5"/>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="273" spans="1:5">
       <c r="A273" s="4">
         <v>46080</v>
       </c>
@@ -4455,7 +5049,7 @@
       <c r="D273" s="7"/>
       <c r="E273" s="5"/>
     </row>
-    <row r="274" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="274" spans="1:5">
       <c r="A274" s="4">
         <v>46081</v>
       </c>
@@ -4468,7 +5062,7 @@
       <c r="D274" s="7"/>
       <c r="E274" s="5"/>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="275" spans="1:5">
       <c r="A275" s="4">
         <v>46082</v>
       </c>
@@ -4481,7 +5075,7 @@
       <c r="D275" s="7"/>
       <c r="E275" s="5"/>
     </row>
-    <row r="276" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="276" spans="1:5">
       <c r="A276" s="4">
         <v>46083</v>
       </c>
@@ -4494,7 +5088,7 @@
       <c r="D276" s="7"/>
       <c r="E276" s="5"/>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="277" spans="1:5">
       <c r="A277" s="4">
         <v>46084</v>
       </c>
@@ -4507,7 +5101,7 @@
       <c r="D277" s="7"/>
       <c r="E277" s="5"/>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="278" spans="1:5">
       <c r="A278" s="4">
         <v>46085</v>
       </c>
@@ -4520,7 +5114,7 @@
       <c r="D278" s="7"/>
       <c r="E278" s="5"/>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="279" spans="1:5">
       <c r="A279" s="4">
         <v>46086</v>
       </c>
@@ -4533,7 +5127,7 @@
       <c r="D279" s="7"/>
       <c r="E279" s="5"/>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="280" spans="1:5">
       <c r="A280" s="4">
         <v>46087</v>
       </c>
@@ -4546,7 +5140,7 @@
       <c r="D280" s="7"/>
       <c r="E280" s="5"/>
     </row>
-    <row r="281" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="281" spans="1:5">
       <c r="A281" s="4">
         <v>46088</v>
       </c>
@@ -4559,7 +5153,7 @@
       <c r="D281" s="7"/>
       <c r="E281" s="5"/>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="282" spans="1:5">
       <c r="A282" s="4">
         <v>46089</v>
       </c>
@@ -4572,7 +5166,7 @@
       <c r="D282" s="7"/>
       <c r="E282" s="5"/>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="283" spans="1:5">
       <c r="A283" s="4">
         <v>46090</v>
       </c>
@@ -4585,7 +5179,7 @@
       <c r="D283" s="7"/>
       <c r="E283" s="5"/>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="284" spans="1:5">
       <c r="A284" s="4">
         <v>46091</v>
       </c>
@@ -4598,7 +5192,7 @@
       <c r="D284" s="7"/>
       <c r="E284" s="5"/>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="285" spans="1:5">
       <c r="A285" s="4">
         <v>46092</v>
       </c>
@@ -4611,7 +5205,7 @@
       <c r="D285" s="7"/>
       <c r="E285" s="5"/>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="286" spans="1:5">
       <c r="A286" s="4">
         <v>46093</v>
       </c>
@@ -4624,7 +5218,7 @@
       <c r="D286" s="7"/>
       <c r="E286" s="5"/>
     </row>
-    <row r="287" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="287" spans="1:5">
       <c r="A287" s="4">
         <v>46094</v>
       </c>
@@ -4637,7 +5231,7 @@
       <c r="D287" s="7"/>
       <c r="E287" s="5"/>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="288" spans="1:5">
       <c r="A288" s="4">
         <v>46095</v>
       </c>
@@ -4650,7 +5244,7 @@
       <c r="D288" s="7"/>
       <c r="E288" s="5"/>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="289" spans="1:5">
       <c r="A289" s="4">
         <v>46096</v>
       </c>
@@ -4663,7 +5257,7 @@
       <c r="D289" s="7"/>
       <c r="E289" s="5"/>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="290" spans="1:5">
       <c r="A290" s="4">
         <v>46097</v>
       </c>
@@ -4676,7 +5270,7 @@
       <c r="D290" s="7"/>
       <c r="E290" s="5"/>
     </row>
-    <row r="291" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="291" spans="1:5">
       <c r="A291" s="4">
         <v>46098</v>
       </c>
@@ -4689,7 +5283,7 @@
       <c r="D291" s="7"/>
       <c r="E291" s="5"/>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="292" spans="1:5">
       <c r="A292" s="4">
         <v>46099</v>
       </c>
@@ -4702,7 +5296,7 @@
       <c r="D292" s="7"/>
       <c r="E292" s="5"/>
     </row>
-    <row r="293" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="293" spans="1:5">
       <c r="A293" s="4">
         <v>46100</v>
       </c>
@@ -4715,7 +5309,7 @@
       <c r="D293" s="7"/>
       <c r="E293" s="5"/>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="294" spans="1:5">
       <c r="A294" s="4">
         <v>46101</v>
       </c>
@@ -4728,7 +5322,7 @@
       <c r="D294" s="7"/>
       <c r="E294" s="5"/>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="295" spans="1:5">
       <c r="A295" s="4">
         <v>46102</v>
       </c>
@@ -4741,7 +5335,7 @@
       <c r="D295" s="7"/>
       <c r="E295" s="5"/>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="296" spans="1:5">
       <c r="A296" s="4">
         <v>46103</v>
       </c>
@@ -4754,7 +5348,7 @@
       <c r="D296" s="7"/>
       <c r="E296" s="5"/>
     </row>
-    <row r="297" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="297" spans="1:5">
       <c r="A297" s="4">
         <v>46104</v>
       </c>
@@ -4767,7 +5361,7 @@
       <c r="D297" s="7"/>
       <c r="E297" s="5"/>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="298" spans="1:5">
       <c r="A298" s="4">
         <v>46105</v>
       </c>
@@ -4780,7 +5374,7 @@
       <c r="D298" s="7"/>
       <c r="E298" s="5"/>
     </row>
-    <row r="299" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="299" spans="1:5">
       <c r="A299" s="4">
         <v>46106</v>
       </c>
@@ -4793,7 +5387,7 @@
       <c r="D299" s="7"/>
       <c r="E299" s="5"/>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="300" spans="1:5">
       <c r="A300" s="4">
         <v>46107</v>
       </c>
@@ -4806,7 +5400,7 @@
       <c r="D300" s="7"/>
       <c r="E300" s="5"/>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="301" spans="1:5">
       <c r="A301" s="4">
         <v>46108</v>
       </c>
@@ -4819,7 +5413,7 @@
       <c r="D301" s="7"/>
       <c r="E301" s="5"/>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="302" spans="1:5">
       <c r="A302" s="4">
         <v>46109</v>
       </c>
@@ -4832,7 +5426,7 @@
       <c r="D302" s="7"/>
       <c r="E302" s="5"/>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="303" spans="1:5">
       <c r="A303" s="4">
         <v>46110</v>
       </c>
@@ -4845,7 +5439,7 @@
       <c r="D303" s="7"/>
       <c r="E303" s="5"/>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="304" spans="1:5">
       <c r="A304" s="4">
         <v>46111</v>
       </c>
@@ -4858,7 +5452,7 @@
       <c r="D304" s="7"/>
       <c r="E304" s="5"/>
     </row>
-    <row r="305" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="305" spans="1:5">
       <c r="A305" s="4">
         <v>46112</v>
       </c>
@@ -4871,7 +5465,7 @@
       <c r="D305" s="7"/>
       <c r="E305" s="5"/>
     </row>
-    <row r="306" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="306" spans="1:5">
       <c r="A306" s="4">
         <v>46113</v>
       </c>
@@ -4884,7 +5478,7 @@
       <c r="D306" s="7"/>
       <c r="E306" s="5"/>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="307" spans="1:5">
       <c r="A307" s="4">
         <v>46114</v>
       </c>
@@ -4897,7 +5491,7 @@
       <c r="D307" s="7"/>
       <c r="E307" s="5"/>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="308" spans="1:5">
       <c r="A308" s="4">
         <v>46115</v>
       </c>
@@ -4910,7 +5504,7 @@
       <c r="D308" s="7"/>
       <c r="E308" s="5"/>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="309" spans="1:5">
       <c r="A309" s="4">
         <v>46116</v>
       </c>
@@ -4923,7 +5517,7 @@
       <c r="D309" s="7"/>
       <c r="E309" s="5"/>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="310" spans="1:5">
       <c r="A310" s="4">
         <v>46117</v>
       </c>
@@ -4936,7 +5530,7 @@
       <c r="D310" s="7"/>
       <c r="E310" s="5"/>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="311" spans="1:5">
       <c r="A311" s="4">
         <v>46118</v>
       </c>
@@ -4949,7 +5543,7 @@
       <c r="D311" s="7"/>
       <c r="E311" s="5"/>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="312" spans="1:5">
       <c r="A312" s="4">
         <v>46119</v>
       </c>
@@ -4962,7 +5556,7 @@
       <c r="D312" s="7"/>
       <c r="E312" s="5"/>
     </row>
-    <row r="313" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="313" spans="1:5">
       <c r="A313" s="4">
         <v>46120</v>
       </c>
@@ -4975,7 +5569,7 @@
       <c r="D313" s="7"/>
       <c r="E313" s="5"/>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="314" spans="1:5">
       <c r="A314" s="4">
         <v>46121</v>
       </c>
@@ -4988,7 +5582,7 @@
       <c r="D314" s="7"/>
       <c r="E314" s="5"/>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="315" spans="1:5">
       <c r="A315" s="4">
         <v>46122</v>
       </c>
@@ -5001,7 +5595,7 @@
       <c r="D315" s="7"/>
       <c r="E315" s="5"/>
     </row>
-    <row r="316" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="316" spans="1:5">
       <c r="A316" s="4">
         <v>46123</v>
       </c>
@@ -5014,7 +5608,7 @@
       <c r="D316" s="7"/>
       <c r="E316" s="5"/>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="317" spans="1:5">
       <c r="A317" s="4">
         <v>46124</v>
       </c>
@@ -5027,7 +5621,7 @@
       <c r="D317" s="7"/>
       <c r="E317" s="5"/>
     </row>
-    <row r="318" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="318" spans="1:5">
       <c r="A318" s="4">
         <v>46125</v>
       </c>
@@ -5040,7 +5634,7 @@
       <c r="D318" s="7"/>
       <c r="E318" s="5"/>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="319" spans="1:5">
       <c r="A319" s="4">
         <v>46126</v>
       </c>
@@ -5053,7 +5647,7 @@
       <c r="D319" s="7"/>
       <c r="E319" s="5"/>
     </row>
-    <row r="320" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="320" spans="1:5">
       <c r="A320" s="4">
         <v>46127</v>
       </c>
@@ -5066,7 +5660,7 @@
       <c r="D320" s="7"/>
       <c r="E320" s="5"/>
     </row>
-    <row r="321" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="321" spans="1:5">
       <c r="A321" s="4">
         <v>46128</v>
       </c>
@@ -5079,7 +5673,7 @@
       <c r="D321" s="7"/>
       <c r="E321" s="5"/>
     </row>
-    <row r="322" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="322" spans="1:5">
       <c r="A322" s="4">
         <v>46129</v>
       </c>
@@ -5092,7 +5686,7 @@
       <c r="D322" s="7"/>
       <c r="E322" s="5"/>
     </row>
-    <row r="323" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="323" spans="1:5">
       <c r="A323" s="4">
         <v>46130</v>
       </c>
@@ -5105,7 +5699,7 @@
       <c r="D323" s="7"/>
       <c r="E323" s="5"/>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="324" spans="1:5">
       <c r="A324" s="4">
         <v>46131</v>
       </c>
@@ -5118,7 +5712,7 @@
       <c r="D324" s="7"/>
       <c r="E324" s="5"/>
     </row>
-    <row r="325" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="325" spans="1:5">
       <c r="A325" s="4">
         <v>46132</v>
       </c>
@@ -5131,7 +5725,7 @@
       <c r="D325" s="7"/>
       <c r="E325" s="5"/>
     </row>
-    <row r="326" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="326" spans="1:5">
       <c r="A326" s="4">
         <v>46133</v>
       </c>
@@ -5144,7 +5738,7 @@
       <c r="D326" s="7"/>
       <c r="E326" s="5"/>
     </row>
-    <row r="327" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="327" spans="1:5">
       <c r="A327" s="4">
         <v>46134</v>
       </c>
@@ -5157,7 +5751,7 @@
       <c r="D327" s="7"/>
       <c r="E327" s="5"/>
     </row>
-    <row r="328" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="328" spans="1:5">
       <c r="A328" s="4">
         <v>46135</v>
       </c>
@@ -5170,7 +5764,7 @@
       <c r="D328" s="7"/>
       <c r="E328" s="5"/>
     </row>
-    <row r="329" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="329" spans="1:5">
       <c r="A329" s="4">
         <v>46136</v>
       </c>
@@ -5183,7 +5777,7 @@
       <c r="D329" s="7"/>
       <c r="E329" s="5"/>
     </row>
-    <row r="330" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="330" spans="1:5">
       <c r="A330" s="4">
         <v>46137</v>
       </c>
@@ -5196,7 +5790,7 @@
       <c r="D330" s="7"/>
       <c r="E330" s="5"/>
     </row>
-    <row r="331" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="331" spans="1:5">
       <c r="A331" s="4">
         <v>46138</v>
       </c>
@@ -5209,7 +5803,7 @@
       <c r="D331" s="7"/>
       <c r="E331" s="5"/>
     </row>
-    <row r="332" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="332" spans="1:5">
       <c r="A332" s="4">
         <v>46139</v>
       </c>
@@ -5222,7 +5816,7 @@
       <c r="D332" s="7"/>
       <c r="E332" s="5"/>
     </row>
-    <row r="333" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="333" spans="1:5">
       <c r="A333" s="4">
         <v>46140</v>
       </c>
@@ -5235,7 +5829,7 @@
       <c r="D333" s="7"/>
       <c r="E333" s="5"/>
     </row>
-    <row r="334" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="334" spans="1:5">
       <c r="A334" s="4">
         <v>46141</v>
       </c>
@@ -5248,7 +5842,7 @@
       <c r="D334" s="7"/>
       <c r="E334" s="5"/>
     </row>
-    <row r="335" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="335" spans="1:5">
       <c r="A335" s="4">
         <v>46142</v>
       </c>
@@ -5261,7 +5855,7 @@
       <c r="D335" s="7"/>
       <c r="E335" s="5"/>
     </row>
-    <row r="336" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="336" spans="1:5">
       <c r="A336" s="4">
         <v>46143</v>
       </c>
@@ -5274,7 +5868,7 @@
       <c r="D336" s="7"/>
       <c r="E336" s="5"/>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="337" spans="1:5">
       <c r="A337" s="4">
         <v>46144</v>
       </c>
@@ -5287,7 +5881,7 @@
       <c r="D337" s="7"/>
       <c r="E337" s="5"/>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="338" spans="1:5">
       <c r="A338" s="4">
         <v>46145</v>
       </c>
@@ -5300,7 +5894,7 @@
       <c r="D338" s="7"/>
       <c r="E338" s="5"/>
     </row>
-    <row r="339" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="339" spans="1:5">
       <c r="A339" s="4">
         <v>46146</v>
       </c>
@@ -5313,7 +5907,7 @@
       <c r="D339" s="7"/>
       <c r="E339" s="5"/>
     </row>
-    <row r="340" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="340" spans="1:5">
       <c r="A340" s="4">
         <v>46147</v>
       </c>
@@ -5326,7 +5920,7 @@
       <c r="D340" s="7"/>
       <c r="E340" s="5"/>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="341" spans="1:5">
       <c r="A341" s="4">
         <v>46148</v>
       </c>
@@ -5339,7 +5933,7 @@
       <c r="D341" s="7"/>
       <c r="E341" s="5"/>
     </row>
-    <row r="342" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="342" spans="1:5">
       <c r="A342" s="4">
         <v>46149</v>
       </c>
@@ -5352,7 +5946,7 @@
       <c r="D342" s="7"/>
       <c r="E342" s="5"/>
     </row>
-    <row r="343" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="343" spans="1:5">
       <c r="A343" s="4">
         <v>46150</v>
       </c>
@@ -5365,7 +5959,7 @@
       <c r="D343" s="7"/>
       <c r="E343" s="5"/>
     </row>
-    <row r="344" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="344" spans="1:5">
       <c r="A344" s="4">
         <v>46151</v>
       </c>
@@ -5378,7 +5972,7 @@
       <c r="D344" s="7"/>
       <c r="E344" s="5"/>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="345" spans="1:5">
       <c r="A345" s="4">
         <v>46152</v>
       </c>
@@ -5391,7 +5985,7 @@
       <c r="D345" s="7"/>
       <c r="E345" s="5"/>
     </row>
-    <row r="346" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="346" spans="1:5">
       <c r="A346" s="4">
         <v>46153</v>
       </c>
@@ -5404,7 +5998,7 @@
       <c r="D346" s="7"/>
       <c r="E346" s="5"/>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="347" spans="1:5">
       <c r="A347" s="4">
         <v>46154</v>
       </c>
@@ -5417,7 +6011,7 @@
       <c r="D347" s="7"/>
       <c r="E347" s="5"/>
     </row>
-    <row r="348" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="348" spans="1:5">
       <c r="A348" s="4">
         <v>46155</v>
       </c>
@@ -5430,7 +6024,7 @@
       <c r="D348" s="7"/>
       <c r="E348" s="5"/>
     </row>
-    <row r="349" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="349" spans="1:5">
       <c r="A349" s="4">
         <v>46156</v>
       </c>
@@ -5443,7 +6037,7 @@
       <c r="D349" s="7"/>
       <c r="E349" s="5"/>
     </row>
-    <row r="350" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="350" spans="1:5">
       <c r="A350" s="4">
         <v>46157</v>
       </c>
@@ -5456,7 +6050,7 @@
       <c r="D350" s="7"/>
       <c r="E350" s="5"/>
     </row>
-    <row r="351" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="351" spans="1:5">
       <c r="A351" s="4">
         <v>46158</v>
       </c>
@@ -5469,7 +6063,7 @@
       <c r="D351" s="7"/>
       <c r="E351" s="5"/>
     </row>
-    <row r="352" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="352" spans="1:5">
       <c r="A352" s="4">
         <v>46159</v>
       </c>
@@ -5482,7 +6076,7 @@
       <c r="D352" s="7"/>
       <c r="E352" s="5"/>
     </row>
-    <row r="353" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="353" spans="1:5">
       <c r="A353" s="4">
         <v>46160</v>
       </c>
@@ -5495,7 +6089,7 @@
       <c r="D353" s="7"/>
       <c r="E353" s="5"/>
     </row>
-    <row r="354" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="354" spans="1:5">
       <c r="A354" s="4">
         <v>46161</v>
       </c>
@@ -5508,7 +6102,7 @@
       <c r="D354" s="7"/>
       <c r="E354" s="5"/>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="355" spans="1:5">
       <c r="A355" s="4">
         <v>46162</v>
       </c>
@@ -5521,7 +6115,7 @@
       <c r="D355" s="7"/>
       <c r="E355" s="5"/>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="356" spans="1:5">
       <c r="A356" s="4">
         <v>46163</v>
       </c>
@@ -5534,7 +6128,7 @@
       <c r="D356" s="7"/>
       <c r="E356" s="5"/>
     </row>
-    <row r="357" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="357" spans="1:5">
       <c r="A357" s="4">
         <v>46164</v>
       </c>
@@ -5547,7 +6141,7 @@
       <c r="D357" s="7"/>
       <c r="E357" s="5"/>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="358" spans="1:5">
       <c r="A358" s="4">
         <v>46165</v>
       </c>
@@ -5560,7 +6154,7 @@
       <c r="D358" s="7"/>
       <c r="E358" s="5"/>
     </row>
-    <row r="359" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="359" spans="1:5">
       <c r="A359" s="4">
         <v>46166</v>
       </c>
@@ -5573,7 +6167,7 @@
       <c r="D359" s="7"/>
       <c r="E359" s="5"/>
     </row>
-    <row r="360" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="360" spans="1:5">
       <c r="A360" s="4">
         <v>46167</v>
       </c>
@@ -5586,7 +6180,7 @@
       <c r="D360" s="7"/>
       <c r="E360" s="5"/>
     </row>
-    <row r="361" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="361" spans="1:5">
       <c r="A361" s="4">
         <v>46168</v>
       </c>
@@ -5599,7 +6193,7 @@
       <c r="D361" s="7"/>
       <c r="E361" s="5"/>
     </row>
-    <row r="362" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="362" spans="1:5">
       <c r="A362" s="4">
         <v>46169</v>
       </c>
@@ -5612,7 +6206,7 @@
       <c r="D362" s="7"/>
       <c r="E362" s="5"/>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="363" spans="1:5">
       <c r="A363" s="4">
         <v>46170</v>
       </c>
@@ -5625,7 +6219,7 @@
       <c r="D363" s="7"/>
       <c r="E363" s="5"/>
     </row>
-    <row r="364" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="364" spans="1:5">
       <c r="A364" s="4">
         <v>46171</v>
       </c>
@@ -5638,7 +6232,7 @@
       <c r="D364" s="7"/>
       <c r="E364" s="5"/>
     </row>
-    <row r="365" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="365" spans="1:5">
       <c r="A365" s="4">
         <v>46172</v>
       </c>
@@ -5651,7 +6245,7 @@
       <c r="D365" s="7"/>
       <c r="E365" s="5"/>
     </row>
-    <row r="366" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="366" spans="1:5">
       <c r="A366" s="4">
         <v>46173</v>
       </c>
@@ -5664,7 +6258,7 @@
       <c r="D366" s="7"/>
       <c r="E366" s="5"/>
     </row>
-    <row r="367" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="367" spans="1:5">
       <c r="A367" s="4">
         <v>46174</v>
       </c>
@@ -5677,7 +6271,7 @@
       <c r="D367" s="7"/>
       <c r="E367" s="5"/>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="368" spans="1:5">
       <c r="A368" s="4">
         <v>46175</v>
       </c>
@@ -5690,7 +6284,7 @@
       <c r="D368" s="7"/>
       <c r="E368" s="5"/>
     </row>
-    <row r="369" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="369" spans="1:5">
       <c r="A369" s="4">
         <v>46176</v>
       </c>
@@ -5703,7 +6297,7 @@
       <c r="D369" s="7"/>
       <c r="E369" s="5"/>
     </row>
-    <row r="370" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="370" spans="1:5">
       <c r="A370" s="4">
         <v>46177</v>
       </c>
@@ -5716,7 +6310,7 @@
       <c r="D370" s="7"/>
       <c r="E370" s="5"/>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="371" spans="1:5">
       <c r="A371" s="4">
         <v>46178</v>
       </c>
@@ -5729,7 +6323,7 @@
       <c r="D371" s="7"/>
       <c r="E371" s="5"/>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="372" spans="1:5">
       <c r="A372" s="4">
         <v>46179</v>
       </c>
@@ -5742,7 +6336,7 @@
       <c r="D372" s="7"/>
       <c r="E372" s="5"/>
     </row>
-    <row r="373" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="373" spans="1:5">
       <c r="A373" s="4">
         <v>46180</v>
       </c>
@@ -5755,7 +6349,7 @@
       <c r="D373" s="7"/>
       <c r="E373" s="5"/>
     </row>
-    <row r="374" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="374" spans="1:5">
       <c r="A374" s="4">
         <v>46181</v>
       </c>
@@ -5768,7 +6362,7 @@
       <c r="D374" s="7"/>
       <c r="E374" s="5"/>
     </row>
-    <row r="375" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="375" spans="1:5">
       <c r="A375" s="4">
         <v>46182</v>
       </c>
@@ -5781,7 +6375,7 @@
       <c r="D375" s="7"/>
       <c r="E375" s="5"/>
     </row>
-    <row r="376" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="376" spans="1:5">
       <c r="A376" s="4">
         <v>46183</v>
       </c>
@@ -5794,7 +6388,7 @@
       <c r="D376" s="7"/>
       <c r="E376" s="5"/>
     </row>
-    <row r="377" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="377" spans="1:5">
       <c r="A377" s="4">
         <v>46184</v>
       </c>
@@ -5807,7 +6401,7 @@
       <c r="D377" s="7"/>
       <c r="E377" s="5"/>
     </row>
-    <row r="378" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="378" spans="1:5">
       <c r="A378" s="4">
         <v>46185</v>
       </c>
@@ -5820,7 +6414,7 @@
       <c r="D378" s="7"/>
       <c r="E378" s="5"/>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="379" spans="1:5">
       <c r="A379" s="4">
         <v>46186</v>
       </c>
@@ -5833,7 +6427,7 @@
       <c r="D379" s="7"/>
       <c r="E379" s="5"/>
     </row>
-    <row r="380" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="380" spans="1:5">
       <c r="A380" s="4">
         <v>46187</v>
       </c>
@@ -5846,7 +6440,7 @@
       <c r="D380" s="7"/>
       <c r="E380" s="5"/>
     </row>
-    <row r="381" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="381" spans="1:5">
       <c r="A381" s="4">
         <v>46188</v>
       </c>
@@ -5859,7 +6453,7 @@
       <c r="D381" s="7"/>
       <c r="E381" s="5"/>
     </row>
-    <row r="382" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="382" spans="1:5">
       <c r="A382" s="4">
         <v>46189</v>
       </c>
@@ -5872,7 +6466,7 @@
       <c r="D382" s="7"/>
       <c r="E382" s="5"/>
     </row>
-    <row r="383" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="383" spans="1:5">
       <c r="A383" s="4">
         <v>46190</v>
       </c>
@@ -5885,7 +6479,7 @@
       <c r="D383" s="7"/>
       <c r="E383" s="5"/>
     </row>
-    <row r="384" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="384" spans="1:5">
       <c r="A384" s="4">
         <v>46191</v>
       </c>
@@ -5898,7 +6492,7 @@
       <c r="D384" s="7"/>
       <c r="E384" s="5"/>
     </row>
-    <row r="385" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="385" spans="1:5">
       <c r="A385" s="4">
         <v>46192</v>
       </c>
@@ -5911,7 +6505,7 @@
       <c r="D385" s="7"/>
       <c r="E385" s="5"/>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="386" spans="1:5">
       <c r="A386" s="4">
         <v>46193</v>
       </c>
@@ -5924,7 +6518,7 @@
       <c r="D386" s="7"/>
       <c r="E386" s="5"/>
     </row>
-    <row r="387" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="387" spans="1:5">
       <c r="A387" s="4">
         <v>46194</v>
       </c>
@@ -5937,7 +6531,7 @@
       <c r="D387" s="7"/>
       <c r="E387" s="5"/>
     </row>
-    <row r="388" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="388" spans="1:5">
       <c r="A388" s="4">
         <v>46195</v>
       </c>
@@ -5950,7 +6544,7 @@
       <c r="D388" s="7"/>
       <c r="E388" s="5"/>
     </row>
-    <row r="389" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="389" spans="1:5">
       <c r="A389" s="4">
         <v>46196</v>
       </c>
@@ -5963,7 +6557,7 @@
       <c r="D389" s="7"/>
       <c r="E389" s="5"/>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="390" spans="1:5">
       <c r="A390" s="4">
         <v>46197</v>
       </c>
@@ -5976,7 +6570,7 @@
       <c r="D390" s="7"/>
       <c r="E390" s="5"/>
     </row>
-    <row r="391" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="391" spans="1:5">
       <c r="A391" s="4">
         <v>46198</v>
       </c>
@@ -5989,7 +6583,7 @@
       <c r="D391" s="7"/>
       <c r="E391" s="5"/>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="392" spans="1:5">
       <c r="A392" s="4">
         <v>46199</v>
       </c>
@@ -6002,7 +6596,7 @@
       <c r="D392" s="7"/>
       <c r="E392" s="5"/>
     </row>
-    <row r="393" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="393" spans="1:5">
       <c r="A393" s="4">
         <v>46200</v>
       </c>
@@ -6015,7 +6609,7 @@
       <c r="D393" s="7"/>
       <c r="E393" s="5"/>
     </row>
-    <row r="394" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="394" spans="1:5">
       <c r="A394" s="4">
         <v>46201</v>
       </c>
@@ -6028,7 +6622,7 @@
       <c r="D394" s="7"/>
       <c r="E394" s="5"/>
     </row>
-    <row r="395" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="395" spans="1:5">
       <c r="A395" s="4">
         <v>46202</v>
       </c>
@@ -6041,7 +6635,7 @@
       <c r="D395" s="7"/>
       <c r="E395" s="5"/>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="396" spans="1:5">
       <c r="A396" s="4">
         <v>46203</v>
       </c>
@@ -6054,7 +6648,7 @@
       <c r="D396" s="7"/>
       <c r="E396" s="5"/>
     </row>
-    <row r="397" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="397" spans="1:5">
       <c r="A397" s="4">
         <v>46204</v>
       </c>
@@ -6067,7 +6661,7 @@
       <c r="D397" s="7"/>
       <c r="E397" s="5"/>
     </row>
-    <row r="398" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="398" spans="1:5">
       <c r="A398" s="4">
         <v>46205</v>
       </c>
@@ -6080,7 +6674,7 @@
       <c r="D398" s="7"/>
       <c r="E398" s="5"/>
     </row>
-    <row r="399" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="399" spans="1:5">
       <c r="A399" s="4">
         <v>46206</v>
       </c>
@@ -6093,7 +6687,7 @@
       <c r="D399" s="7"/>
       <c r="E399" s="5"/>
     </row>
-    <row r="400" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="400" spans="1:5">
       <c r="A400" s="4">
         <v>46207</v>
       </c>
@@ -6106,7 +6700,7 @@
       <c r="D400" s="7"/>
       <c r="E400" s="5"/>
     </row>
-    <row r="401" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="401" spans="1:5">
       <c r="A401" s="4">
         <v>46208</v>
       </c>
@@ -6119,7 +6713,7 @@
       <c r="D401" s="7"/>
       <c r="E401" s="5"/>
     </row>
-    <row r="402" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="402" spans="1:5">
       <c r="A402" s="4">
         <v>46209</v>
       </c>
@@ -6132,7 +6726,7 @@
       <c r="D402" s="7"/>
       <c r="E402" s="5"/>
     </row>
-    <row r="403" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="403" spans="1:5">
       <c r="A403" s="4">
         <v>46210</v>
       </c>
@@ -6145,7 +6739,7 @@
       <c r="D403" s="7"/>
       <c r="E403" s="5"/>
     </row>
-    <row r="404" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="404" spans="1:5">
       <c r="A404" s="4">
         <v>46211</v>
       </c>
@@ -6158,7 +6752,7 @@
       <c r="D404" s="7"/>
       <c r="E404" s="5"/>
     </row>
-    <row r="405" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="405" spans="1:5">
       <c r="A405" s="4">
         <v>46212</v>
       </c>
@@ -6171,7 +6765,7 @@
       <c r="D405" s="7"/>
       <c r="E405" s="5"/>
     </row>
-    <row r="406" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="406" spans="1:5">
       <c r="A406" s="4">
         <v>46213</v>
       </c>
@@ -6184,7 +6778,7 @@
       <c r="D406" s="7"/>
       <c r="E406" s="5"/>
     </row>
-    <row r="407" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="407" spans="1:5">
       <c r="A407" s="4">
         <v>46214</v>
       </c>
@@ -6197,7 +6791,7 @@
       <c r="D407" s="7"/>
       <c r="E407" s="5"/>
     </row>
-    <row r="408" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="408" spans="1:5">
       <c r="A408" s="4">
         <v>46215</v>
       </c>
@@ -6210,7 +6804,7 @@
       <c r="D408" s="7"/>
       <c r="E408" s="5"/>
     </row>
-    <row r="409" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="409" spans="1:5">
       <c r="A409" s="4">
         <v>46216</v>
       </c>
@@ -6223,7 +6817,7 @@
       <c r="D409" s="7"/>
       <c r="E409" s="5"/>
     </row>
-    <row r="410" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="410" spans="1:5">
       <c r="A410" s="4">
         <v>46217</v>
       </c>
@@ -6236,7 +6830,7 @@
       <c r="D410" s="7"/>
       <c r="E410" s="5"/>
     </row>
-    <row r="411" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="411" spans="1:5">
       <c r="A411" s="4">
         <v>46218</v>
       </c>
@@ -6249,7 +6843,7 @@
       <c r="D411" s="7"/>
       <c r="E411" s="5"/>
     </row>
-    <row r="412" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="412" spans="1:5">
       <c r="A412" s="4">
         <v>46219</v>
       </c>
@@ -6262,7 +6856,7 @@
       <c r="D412" s="7"/>
       <c r="E412" s="5"/>
     </row>
-    <row r="413" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="413" spans="1:5">
       <c r="A413" s="4">
         <v>46220</v>
       </c>
@@ -6275,7 +6869,7 @@
       <c r="D413" s="7"/>
       <c r="E413" s="5"/>
     </row>
-    <row r="414" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="414" spans="1:5">
       <c r="A414" s="4">
         <v>46221</v>
       </c>
@@ -6288,7 +6882,7 @@
       <c r="D414" s="7"/>
       <c r="E414" s="5"/>
     </row>
-    <row r="415" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="415" spans="1:5">
       <c r="A415" s="4">
         <v>46222</v>
       </c>
@@ -6301,7 +6895,7 @@
       <c r="D415" s="7"/>
       <c r="E415" s="5"/>
     </row>
-    <row r="416" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="416" spans="1:5">
       <c r="A416" s="4">
         <v>46223</v>
       </c>
@@ -6314,7 +6908,7 @@
       <c r="D416" s="7"/>
       <c r="E416" s="5"/>
     </row>
-    <row r="417" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="417" spans="1:5">
       <c r="A417" s="4">
         <v>46224</v>
       </c>
@@ -6327,7 +6921,7 @@
       <c r="D417" s="7"/>
       <c r="E417" s="5"/>
     </row>
-    <row r="418" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="418" spans="1:5">
       <c r="A418" s="4">
         <v>46225</v>
       </c>
@@ -6340,7 +6934,7 @@
       <c r="D418" s="7"/>
       <c r="E418" s="5"/>
     </row>
-    <row r="419" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="419" spans="1:5">
       <c r="A419" s="4">
         <v>46226</v>
       </c>
@@ -6353,7 +6947,7 @@
       <c r="D419" s="7"/>
       <c r="E419" s="5"/>
     </row>
-    <row r="420" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="420" spans="1:5">
       <c r="A420" s="4">
         <v>46227</v>
       </c>
@@ -6366,7 +6960,7 @@
       <c r="D420" s="7"/>
       <c r="E420" s="5"/>
     </row>
-    <row r="421" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="421" spans="1:5">
       <c r="A421" s="4">
         <v>46228</v>
       </c>
@@ -6379,7 +6973,7 @@
       <c r="D421" s="7"/>
       <c r="E421" s="5"/>
     </row>
-    <row r="422" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="422" spans="1:5">
       <c r="A422" s="4">
         <v>46229</v>
       </c>
@@ -6392,7 +6986,7 @@
       <c r="D422" s="7"/>
       <c r="E422" s="5"/>
     </row>
-    <row r="423" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="423" spans="1:5">
       <c r="A423" s="4">
         <v>46230</v>
       </c>
@@ -6405,7 +6999,7 @@
       <c r="D423" s="7"/>
       <c r="E423" s="5"/>
     </row>
-    <row r="424" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="424" spans="1:5">
       <c r="A424" s="4">
         <v>46231</v>
       </c>
@@ -6418,7 +7012,7 @@
       <c r="D424" s="7"/>
       <c r="E424" s="5"/>
     </row>
-    <row r="425" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="425" spans="1:5">
       <c r="A425" s="4">
         <v>46232</v>
       </c>
@@ -6431,7 +7025,7 @@
       <c r="D425" s="7"/>
       <c r="E425" s="5"/>
     </row>
-    <row r="426" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="426" spans="1:5">
       <c r="A426" s="4">
         <v>46233</v>
       </c>
@@ -6444,7 +7038,7 @@
       <c r="D426" s="7"/>
       <c r="E426" s="5"/>
     </row>
-    <row r="427" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="427" spans="1:5">
       <c r="A427" s="4">
         <v>46234</v>
       </c>
@@ -6457,7 +7051,7 @@
       <c r="D427" s="7"/>
       <c r="E427" s="5"/>
     </row>
-    <row r="428" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="428" spans="1:5">
       <c r="A428" s="4">
         <v>46235</v>
       </c>
@@ -6470,7 +7064,7 @@
       <c r="D428" s="7"/>
       <c r="E428" s="5"/>
     </row>
-    <row r="429" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="429" spans="1:5">
       <c r="A429" s="4">
         <v>46236</v>
       </c>
@@ -6483,7 +7077,7 @@
       <c r="D429" s="7"/>
       <c r="E429" s="5"/>
     </row>
-    <row r="430" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="430" spans="1:5">
       <c r="A430" s="4">
         <v>46237</v>
       </c>
@@ -6496,7 +7090,7 @@
       <c r="D430" s="7"/>
       <c r="E430" s="5"/>
     </row>
-    <row r="431" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="431" spans="1:5">
       <c r="A431" s="4">
         <v>46238</v>
       </c>
@@ -6509,7 +7103,7 @@
       <c r="D431" s="7"/>
       <c r="E431" s="5"/>
     </row>
-    <row r="432" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="432" spans="1:5">
       <c r="A432" s="4">
         <v>46239</v>
       </c>
@@ -6522,7 +7116,7 @@
       <c r="D432" s="7"/>
       <c r="E432" s="5"/>
     </row>
-    <row r="433" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="433" spans="1:5">
       <c r="A433" s="4">
         <v>46240</v>
       </c>
@@ -6535,7 +7129,7 @@
       <c r="D433" s="7"/>
       <c r="E433" s="5"/>
     </row>
-    <row r="434" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="434" spans="1:5">
       <c r="A434" s="4">
         <v>46241</v>
       </c>
@@ -6548,7 +7142,7 @@
       <c r="D434" s="7"/>
       <c r="E434" s="5"/>
     </row>
-    <row r="435" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="435" spans="1:5">
       <c r="A435" s="4">
         <v>46242</v>
       </c>
@@ -6561,7 +7155,7 @@
       <c r="D435" s="7"/>
       <c r="E435" s="5"/>
     </row>
-    <row r="436" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="436" spans="1:5">
       <c r="A436" s="4">
         <v>46243</v>
       </c>
@@ -6574,7 +7168,7 @@
       <c r="D436" s="7"/>
       <c r="E436" s="5"/>
     </row>
-    <row r="437" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="437" spans="1:5">
       <c r="A437" s="4">
         <v>46244</v>
       </c>
@@ -6587,7 +7181,7 @@
       <c r="D437" s="7"/>
       <c r="E437" s="5"/>
     </row>
-    <row r="438" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="438" spans="1:5">
       <c r="A438" s="4">
         <v>46245</v>
       </c>
@@ -6600,7 +7194,7 @@
       <c r="D438" s="7"/>
       <c r="E438" s="5"/>
     </row>
-    <row r="439" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="439" spans="1:5">
       <c r="A439" s="4">
         <v>46246</v>
       </c>
@@ -6613,7 +7207,7 @@
       <c r="D439" s="7"/>
       <c r="E439" s="5"/>
     </row>
-    <row r="440" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="440" spans="1:5">
       <c r="A440" s="4">
         <v>46247</v>
       </c>
@@ -6626,7 +7220,7 @@
       <c r="D440" s="7"/>
       <c r="E440" s="5"/>
     </row>
-    <row r="441" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="441" spans="1:5">
       <c r="A441" s="4">
         <v>46248</v>
       </c>
@@ -6639,7 +7233,7 @@
       <c r="D441" s="7"/>
       <c r="E441" s="5"/>
     </row>
-    <row r="442" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="442" spans="1:5">
       <c r="A442" s="4">
         <v>46249</v>
       </c>
@@ -6652,7 +7246,7 @@
       <c r="D442" s="7"/>
       <c r="E442" s="5"/>
     </row>
-    <row r="443" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="443" spans="1:5">
       <c r="A443" s="4">
         <v>46250</v>
       </c>
@@ -6665,7 +7259,7 @@
       <c r="D443" s="7"/>
       <c r="E443" s="5"/>
     </row>
-    <row r="444" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="444" spans="1:5">
       <c r="A444" s="4">
         <v>46251</v>
       </c>
@@ -6678,7 +7272,7 @@
       <c r="D444" s="7"/>
       <c r="E444" s="5"/>
     </row>
-    <row r="445" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="445" spans="1:5">
       <c r="A445" s="4">
         <v>46252</v>
       </c>
@@ -6691,7 +7285,7 @@
       <c r="D445" s="7"/>
       <c r="E445" s="5"/>
     </row>
-    <row r="446" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="446" spans="1:5">
       <c r="A446" s="4">
         <v>46253</v>
       </c>
@@ -6704,7 +7298,7 @@
       <c r="D446" s="7"/>
       <c r="E446" s="5"/>
     </row>
-    <row r="447" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="447" spans="1:5">
       <c r="A447" s="4">
         <v>46254</v>
       </c>
@@ -6717,7 +7311,7 @@
       <c r="D447" s="7"/>
       <c r="E447" s="5"/>
     </row>
-    <row r="448" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="448" spans="1:5">
       <c r="A448" s="4">
         <v>46255</v>
       </c>
@@ -6730,7 +7324,7 @@
       <c r="D448" s="7"/>
       <c r="E448" s="5"/>
     </row>
-    <row r="449" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="449" spans="1:5">
       <c r="A449" s="4">
         <v>46256</v>
       </c>
@@ -6743,7 +7337,7 @@
       <c r="D449" s="7"/>
       <c r="E449" s="5"/>
     </row>
-    <row r="450" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="450" spans="1:5">
       <c r="A450" s="4">
         <v>46257</v>
       </c>
@@ -6756,7 +7350,7 @@
       <c r="D450" s="7"/>
       <c r="E450" s="5"/>
     </row>
-    <row r="451" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="451" spans="1:5">
       <c r="A451" s="4">
         <v>46258</v>
       </c>
@@ -6769,7 +7363,7 @@
       <c r="D451" s="7"/>
       <c r="E451" s="5"/>
     </row>
-    <row r="452" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="452" spans="1:5">
       <c r="A452" s="4">
         <v>46259</v>
       </c>
@@ -6782,7 +7376,7 @@
       <c r="D452" s="7"/>
       <c r="E452" s="5"/>
     </row>
-    <row r="453" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="453" spans="1:5">
       <c r="A453" s="4">
         <v>46260</v>
       </c>
@@ -6795,7 +7389,7 @@
       <c r="D453" s="7"/>
       <c r="E453" s="5"/>
     </row>
-    <row r="454" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="454" spans="1:5">
       <c r="A454" s="4">
         <v>46261</v>
       </c>
@@ -6808,7 +7402,7 @@
       <c r="D454" s="7"/>
       <c r="E454" s="5"/>
     </row>
-    <row r="455" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="455" spans="1:5">
       <c r="A455" s="4">
         <v>46262</v>
       </c>
@@ -6821,7 +7415,7 @@
       <c r="D455" s="7"/>
       <c r="E455" s="5"/>
     </row>
-    <row r="456" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="456" spans="1:5">
       <c r="A456" s="4">
         <v>46263</v>
       </c>
@@ -6834,7 +7428,7 @@
       <c r="D456" s="7"/>
       <c r="E456" s="5"/>
     </row>
-    <row r="457" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="457" spans="1:5">
       <c r="A457" s="4">
         <v>46264</v>
       </c>
@@ -6847,7 +7441,7 @@
       <c r="D457" s="7"/>
       <c r="E457" s="5"/>
     </row>
-    <row r="458" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="458" spans="1:5">
       <c r="A458" s="4">
         <v>46265</v>
       </c>
@@ -6860,7 +7454,7 @@
       <c r="D458" s="7"/>
       <c r="E458" s="5"/>
     </row>
-    <row r="459" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="459" spans="1:5">
       <c r="A459" s="4">
         <v>46266</v>
       </c>
@@ -6873,7 +7467,7 @@
       <c r="D459" s="7"/>
       <c r="E459" s="5"/>
     </row>
-    <row r="460" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="460" spans="1:5">
       <c r="A460" s="4">
         <v>46267</v>
       </c>
@@ -6886,7 +7480,7 @@
       <c r="D460" s="7"/>
       <c r="E460" s="5"/>
     </row>
-    <row r="461" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="461" spans="1:5">
       <c r="A461" s="4">
         <v>46268</v>
       </c>
@@ -6899,7 +7493,7 @@
       <c r="D461" s="7"/>
       <c r="E461" s="5"/>
     </row>
-    <row r="462" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="462" spans="1:5">
       <c r="A462" s="4">
         <v>46269</v>
       </c>
@@ -6912,7 +7506,7 @@
       <c r="D462" s="7"/>
       <c r="E462" s="5"/>
     </row>
-    <row r="463" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="463" spans="1:5">
       <c r="A463" s="4">
         <v>46270</v>
       </c>
@@ -6925,7 +7519,7 @@
       <c r="D463" s="7"/>
       <c r="E463" s="5"/>
     </row>
-    <row r="464" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="464" spans="1:5">
       <c r="A464" s="4">
         <v>46271</v>
       </c>
@@ -6938,7 +7532,7 @@
       <c r="D464" s="7"/>
       <c r="E464" s="5"/>
     </row>
-    <row r="465" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="465" spans="1:5">
       <c r="A465" s="4">
         <v>46272</v>
       </c>
@@ -6951,7 +7545,7 @@
       <c r="D465" s="7"/>
       <c r="E465" s="5"/>
     </row>
-    <row r="466" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="466" spans="1:5">
       <c r="A466" s="4">
         <v>46273</v>
       </c>
@@ -6964,7 +7558,7 @@
       <c r="D466" s="7"/>
       <c r="E466" s="5"/>
     </row>
-    <row r="467" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="467" spans="1:5">
       <c r="A467" s="4">
         <v>46274</v>
       </c>
@@ -6977,7 +7571,7 @@
       <c r="D467" s="7"/>
       <c r="E467" s="5"/>
     </row>
-    <row r="468" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="468" spans="1:5">
       <c r="A468" s="4">
         <v>46275</v>
       </c>
@@ -6990,7 +7584,7 @@
       <c r="D468" s="7"/>
       <c r="E468" s="5"/>
     </row>
-    <row r="469" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="469" spans="1:5">
       <c r="A469" s="4">
         <v>46276</v>
       </c>
@@ -7003,7 +7597,7 @@
       <c r="D469" s="7"/>
       <c r="E469" s="5"/>
     </row>
-    <row r="470" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="470" spans="1:5">
       <c r="A470" s="4">
         <v>46277</v>
       </c>
@@ -7016,7 +7610,7 @@
       <c r="D470" s="7"/>
       <c r="E470" s="5"/>
     </row>
-    <row r="471" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="471" spans="1:5">
       <c r="A471" s="4">
         <v>46278</v>
       </c>
@@ -7029,7 +7623,7 @@
       <c r="D471" s="7"/>
       <c r="E471" s="5"/>
     </row>
-    <row r="472" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="472" spans="1:5">
       <c r="A472" s="4">
         <v>46279</v>
       </c>
@@ -7042,7 +7636,7 @@
       <c r="D472" s="7"/>
       <c r="E472" s="5"/>
     </row>
-    <row r="473" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="473" spans="1:3">
       <c r="A473" s="1">
         <v>46280</v>
       </c>
@@ -7053,7 +7647,7 @@
         <v>555550</v>
       </c>
     </row>
-    <row r="474" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="474" spans="1:3">
       <c r="A474" s="1">
         <v>46281</v>
       </c>
@@ -7064,7 +7658,7 @@
         <v>516570</v>
       </c>
     </row>
-    <row r="475" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="475" spans="1:3">
       <c r="A475" s="1">
         <v>46282</v>
       </c>
@@ -7075,7 +7669,7 @@
         <v>595650</v>
       </c>
     </row>
-    <row r="476" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="476" spans="1:3">
       <c r="A476" s="1">
         <v>46283</v>
       </c>
@@ -7086,7 +7680,7 @@
         <v>658970</v>
       </c>
     </row>
-    <row r="477" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="477" spans="1:3">
       <c r="A477" s="1">
         <v>46284</v>
       </c>
@@ -7097,7 +7691,7 @@
         <v>626120</v>
       </c>
     </row>
-    <row r="478" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="478" spans="1:3">
       <c r="A478" s="1">
         <v>46285</v>
       </c>
@@ -7108,7 +7702,7 @@
         <v>652800</v>
       </c>
     </row>
-    <row r="479" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="479" spans="1:3">
       <c r="A479" s="1">
         <v>46286</v>
       </c>
@@ -7119,7 +7713,7 @@
         <v>628280</v>
       </c>
     </row>
-    <row r="480" spans="1:5" x14ac:dyDescent="0.15">
+    <row r="480" spans="1:3">
       <c r="A480" s="1">
         <v>46287</v>
       </c>
@@ -7130,7 +7724,7 @@
         <v>611160</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="481" spans="1:3">
       <c r="A481" s="1">
         <v>46288</v>
       </c>
@@ -7141,7 +7735,7 @@
         <v>519580</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="482" spans="1:3">
       <c r="A482" s="1">
         <v>46289</v>
       </c>
@@ -7152,7 +7746,7 @@
         <v>564680</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="483" spans="1:3">
       <c r="A483" s="1">
         <v>46290</v>
       </c>
@@ -7163,7 +7757,7 @@
         <v>710760</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="484" spans="1:3">
       <c r="A484" s="1">
         <v>46291</v>
       </c>
@@ -7174,7 +7768,7 @@
         <v>602540</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="485" spans="1:3">
       <c r="A485" s="1">
         <v>46292</v>
       </c>
@@ -7185,7 +7779,7 @@
         <v>626500</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="486" spans="1:3">
       <c r="A486" s="1">
         <v>46293</v>
       </c>
@@ -7196,7 +7790,7 @@
         <v>534220</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="487" spans="1:3">
       <c r="A487" s="1">
         <v>46294</v>
       </c>
@@ -7207,7 +7801,7 @@
         <v>597240</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.15">
+    <row r="488" spans="1:3">
       <c r="A488" s="1">
         <v>46295</v>
       </c>
@@ -7218,21 +7812,27 @@
         <v>646720</v>
       </c>
     </row>
+    <row r="489" spans="1:3">
+      <c r="A489" s="1">
+        <v>46296</v>
+      </c>
+      <c r="B489" t="s">
+        <v>38</v>
+      </c>
+      <c r="C489">
+        <v>721120</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E488" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
-  <phoneticPr fontId="5"/>
+  <autoFilter ref="A1:E488">
+    <extLst/>
+  </autoFilter>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" sqref="B2:B15 B35:B64 B86:B472">
+      <formula1>店舗マスタ!$A$2:$A$31</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" errorTitle="店舗名エラー" error="店舗マスタの一覧にある店舗名を選択してください。" xr:uid="{00000000-0002-0000-0200-000000000000}">
-          <x14:formula1>
-            <xm:f>店舗マスタ!$A$2:$A$31</xm:f>
-          </x14:formula1>
-          <xm:sqref>B2:B15 B35:B64 B86:B472</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$488</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$489</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="535" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,15 +204,60 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,36 +271,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -264,16 +279,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -283,6 +290,14 @@
       <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -310,25 +325,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,13 +362,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +422,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,19 +434,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,7 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -440,43 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -494,6 +500,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -506,25 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +530,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,30 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -611,25 +587,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -660,6 +627,39 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E489"/>
+  <dimension ref="A1:E490"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7823,8 +7823,19 @@
         <v>721120</v>
       </c>
     </row>
+    <row r="490" spans="1:3">
+      <c r="A490" s="1">
+        <v>46297</v>
+      </c>
+      <c r="B490" t="s">
+        <v>38</v>
+      </c>
+      <c r="C490">
+        <v>659700</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E488">
+  <autoFilter ref="A1:E489">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$489</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$490</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,24 +203,16 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,40 +226,18 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -286,8 +256,54 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -301,34 +317,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -340,8 +332,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,49 +404,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +434,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +446,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,7 +500,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +536,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,16 +572,16 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,6 +601,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -616,11 +625,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -629,22 +644,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E490"/>
+  <dimension ref="A1:E491"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7834,8 +7834,19 @@
         <v>659700</v>
       </c>
     </row>
+    <row r="491" spans="1:3">
+      <c r="A491" s="1">
+        <v>46298</v>
+      </c>
+      <c r="B491" t="s">
+        <v>38</v>
+      </c>
+      <c r="C491">
+        <v>690260</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E489">
+  <autoFilter ref="A1:E490">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$490</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$491</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="537" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,15 +204,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,6 +219,36 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,23 +263,23 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,31 +293,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -303,22 +310,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,7 +325,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +339,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,19 +380,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,37 +392,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,13 +440,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,55 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -572,21 +572,6 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -610,21 +595,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -642,9 +612,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,13 +630,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E491"/>
+  <dimension ref="A1:E492"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7845,8 +7845,19 @@
         <v>690260</v>
       </c>
     </row>
+    <row r="492" spans="1:3">
+      <c r="A492" s="1">
+        <v>46299</v>
+      </c>
+      <c r="B492" t="s">
+        <v>38</v>
+      </c>
+      <c r="C492">
+        <v>721660</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E490">
+  <autoFilter ref="A1:E491">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$491</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$492</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,21 +204,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,52 +233,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -293,9 +256,61 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,41 +324,26 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,13 +482,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -404,7 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -610,13 +610,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -630,17 +634,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E492"/>
+  <dimension ref="A1:E493"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7856,8 +7856,19 @@
         <v>721660</v>
       </c>
     </row>
+    <row r="493" spans="1:3">
+      <c r="A493" s="1">
+        <v>46300</v>
+      </c>
+      <c r="B493" t="s">
+        <v>38</v>
+      </c>
+      <c r="C493">
+        <v>670220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E491">
+  <autoFilter ref="A1:E492">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$492</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$493</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,18 +203,18 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,24 +225,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,13 +241,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -271,31 +248,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,6 +278,36 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -324,24 +316,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,31 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,55 +398,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -464,7 +416,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -476,7 +452,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,13 +470,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -596,6 +611,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
       <right style="thin">
@@ -606,30 +636,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,17 +651,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,7 +674,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -683,7 +683,7 @@
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,127 +692,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E493"/>
+  <dimension ref="A1:E494"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7867,8 +7867,19 @@
         <v>670220</v>
       </c>
     </row>
+    <row r="494" spans="1:3">
+      <c r="A494" s="1">
+        <v>46301</v>
+      </c>
+      <c r="B494" t="s">
+        <v>38</v>
+      </c>
+      <c r="C494">
+        <v>681640</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E492">
+  <autoFilter ref="A1:E493">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$493</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$494</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -203,16 +203,9 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -226,61 +219,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,44 +227,6 @@
     <font>
       <b/>
       <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +242,106 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +386,127 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,91 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,61 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,69 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -595,51 +658,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -650,169 +668,151 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E494"/>
+  <dimension ref="A1:E495"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7878,8 +7878,19 @@
         <v>681640</v>
       </c>
     </row>
+    <row r="495" spans="1:3">
+      <c r="A495" s="1">
+        <v>46302</v>
+      </c>
+      <c r="B495" t="s">
+        <v>38</v>
+      </c>
+      <c r="C495">
+        <v>572100</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E493">
+  <autoFilter ref="A1:E494">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$494</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$495</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="541" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,11 +203,63 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,6 +277,22 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="18"/>
       <color theme="3"/>
@@ -233,38 +301,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,30 +316,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,32 +333,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +392,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +440,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,139 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,50 +571,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -637,8 +598,32 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +653,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E495"/>
+  <dimension ref="A1:E496"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7889,8 +7889,19 @@
         <v>572100</v>
       </c>
     </row>
+    <row r="496" spans="1:3">
+      <c r="A496" s="1">
+        <v>46303</v>
+      </c>
+      <c r="B496" t="s">
+        <v>38</v>
+      </c>
+      <c r="C496">
+        <v>608240</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E494">
+  <autoFilter ref="A1:E495">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$495</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$496</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,53 +203,15 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -263,15 +225,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -287,24 +243,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -318,7 +267,65 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,13 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,31 +398,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,31 +422,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -452,31 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -500,13 +470,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,19 +494,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,7 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -597,17 +597,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -645,11 +638,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,145 +674,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="22" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E496"/>
+  <dimension ref="A1:E497"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7900,8 +7900,19 @@
         <v>608240</v>
       </c>
     </row>
+    <row r="497" spans="1:3">
+      <c r="A497" s="1">
+        <v>46304</v>
+      </c>
+      <c r="B497" t="s">
+        <v>38</v>
+      </c>
+      <c r="C497">
+        <v>597440</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E495">
+  <autoFilter ref="A1:E496">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$496</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$497</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,30 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -241,19 +218,48 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -273,38 +279,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -318,14 +302,30 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -333,17 +333,17 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +434,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +458,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,19 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,43 +518,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,43 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,19 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -591,17 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,17 +601,20 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,15 +624,6 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +642,190 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="19" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E497"/>
+  <dimension ref="A1:E498"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7911,8 +7911,19 @@
         <v>597440</v>
       </c>
     </row>
+    <row r="498" spans="1:3">
+      <c r="A498" s="1">
+        <v>46305</v>
+      </c>
+      <c r="B498" t="s">
+        <v>38</v>
+      </c>
+      <c r="C498">
+        <v>650020</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E496">
+  <autoFilter ref="A1:E497">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$497</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$498</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,7 +204,77 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,22 +289,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -249,44 +311,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -302,46 +333,15 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +374,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +404,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,7 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,85 +452,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,19 +470,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,45 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -624,6 +585,56 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,28 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E498"/>
+  <dimension ref="A1:E499"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7922,8 +7922,19 @@
         <v>650020</v>
       </c>
     </row>
+    <row r="499" spans="1:3">
+      <c r="A499" s="1">
+        <v>46306</v>
+      </c>
+      <c r="B499" t="s">
+        <v>38</v>
+      </c>
+      <c r="C499">
+        <v>555040</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E497">
+  <autoFilter ref="A1:E498">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$498</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$499</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,100 +203,8 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -317,7 +225,52 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -332,16 +285,63 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +482,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,25 +494,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -416,133 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -574,8 +574,49 @@
       <left/>
       <right/>
       <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -583,17 +624,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -615,11 +647,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -638,194 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E499"/>
+  <dimension ref="A1:E500"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7933,8 +7933,19 @@
         <v>555040</v>
       </c>
     </row>
+    <row r="500" spans="1:3">
+      <c r="A500" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B500" t="s">
+        <v>38</v>
+      </c>
+      <c r="C500">
+        <v>621740</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E498">
+  <autoFilter ref="A1:E499">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12450" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" r:id="rId1"/>
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$499</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$500</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="546" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,11 +203,32 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -218,8 +239,40 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,22 +287,21 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -257,37 +309,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,22 +324,7 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -333,17 +340,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +428,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,157 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,15 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -621,15 +612,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -654,6 +636,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,140 +692,140 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E500"/>
+  <dimension ref="A1:E501"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7944,8 +7944,19 @@
         <v>621740</v>
       </c>
     </row>
+    <row r="501" spans="1:3">
+      <c r="A501" s="1">
+        <v>46307</v>
+      </c>
+      <c r="B501" t="s">
+        <v>38</v>
+      </c>
+      <c r="C501">
+        <v>621740</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E499">
+  <autoFilter ref="A1:E500">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$500</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$501</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="547" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,8 +203,47 @@
       <charset val="128"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -217,9 +256,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -232,8 +277,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -248,24 +294,24 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -278,33 +324,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -315,32 +339,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -362,7 +362,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +386,139 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,151 +530,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,27 +586,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -629,9 +612,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -641,15 +641,6 @@
       <top/>
       <bottom style="double">
         <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +659,31 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,137 +695,137 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E501"/>
+  <dimension ref="A1:E502"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7955,8 +7955,19 @@
         <v>621740</v>
       </c>
     </row>
+    <row r="502" spans="1:3">
+      <c r="A502" s="1">
+        <v>46308</v>
+      </c>
+      <c r="B502" t="s">
+        <v>38</v>
+      </c>
+      <c r="C502">
+        <v>700700</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E500">
+  <autoFilter ref="A1:E501">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$501</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$502</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -205,7 +205,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -220,30 +220,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -271,9 +248,48 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -301,14 +317,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
@@ -318,7 +326,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -329,21 +344,6 @@
       <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,19 +440,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,31 +452,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,13 +500,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,79 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,30 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -612,11 +588,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF7F7F7F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,6 +634,26 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -659,173 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E502"/>
+  <dimension ref="A1:E503"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7966,8 +7966,19 @@
         <v>700700</v>
       </c>
     </row>
+    <row r="503" spans="1:3">
+      <c r="A503" s="1">
+        <v>46309</v>
+      </c>
+      <c r="B503" t="s">
+        <v>38</v>
+      </c>
+      <c r="C503">
+        <v>596980</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E501">
+  <autoFilter ref="A1:E502">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$502</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$503</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -165,10 +165,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,19 +203,10 @@
       <charset val="128"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -226,6 +217,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -233,15 +225,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -256,7 +272,53 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,69 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,13 +362,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -380,13 +398,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,55 +494,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,13 +506,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,67 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,25 +571,12 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -606,6 +593,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,15 +654,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -645,26 +662,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,16 +674,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -695,124 +695,124 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E503"/>
+  <dimension ref="A1:E504"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7977,8 +7977,19 @@
         <v>596980</v>
       </c>
     </row>
+    <row r="504" spans="1:3">
+      <c r="A504" s="1">
+        <v>46310</v>
+      </c>
+      <c r="B504" t="s">
+        <v>38</v>
+      </c>
+      <c r="C504">
+        <v>562820</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E502">
+  <autoFilter ref="A1:E503">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$503</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$504</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,22 +204,45 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -234,7 +257,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -245,51 +268,6 @@
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -308,24 +286,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -334,6 +296,44 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,175 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,175 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,41 +573,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -623,15 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -654,8 +613,49 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -663,8 +663,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="21" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E504"/>
+  <dimension ref="A1:E505"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7988,8 +7988,19 @@
         <v>562820</v>
       </c>
     </row>
+    <row r="505" spans="1:3">
+      <c r="A505" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B505" t="s">
+        <v>38</v>
+      </c>
+      <c r="C505">
+        <v>713520</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E503">
+  <autoFilter ref="A1:E504">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$504</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$506</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -210,10 +210,42 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -225,24 +257,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -257,37 +273,60 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,46 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +404,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,25 +422,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -428,73 +506,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,43 +524,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -595,17 +586,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -645,26 +654,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
       </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
       </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
       </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E505"/>
+  <dimension ref="A1:E507"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -7999,8 +7999,30 @@
         <v>713520</v>
       </c>
     </row>
+    <row r="506" spans="1:3">
+      <c r="A506" s="1">
+        <v>46311</v>
+      </c>
+      <c r="B506" t="s">
+        <v>38</v>
+      </c>
+      <c r="C506">
+        <v>713520</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3">
+      <c r="A507" s="1">
+        <v>46312</v>
+      </c>
+      <c r="B507" t="s">
+        <v>38</v>
+      </c>
+      <c r="C507">
+        <v>562700</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E504">
+  <autoFilter ref="A1:E506">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$506</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$507</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,31 +204,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -242,67 +232,8 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -326,15 +257,23 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -344,6 +283,67 @@
       <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,13 +404,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,13 +440,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,73 +458,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -488,31 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +488,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +536,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -567,63 +567,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FFD9D9D9"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +611,221 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="9" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E507"/>
+  <dimension ref="A1:E508"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8021,8 +8021,19 @@
         <v>562700</v>
       </c>
     </row>
+    <row r="508" spans="1:3">
+      <c r="A508" s="1">
+        <v>46313</v>
+      </c>
+      <c r="B508" t="s">
+        <v>38</v>
+      </c>
+      <c r="C508">
+        <v>616560</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E506">
+  <autoFilter ref="A1:E507">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$507</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$508</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,66 +203,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -279,13 +219,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -294,8 +227,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,8 +271,30 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -325,7 +302,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -340,10 +317,33 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -362,7 +362,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,31 +410,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,121 +434,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +458,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,39 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -588,11 +621,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
+      <top/>
       <bottom style="double">
-        <color theme="4"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -614,18 +645,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -644,188 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="178" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E508"/>
+  <dimension ref="A1:E509"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8032,8 +8032,19 @@
         <v>616560</v>
       </c>
     </row>
+    <row r="509" spans="1:3">
+      <c r="A509" s="1">
+        <v>46314</v>
+      </c>
+      <c r="B509" t="s">
+        <v>38</v>
+      </c>
+      <c r="C509">
+        <v>555220</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E507">
+  <autoFilter ref="A1:E508">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$508</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$509</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="555" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,6 +203,28 @@
       <charset val="128"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -211,9 +233,99 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -229,119 +341,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +380,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +452,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,13 +482,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -434,19 +512,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,85 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -583,23 +583,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -619,11 +604,41 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -653,179 +668,164 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="7" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E509"/>
+  <dimension ref="A1:E510"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8043,8 +8043,19 @@
         <v>555220</v>
       </c>
     </row>
+    <row r="510" spans="1:3">
+      <c r="A510" s="1">
+        <v>46315</v>
+      </c>
+      <c r="B510" t="s">
+        <v>38</v>
+      </c>
+      <c r="C510">
+        <v>591120</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E508">
+  <autoFilter ref="A1:E509">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$510</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -211,15 +211,38 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -227,21 +250,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -254,8 +263,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -269,48 +279,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -331,11 +301,41 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -362,7 +362,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +446,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,55 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -446,103 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -575,16 +575,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -600,30 +591,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -658,6 +625,39 @@
       <diagonal/>
     </border>
     <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -674,158 +674,158 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="27" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E510"/>
+  <dimension ref="A1:E511"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8054,8 +8054,19 @@
         <v>591120</v>
       </c>
     </row>
+    <row r="511" spans="1:3">
+      <c r="A511" s="1">
+        <v>46316</v>
+      </c>
+      <c r="B511" t="s">
+        <v>38</v>
+      </c>
+      <c r="C511">
+        <v>592700</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E509">
+  <autoFilter ref="A1:E510">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$510</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$511</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
+    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -203,9 +203,22 @@
       <charset val="128"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -219,50 +232,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
@@ -271,9 +240,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -302,13 +270,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -316,15 +277,31 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +318,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,25 +362,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -392,55 +374,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,7 +392,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,31 +470,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -506,13 +482,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -530,7 +530,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -542,7 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,15 +571,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -591,21 +582,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -625,17 +601,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -643,8 +613,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,164 +653,179 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E511"/>
+  <dimension ref="A1:E512"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8065,8 +8065,19 @@
         <v>592700</v>
       </c>
     </row>
+    <row r="512" spans="1:3">
+      <c r="A512" s="1">
+        <v>46317</v>
+      </c>
+      <c r="B512" t="s">
+        <v>38</v>
+      </c>
+      <c r="C512">
+        <v>742280</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E510">
+  <autoFilter ref="A1:E511">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$511</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$512</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -166,9 +166,9 @@
   <numFmts count="5">
     <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -217,62 +217,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -292,9 +241,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -309,24 +264,15 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -341,7 +287,61 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,7 +362,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +428,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,19 +464,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -410,37 +488,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -458,55 +524,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -518,31 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -571,6 +571,24 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -582,6 +600,41 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -601,24 +654,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -633,111 +668,28 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -746,73 +698,121 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E512"/>
+  <dimension ref="A1:E513"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8076,8 +8076,19 @@
         <v>742280</v>
       </c>
     </row>
+    <row r="513" spans="1:3">
+      <c r="A513" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B513" t="s">
+        <v>38</v>
+      </c>
+      <c r="C513">
+        <v>703900</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E511">
+  <autoFilter ref="A1:E512">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$512</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$514</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,11 +164,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
     <font>
@@ -204,14 +204,60 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -225,6 +271,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -233,9 +286,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -243,13 +304,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -264,46 +318,8 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -316,30 +332,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -362,7 +362,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -374,7 +416,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -386,7 +440,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -398,133 +512,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -536,13 +542,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -573,18 +573,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -604,41 +612,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -650,6 +623,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -668,22 +650,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -692,100 +692,115 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="24" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="16" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -794,38 +809,23 @@
     <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="176" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="179" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
@@ -1487,7 +1487,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E513"/>
+  <dimension ref="A1:E515"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="14" style="1" customWidth="1"/>
@@ -8087,8 +8087,30 @@
         <v>703900</v>
       </c>
     </row>
+    <row r="514" spans="1:3">
+      <c r="A514" s="1">
+        <v>46318</v>
+      </c>
+      <c r="B514" t="s">
+        <v>38</v>
+      </c>
+      <c r="C514">
+        <v>703900</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3">
+      <c r="A515" s="1">
+        <v>46319</v>
+      </c>
+      <c r="B515" t="s">
+        <v>38</v>
+      </c>
+      <c r="C515">
+        <v>726740</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:E512">
+  <autoFilter ref="A1:E514">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">

--- a/dashboard/data/incoming/LINEギフト.xlsx
+++ b/dashboard/data/incoming/LINEギフト.xlsx
@@ -12,14 +12,14 @@
     <sheet name="売上入力" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$514</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">売上入力!$A$1:$E$515</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="562" uniqueCount="46">
   <si>
     <t>このファイルの使い方</t>
   </si>
@@ -164,10 +164,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="24">
@@ -204,46 +204,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -251,6 +212,13 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -265,6 +233,84 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -272,7 +318,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -288,52 +334,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -341,7 +341,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -362,66 +362,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fi